--- a/upload/informacoes_classificadas_desclassificadas.xlsx
+++ b/upload/informacoes_classificadas_desclassificadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28892EA3-D0BC-4381-AF76-6647C5EE98E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D8B20F-BA05-42C4-B543-60F5E7C479D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{DF40FCA1-B2E4-4937-A10F-23A8137D7072}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="361">
   <si>
     <t>orgao_entidade</t>
   </si>
@@ -128,12 +128,6 @@
     <t>Reservado</t>
   </si>
   <si>
-    <t>04 – Controle Interno</t>
-  </si>
-  <si>
-    <t>inc. VIII do art. 23 da Lei Federal 12.527/2011</t>
-  </si>
-  <si>
     <t>002.04.2021</t>
   </si>
   <si>
@@ -188,9 +182,6 @@
     <t>Produtos de auditoria – Relatórios, Pareceres, Notas de Auditoria relativos à avaliação e à consultoria de gestão de riscos</t>
   </si>
   <si>
-    <t>art. 23, Caput da Lei Federal 12.527/2011</t>
-  </si>
-  <si>
     <t>011.04.2021</t>
   </si>
   <si>
@@ -227,12 +218,6 @@
     <t>Mapas de risco da Controladoria-Geral do Estado</t>
   </si>
   <si>
-    <t>5 – Controle Interno</t>
-  </si>
-  <si>
-    <t>inc. VIII do art. 23 da Lei Federal 12.527/2012</t>
-  </si>
-  <si>
     <t>https://www.feam.br/informa%C3%A7%C3%B5es-classificadas-e-desclassificadas</t>
   </si>
   <si>
@@ -245,16 +230,7 @@
     <t>Informações relacionadas à biossegurança nos laboratórios de pesquisa</t>
   </si>
   <si>
-    <t>Saúde</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso VI da Lei 12.527/2011</t>
-  </si>
-  <si>
     <t>Ofícios enviados ao Ministério Público, Polícia Civil, Federal ou congêneres, acompanhados de laudos analíticos ou fiscais, bem como aqueles contendo respostas a demandas judiciais</t>
-  </si>
-  <si>
-    <t>Lei 12.527/2011, art. 23, incisos III e IV</t>
   </si>
   <si>
     <t>Ofício externo - Documentos recebidos de órgãos externos como Polícia Civil, Federal, Ministério Público ou congênere, com finalidade de elucidação de crimes contra Saúde Pública ou Estado</t>
@@ -264,27 +240,15 @@
 proficiência ofertados pelo IOM.</t>
   </si>
   <si>
-    <t>Lei 12.527/2011, Inciso VI</t>
-  </si>
-  <si>
     <t>Relatórios de Auditorias Internas</t>
   </si>
   <si>
-    <t>Lei 12.527/2011, Inciso III</t>
-  </si>
-  <si>
     <t>Informações utilizadas como fundamento da tomada de decisão ou de ato administrativo.</t>
   </si>
   <si>
-    <t>Art. 7º, § 3º da Lei nº 12.527.</t>
-  </si>
-  <si>
     <t>Ofícios, comunicados, expediente de exigências e demandas de autoridades sanitárias local, estadual ou federal.</t>
   </si>
   <si>
-    <t>Lei 12.527/2011 - Art. 23, inciso VI</t>
-  </si>
-  <si>
     <t>Relatórios de Auditoria Externa.</t>
   </si>
   <si>
@@ -336,18 +300,12 @@
     <t>Estudos regionais e setoriais (direcionados às empresas e investidores), quando encomendados</t>
   </si>
   <si>
-    <t>Art. 23, II, da Lei nº 12.527/2011</t>
-  </si>
-  <si>
     <t>5 anos</t>
   </si>
   <si>
     <t>Relatórios de investimentos e projetos ativos/inativos para os mantenedores</t>
   </si>
   <si>
-    <t>Art. 23,VI, da Lei nº 12.527/2011</t>
-  </si>
-  <si>
     <t>Informações consolidadas em Notas Técnicas sobre detalhes de projetos empresariais, como valor do investimento, localização, descrição do projeto, produtos, geração de empregos, pleitos das empresas, necessidades de licenciamento ambiental e infraestrutura</t>
   </si>
   <si>
@@ -357,18 +315,12 @@
     <t>Íntegra dos Protocolos de Intenções/Aditivos</t>
   </si>
   <si>
-    <t>Art. 23, II e IV, da Lei nº 12.527/2011</t>
-  </si>
-  <si>
     <t>Íntegra de Acordos de cooperação técnica</t>
   </si>
   <si>
     <t>Pareceres jurídicos relacionados a assuntos estratégicos</t>
   </si>
   <si>
-    <t>Art. 23, VIII, da Lei nº 12.527/2011</t>
-  </si>
-  <si>
     <t>Atas de reunião de Conselho Superior, na íntegra. Resalvada a parte que tratar de protocolo de intenção que deve obdecer a classificação de ultrassecreto</t>
   </si>
   <si>
@@ -379,12 +331,6 @@
   </si>
   <si>
     <t>https://investminas.mg.gov.br/pt/sobre/</t>
-  </si>
-  <si>
-    <t>Comércio e Serviços</t>
-  </si>
-  <si>
-    <t>Lei Federal 12.527/2011, Art. 23, Inciso VIII.</t>
   </si>
   <si>
     <t>Roteiros de verificação e fiscalização das áreas metrológica e avaliação da conformidade.</t>
@@ -412,18 +358,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>Reservado</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>inciso VIII art. 23 da Lei Federal
-12.527/2011</t>
     </r>
   </si>
   <si>
@@ -446,17 +380,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>art 23, caput da  Lei Federal 12.527/2011</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Produtos de auditoria – Relatórios,
 Pareceres, Notas de Auditoria relativos à avaliação e à consultoria de gestão de riscos</t>
     </r>
@@ -470,17 +393,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>Plano Anual de Fiscalização 2022</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>inciso VIII art. 23 da Lei Federal 12.527/2011</t>
     </r>
   </si>
   <si>
@@ -608,81 +520,42 @@
     <t>Equipamento e Especificações Técnicas</t>
   </si>
   <si>
-    <t>Defesa e Segurança</t>
-  </si>
-  <si>
-    <t>Inciso VIII do artigo 23 da Lei 12.527/2012 e inciso IX do artigo 25 do Decreto no 7724/2012.</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1wJWy2gwiSn6HX1_FjDDWDAvX-NXsQuuQ/view</t>
   </si>
   <si>
     <t>Extrato   de contas e movimentações financeiras</t>
   </si>
   <si>
-    <t>07   - Economia e Finanças</t>
-  </si>
-  <si>
-    <t>Incisos   II, IV e VI do Artigo 23 da Lei Federal nº 12.527, de 18/11/2011</t>
-  </si>
-  <si>
     <t>Protocolos de Intenções</t>
   </si>
   <si>
-    <t>07 - Economia e Finanças</t>
-  </si>
-  <si>
-    <t>Incisos II, IV e VI do Artigo 23 da Lei Federal   nº 12.527, de 18/11/2011</t>
-  </si>
-  <si>
     <t>Informações   sobre acesso, perfil e rastreabilidade de usuários e registros de transações   executadas no Sistema Integrado de Administração Financeira (SIAFI/MG)</t>
   </si>
   <si>
-    <t>Inciso   IV do Artigo 23 da Lei Federal nº 12.527, de 18/11/2011</t>
-  </si>
-  <si>
     <t>Informações contábeis custodiadas pela   Superintendência Central de Contadoria-Geral (SCCG) específicas de unidades   orçamentárias e/ou executoras</t>
   </si>
   <si>
-    <t>Inciso IV do Artigo 23 da Lei Federal nº   12.527, de 18/11/2011</t>
-  </si>
-  <si>
     <t>Regimes   especiais que dispõem sobre obrigações principais e acessórias, e respectivos   pareceres e estudos que os embasaram</t>
   </si>
   <si>
-    <t>Artigos   23, IV, 24, Caput, § 1º, I e § 5º, I, da Lei Federal nº 12.527, de   18/11/2011; Decreto Estadual nº 45.969, de 24/05/2012; Artigos 1º, Caput, 4º,   7º, 8º, III, 9º e 13 da Resolução nº 4.671, de 13/06/2014, do secretário de   Estado de Fazenda de Minas Gerais</t>
-  </si>
-  <si>
     <t>Processos e documentos referentes à aplicação   de benefícios fiscais de que tratam o RICMS/02 e seus anexos I, II, IV, IX e   XVI, exceto as consultas sobre aplicação da Legislação Tributária</t>
   </si>
   <si>
-    <t>Artigos 23, IV, 24, Caput, § 1º, I e § 5º, I,   da Lei Federal nº 12.527, de 18/11/2011; Decreto Estadual nº 45.969, de   24/05/2012; Artigos 1º, Caput, 4º, 7º, 8º, III, 9º e 13 da Resolução nº   4.671, de 13/06/2014, do secretário de Estado de Fazenda de Minas Gerais</t>
-  </si>
-  <si>
     <t>Processos   e documentos referentes à imunidade, isenções e demais benefícios fiscais do   IPVA, ITCD e Taxas Estaduais, exceto as consultas sobre aplicação da   Legislação Tributária</t>
   </si>
   <si>
     <t>Regimes especiais que dispõem sobre benefícios   fiscais e respectivos pareceres, estudo que embasaram e consultas de   contribuintes a eles referentes</t>
   </si>
   <si>
-    <t>Artigos 23, VI, 24, Caput, § 1º, I, e § 5º, I,   da Lei Federal nº 12.527, de 18/11/2011; Artigos 29, I, 30, e 36 do Decreto   Estadual nº 45.969, de 24/05/2012; Artigos 1º, Caput, 4º, 7º, III, 8º, I, 9º   e 13 da Resolução nº 4.671, de 13/06/2014, do secretário de Estado de Fazenda   de Minas Gerais</t>
-  </si>
-  <si>
     <t>Acordo   de Cooperação Técnica nº 1910003054/SEF-MG. Processo SEI nº   1190.01.0006287/2022-26 Estado de Minas Gerais / Secretaria de Estado de   Fazenda e União / Superintendência da Polícia Rodoviária Federal do Estado de   Minas Gerais</t>
   </si>
   <si>
-    <t>Artigos   23, VI, VII e VIII, 24, Caput, § 1º, I, da Lei Federal nº 12.527, de   18/11/2011; Artigo 28 do Decreto Estadual nº 45.969, de 24/05/2012</t>
-  </si>
-  <si>
     <t>Disponibilidade de Caixa - Contrato de Prestação de Serviços   Financeiros e outras Avenças, N.º 1900010998, que entre si celebram o Estado   de Minas Gerais e o Banco do Brasil S.A., de 21/12/2021, exceto as   informações publicadas no Diário Oficial do Estado de Minas Gerais em   22/12/2021</t>
   </si>
   <si>
     <t>Folha de Pagamento - CONTRATO Nº 1900010957/2021, DE PRESTAÇÃO   DE SERVIÇOS, QUE ENTRE SI CELEBRAM O ESTADO DE MINAS GERAIS, POR INTERMÉDIO   DA SECRETARIA DE ESTADO DE FAZENDA - SEF/MG E O ITAÚ UNIBANCO S/A, de   02/08/2021, exceto as informações publicadas no Diário Oficial do Estado de   Minas Gerais em em 03/08/2021</t>
   </si>
   <si>
-    <t>Artigos   23, IV, 24, Caput e § 1º, III, e § 5º, I, da Lei Federal nº 12.527, de 18/11/2011, Artigos 29, I, 30, III e 36 do Decreto Estadual nº 45.969, de 24/05/2012, Artigos 1º , Caput ,4º ,7º ,I ,8º ,III ,9º e 13 da Resolução nº4.671,de13/06/2014,do Secretário de Estado de Fazenda de Minas Gerais</t>
-  </si>
-  <si>
     <t>https://www.fazenda.mg.gov.br/transparencia/informacoes-classificadas-e-desclassificadas/</t>
   </si>
   <si>
@@ -692,22 +565,7 @@
     <t>Relatório de auditoria interna - Nº Processo SIGA 1450.145.31.0101.20.</t>
   </si>
   <si>
-    <t>SECRETO</t>
-  </si>
-  <si>
-    <t>06 - DEFESA SOCIAL E SEGURANÇA PÚBLICA</t>
-  </si>
-  <si>
-    <t>Art. 23, incisos VII e VIII, da Lei Federal nº 12.527/2011; Art. 29, inciso I, do Decreto Estadual nº 45.969/2012</t>
-  </si>
-  <si>
     <t>Dados de ocorrências no âmbito das unidades prisionais.</t>
-  </si>
-  <si>
-    <t>RESERVADO</t>
-  </si>
-  <si>
-    <t>Art. 23, inc. VII da Lei 12.527/2011.</t>
   </si>
   <si>
     <r>
@@ -723,19 +581,10 @@
     </r>
   </si>
   <si>
-    <t>Inciso III do art. 23 da Lei Federal nº 12.527 de 2011.</t>
-  </si>
-  <si>
     <t>Informações das atas das reuniões do eixo Núcleo Integrado de monitoramento à violência contra a mulher do programa MG Mulher.</t>
   </si>
   <si>
-    <t>Incisos III, VII e VIII do art. 23 da Lei Federal nº 12.527 de 2011.</t>
-  </si>
-  <si>
     <t>Informações de localização física dos Indivíduos Privados de Liberdade.</t>
-  </si>
-  <si>
-    <t>Incisos III e VII do art. 23 da Lei Federal nº 12.527 de 2011.</t>
   </si>
   <si>
     <t>Informações de visitação a locais, divisões ou seções em unidades prisionais.</t>
@@ -790,21 +639,12 @@
     <t>Informações contidas em relatórios de auditoria consolidados pela inteligência.</t>
   </si>
   <si>
-    <t>Inciso VIII do art. 23 da Lei Federal nº 12.527 de 2011.</t>
-  </si>
-  <si>
     <t>Informações contidas em bancos de dados internos e soluções tecnológicas adotadas pela SEJUSP: descrições, configurações, projetos, códigos fonte e os produtos de soluções tecnológicas, incluindo todos os seus componentes de hardware, software e rede. [8]</t>
   </si>
   <si>
-    <t>Incisos III e VIII do art. 23 da Lei Federal nº 12.527 de 2011.</t>
-  </si>
-  <si>
     <t>Informações das abas Homicídios / Vulnerabilidade Criminal / Dinâmica das Vulnerabilidades dos Relatórios de Gestão Estratégica (RGE).</t>
   </si>
   <si>
-    <t>ULTRASSECRETO</t>
-  </si>
-  <si>
     <t>Informações dos Relatórios Analíticos de Dinâmica Criminal.</t>
   </si>
   <si>
@@ -835,9 +675,6 @@
     <t>Informações contidas em processos do sistema SEI! que tratam especificamente do Termo de Compromisso firmado entre a Sejusp, Vale e Ministério Público.</t>
   </si>
   <si>
-    <t>Artigo 22 e incisos III, VI e VII do art. 23 da Lei Federal nº 12.527 de 2011.</t>
-  </si>
-  <si>
     <t>001.06.1450</t>
   </si>
   <si>
@@ -943,17 +780,10 @@
     <t>Planejamento Anual de Fiscalização 2017</t>
   </si>
   <si>
-    <t>inciso VIII art. 23 da Lei Federal 12.527/2011.</t>
-  </si>
-  <si>
     <t>002.13.1371</t>
   </si>
   <si>
     <t>Plano de Fiscalização Ambiental 2018</t>
-  </si>
-  <si>
-    <t>inciso VIII art. 23 da Lei
-Federal 12.527/2011.</t>
   </si>
   <si>
     <t>003.13.1371</t>
@@ -973,10 +803,6 @@
   <si>
     <t>Papéis de Trabalho produzidos para subsidiar
 a opinião e convicção do auditor</t>
-  </si>
-  <si>
-    <t>caput do art. 23 da Lei
-Federal 12.527/2011.</t>
   </si>
   <si>
     <t>006.04.1371</t>
@@ -987,9 +813,6 @@
 à consultoria de gestão de riscos</t>
   </si>
   <si>
-    <t>caput do art. 23 da Lei Federal 12.527/2011.</t>
-  </si>
-  <si>
     <t>007.13.1371</t>
   </si>
   <si>
@@ -1008,19 +831,12 @@
     <t>Plano Anual de Fiscalização 2023</t>
   </si>
   <si>
-    <t>Inciso VIII art. 23 da Lei
-Federal 12.527/2011.</t>
-  </si>
-  <si>
     <t>010.13.1371</t>
   </si>
   <si>
     <t>Plano Anual de Fiscalização 2024</t>
   </si>
   <si>
-    <t>Inciso VIII art. 23 da Lei Federal 12.527/2011.</t>
-  </si>
-  <si>
     <t>011.13.1371</t>
   </si>
   <si>
@@ -1036,12 +852,6 @@
     <t>Postos de combustível Orgânico da PMMG</t>
   </si>
   <si>
-    <t>05 - Defesa e Segurança</t>
-  </si>
-  <si>
-    <t>Art. 23 , inciso(s) VII, da Lei 12527/2011</t>
-  </si>
-  <si>
     <t>7460.112495/2023-52.R.05.31/10/2023.31/10/2028.N</t>
   </si>
   <si>
@@ -1057,9 +867,6 @@
     <t>7460.112493/2023-63.R.05.26/10/2023.26/10/2028.N</t>
   </si>
   <si>
-    <t>Art. 23 , inciso(s) V, da Lei 12527/2011</t>
-  </si>
-  <si>
     <t>7460.112494/2023-53.R.05.26/10/2023.26/10/2028.N</t>
   </si>
   <si>
@@ -1072,9 +879,6 @@
     <t>2903.112427/2019-74.R.05.07/02/2019.07/02/2024.N</t>
   </si>
   <si>
-    <t>Art. 23 , inciso(s) VIII, da Lei 12527/2011</t>
-  </si>
-  <si>
     <t>0718.112444/2019-74.R.05.02/05/2019.02/05/2024.N</t>
   </si>
   <si>
@@ -1084,9 +888,6 @@
     <t>7460.112398/2018-52.R.05.20/06/2018.20/06/2023.N</t>
   </si>
   <si>
-    <t>Art. 23 , inciso(s) VIII, da Lei 12527/2011 C/C Art. 29 , inciso(s) I, do Decreto Estadual 45969/2011</t>
-  </si>
-  <si>
     <t>https://www.policiamilitar.mg.gov.br/site/externo/pagina/10081/lei-de-acesso-%C3%A0-informa%C3%A7%C3%A3o</t>
   </si>
   <si>
@@ -1099,9 +900,6 @@
     <t>7460.112401/2018-86.R.05.23/07/2018.23/07/2023.N</t>
   </si>
   <si>
-    <t>Art. 29 , inciso(s) I, do Decreto Estadual 45969/2011</t>
-  </si>
-  <si>
     <t>7460.112403/2018-86.R.05.27/07/2018.27/07/2023.N</t>
   </si>
   <si>
@@ -1111,9 +909,6 @@
     <t>7460.112405/2018-85.R.05.27/07/2018.27/07/2023.N</t>
   </si>
   <si>
-    <t>Art. 23 , inciso(s) VIII, III, da Lei 12527/2011</t>
-  </si>
-  <si>
     <t>7460.112407/2018-75.R.05.13/08/2018.13/08/2023.N</t>
   </si>
   <si>
@@ -1153,9 +948,6 @@
     <t>7460.112422/2019-85.R.05.21/01/2019.21/01/2024.N</t>
   </si>
   <si>
-    <t>Art. 23 , inciso(s) III, da Lei 12527/2011 C/C Art. 29 , inciso(s) I, do Decreto Estadual 45969/2011</t>
-  </si>
-  <si>
     <t>7460.112426/2019-74.R.05.04/02/2019.04/02/2024.N</t>
   </si>
   <si>
@@ -1208,9 +1000,6 @@
   </si>
   <si>
     <t>7460.112457/2019-63.R.05.15/02/2019.15/02/2024.N</t>
-  </si>
-  <si>
-    <t>5 - Defesa e Segurança</t>
   </si>
   <si>
     <t>014.04.2091</t>
@@ -1343,6 +1132,123 @@
   </si>
   <si>
     <t>prazo_classificacao</t>
+  </si>
+  <si>
+    <t>4 – Controle Interno</t>
+  </si>
+  <si>
+    <t>6 - Defesa Social e Segurança Pública</t>
+  </si>
+  <si>
+    <t>7 - Economia e Finanças</t>
+  </si>
+  <si>
+    <t>9 - Governo e Política</t>
+  </si>
+  <si>
+    <t>11 - Indústria</t>
+  </si>
+  <si>
+    <t>12 - Justição e Legislação</t>
+  </si>
+  <si>
+    <t>13 - Meio Ambiente</t>
+  </si>
+  <si>
+    <t>3 - Comércio, Serviços e Turismo</t>
+  </si>
+  <si>
+    <t>16 - Saúde</t>
+  </si>
+  <si>
+    <t>Art 23, caput da Lei Federal 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos II e IV, da Lei Federal  nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso II, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso VII da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso V, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso VI da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso VIII, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso(s) VIII, III, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos VII e VIII, da Lei Federal nº 12.527/2011 e Art. 29, inciso I, do Decreto Estadual nº 45.969/2012</t>
+  </si>
+  <si>
+    <t>Art. 29, inciso I, do Decreto Estadual nº 45.969/2011</t>
+  </si>
+  <si>
+    <t>Art. 7º, § 3º da Lei Federal nº 12.527</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso III, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso IV, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso VI, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos III e IV, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos II, IV e VI, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos III, VII e VIII, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos III e VIII, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos III e VII, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso IV e art. 24, caput, § 1º, inciso I e § 5º, inciso I, da Lei Federal nº 12.527/2011 C/C Decreto Estadual nº 45.969/2012, art. 1º, caput, 4º, art. 7º, art. 8º, inciso III, art. 9º e art. 13 da Resolução nº 4.671/2014, do Secretário de Estado de Fazenda de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso IV e art. 24, caput, § 1º, inciso I e § 5º, inciso I, da Lei Federal nº 12.527/2011 C/C Decreto Estadual nº 45.969, de  24/05/2012; art. 1º, Caput, art. 4º, art. 7º, art. 8º, inciso III, art. 9º e art. 13 da Resolução nº  4.671/2014, do Secretário de Estado de Fazenda de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso VI e art. 24, caput, § 1º, inciso I e § 5º, inciso I, da Lei Federal nº 12.527/2011 C/C art. 29, inciso I, art. 30 e art. 36 do Decreto Estadual nº 45.969/2012 C/C art. 1º, caput,art. 4º, art. 7º, inciso III, art. 8º, inciso I, art. 9º e  art. 13 da Resolução nº 4.671/2014, do Secretário de Estado de Fazenda de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso IV e art. 24, caput e § 1º, inciso III e § 5º, inciso I, da Lei Federal nº 12.527/2011 C/C art. 29, inciso I, art. 30, inciso III e art. 36 do Decreto Estadual nº 45.969/2012, art. 1º , Caput, art. 4º, art. 7º, inciso I, art.  8º, inciso III, art. 9º e art. 13 da Resolução nº 4.671/2014, do Secretário de Estado de Fazenda de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso IV e art. 24, caput e § 1º, inciso III e § 5º, inciso I, da Lei Federal nº 12.527/2011 C/C art. 29, inciso I, art. 30,inciso III e art. 36 do Decreto Estadual nº 45.969/2012, art 1º, Caput, art. 4º, art. 7º, inciso I, art. 8º, inciso III, art. 9º e art. 13 da Resolução nº4.671/2014, do Secretário de Estado de Fazenda de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso IV e art. 24, caput, § 1º, inciso I e § 5º, inciso I, da Lei Federal nº 12.527/2011 C/C Decreto Estadual nº 45.969/2012, art. 1º, caput, art. 4º, art. 7º, art. 8º, inciso III, art. 9º e art. 13 da Resolução nº 4.671/2014, do Secretário de Estado de Fazenda de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Art. 22 e art. 23, incisos III, VI e VII da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso III, da Lei Federal nº 12.527/2011 C/C art. 29, inciso I, do Decreto Estadual 45969/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso VIII, da Lei Federal nº 12.527/2011 C/C art. 29, inciso I, do Decreto Estadual nº 45.969/2011</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso VIII, da Lei Federal nº 12.527/2011 C/C art. 25, inciso IX do Decreto nº 7.724/2012.</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos VI, VII e VIII e art. 24, caput, § 1º, inciso I, da Lei Federal nº 12.527/2011 C/C art. 28 do Decreto Estadual nº 45.969/2012</t>
   </si>
 </sst>
 </file>
@@ -1350,8 +1256,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="166" formatCode="mm/dd/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy;@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -1433,29 +1339,29 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1798,7 +1704,10 @@
   <cols>
     <col min="1" max="2" width="9.140625" style="3"/>
     <col min="3" max="3" width="47.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="9.140625" style="3"/>
+    <col min="4" max="4" width="9.140625" style="3"/>
+    <col min="5" max="5" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="112" style="3" customWidth="1"/>
     <col min="8" max="8" width="19.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26" style="3" bestFit="1" customWidth="1"/>
@@ -1812,34 +1721,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>374</v>
+        <v>313</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>375</v>
+        <v>314</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>376</v>
+        <v>315</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>377</v>
+        <v>316</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>378</v>
+        <v>317</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>379</v>
+        <v>318</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>380</v>
+        <v>319</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>381</v>
+        <v>320</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>382</v>
+        <v>321</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>2</v>
@@ -1856,34 +1765,34 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>331</v>
       </c>
       <c r="H2" s="4">
-        <v>44426</v>
+        <v>44298</v>
       </c>
       <c r="I2" s="4">
-        <v>44473</v>
-      </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="L2" s="6">
+        <v>44298</v>
+      </c>
+      <c r="J2" s="6"/>
+      <c r="K2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="2">
         <v>45819</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1895,34 +1804,34 @@
         <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>331</v>
       </c>
       <c r="H3" s="4">
-        <v>44426</v>
+        <v>44298</v>
       </c>
       <c r="I3" s="4">
-        <v>44473</v>
-      </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" s="6">
+        <v>44298</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L3" s="2">
         <v>45819</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1934,34 +1843,36 @@
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G4" t="s">
+        <v>337</v>
       </c>
       <c r="H4" s="4">
-        <v>44426</v>
+        <v>43613</v>
       </c>
       <c r="I4" s="4">
-        <v>44473</v>
-      </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="L4" s="6">
+        <v>44298</v>
+      </c>
+      <c r="J4" s="4">
+        <v>45440</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="2">
         <v>45819</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1973,34 +1884,36 @@
         <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>322</v>
+      </c>
+      <c r="G5" t="s">
+        <v>337</v>
       </c>
       <c r="H5" s="4">
-        <v>44679</v>
+        <v>43657</v>
       </c>
       <c r="I5" s="4">
-        <v>45763</v>
-      </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" s="6">
+        <v>44298</v>
+      </c>
+      <c r="J5" s="4">
+        <v>45484</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="2">
         <v>45819</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2012,36 +1925,36 @@
         <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G6" t="s">
+        <v>337</v>
       </c>
       <c r="H6" s="4">
-        <v>43613</v>
+        <v>43740</v>
       </c>
       <c r="I6" s="4">
         <v>44298</v>
       </c>
       <c r="J6" s="4">
-        <v>45440</v>
+        <v>45567</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L6" s="6">
+        <v>86</v>
+      </c>
+      <c r="L6" s="2">
         <v>45819</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2053,36 +1966,36 @@
         <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G7" t="s">
+        <v>337</v>
       </c>
       <c r="H7" s="4">
-        <v>43657</v>
+        <v>43753</v>
       </c>
       <c r="I7" s="4">
         <v>44298</v>
       </c>
       <c r="J7" s="4">
-        <v>45484</v>
+        <v>45580</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L7" s="6">
+        <v>86</v>
+      </c>
+      <c r="L7" s="2">
         <v>45819</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2094,36 +2007,36 @@
         <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G8" t="s">
+        <v>337</v>
       </c>
       <c r="H8" s="4">
-        <v>43740</v>
+        <v>43948</v>
       </c>
       <c r="I8" s="4">
         <v>44298</v>
       </c>
       <c r="J8" s="4">
-        <v>45567</v>
+        <v>45774</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L8" s="6">
+        <v>86</v>
+      </c>
+      <c r="L8" s="2">
         <v>45819</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2135,36 +2048,36 @@
         <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G9" t="s">
+        <v>337</v>
       </c>
       <c r="H9" s="4">
-        <v>43753</v>
+        <v>43945</v>
       </c>
       <c r="I9" s="4">
         <v>44298</v>
       </c>
       <c r="J9" s="4">
-        <v>45580</v>
+        <v>45771</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L9" s="6">
+        <v>86</v>
+      </c>
+      <c r="L9" s="2">
         <v>45819</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2176,36 +2089,36 @@
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G10" t="s">
+        <v>337</v>
       </c>
       <c r="H10" s="4">
-        <v>43948</v>
+        <v>43970</v>
       </c>
       <c r="I10" s="4">
         <v>44298</v>
       </c>
       <c r="J10" s="4">
-        <v>45774</v>
+        <v>45796</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L10" s="6">
+        <v>86</v>
+      </c>
+      <c r="L10" s="2">
         <v>45819</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2217,36 +2130,36 @@
         <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G11" t="s">
+        <v>337</v>
       </c>
       <c r="H11" s="4">
-        <v>43945</v>
+        <v>43971</v>
       </c>
       <c r="I11" s="4">
         <v>44298</v>
       </c>
       <c r="J11" s="4">
-        <v>45771</v>
+        <v>45797</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L11" s="6">
+        <v>86</v>
+      </c>
+      <c r="L11" s="2">
         <v>45819</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2258,36 +2171,34 @@
         <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G12" t="s">
+        <v>337</v>
       </c>
       <c r="H12" s="4">
-        <v>43970</v>
+        <v>44082</v>
       </c>
       <c r="I12" s="4">
         <v>44298</v>
       </c>
-      <c r="J12" s="4">
-        <v>45796</v>
-      </c>
+      <c r="J12" s="6"/>
       <c r="K12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L12" s="6">
+        <v>86</v>
+      </c>
+      <c r="L12" s="2">
         <v>45819</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2299,36 +2210,34 @@
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G13" t="s">
+        <v>337</v>
       </c>
       <c r="H13" s="4">
-        <v>43971</v>
+        <v>44426</v>
       </c>
       <c r="I13" s="4">
-        <v>44298</v>
-      </c>
-      <c r="J13" s="4">
-        <v>45797</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L13" s="6">
+        <v>44473</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="2">
         <v>45819</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2340,34 +2249,34 @@
         <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="G14" t="s">
+        <v>337</v>
       </c>
       <c r="H14" s="4">
-        <v>44082</v>
+        <v>44426</v>
       </c>
       <c r="I14" s="4">
-        <v>44298</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L14" s="6">
+        <v>44473</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="2">
         <v>45819</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2379,34 +2288,34 @@
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>49</v>
+        <v>322</v>
+      </c>
+      <c r="G15" t="s">
+        <v>337</v>
       </c>
       <c r="H15" s="4">
-        <v>44298</v>
+        <v>44426</v>
       </c>
       <c r="I15" s="4">
-        <v>44298</v>
-      </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L15" s="6">
+        <v>44473</v>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L15" s="2">
         <v>45819</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2418,34 +2327,34 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>49</v>
+        <v>322</v>
+      </c>
+      <c r="G16" t="s">
+        <v>337</v>
       </c>
       <c r="H16" s="4">
-        <v>44298</v>
+        <v>44679</v>
       </c>
       <c r="I16" s="4">
-        <v>44298</v>
-      </c>
-      <c r="J16" s="7"/>
-      <c r="K16" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L16" s="6">
+        <v>45763</v>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" s="2">
         <v>45819</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2457,34 +2366,34 @@
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" s="3">
-        <v>13</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H17" s="8">
-        <v>44194</v>
-      </c>
-      <c r="I17" s="8">
-        <v>44194</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L17" s="6">
+        <v>100</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H17" s="7">
+        <v>44552</v>
+      </c>
+      <c r="I17" s="7">
+        <v>44552</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L17" s="2">
         <v>45819</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -2495,34 +2404,34 @@
         <v>15</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18" s="3">
-        <v>4</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H18" s="8">
+        <v>100</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H18" s="7">
         <v>44552</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="7">
         <v>44552</v>
       </c>
-      <c r="K18" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L18" s="6">
+      <c r="K18" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L18" s="2">
         <v>45819</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -2533,34 +2442,34 @@
         <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" s="3">
-        <v>4</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" s="8">
-        <v>44552</v>
-      </c>
-      <c r="I19" s="8">
-        <v>44552</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L19" s="6">
+        <v>100</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H19" s="9">
+        <v>44780</v>
+      </c>
+      <c r="I19" s="9">
+        <v>44780</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L19" s="2">
         <v>45819</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -2571,34 +2480,34 @@
         <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" s="3">
-        <v>13</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H20" s="8">
-        <v>44558</v>
-      </c>
-      <c r="I20" s="8">
-        <v>44558</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L20" s="6">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H20" s="9">
+        <v>44780</v>
+      </c>
+      <c r="I20" s="9">
+        <v>44780</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L20" s="2">
         <v>45819</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -2609,34 +2518,34 @@
         <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F21" s="3">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H21" s="10">
-        <v>44780</v>
-      </c>
-      <c r="I21" s="10">
-        <v>44780</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L21" s="6">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H21" s="9">
+        <v>45021</v>
+      </c>
+      <c r="I21" s="9">
+        <v>45021</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L21" s="2">
         <v>45819</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -2647,34 +2556,34 @@
         <v>15</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F22" s="3">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H22" s="10">
-        <v>44780</v>
-      </c>
-      <c r="I22" s="10">
-        <v>44780</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L22" s="6">
+        <v>100</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H22" s="9">
+        <v>45021</v>
+      </c>
+      <c r="I22" s="9">
+        <v>45021</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L22" s="2">
         <v>45819</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -2685,34 +2594,34 @@
         <v>15</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F23" s="3">
-        <v>13</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H23" s="8">
-        <v>44925</v>
-      </c>
-      <c r="I23" s="8">
-        <v>44925</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L23" s="6">
+        <v>100</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H23" s="9">
+        <v>45292</v>
+      </c>
+      <c r="I23" s="9">
+        <v>45292</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L23" s="2">
         <v>45819</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -2723,34 +2632,34 @@
         <v>15</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" s="3">
-        <v>4</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" s="10">
-        <v>45021</v>
-      </c>
-      <c r="I24" s="10">
-        <v>45021</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L24" s="6">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H24" s="9">
+        <v>45292</v>
+      </c>
+      <c r="I24" s="9">
+        <v>45292</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L24" s="2">
         <v>45819</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -2761,34 +2670,34 @@
         <v>15</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>139</v>
+        <v>279</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F25" s="3">
-        <v>4</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H25" s="10">
-        <v>45021</v>
-      </c>
-      <c r="I25" s="10">
-        <v>45021</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L25" s="6">
+        <v>100</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H25" s="9">
+        <v>45658</v>
+      </c>
+      <c r="I25" s="9">
+        <v>45658</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L25" s="2">
         <v>45819</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -2799,34 +2708,34 @@
         <v>15</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>140</v>
+        <v>302</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F26" s="3">
-        <v>13</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H26" s="8">
-        <v>45289</v>
-      </c>
-      <c r="I26" s="8">
-        <v>45289</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L26" s="6">
+        <v>100</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H26" s="9">
+        <v>45658</v>
+      </c>
+      <c r="I26" s="9">
+        <v>45658</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L26" s="2">
         <v>45819</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -2837,34 +2746,34 @@
         <v>15</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F27" s="3">
-        <v>4</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H27" s="10">
-        <v>45292</v>
-      </c>
-      <c r="I27" s="10">
-        <v>45292</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L27" s="6">
+        <v>100</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G27" t="s">
+        <v>337</v>
+      </c>
+      <c r="H27" s="7">
+        <v>44558</v>
+      </c>
+      <c r="I27" s="7">
+        <v>44558</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L27" s="2">
         <v>45819</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -2875,34 +2784,34 @@
         <v>15</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F28" s="3">
-        <v>4</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" s="10">
-        <v>45292</v>
-      </c>
-      <c r="I28" s="10">
-        <v>45292</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L28" s="6">
+        <v>100</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G28" t="s">
+        <v>337</v>
+      </c>
+      <c r="H28" s="7">
+        <v>44925</v>
+      </c>
+      <c r="I28" s="7">
+        <v>44925</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L28" s="2">
         <v>45819</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -2913,34 +2822,34 @@
         <v>15</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F29" s="3">
-        <v>13</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H29" s="8">
-        <v>45656</v>
-      </c>
-      <c r="I29" s="8">
-        <v>45656</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L29" s="6">
+        <v>100</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G29" t="s">
+        <v>337</v>
+      </c>
+      <c r="H29" s="7">
+        <v>45289</v>
+      </c>
+      <c r="I29" s="7">
+        <v>45289</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L29" s="2">
         <v>45819</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -2951,34 +2860,34 @@
         <v>15</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>340</v>
+        <v>122</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F30" s="3">
-        <v>4</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H30" s="10">
-        <v>45658</v>
-      </c>
-      <c r="I30" s="10">
-        <v>45658</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L30" s="6">
+        <v>100</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G30" t="s">
+        <v>337</v>
+      </c>
+      <c r="H30" s="7">
+        <v>45656</v>
+      </c>
+      <c r="I30" s="7">
+        <v>45656</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L30" s="2">
         <v>45819</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -2989,34 +2898,34 @@
         <v>15</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>363</v>
+        <v>123</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F31" s="3">
-        <v>4</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" s="10">
-        <v>45658</v>
-      </c>
-      <c r="I31" s="10">
-        <v>45658</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L31" s="6">
+        <v>100</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G31" t="s">
+        <v>337</v>
+      </c>
+      <c r="H31" s="7">
+        <v>44194</v>
+      </c>
+      <c r="I31" s="7">
+        <v>44194</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L31" s="2">
         <v>45819</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -3027,34 +2936,34 @@
         <v>16</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>369</v>
+        <v>308</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H32" s="6">
+        <v>330</v>
+      </c>
+      <c r="G32" t="s">
+        <v>342</v>
+      </c>
+      <c r="H32" s="2">
         <v>45925</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="2">
         <v>45925</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L32" s="6">
+        <v>72</v>
+      </c>
+      <c r="L32" s="2">
         <v>46072</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -3065,34 +2974,34 @@
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>371</v>
+        <v>304</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H33" s="6">
-        <v>45925</v>
-      </c>
-      <c r="I33" s="6">
-        <v>45925</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L33" s="6">
+        <v>336</v>
+      </c>
+      <c r="H33" s="2">
+        <v>45916</v>
+      </c>
+      <c r="I33" s="2">
+        <v>45916</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L33" s="2">
         <v>46072</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -3103,34 +3012,34 @@
         <v>16</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>372</v>
+        <v>310</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H34" s="6">
+        <v>336</v>
+      </c>
+      <c r="H34" s="2">
         <v>45925</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="2">
         <v>45925</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L34" s="6">
+        <v>72</v>
+      </c>
+      <c r="L34" s="2">
         <v>46072</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -3141,34 +3050,34 @@
         <v>16</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>373</v>
+        <v>311</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H35" s="6">
+        <v>336</v>
+      </c>
+      <c r="H35" s="2">
         <v>45925</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="2">
         <v>45925</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L35" s="6">
+        <v>72</v>
+      </c>
+      <c r="L35" s="2">
         <v>46072</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -3179,34 +3088,34 @@
         <v>16</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>365</v>
+        <v>312</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H36" s="6">
-        <v>45916</v>
-      </c>
-      <c r="I36" s="6">
-        <v>45916</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L36" s="6">
+        <v>336</v>
+      </c>
+      <c r="H36" s="2">
+        <v>45925</v>
+      </c>
+      <c r="I36" s="2">
+        <v>45925</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L36" s="2">
         <v>46072</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -3217,34 +3126,34 @@
         <v>16</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>366</v>
+        <v>307</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H37" s="6">
+        <v>330</v>
+      </c>
+      <c r="G37" t="s">
+        <v>344</v>
+      </c>
+      <c r="H37" s="2">
         <v>45932</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37" s="2">
         <v>45932</v>
       </c>
-      <c r="K37" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L37" s="6">
+      <c r="K37" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L37" s="2">
         <v>46072</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -3255,34 +3164,34 @@
         <v>16</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>367</v>
+        <v>305</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H38" s="6">
+        <v>330</v>
+      </c>
+      <c r="G38" t="s">
+        <v>345</v>
+      </c>
+      <c r="H38" s="2">
         <v>45932</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="2">
         <v>45932</v>
       </c>
-      <c r="K38" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L38" s="6">
+      <c r="K38" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L38" s="2">
         <v>46072</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -3293,34 +3202,34 @@
         <v>16</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>368</v>
+        <v>306</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H39" s="6">
+        <v>330</v>
+      </c>
+      <c r="G39" t="s">
+        <v>345</v>
+      </c>
+      <c r="H39" s="2">
         <v>45932</v>
       </c>
-      <c r="I39" s="6">
+      <c r="I39" s="2">
         <v>45932</v>
       </c>
-      <c r="K39" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L39" s="6">
+      <c r="K39" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L39" s="2">
         <v>46072</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -3331,34 +3240,34 @@
         <v>16</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>370</v>
+        <v>309</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H40" s="6">
+        <v>341</v>
+      </c>
+      <c r="H40" s="2">
         <v>45923</v>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="2">
         <v>45923</v>
       </c>
-      <c r="K40" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L40" s="6">
+      <c r="K40" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L40" s="2">
         <v>46072</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -3369,25 +3278,28 @@
         <v>17</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H41" s="6">
+        <v>51</v>
+      </c>
+      <c r="F41" t="s">
+        <v>323</v>
+      </c>
+      <c r="H41" s="2">
         <v>43705</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="2">
         <v>43705</v>
       </c>
       <c r="K41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L41" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M41" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="L41" s="6">
-        <v>45911</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -3398,25 +3310,28 @@
         <v>17</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H42" s="6">
+        <v>51</v>
+      </c>
+      <c r="F42" t="s">
+        <v>323</v>
+      </c>
+      <c r="H42" s="2">
         <v>45826</v>
       </c>
-      <c r="I42" s="6">
+      <c r="I42" s="2">
         <v>45826</v>
       </c>
       <c r="K42" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L42" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M42" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="L42" s="6">
-        <v>45911</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -3427,25 +3342,28 @@
         <v>17</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H43" s="6">
+        <v>51</v>
+      </c>
+      <c r="F43" t="s">
+        <v>323</v>
+      </c>
+      <c r="H43" s="2">
         <v>43705</v>
       </c>
-      <c r="I43" s="6">
+      <c r="I43" s="2">
         <v>43705</v>
       </c>
       <c r="K43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L43" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="L43" s="6">
-        <v>45911</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -3456,25 +3374,28 @@
         <v>17</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H44" s="6">
+        <v>51</v>
+      </c>
+      <c r="F44" t="s">
+        <v>323</v>
+      </c>
+      <c r="H44" s="2">
         <v>43705</v>
       </c>
-      <c r="I44" s="6">
+      <c r="I44" s="2">
         <v>43705</v>
       </c>
       <c r="K44" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L44" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M44" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="L44" s="6">
-        <v>45911</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -3485,25 +3406,28 @@
         <v>17</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H45" s="6">
+        <v>51</v>
+      </c>
+      <c r="F45" t="s">
+        <v>323</v>
+      </c>
+      <c r="H45" s="2">
         <v>45833</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45" s="2">
         <v>45833</v>
       </c>
       <c r="K45" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L45" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M45" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="L45" s="6">
-        <v>45911</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -3514,25 +3438,28 @@
         <v>17</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H46" s="6">
+        <v>51</v>
+      </c>
+      <c r="F46" t="s">
+        <v>323</v>
+      </c>
+      <c r="H46" s="2">
         <v>43705</v>
       </c>
-      <c r="I46" s="6">
+      <c r="I46" s="2">
         <v>43705</v>
       </c>
       <c r="K46" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L46" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M46" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="L46" s="6">
-        <v>45911</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -3543,25 +3470,28 @@
         <v>17</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H47" s="6">
+        <v>51</v>
+      </c>
+      <c r="F47" t="s">
+        <v>323</v>
+      </c>
+      <c r="H47" s="2">
         <v>43705</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I47" s="2">
         <v>43705</v>
       </c>
       <c r="K47" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L47" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M47" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="L47" s="6">
-        <v>45911</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -3572,25 +3502,28 @@
         <v>17</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H48" s="6">
+        <v>51</v>
+      </c>
+      <c r="F48" t="s">
+        <v>323</v>
+      </c>
+      <c r="H48" s="2">
         <v>43705</v>
       </c>
-      <c r="I48" s="6">
+      <c r="I48" s="2">
         <v>43705</v>
       </c>
       <c r="K48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L48" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M48" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="L48" s="6">
-        <v>45911</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -3601,25 +3534,28 @@
         <v>17</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H49" s="6">
+        <v>51</v>
+      </c>
+      <c r="F49" t="s">
+        <v>323</v>
+      </c>
+      <c r="H49" s="2">
         <v>43697</v>
       </c>
-      <c r="I49" s="6">
+      <c r="I49" s="2">
         <v>43697</v>
       </c>
       <c r="K49" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L49" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M49" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="L49" s="6">
-        <v>45911</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -3630,25 +3566,28 @@
         <v>17</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H50" s="6">
+        <v>82</v>
+      </c>
+      <c r="F50" t="s">
+        <v>323</v>
+      </c>
+      <c r="H50" s="2">
         <v>43705</v>
       </c>
-      <c r="I50" s="6">
+      <c r="I50" s="2">
         <v>43705</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L50" s="6">
+        <v>83</v>
+      </c>
+      <c r="L50" s="2">
         <v>45911</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -3659,31 +3598,31 @@
         <v>18</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>345</v>
+        <v>280</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F51" s="3">
-        <v>11</v>
+        <v>28</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>105</v>
+        <v>333</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L51" s="6">
+        <v>86</v>
+      </c>
+      <c r="L51" s="2">
         <v>45814</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -3694,31 +3633,31 @@
         <v>18</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>344</v>
+        <v>282</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F52" s="3">
-        <v>9</v>
+        <v>28</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>105</v>
+        <v>333</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L52" s="6">
+        <v>86</v>
+      </c>
+      <c r="L52" s="2">
         <v>45814</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -3729,31 +3668,31 @@
         <v>18</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>341</v>
+        <v>285</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F53" s="3">
-        <v>11</v>
+      <c r="F53" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>98</v>
+        <v>333</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L53" s="6">
+        <v>86</v>
+      </c>
+      <c r="L53" s="2">
         <v>45814</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -3764,31 +3703,31 @@
         <v>18</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>100</v>
+        <v>292</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F54" s="3">
-        <v>11</v>
+      <c r="F54" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>101</v>
+        <v>333</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L54" s="6">
+        <v>86</v>
+      </c>
+      <c r="L54" s="2">
         <v>45814</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -3799,31 +3738,31 @@
         <v>18</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>102</v>
+        <v>293</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="3">
-        <v>11</v>
+      <c r="F55" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>98</v>
+        <v>333</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L55" s="6">
+        <v>86</v>
+      </c>
+      <c r="L55" s="2">
         <v>45814</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -3834,31 +3773,31 @@
         <v>18</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>346</v>
+        <v>296</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>106</v>
+        <v>301</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F56" s="3">
-        <v>11</v>
+      <c r="F56" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>98</v>
+        <v>333</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L56" s="6">
+        <v>86</v>
+      </c>
+      <c r="L56" s="2">
         <v>45814</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -3869,31 +3808,31 @@
         <v>18</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>347</v>
+        <v>298</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>107</v>
+        <v>300</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F57" s="3">
-        <v>12</v>
+      <c r="F57" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>105</v>
+        <v>333</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L57" s="6">
+        <v>86</v>
+      </c>
+      <c r="L57" s="2">
         <v>45814</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -3904,31 +3843,31 @@
         <v>18</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>111</v>
+        <v>299</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F58" s="3">
-        <v>4</v>
+      <c r="F58" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>108</v>
+        <v>333</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L58" s="6">
+        <v>86</v>
+      </c>
+      <c r="L58" s="2">
         <v>45814</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -3939,31 +3878,31 @@
         <v>18</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>349</v>
+        <v>281</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F59" s="3">
-        <v>9</v>
+      <c r="F59" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>105</v>
+        <v>336</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L59" s="6">
+        <v>86</v>
+      </c>
+      <c r="L59" s="2">
         <v>45814</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -3974,31 +3913,31 @@
         <v>18</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>350</v>
+        <v>287</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F60" s="3">
-        <v>11</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>105</v>
+      <c r="F60" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G60" t="s">
+        <v>337</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L60" s="6">
+        <v>86</v>
+      </c>
+      <c r="L60" s="2">
         <v>45814</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -4009,31 +3948,31 @@
         <v>18</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>355</v>
+        <v>289</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>353</v>
+        <v>93</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F61" s="3">
-        <v>11</v>
+      <c r="F61" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>98</v>
+        <v>332</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L61" s="6">
+        <v>86</v>
+      </c>
+      <c r="L61" s="2">
         <v>45814</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -4044,31 +3983,31 @@
         <v>18</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>356</v>
+        <v>284</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>354</v>
+        <v>91</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F62" s="3">
-        <v>11</v>
+        <v>51</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>98</v>
+        <v>332</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L62" s="6">
+        <v>72</v>
+      </c>
+      <c r="L62" s="2">
         <v>45814</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -4079,31 +4018,31 @@
         <v>18</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>357</v>
+        <v>286</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>362</v>
+        <v>92</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F63" s="3">
-        <v>11</v>
+      <c r="F63" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>98</v>
+        <v>332</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L63" s="6">
+        <v>86</v>
+      </c>
+      <c r="L63" s="2">
         <v>45814</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -4114,31 +4053,31 @@
         <v>18</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>359</v>
+        <v>288</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>361</v>
+        <v>94</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F64" s="3">
-        <v>11</v>
+      <c r="F64" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>98</v>
+        <v>332</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L64" s="6">
+        <v>86</v>
+      </c>
+      <c r="L64" s="2">
         <v>45814</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -4149,31 +4088,31 @@
         <v>18</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>358</v>
+        <v>283</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F65" s="3">
-        <v>11</v>
+        <v>82</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>98</v>
+        <v>332</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L65" s="6">
+        <v>83</v>
+      </c>
+      <c r="L65" s="2">
         <v>45814</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -4184,34 +4123,34 @@
         <v>19</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>351</v>
+        <v>290</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H66" s="6">
+        <v>329</v>
+      </c>
+      <c r="G66" t="s">
+        <v>337</v>
+      </c>
+      <c r="H66" s="2">
         <v>45352</v>
       </c>
-      <c r="I66" s="6">
+      <c r="I66" s="2">
         <v>45352</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L66" s="6">
+        <v>86</v>
+      </c>
+      <c r="L66" s="2">
         <v>45819</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -4222,34 +4161,34 @@
         <v>19</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>352</v>
+        <v>291</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H67" s="6">
+        <v>329</v>
+      </c>
+      <c r="G67" t="s">
+        <v>337</v>
+      </c>
+      <c r="H67" s="2">
         <v>45352</v>
       </c>
-      <c r="I67" s="6">
+      <c r="I67" s="2">
         <v>45352</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L67" s="6">
+        <v>86</v>
+      </c>
+      <c r="L67" s="2">
         <v>45819</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -4260,37 +4199,37 @@
         <v>20</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>147</v>
+      <c r="F68" t="s">
+        <v>323</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>148</v>
+        <v>359</v>
       </c>
       <c r="H68" s="2">
         <v>42191</v>
       </c>
-      <c r="I68" s="6">
+      <c r="I68" s="2">
         <v>44376</v>
       </c>
-      <c r="J68" s="6">
+      <c r="J68" s="2">
         <v>46202</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L68" s="6">
+        <v>86</v>
+      </c>
+      <c r="L68" s="2">
         <v>45817</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" spans="1:13" customFormat="1">
@@ -4300,32 +4239,36 @@
       <c r="B69" t="s">
         <v>21</v>
       </c>
-      <c r="C69" t="s">
-        <v>279</v>
-      </c>
-      <c r="D69" t="s">
-        <v>280</v>
+      <c r="C69" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>281</v>
+      <c r="F69" t="s">
+        <v>323</v>
       </c>
       <c r="G69" t="s">
-        <v>282</v>
-      </c>
-      <c r="H69" s="6">
-        <v>42990</v>
+        <v>357</v>
+      </c>
+      <c r="H69" s="2">
+        <v>44349</v>
       </c>
       <c r="I69" s="2">
-        <v>45967</v>
+        <v>43486</v>
+      </c>
+      <c r="J69" s="2">
+        <v>45428</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>99</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L69" s="3"/>
       <c r="M69" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -4336,31 +4279,31 @@
         <v>21</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>283</v>
+        <v>233</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>284</v>
+        <v>230</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>281</v>
+      <c r="F70" t="s">
+        <v>323</v>
       </c>
       <c r="G70" t="s">
-        <v>282</v>
-      </c>
-      <c r="H70" s="6">
-        <v>42990</v>
-      </c>
-      <c r="I70" s="6">
-        <v>45230</v>
+        <v>335</v>
+      </c>
+      <c r="H70" s="2">
+        <v>44617</v>
+      </c>
+      <c r="I70" s="2">
+        <v>45225</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M70" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -4371,31 +4314,31 @@
         <v>21</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>285</v>
+        <v>234</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>281</v>
+      <c r="F71" t="s">
+        <v>323</v>
       </c>
       <c r="G71" t="s">
-        <v>282</v>
-      </c>
-      <c r="H71" s="6">
-        <v>42990</v>
-      </c>
-      <c r="I71" s="6">
-        <v>45230</v>
+        <v>335</v>
+      </c>
+      <c r="H71" s="2">
+        <v>44617</v>
+      </c>
+      <c r="I71" s="2">
+        <v>45225</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M71" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -4405,32 +4348,34 @@
       <c r="B72" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>284</v>
+      <c r="C72" t="s">
+        <v>227</v>
+      </c>
+      <c r="D72" t="s">
+        <v>228</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G72" t="s">
-        <v>288</v>
-      </c>
-      <c r="H72" s="6">
-        <v>44617</v>
-      </c>
-      <c r="I72" s="6">
-        <v>45225</v>
-      </c>
+      <c r="F72" t="s">
+        <v>323</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H72" s="2">
+        <v>42990</v>
+      </c>
+      <c r="I72" s="2">
+        <v>45967</v>
+      </c>
+      <c r="J72"/>
       <c r="K72" s="3" t="s">
-        <v>99</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L72"/>
       <c r="M72" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -4441,31 +4386,31 @@
         <v>21</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>289</v>
+        <v>229</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G73" t="s">
-        <v>288</v>
-      </c>
-      <c r="H73" s="6">
-        <v>44617</v>
-      </c>
-      <c r="I73" s="6">
-        <v>45225</v>
+      <c r="F73" t="s">
+        <v>323</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H73" s="2">
+        <v>42990</v>
+      </c>
+      <c r="I73" s="2">
+        <v>45230</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M73" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -4476,34 +4421,31 @@
         <v>21</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>290</v>
+        <v>231</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>291</v>
+        <v>232</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G74" t="s">
-        <v>282</v>
-      </c>
-      <c r="H74" s="6">
-        <v>44617</v>
-      </c>
-      <c r="I74" s="6">
-        <v>43486</v>
-      </c>
-      <c r="J74" s="6">
-        <v>45432</v>
+      <c r="F74" t="s">
+        <v>323</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H74" s="2">
+        <v>42990</v>
+      </c>
+      <c r="I74" s="2">
+        <v>45230</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M74" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -4514,34 +4456,34 @@
         <v>21</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G75" t="s">
-        <v>293</v>
-      </c>
-      <c r="H75" s="6">
+      <c r="F75" t="s">
+        <v>323</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H75" s="2">
         <v>44617</v>
       </c>
-      <c r="I75" s="6">
-        <v>43503</v>
-      </c>
-      <c r="J75" s="6">
+      <c r="I75" s="2">
+        <v>43486</v>
+      </c>
+      <c r="J75" s="2">
         <v>45432</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M75" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -4552,34 +4494,34 @@
         <v>21</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>294</v>
+        <v>238</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G76" t="s">
-        <v>282</v>
-      </c>
-      <c r="H76" s="6">
+      <c r="F76" t="s">
+        <v>323</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H76" s="2">
         <v>44734</v>
       </c>
-      <c r="I76" s="6">
+      <c r="I76" s="2">
         <v>43587</v>
       </c>
-      <c r="J76" s="6">
+      <c r="J76" s="2">
         <v>45432</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M76" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -4590,34 +4532,34 @@
         <v>21</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>295</v>
+        <v>263</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G77" t="s">
-        <v>293</v>
-      </c>
-      <c r="H77" s="6">
-        <v>45820</v>
-      </c>
-      <c r="I77" s="6">
-        <v>43264</v>
-      </c>
-      <c r="J77" s="6">
-        <v>45432</v>
+      <c r="F77" t="s">
+        <v>323</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H77" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I77" s="2">
+        <v>43511</v>
+      </c>
+      <c r="J77" s="2">
+        <v>45428</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M77" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -4628,34 +4570,34 @@
         <v>21</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F78" s="3" t="s">
-        <v>281</v>
+      <c r="F78" t="s">
+        <v>323</v>
       </c>
       <c r="G78" t="s">
-        <v>297</v>
-      </c>
-      <c r="H78" s="6">
-        <v>45820</v>
-      </c>
-      <c r="I78" s="6">
-        <v>43271</v>
-      </c>
-      <c r="J78" s="6">
+        <v>337</v>
+      </c>
+      <c r="H78" s="2">
+        <v>44617</v>
+      </c>
+      <c r="I78" s="2">
+        <v>43503</v>
+      </c>
+      <c r="J78" s="2">
         <v>45432</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M78" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -4666,34 +4608,34 @@
         <v>21</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>299</v>
+        <v>239</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>281</v>
+      <c r="F79" t="s">
+        <v>323</v>
       </c>
       <c r="G79" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="H79" s="2">
-        <v>46013</v>
-      </c>
-      <c r="I79" s="6">
-        <v>43294</v>
-      </c>
-      <c r="J79" s="6">
-        <v>45428</v>
+        <v>45820</v>
+      </c>
+      <c r="I79" s="2">
+        <v>43264</v>
+      </c>
+      <c r="J79" s="2">
+        <v>45432</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M79" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -4704,34 +4646,34 @@
         <v>21</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>300</v>
+        <v>242</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>281</v>
+      <c r="F80" t="s">
+        <v>323</v>
       </c>
       <c r="G80" t="s">
-        <v>293</v>
-      </c>
-      <c r="H80" s="6">
-        <v>44176</v>
-      </c>
-      <c r="I80" s="6">
-        <v>43297</v>
-      </c>
-      <c r="J80" s="6">
+        <v>337</v>
+      </c>
+      <c r="H80" s="2">
+        <v>46013</v>
+      </c>
+      <c r="I80" s="2">
+        <v>43294</v>
+      </c>
+      <c r="J80" s="2">
         <v>45428</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M80" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -4742,34 +4684,34 @@
         <v>21</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>301</v>
+        <v>243</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>281</v>
+      <c r="F81" t="s">
+        <v>323</v>
       </c>
       <c r="G81" t="s">
-        <v>302</v>
-      </c>
-      <c r="H81" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I81" s="6">
-        <v>43304</v>
-      </c>
-      <c r="J81" s="6">
+        <v>337</v>
+      </c>
+      <c r="H81" s="2">
+        <v>44176</v>
+      </c>
+      <c r="I81" s="2">
+        <v>43297</v>
+      </c>
+      <c r="J81" s="2">
         <v>45428</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M81" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -4780,34 +4722,34 @@
         <v>21</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>303</v>
+        <v>245</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>281</v>
+      <c r="F82" t="s">
+        <v>323</v>
       </c>
       <c r="G82" t="s">
-        <v>293</v>
-      </c>
-      <c r="H82" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I82" s="6">
+        <v>337</v>
+      </c>
+      <c r="H82" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I82" s="2">
         <v>43308</v>
       </c>
-      <c r="J82" s="6">
+      <c r="J82" s="2">
         <v>45428</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M82" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -4818,34 +4760,34 @@
         <v>21</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>304</v>
+        <v>249</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>281</v>
+      <c r="F83" t="s">
+        <v>323</v>
       </c>
       <c r="G83" t="s">
-        <v>306</v>
-      </c>
-      <c r="H83" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I83" s="6">
-        <v>43308</v>
-      </c>
-      <c r="J83" s="6">
+        <v>337</v>
+      </c>
+      <c r="H83" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I83" s="2">
+        <v>43328</v>
+      </c>
+      <c r="J83" s="2">
         <v>45428</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M83" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -4856,34 +4798,34 @@
         <v>21</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>281</v>
+      <c r="F84" t="s">
+        <v>323</v>
       </c>
       <c r="G84" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="H84" s="2">
         <v>44349</v>
       </c>
-      <c r="I84" s="6">
-        <v>43308</v>
-      </c>
-      <c r="J84" s="6">
+      <c r="I84" s="2">
+        <v>43328</v>
+      </c>
+      <c r="J84" s="2">
         <v>45428</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M84" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -4894,34 +4836,34 @@
         <v>21</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>307</v>
+        <v>251</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>281</v>
+      <c r="F85" t="s">
+        <v>323</v>
       </c>
       <c r="G85" t="s">
-        <v>302</v>
-      </c>
-      <c r="H85" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I85" s="6">
-        <v>43325</v>
-      </c>
-      <c r="J85" s="6">
+        <v>337</v>
+      </c>
+      <c r="H85" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I85" s="2">
+        <v>43329</v>
+      </c>
+      <c r="J85" s="2">
         <v>45428</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M85" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -4932,34 +4874,34 @@
         <v>21</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>308</v>
+        <v>252</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F86" s="3" t="s">
-        <v>281</v>
+      <c r="F86" t="s">
+        <v>323</v>
       </c>
       <c r="G86" t="s">
-        <v>293</v>
-      </c>
-      <c r="H86" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I86" s="6">
-        <v>43328</v>
-      </c>
-      <c r="J86" s="6">
+        <v>337</v>
+      </c>
+      <c r="H86" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I86" s="2">
+        <v>43339</v>
+      </c>
+      <c r="J86" s="2">
         <v>45428</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M86" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -4970,34 +4912,34 @@
         <v>21</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F87" s="3" t="s">
-        <v>281</v>
+      <c r="F87" t="s">
+        <v>323</v>
       </c>
       <c r="G87" t="s">
-        <v>293</v>
-      </c>
-      <c r="H87" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I87" s="6">
-        <v>43328</v>
-      </c>
-      <c r="J87" s="6">
+        <v>337</v>
+      </c>
+      <c r="H87" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I87" s="2">
+        <v>43353</v>
+      </c>
+      <c r="J87" s="2">
         <v>45428</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M87" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -5008,34 +4950,34 @@
         <v>21</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>310</v>
+        <v>255</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>281</v>
+      <c r="F88" t="s">
+        <v>323</v>
       </c>
       <c r="G88" t="s">
-        <v>293</v>
-      </c>
-      <c r="H88" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I88" s="6">
-        <v>43329</v>
-      </c>
-      <c r="J88" s="6">
+        <v>337</v>
+      </c>
+      <c r="H88" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I88" s="2">
+        <v>43415</v>
+      </c>
+      <c r="J88" s="2">
         <v>45428</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M88" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -5046,34 +4988,34 @@
         <v>21</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>311</v>
+        <v>256</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>339</v>
+      <c r="F89" t="s">
+        <v>323</v>
       </c>
       <c r="G89" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="H89" s="2">
         <v>44349</v>
       </c>
-      <c r="I89" s="6">
-        <v>43339</v>
-      </c>
-      <c r="J89" s="6">
+      <c r="I89" s="2">
+        <v>43416</v>
+      </c>
+      <c r="J89" s="2">
         <v>45428</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M89" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -5084,34 +5026,34 @@
         <v>21</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>312</v>
+        <v>258</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F90" s="3" t="s">
-        <v>339</v>
+      <c r="F90" t="s">
+        <v>323</v>
       </c>
       <c r="G90" t="s">
-        <v>302</v>
-      </c>
-      <c r="H90" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I90" s="6">
-        <v>43346</v>
-      </c>
-      <c r="J90" s="6">
+        <v>337</v>
+      </c>
+      <c r="H90" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I90" s="2">
+        <v>43472</v>
+      </c>
+      <c r="J90" s="2">
         <v>45428</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M90" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -5122,34 +5064,34 @@
         <v>21</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>313</v>
+        <v>259</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>339</v>
+      <c r="F91" t="s">
+        <v>323</v>
       </c>
       <c r="G91" t="s">
-        <v>293</v>
-      </c>
-      <c r="H91" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I91" s="6">
-        <v>43353</v>
-      </c>
-      <c r="J91" s="6">
+        <v>337</v>
+      </c>
+      <c r="H91" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I91" s="2">
+        <v>43480</v>
+      </c>
+      <c r="J91" s="2">
         <v>45428</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M91" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -5160,34 +5102,34 @@
         <v>21</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>314</v>
+        <v>261</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>339</v>
+      <c r="F92" t="s">
+        <v>323</v>
       </c>
       <c r="G92" t="s">
-        <v>293</v>
-      </c>
-      <c r="H92" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I92" s="6">
-        <v>43415</v>
-      </c>
-      <c r="J92" s="6">
+        <v>337</v>
+      </c>
+      <c r="H92" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I92" s="2">
+        <v>43500</v>
+      </c>
+      <c r="J92" s="2">
         <v>45428</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M92" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -5198,34 +5140,34 @@
         <v>21</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>315</v>
+        <v>262</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>339</v>
+      <c r="F93" t="s">
+        <v>323</v>
       </c>
       <c r="G93" t="s">
-        <v>293</v>
-      </c>
-      <c r="H93" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I93" s="6">
-        <v>43416</v>
-      </c>
-      <c r="J93" s="6">
+        <v>337</v>
+      </c>
+      <c r="H93" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I93" s="2">
+        <v>43509</v>
+      </c>
+      <c r="J93" s="2">
         <v>45428</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M93" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -5236,34 +5178,34 @@
         <v>21</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>316</v>
+        <v>264</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>339</v>
+      <c r="F94" t="s">
+        <v>323</v>
       </c>
       <c r="G94" t="s">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="H94" s="2">
         <v>44349</v>
       </c>
-      <c r="I94" s="6">
-        <v>43461</v>
-      </c>
-      <c r="J94" s="6">
+      <c r="I94" s="2">
+        <v>43524</v>
+      </c>
+      <c r="J94" s="2">
         <v>45428</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M94" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -5274,34 +5216,34 @@
         <v>21</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>339</v>
+      <c r="F95" t="s">
+        <v>323</v>
       </c>
       <c r="G95" t="s">
-        <v>293</v>
-      </c>
-      <c r="H95" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I95" s="6">
-        <v>43472</v>
-      </c>
-      <c r="J95" s="6">
+        <v>337</v>
+      </c>
+      <c r="H95" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I95" s="2">
+        <v>43545</v>
+      </c>
+      <c r="J95" s="2">
         <v>45428</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M95" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -5312,34 +5254,34 @@
         <v>21</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>318</v>
+        <v>267</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>339</v>
+      <c r="F96" t="s">
+        <v>323</v>
       </c>
       <c r="G96" t="s">
-        <v>293</v>
-      </c>
-      <c r="H96" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I96" s="6">
-        <v>43480</v>
-      </c>
-      <c r="J96" s="6">
+        <v>337</v>
+      </c>
+      <c r="H96" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I96" s="2">
+        <v>43545</v>
+      </c>
+      <c r="J96" s="2">
         <v>45428</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M96" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -5350,34 +5292,34 @@
         <v>21</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F97" s="3" t="s">
-        <v>339</v>
+      <c r="F97" t="s">
+        <v>323</v>
       </c>
       <c r="G97" t="s">
-        <v>320</v>
-      </c>
-      <c r="H97" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I97" s="6">
-        <v>43486</v>
-      </c>
-      <c r="J97" s="6">
+        <v>337</v>
+      </c>
+      <c r="H97" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I97" s="2">
+        <v>43545</v>
+      </c>
+      <c r="J97" s="2">
         <v>45428</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M97" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -5388,34 +5330,34 @@
         <v>21</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>321</v>
+        <v>269</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F98" s="3" t="s">
-        <v>339</v>
+      <c r="F98" t="s">
+        <v>323</v>
       </c>
       <c r="G98" t="s">
-        <v>293</v>
-      </c>
-      <c r="H98" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I98" s="6">
-        <v>43500</v>
-      </c>
-      <c r="J98" s="6">
+        <v>337</v>
+      </c>
+      <c r="H98" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I98" s="2">
+        <v>43549</v>
+      </c>
+      <c r="J98" s="2">
         <v>45428</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M98" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -5426,34 +5368,34 @@
         <v>21</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>322</v>
+        <v>270</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F99" s="3" t="s">
-        <v>339</v>
+      <c r="F99" t="s">
+        <v>323</v>
       </c>
       <c r="G99" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="H99" s="2">
         <v>44349</v>
       </c>
-      <c r="I99" s="6">
-        <v>43509</v>
-      </c>
-      <c r="J99" s="6">
+      <c r="I99" s="2">
+        <v>43551</v>
+      </c>
+      <c r="J99" s="2">
         <v>45428</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M99" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -5464,34 +5406,34 @@
         <v>21</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>339</v>
+      <c r="F100" t="s">
+        <v>323</v>
       </c>
       <c r="G100" t="s">
-        <v>282</v>
-      </c>
-      <c r="H100" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I100" s="6">
-        <v>43511</v>
-      </c>
-      <c r="J100" s="6">
+        <v>337</v>
+      </c>
+      <c r="H100" s="2">
+        <v>45656</v>
+      </c>
+      <c r="I100" s="2">
+        <v>43559</v>
+      </c>
+      <c r="J100" s="2">
         <v>45428</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M100" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -5502,34 +5444,34 @@
         <v>21</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>339</v>
+      <c r="F101" t="s">
+        <v>323</v>
       </c>
       <c r="G101" t="s">
-        <v>293</v>
-      </c>
-      <c r="H101" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I101" s="6">
-        <v>43524</v>
-      </c>
-      <c r="J101" s="6">
+        <v>337</v>
+      </c>
+      <c r="H101" s="2">
+        <v>43500</v>
+      </c>
+      <c r="I101" s="2">
+        <v>43599</v>
+      </c>
+      <c r="J101" s="2">
         <v>45428</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M101" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -5540,34 +5482,34 @@
         <v>21</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>325</v>
+        <v>240</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>339</v>
+      <c r="F102" t="s">
+        <v>323</v>
       </c>
       <c r="G102" t="s">
-        <v>297</v>
-      </c>
-      <c r="H102" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I102" s="6">
-        <v>43543</v>
-      </c>
-      <c r="J102" s="6">
-        <v>45428</v>
+        <v>358</v>
+      </c>
+      <c r="H102" s="2">
+        <v>45820</v>
+      </c>
+      <c r="I102" s="2">
+        <v>43271</v>
+      </c>
+      <c r="J102" s="2">
+        <v>45432</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M102" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -5578,34 +5520,34 @@
         <v>21</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>326</v>
+        <v>257</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F103" s="3" t="s">
-        <v>339</v>
+      <c r="F103" t="s">
+        <v>323</v>
       </c>
       <c r="G103" t="s">
-        <v>293</v>
-      </c>
-      <c r="H103" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I103" s="6">
-        <v>43545</v>
-      </c>
-      <c r="J103" s="6">
+        <v>358</v>
+      </c>
+      <c r="H103" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I103" s="2">
+        <v>43461</v>
+      </c>
+      <c r="J103" s="2">
         <v>45428</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M103" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -5616,34 +5558,34 @@
         <v>21</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>327</v>
+        <v>265</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F104" s="3" t="s">
-        <v>339</v>
+      <c r="F104" t="s">
+        <v>323</v>
       </c>
       <c r="G104" t="s">
-        <v>293</v>
+        <v>358</v>
       </c>
       <c r="H104" s="2">
         <v>44349</v>
       </c>
-      <c r="I104" s="6">
-        <v>43545</v>
-      </c>
-      <c r="J104" s="6">
+      <c r="I104" s="2">
+        <v>43543</v>
+      </c>
+      <c r="J104" s="2">
         <v>45428</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M104" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -5654,34 +5596,34 @@
         <v>21</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>328</v>
+        <v>274</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F105" s="3" t="s">
-        <v>339</v>
+      <c r="F105" t="s">
+        <v>323</v>
       </c>
       <c r="G105" t="s">
-        <v>293</v>
-      </c>
-      <c r="H105" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I105" s="6">
-        <v>43545</v>
-      </c>
-      <c r="J105" s="6">
+        <v>358</v>
+      </c>
+      <c r="H105" s="2">
+        <v>42734</v>
+      </c>
+      <c r="I105" s="2">
+        <v>43571</v>
+      </c>
+      <c r="J105" s="2">
         <v>45428</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M105" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -5692,34 +5634,34 @@
         <v>21</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F106" s="3" t="s">
-        <v>339</v>
+      <c r="F106" t="s">
+        <v>323</v>
       </c>
       <c r="G106" t="s">
-        <v>293</v>
-      </c>
-      <c r="H106" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I106" s="6">
-        <v>43549</v>
-      </c>
-      <c r="J106" s="6">
+        <v>358</v>
+      </c>
+      <c r="H106" s="2">
+        <v>43132</v>
+      </c>
+      <c r="I106" s="2">
+        <v>43571</v>
+      </c>
+      <c r="J106" s="2">
         <v>45428</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M106" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -5730,34 +5672,34 @@
         <v>21</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F107" s="3" t="s">
-        <v>339</v>
+      <c r="F107" t="s">
+        <v>323</v>
       </c>
       <c r="G107" t="s">
-        <v>293</v>
-      </c>
-      <c r="H107" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I107" s="6">
-        <v>43551</v>
-      </c>
-      <c r="J107" s="6">
+        <v>358</v>
+      </c>
+      <c r="H107" s="2">
+        <v>43819</v>
+      </c>
+      <c r="I107" s="2">
+        <v>43609</v>
+      </c>
+      <c r="J107" s="2">
         <v>45428</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M107" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -5768,34 +5710,34 @@
         <v>21</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>331</v>
+        <v>278</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F108" s="3" t="s">
-        <v>339</v>
+      <c r="F108" t="s">
+        <v>323</v>
       </c>
       <c r="G108" t="s">
-        <v>302</v>
-      </c>
-      <c r="H108" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I108" s="6">
-        <v>43551</v>
-      </c>
-      <c r="J108" s="6">
+        <v>358</v>
+      </c>
+      <c r="H108" s="2">
+        <v>44426</v>
+      </c>
+      <c r="I108" s="2">
+        <v>43511</v>
+      </c>
+      <c r="J108" s="2">
         <v>45428</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M108" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -5806,34 +5748,34 @@
         <v>21</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F109" s="3" t="s">
-        <v>339</v>
+      <c r="F109" t="s">
+        <v>323</v>
       </c>
       <c r="G109" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="H109" s="2">
-        <v>45656</v>
-      </c>
-      <c r="I109" s="6">
-        <v>43559</v>
-      </c>
-      <c r="J109" s="6">
+        <v>44349</v>
+      </c>
+      <c r="I109" s="2">
+        <v>43308</v>
+      </c>
+      <c r="J109" s="2">
         <v>45428</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M109" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -5844,34 +5786,34 @@
         <v>21</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>333</v>
+        <v>247</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F110" s="3" t="s">
-        <v>339</v>
+      <c r="F110" t="s">
+        <v>323</v>
       </c>
       <c r="G110" t="s">
-        <v>302</v>
-      </c>
-      <c r="H110" s="6">
-        <v>43712</v>
-      </c>
-      <c r="I110" s="6">
-        <v>43570</v>
-      </c>
-      <c r="J110" s="6">
+        <v>338</v>
+      </c>
+      <c r="H110" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I110" s="2">
+        <v>43308</v>
+      </c>
+      <c r="J110" s="2">
         <v>45428</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M110" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -5882,34 +5824,34 @@
         <v>21</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>334</v>
+        <v>244</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F111" s="3" t="s">
-        <v>339</v>
+      <c r="F111" t="s">
+        <v>323</v>
       </c>
       <c r="G111" t="s">
-        <v>297</v>
+        <v>340</v>
       </c>
       <c r="H111" s="2">
-        <v>42734</v>
-      </c>
-      <c r="I111" s="6">
-        <v>43571</v>
-      </c>
-      <c r="J111" s="6">
+        <v>44349</v>
+      </c>
+      <c r="I111" s="2">
+        <v>43304</v>
+      </c>
+      <c r="J111" s="2">
         <v>45428</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M111" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -5920,34 +5862,34 @@
         <v>21</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>335</v>
+        <v>248</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F112" s="3" t="s">
-        <v>339</v>
+      <c r="F112" t="s">
+        <v>323</v>
       </c>
       <c r="G112" t="s">
-        <v>297</v>
-      </c>
-      <c r="H112" s="6">
-        <v>43132</v>
-      </c>
-      <c r="I112" s="6">
-        <v>43571</v>
-      </c>
-      <c r="J112" s="6">
+        <v>340</v>
+      </c>
+      <c r="H112" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I112" s="2">
+        <v>43325</v>
+      </c>
+      <c r="J112" s="2">
         <v>45428</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M112" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -5958,34 +5900,34 @@
         <v>21</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>336</v>
+        <v>253</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F113" s="3" t="s">
-        <v>339</v>
+      <c r="F113" t="s">
+        <v>323</v>
       </c>
       <c r="G113" t="s">
-        <v>293</v>
-      </c>
-      <c r="H113" s="6">
-        <v>43500</v>
-      </c>
-      <c r="I113" s="6">
-        <v>43599</v>
-      </c>
-      <c r="J113" s="6">
+        <v>340</v>
+      </c>
+      <c r="H113" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I113" s="2">
+        <v>43346</v>
+      </c>
+      <c r="J113" s="2">
         <v>45428</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M113" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -5996,34 +5938,34 @@
         <v>21</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>337</v>
+        <v>271</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F114" s="3" t="s">
-        <v>339</v>
+      <c r="F114" t="s">
+        <v>323</v>
       </c>
       <c r="G114" t="s">
-        <v>297</v>
+        <v>340</v>
       </c>
       <c r="H114" s="2">
-        <v>43819</v>
-      </c>
-      <c r="I114" s="6">
-        <v>43609</v>
-      </c>
-      <c r="J114" s="6">
+        <v>44349</v>
+      </c>
+      <c r="I114" s="2">
+        <v>43551</v>
+      </c>
+      <c r="J114" s="2">
         <v>45428</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M114" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -6034,34 +5976,34 @@
         <v>21</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>338</v>
+        <v>273</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F115" s="3" t="s">
-        <v>339</v>
+      <c r="F115" t="s">
+        <v>323</v>
       </c>
       <c r="G115" t="s">
-        <v>297</v>
-      </c>
-      <c r="H115" s="6">
-        <v>44426</v>
-      </c>
-      <c r="I115" s="6">
-        <v>43511</v>
-      </c>
-      <c r="J115" s="6">
+        <v>340</v>
+      </c>
+      <c r="H115" s="2">
+        <v>43712</v>
+      </c>
+      <c r="I115" s="2">
+        <v>43570</v>
+      </c>
+      <c r="J115" s="2">
         <v>45428</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M115" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="116" spans="1:13" customFormat="1">
@@ -6073,32 +6015,32 @@
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="3" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>154</v>
+        <v>324</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H116" s="6">
-        <v>44194</v>
-      </c>
-      <c r="I116" s="6">
-        <v>42990</v>
+        <v>350</v>
+      </c>
+      <c r="H116" s="2">
+        <v>45821</v>
+      </c>
+      <c r="I116" s="2">
+        <v>44617</v>
       </c>
       <c r="J116" s="3"/>
       <c r="K116" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="L116" s="1">
         <v>45820</v>
       </c>
       <c r="M116" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -6109,31 +6051,31 @@
         <v>22</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>154</v>
+        <v>324</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>159</v>
+        <v>355</v>
       </c>
       <c r="H117" s="2">
-        <v>44925</v>
-      </c>
-      <c r="I117" s="6">
-        <v>42990</v>
+        <v>44617</v>
+      </c>
+      <c r="I117" s="2">
+        <v>44617</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="L117" s="1">
         <v>45820</v>
       </c>
       <c r="M117" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -6144,31 +6086,31 @@
         <v>22</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>154</v>
+        <v>324</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H118" s="6">
+        <v>351</v>
+      </c>
+      <c r="H118" s="2">
         <v>45821</v>
       </c>
-      <c r="I118" s="6">
+      <c r="I118" s="2">
         <v>44617</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="L118" s="1">
         <v>45820</v>
       </c>
       <c r="M118" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -6179,31 +6121,31 @@
         <v>22</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H119" s="6">
-        <v>44617</v>
-      </c>
-      <c r="I119" s="6">
-        <v>44617</v>
+        <v>324</v>
+      </c>
+      <c r="G119" t="s">
+        <v>343</v>
+      </c>
+      <c r="H119" s="2">
+        <v>44925</v>
+      </c>
+      <c r="I119" s="2">
+        <v>42990</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="L119" s="1">
         <v>45820</v>
       </c>
       <c r="M119" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -6213,33 +6155,32 @@
       <c r="B120" t="s">
         <v>22</v>
       </c>
-      <c r="C120"/>
-      <c r="D120" t="s">
-        <v>150</v>
-      </c>
-      <c r="E120" t="s">
-        <v>94</v>
-      </c>
-      <c r="F120" t="s">
-        <v>151</v>
+      <c r="D120" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>324</v>
       </c>
       <c r="G120" t="s">
-        <v>152</v>
-      </c>
-      <c r="H120" s="6">
-        <v>44426</v>
+        <v>343</v>
+      </c>
+      <c r="H120" s="2">
+        <v>44923</v>
       </c>
       <c r="I120" s="2">
-        <v>42191</v>
+        <v>42990</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="L120" s="1">
         <v>45820</v>
       </c>
       <c r="M120" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -6250,31 +6191,31 @@
         <v>22</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>151</v>
+        <v>324</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="H121" s="6">
-        <v>44923</v>
-      </c>
-      <c r="I121" s="6">
-        <v>42990</v>
+        <v>352</v>
+      </c>
+      <c r="H121" s="2">
+        <v>44617</v>
+      </c>
+      <c r="I121" s="2">
+        <v>44617</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="L121" s="1">
         <v>45820</v>
       </c>
       <c r="M121" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -6285,31 +6226,31 @@
         <v>22</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G122" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H122" s="6">
-        <v>45821</v>
-      </c>
-      <c r="I122" s="6">
-        <v>44617</v>
+        <v>324</v>
+      </c>
+      <c r="G122" t="s">
+        <v>346</v>
+      </c>
+      <c r="H122" s="2">
+        <v>44194</v>
+      </c>
+      <c r="I122" s="2">
+        <v>42990</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="L122" s="1">
         <v>45820</v>
       </c>
       <c r="M122" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -6319,32 +6260,33 @@
       <c r="B123" t="s">
         <v>22</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>94</v>
+      <c r="C123"/>
+      <c r="D123" t="s">
+        <v>127</v>
+      </c>
+      <c r="E123" t="s">
+        <v>82</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H123" s="6">
-        <v>44617</v>
-      </c>
-      <c r="I123" s="6">
-        <v>44617</v>
+        <v>324</v>
+      </c>
+      <c r="G123" t="s">
+        <v>346</v>
+      </c>
+      <c r="H123" s="2">
+        <v>44426</v>
+      </c>
+      <c r="I123" s="2">
+        <v>42191</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="L123" s="1">
         <v>45820</v>
       </c>
       <c r="M123" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -6355,31 +6297,31 @@
         <v>22</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>151</v>
+        <v>324</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H124" s="6">
+        <v>360</v>
+      </c>
+      <c r="H124" s="2">
         <v>44734</v>
       </c>
-      <c r="I124" s="6">
+      <c r="I124" s="2">
         <v>44734</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L124" s="1">
         <v>45820</v>
       </c>
       <c r="M124" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -6390,31 +6332,31 @@
         <v>22</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>151</v>
+        <v>324</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H125" s="6">
+        <v>353</v>
+      </c>
+      <c r="H125" s="2">
         <v>45820</v>
       </c>
-      <c r="I125" s="6">
+      <c r="I125" s="2">
         <v>45820</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L125" s="1">
         <v>45820</v>
       </c>
       <c r="M125" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -6425,31 +6367,31 @@
         <v>22</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>151</v>
+        <v>324</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H126" s="6">
+        <v>354</v>
+      </c>
+      <c r="H126" s="2">
         <v>45820</v>
       </c>
-      <c r="I126" s="6">
+      <c r="I126" s="2">
         <v>45820</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L126" s="1">
         <v>45820</v>
       </c>
       <c r="M126" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="127" spans="1:13" customFormat="1">
@@ -6460,35 +6402,35 @@
         <v>23</v>
       </c>
       <c r="C127" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="D127" t="s">
-        <v>174</v>
-      </c>
-      <c r="E127" t="s">
-        <v>175</v>
+        <v>170</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="F127" t="s">
-        <v>176</v>
+        <v>323</v>
       </c>
       <c r="G127" t="s">
-        <v>177</v>
+        <v>356</v>
       </c>
       <c r="H127" s="2">
-        <v>46013</v>
+        <v>45656</v>
       </c>
       <c r="I127" s="2">
-        <v>46013</v>
+        <v>45656</v>
       </c>
       <c r="J127" s="3"/>
       <c r="K127" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L127" s="1">
         <v>45656</v>
       </c>
       <c r="M127" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -6498,20 +6440,20 @@
       <c r="B128" t="s">
         <v>23</v>
       </c>
-      <c r="C128" t="s">
-        <v>227</v>
-      </c>
-      <c r="D128" t="s">
-        <v>192</v>
-      </c>
-      <c r="E128" t="s">
-        <v>175</v>
+      <c r="C128" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="F128" t="s">
-        <v>176</v>
+        <v>323</v>
       </c>
       <c r="G128" t="s">
-        <v>186</v>
+        <v>342</v>
       </c>
       <c r="H128" s="2">
         <v>44349</v>
@@ -6520,13 +6462,13 @@
         <v>44349</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L128" s="1">
         <v>45656</v>
       </c>
       <c r="M128" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -6537,34 +6479,34 @@
         <v>23</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>193</v>
+        <v>146</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F129" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H129" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I129" s="6">
+        <v>28</v>
+      </c>
+      <c r="F129" t="s">
+        <v>323</v>
+      </c>
+      <c r="G129" t="s">
+        <v>342</v>
+      </c>
+      <c r="H129" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I129" s="2">
         <v>44349</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L129" s="1">
         <v>45656</v>
       </c>
       <c r="M129" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -6575,34 +6517,34 @@
         <v>23</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>194</v>
+        <v>147</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H130" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I130" s="6">
+        <v>28</v>
+      </c>
+      <c r="F130" t="s">
+        <v>323</v>
+      </c>
+      <c r="G130" t="s">
+        <v>342</v>
+      </c>
+      <c r="H130" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I130" s="2">
         <v>44349</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L130" s="1">
         <v>45656</v>
       </c>
       <c r="M130" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -6613,34 +6555,34 @@
         <v>23</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>195</v>
+        <v>148</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G131" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H131" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I131" s="6">
+        <v>28</v>
+      </c>
+      <c r="F131" t="s">
+        <v>323</v>
+      </c>
+      <c r="G131" t="s">
+        <v>342</v>
+      </c>
+      <c r="H131" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I131" s="2">
         <v>44349</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L131" s="1">
         <v>45656</v>
       </c>
       <c r="M131" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="132" spans="1:13" customFormat="1">
@@ -6651,35 +6593,35 @@
         <v>23</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>231</v>
+        <v>185</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G132" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H132" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I132" s="6">
+        <v>51</v>
+      </c>
+      <c r="F132" t="s">
+        <v>323</v>
+      </c>
+      <c r="G132" t="s">
+        <v>342</v>
+      </c>
+      <c r="H132" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I132" s="2">
         <v>44349</v>
       </c>
       <c r="J132" s="3"/>
       <c r="K132" s="3" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="L132" s="1">
         <v>45656</v>
       </c>
       <c r="M132" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -6690,19 +6632,19 @@
         <v>23</v>
       </c>
       <c r="C133" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D133" t="s">
-        <v>197</v>
-      </c>
-      <c r="E133" t="s">
-        <v>175</v>
+        <v>165</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="F133" t="s">
-        <v>176</v>
+        <v>323</v>
       </c>
       <c r="G133" t="s">
-        <v>186</v>
+        <v>342</v>
       </c>
       <c r="H133" s="2">
         <v>44349</v>
@@ -6711,13 +6653,13 @@
         <v>44349</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L133" s="1">
         <v>45656</v>
       </c>
       <c r="M133" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -6728,34 +6670,34 @@
         <v>23</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H134" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I134" s="6">
+        <v>82</v>
+      </c>
+      <c r="F134" t="s">
+        <v>323</v>
+      </c>
+      <c r="G134" t="s">
+        <v>342</v>
+      </c>
+      <c r="H134" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I134" s="2">
         <v>44349</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L134" s="1">
         <v>45656</v>
       </c>
       <c r="M134" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -6766,34 +6708,34 @@
         <v>23</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F135" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G135" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H135" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I135" s="6">
+        <v>82</v>
+      </c>
+      <c r="F135" t="s">
+        <v>323</v>
+      </c>
+      <c r="G135" t="s">
+        <v>342</v>
+      </c>
+      <c r="H135" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I135" s="2">
         <v>44349</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L135" s="1">
         <v>45656</v>
       </c>
       <c r="M135" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -6804,34 +6746,34 @@
         <v>23</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F136" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G136" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="H136" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I136" s="6">
+        <v>82</v>
+      </c>
+      <c r="F136" t="s">
+        <v>323</v>
+      </c>
+      <c r="G136" t="s">
+        <v>342</v>
+      </c>
+      <c r="H136" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I136" s="2">
         <v>44349</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L136" s="1">
         <v>45656</v>
       </c>
       <c r="M136" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="137" spans="1:13" customFormat="1">
@@ -6842,35 +6784,35 @@
         <v>23</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F137" s="3" t="s">
-        <v>176</v>
+        <v>28</v>
+      </c>
+      <c r="F137" t="s">
+        <v>323</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="H137" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I137" s="6">
-        <v>44349</v>
+        <v>334</v>
+      </c>
+      <c r="H137" s="2">
+        <v>44176</v>
+      </c>
+      <c r="I137" s="2">
+        <v>44176</v>
       </c>
       <c r="J137" s="3"/>
       <c r="K137" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L137" s="1">
         <v>45656</v>
       </c>
       <c r="M137" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -6880,20 +6822,20 @@
       <c r="B138" t="s">
         <v>23</v>
       </c>
-      <c r="C138" t="s">
-        <v>237</v>
-      </c>
-      <c r="D138" t="s">
-        <v>204</v>
-      </c>
-      <c r="E138" t="s">
-        <v>205</v>
+      <c r="C138" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="F138" t="s">
-        <v>176</v>
+        <v>323</v>
       </c>
       <c r="G138" t="s">
-        <v>184</v>
+        <v>337</v>
       </c>
       <c r="H138" s="2">
         <v>44349</v>
@@ -6902,13 +6844,13 @@
         <v>44349</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L138" s="1">
         <v>45656</v>
       </c>
       <c r="M138" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -6919,34 +6861,34 @@
         <v>23</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F139" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G139" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H139" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I139" s="6">
+        <v>28</v>
+      </c>
+      <c r="F139" t="s">
+        <v>323</v>
+      </c>
+      <c r="G139" t="s">
+        <v>349</v>
+      </c>
+      <c r="H139" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I139" s="2">
         <v>44349</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="L139" s="1">
         <v>45656</v>
       </c>
       <c r="M139" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -6956,35 +6898,35 @@
       <c r="B140" t="s">
         <v>23</v>
       </c>
-      <c r="C140" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>207</v>
+      <c r="C140" t="s">
+        <v>176</v>
+      </c>
+      <c r="D140" t="s">
+        <v>145</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F140" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G140" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H140" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I140" s="6">
+        <v>28</v>
+      </c>
+      <c r="F140" t="s">
+        <v>323</v>
+      </c>
+      <c r="G140" t="s">
+        <v>349</v>
+      </c>
+      <c r="H140" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I140" s="2">
         <v>44349</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="L140" s="1">
         <v>45656</v>
       </c>
       <c r="M140" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -6995,34 +6937,34 @@
         <v>23</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>208</v>
+        <v>149</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F141" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H141" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I141" s="6">
+        <v>28</v>
+      </c>
+      <c r="F141" t="s">
+        <v>323</v>
+      </c>
+      <c r="G141" t="s">
+        <v>349</v>
+      </c>
+      <c r="H141" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I141" s="2">
         <v>44349</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="L141" s="1">
         <v>45656</v>
       </c>
       <c r="M141" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142" spans="1:13" customFormat="1">
@@ -7032,36 +6974,38 @@
       <c r="B142" t="s">
         <v>23</v>
       </c>
-      <c r="C142" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>209</v>
+      <c r="C142" t="s">
+        <v>203</v>
+      </c>
+      <c r="D142" t="s">
+        <v>202</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G142" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H142" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I142" s="6">
-        <v>44349</v>
-      </c>
-      <c r="J142" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="F142" t="s">
+        <v>323</v>
+      </c>
+      <c r="G142" t="s">
+        <v>349</v>
+      </c>
+      <c r="H142" s="2">
+        <v>43712</v>
+      </c>
+      <c r="I142" s="2">
+        <v>43712</v>
+      </c>
+      <c r="J142" s="2">
+        <v>45539</v>
+      </c>
       <c r="K142" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="L142" s="1">
         <v>45656</v>
       </c>
       <c r="M142" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -7072,19 +7016,19 @@
         <v>23</v>
       </c>
       <c r="C143" t="s">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="D143" t="s">
-        <v>210</v>
-      </c>
-      <c r="E143" t="s">
-        <v>205</v>
+        <v>150</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="F143" t="s">
-        <v>176</v>
+        <v>323</v>
       </c>
       <c r="G143" t="s">
-        <v>182</v>
+        <v>349</v>
       </c>
       <c r="H143" s="2">
         <v>44349</v>
@@ -7093,13 +7037,13 @@
         <v>44349</v>
       </c>
       <c r="K143" s="3" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L143" s="1">
         <v>45656</v>
       </c>
       <c r="M143" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -7110,34 +7054,34 @@
         <v>23</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>243</v>
+        <v>182</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>211</v>
+        <v>151</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G144" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H144" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I144" s="6">
+        <v>51</v>
+      </c>
+      <c r="F144" t="s">
+        <v>323</v>
+      </c>
+      <c r="G144" t="s">
+        <v>349</v>
+      </c>
+      <c r="H144" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I144" s="2">
         <v>44349</v>
       </c>
       <c r="K144" s="3" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L144" s="1">
         <v>45656</v>
       </c>
       <c r="M144" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -7148,34 +7092,34 @@
         <v>23</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>244</v>
+        <v>183</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G145" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H145" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I145" s="6">
+        <v>51</v>
+      </c>
+      <c r="F145" t="s">
+        <v>323</v>
+      </c>
+      <c r="G145" t="s">
+        <v>349</v>
+      </c>
+      <c r="H145" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I145" s="2">
         <v>44349</v>
       </c>
       <c r="K145" s="3" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L145" s="1">
         <v>45656</v>
       </c>
       <c r="M145" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -7186,34 +7130,34 @@
         <v>23</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>245</v>
+        <v>184</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F146" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H146" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I146" s="6">
+        <v>51</v>
+      </c>
+      <c r="F146" t="s">
+        <v>323</v>
+      </c>
+      <c r="G146" t="s">
+        <v>349</v>
+      </c>
+      <c r="H146" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I146" s="2">
         <v>44349</v>
       </c>
       <c r="K146" s="3" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L146" s="1">
         <v>45656</v>
       </c>
       <c r="M146" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="147" spans="1:13" customFormat="1">
@@ -7223,36 +7167,36 @@
       <c r="B147" t="s">
         <v>23</v>
       </c>
-      <c r="C147" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>214</v>
+      <c r="C147" t="s">
+        <v>186</v>
+      </c>
+      <c r="D147" t="s">
+        <v>155</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G147" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H147" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I147" s="6">
+        <v>51</v>
+      </c>
+      <c r="F147" t="s">
+        <v>323</v>
+      </c>
+      <c r="G147" t="s">
+        <v>349</v>
+      </c>
+      <c r="H147" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I147" s="2">
         <v>44349</v>
       </c>
       <c r="J147" s="3"/>
       <c r="K147" s="3" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L147" s="1">
         <v>45656</v>
       </c>
       <c r="M147" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -7262,35 +7206,35 @@
       <c r="B148" t="s">
         <v>23</v>
       </c>
-      <c r="C148" t="s">
-        <v>247</v>
-      </c>
-      <c r="D148" t="s">
-        <v>215</v>
-      </c>
-      <c r="E148" t="s">
-        <v>205</v>
+      <c r="C148" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="F148" t="s">
-        <v>176</v>
+        <v>323</v>
       </c>
       <c r="G148" t="s">
-        <v>216</v>
+        <v>349</v>
       </c>
       <c r="H148" s="2">
-        <v>45656</v>
+        <v>44349</v>
       </c>
       <c r="I148" s="2">
-        <v>45656</v>
+        <v>44349</v>
       </c>
       <c r="K148" s="3" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="L148" s="1">
         <v>45656</v>
       </c>
       <c r="M148" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -7301,34 +7245,34 @@
         <v>23</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G149" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H149" s="6">
-        <v>44176</v>
-      </c>
-      <c r="I149" s="6">
-        <v>44176</v>
+        <v>82</v>
+      </c>
+      <c r="F149" t="s">
+        <v>323</v>
+      </c>
+      <c r="G149" t="s">
+        <v>349</v>
+      </c>
+      <c r="H149" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I149" s="2">
+        <v>44349</v>
       </c>
       <c r="K149" s="3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="L149" s="1">
         <v>45656</v>
       </c>
       <c r="M149" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -7339,34 +7283,34 @@
         <v>23</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G150" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H150" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I150" s="6">
+        <v>51</v>
+      </c>
+      <c r="F150" t="s">
+        <v>323</v>
+      </c>
+      <c r="G150" t="s">
+        <v>348</v>
+      </c>
+      <c r="H150" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I150" s="2">
         <v>44349</v>
       </c>
       <c r="K150" s="3" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="L150" s="1">
         <v>45656</v>
       </c>
       <c r="M150" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -7377,34 +7321,34 @@
         <v>23</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G151" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H151" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I151" s="6">
+        <v>28</v>
+      </c>
+      <c r="F151" t="s">
+        <v>323</v>
+      </c>
+      <c r="G151" t="s">
+        <v>347</v>
+      </c>
+      <c r="H151" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I151" s="2">
         <v>44349</v>
       </c>
       <c r="K151" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L151" s="1">
         <v>45656</v>
       </c>
       <c r="M151" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="152" spans="1:13" customFormat="1">
@@ -7415,35 +7359,35 @@
         <v>23</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H152" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I152" s="6">
+        <v>51</v>
+      </c>
+      <c r="F152" t="s">
+        <v>323</v>
+      </c>
+      <c r="G152" t="s">
+        <v>347</v>
+      </c>
+      <c r="H152" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I152" s="2">
         <v>44349</v>
       </c>
       <c r="J152" s="3"/>
       <c r="K152" s="3" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="L152" s="1">
         <v>45656</v>
       </c>
       <c r="M152" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -7454,19 +7398,19 @@
         <v>23</v>
       </c>
       <c r="C153" t="s">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="D153" t="s">
-        <v>187</v>
-      </c>
-      <c r="E153" t="s">
-        <v>179</v>
+        <v>160</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="F153" t="s">
-        <v>176</v>
+        <v>323</v>
       </c>
       <c r="G153" t="s">
-        <v>186</v>
+        <v>347</v>
       </c>
       <c r="H153" s="2">
         <v>44349</v>
@@ -7475,13 +7419,13 @@
         <v>44349</v>
       </c>
       <c r="K153" s="3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="L153" s="1">
         <v>45656</v>
       </c>
       <c r="M153" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -7492,34 +7436,34 @@
         <v>23</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H154" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I154" s="6">
+        <v>82</v>
+      </c>
+      <c r="F154" t="s">
+        <v>323</v>
+      </c>
+      <c r="G154" t="s">
+        <v>347</v>
+      </c>
+      <c r="H154" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I154" s="2">
         <v>44349</v>
       </c>
       <c r="K154" s="3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="L154" s="1">
         <v>45656</v>
       </c>
       <c r="M154" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -7530,34 +7474,34 @@
         <v>23</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G155" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H155" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I155" s="6">
+        <v>82</v>
+      </c>
+      <c r="F155" t="s">
+        <v>323</v>
+      </c>
+      <c r="G155" t="s">
+        <v>347</v>
+      </c>
+      <c r="H155" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I155" s="2">
         <v>44349</v>
       </c>
       <c r="K155" s="3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="L155" s="1">
         <v>45656</v>
       </c>
       <c r="M155" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -7568,34 +7512,34 @@
         <v>23</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G156" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H156" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I156" s="6">
+        <v>82</v>
+      </c>
+      <c r="F156" t="s">
+        <v>323</v>
+      </c>
+      <c r="G156" t="s">
+        <v>347</v>
+      </c>
+      <c r="H156" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I156" s="2">
         <v>44349</v>
       </c>
       <c r="K156" s="3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="L156" s="1">
         <v>45656</v>
       </c>
       <c r="M156" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="157" spans="1:13" customFormat="1">
@@ -7606,35 +7550,35 @@
         <v>23</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H157" s="6">
-        <v>44349</v>
-      </c>
-      <c r="I157" s="6">
+        <v>82</v>
+      </c>
+      <c r="F157" t="s">
+        <v>323</v>
+      </c>
+      <c r="G157" t="s">
+        <v>347</v>
+      </c>
+      <c r="H157" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I157" s="2">
         <v>44349</v>
       </c>
       <c r="J157" s="3"/>
       <c r="K157" s="3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="L157" s="1">
         <v>45656</v>
       </c>
       <c r="M157" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="158" spans="1:13" customFormat="1">
@@ -7645,37 +7589,35 @@
         <v>23</v>
       </c>
       <c r="C158" t="s">
-        <v>249</v>
+        <v>171</v>
       </c>
       <c r="D158" t="s">
-        <v>248</v>
-      </c>
-      <c r="E158" t="s">
-        <v>179</v>
+        <v>140</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="F158" t="s">
-        <v>176</v>
+        <v>323</v>
       </c>
       <c r="G158" t="s">
-        <v>186</v>
-      </c>
-      <c r="H158" s="6">
-        <v>43712</v>
-      </c>
-      <c r="I158" s="6">
-        <v>43712</v>
-      </c>
-      <c r="J158" s="6">
-        <v>45539</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="H158" s="2">
+        <v>46013</v>
+      </c>
+      <c r="I158" s="2">
+        <v>46013</v>
+      </c>
+      <c r="J158" s="3"/>
       <c r="K158" s="3" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="L158" s="1">
         <v>45656</v>
       </c>
       <c r="M158" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="159" spans="1:13" customFormat="1">
@@ -7685,38 +7627,36 @@
       <c r="B159" t="s">
         <v>24</v>
       </c>
-      <c r="C159" t="s">
-        <v>250</v>
-      </c>
-      <c r="D159" t="s">
-        <v>251</v>
-      </c>
-      <c r="E159" t="s">
-        <v>28</v>
-      </c>
-      <c r="F159" s="3">
-        <v>13</v>
-      </c>
-      <c r="G159" t="s">
-        <v>252</v>
+      <c r="C159" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G159" s="10" t="s">
+        <v>331</v>
       </c>
       <c r="H159" s="2">
-        <v>42734</v>
+        <v>44426</v>
       </c>
       <c r="I159" s="2">
-        <v>42734</v>
-      </c>
-      <c r="J159" s="2">
-        <v>44925</v>
-      </c>
+        <v>44426</v>
+      </c>
+      <c r="J159" s="3"/>
       <c r="K159" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L159" s="1">
         <v>45821</v>
       </c>
       <c r="M159" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -7727,37 +7667,34 @@
         <v>24</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F160" s="3">
-        <v>13</v>
-      </c>
-      <c r="G160" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="H160" s="6">
-        <v>43132</v>
-      </c>
-      <c r="I160" s="6">
-        <v>43132</v>
-      </c>
-      <c r="J160" s="6">
-        <v>44966</v>
+      <c r="F160" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G160" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H160" s="2">
+        <v>44426</v>
+      </c>
+      <c r="I160" s="2">
+        <v>44426</v>
       </c>
       <c r="K160" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L160" s="1">
         <v>45821</v>
       </c>
       <c r="M160" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -7767,38 +7704,38 @@
       <c r="B161" t="s">
         <v>24</v>
       </c>
-      <c r="C161" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>257</v>
+      <c r="C161" t="s">
+        <v>204</v>
+      </c>
+      <c r="D161" t="s">
+        <v>205</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F161" s="3">
-        <v>13</v>
-      </c>
-      <c r="G161" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="H161" s="6">
-        <v>43500</v>
-      </c>
-      <c r="I161" s="6">
-        <v>43500</v>
-      </c>
-      <c r="J161" s="6">
-        <v>45821</v>
+      <c r="F161" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G161" t="s">
+        <v>337</v>
+      </c>
+      <c r="H161" s="2">
+        <v>42734</v>
+      </c>
+      <c r="I161" s="2">
+        <v>42734</v>
+      </c>
+      <c r="J161" s="2">
+        <v>44925</v>
       </c>
       <c r="K161" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L161" s="1">
         <v>45821</v>
       </c>
       <c r="M161" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="162" spans="1:13" customFormat="1">
@@ -7809,19 +7746,19 @@
         <v>24</v>
       </c>
       <c r="C162" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D162" t="s">
-        <v>259</v>
-      </c>
-      <c r="E162" t="s">
-        <v>28</v>
-      </c>
-      <c r="F162" s="3">
-        <v>13</v>
+        <v>211</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>328</v>
       </c>
       <c r="G162" t="s">
-        <v>252</v>
+        <v>337</v>
       </c>
       <c r="H162" s="2">
         <v>43819</v>
@@ -7829,17 +7766,17 @@
       <c r="I162" s="2">
         <v>43819</v>
       </c>
-      <c r="J162" s="6">
+      <c r="J162" s="2">
         <v>45824</v>
       </c>
       <c r="K162" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L162" s="1">
         <v>45821</v>
       </c>
       <c r="M162" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -7850,34 +7787,34 @@
         <v>24</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F163" s="3">
-        <v>4</v>
-      </c>
-      <c r="G163" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="H163" s="6">
-        <v>44426</v>
-      </c>
-      <c r="I163" s="6">
-        <v>44426</v>
+      <c r="F163" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G163" t="s">
+        <v>337</v>
+      </c>
+      <c r="H163" s="2">
+        <v>44923</v>
+      </c>
+      <c r="I163" s="2">
+        <v>44923</v>
       </c>
       <c r="K163" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L163" s="1">
         <v>45821</v>
       </c>
       <c r="M163" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="164" spans="1:13">
@@ -7888,34 +7825,34 @@
         <v>24</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>263</v>
+        <v>222</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>264</v>
+        <v>223</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F164" s="3">
-        <v>4</v>
-      </c>
-      <c r="G164" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H164" s="6">
-        <v>44426</v>
-      </c>
-      <c r="I164" s="6">
-        <v>44426</v>
+      <c r="F164" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G164" t="s">
+        <v>337</v>
+      </c>
+      <c r="H164" s="2">
+        <v>45821</v>
+      </c>
+      <c r="I164" s="2">
+        <v>45821</v>
       </c>
       <c r="K164" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L164" s="1">
         <v>45821</v>
       </c>
       <c r="M164" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="165" spans="1:13">
@@ -7926,34 +7863,37 @@
         <v>24</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F165" s="3">
-        <v>13</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="H165" s="6">
-        <v>44194</v>
-      </c>
-      <c r="I165" s="6">
-        <v>44194</v>
+      <c r="F165" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G165" t="s">
+        <v>337</v>
+      </c>
+      <c r="H165" s="2">
+        <v>43132</v>
+      </c>
+      <c r="I165" s="2">
+        <v>43132</v>
+      </c>
+      <c r="J165" s="2">
+        <v>44966</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L165" s="1">
         <v>45821</v>
       </c>
       <c r="M165" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="166" spans="1:13">
@@ -7964,34 +7904,37 @@
         <v>24</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>269</v>
+        <v>209</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F166" s="3">
-        <v>13</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="H166" s="6">
-        <v>44923</v>
-      </c>
-      <c r="I166" s="6">
-        <v>44923</v>
+      <c r="F166" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G166" t="s">
+        <v>337</v>
+      </c>
+      <c r="H166" s="2">
+        <v>43500</v>
+      </c>
+      <c r="I166" s="2">
+        <v>43500</v>
+      </c>
+      <c r="J166" s="2">
+        <v>45821</v>
       </c>
       <c r="K166" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L166" s="1">
         <v>45821</v>
       </c>
       <c r="M166" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="167" spans="1:13" customFormat="1">
@@ -8001,36 +7944,36 @@
       <c r="B167" t="s">
         <v>24</v>
       </c>
-      <c r="C167" t="s">
-        <v>270</v>
-      </c>
-      <c r="D167" t="s">
-        <v>271</v>
-      </c>
-      <c r="E167" t="s">
-        <v>28</v>
-      </c>
-      <c r="F167" s="3">
-        <v>13</v>
+      <c r="C167" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>328</v>
       </c>
       <c r="G167" t="s">
-        <v>272</v>
+        <v>337</v>
       </c>
       <c r="H167" s="2">
-        <v>44925</v>
+        <v>44194</v>
       </c>
       <c r="I167" s="2">
-        <v>44925</v>
+        <v>44194</v>
       </c>
       <c r="J167" s="3"/>
       <c r="K167" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L167" s="1">
         <v>45821</v>
       </c>
       <c r="M167" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="168" spans="1:13">
@@ -8040,35 +7983,35 @@
       <c r="B168" t="s">
         <v>24</v>
       </c>
-      <c r="C168" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>274</v>
+      <c r="C168" t="s">
+        <v>220</v>
+      </c>
+      <c r="D168" t="s">
+        <v>221</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F168" s="3">
-        <v>13</v>
-      </c>
-      <c r="G168" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="H168" s="6">
-        <v>45821</v>
-      </c>
-      <c r="I168" s="6">
-        <v>45821</v>
+      <c r="F168" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G168" t="s">
+        <v>337</v>
+      </c>
+      <c r="H168" s="2">
+        <v>44925</v>
+      </c>
+      <c r="I168" s="2">
+        <v>44925</v>
       </c>
       <c r="K168" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L168" s="1">
         <v>45821</v>
       </c>
       <c r="M168" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="169" spans="1:13">
@@ -8079,39 +8022,40 @@
         <v>24</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>276</v>
+        <v>224</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F169" s="3">
-        <v>13</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="H169" s="6">
+      <c r="F169" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G169" t="s">
+        <v>337</v>
+      </c>
+      <c r="H169" s="2">
         <v>45821</v>
       </c>
-      <c r="I169" s="6">
+      <c r="I169" s="2">
         <v>45821</v>
       </c>
       <c r="K169" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L169" s="1">
         <v>45821</v>
       </c>
       <c r="M169" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="170" spans="1:13">
+      <c r="F170"/>
       <c r="K170" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/upload/informacoes_classificadas_desclassificadas.xlsx
+++ b/upload/informacoes_classificadas_desclassificadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D8B20F-BA05-42C4-B543-60F5E7C479D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10DA19D-4447-43BD-8A0F-DAB6F3B36027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{DF40FCA1-B2E4-4937-A10F-23A8137D7072}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="361">
   <si>
     <t>orgao_entidade</t>
   </si>
@@ -8054,9 +8054,6 @@
     </row>
     <row r="170" spans="1:13">
       <c r="F170"/>
-      <c r="K170" s="3" t="s">
-        <v>86</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M169" xr:uid="{CC06B792-B278-4FD9-89F7-02F8181B0784}">

--- a/upload/informacoes_classificadas_desclassificadas.xlsx
+++ b/upload/informacoes_classificadas_desclassificadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10DA19D-4447-43BD-8A0F-DAB6F3B36027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9B8252-A32F-4806-A47E-8471CD9AAF5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{DF40FCA1-B2E4-4937-A10F-23A8137D7072}"/>
   </bookViews>
@@ -615,9 +615,6 @@
     <t>Informações referentes a estudo de dimensionamento da força de trabalho do Sistema Prisional.</t>
   </si>
   <si>
-    <t>Informações relacionadas a nomes; a lotação; a exercício; a quantitativos; a escala de trabalhos; e a postos de serviço de agentes públicos (ativos, inativos ou desligados) das unidades administrativas, das unidades prisionais, das unidades socioeducativas e das Regiões Integradas de Segurança Pública (RISP). [5]</t>
-  </si>
-  <si>
     <t>Lista e quantitativo de servidores afastados e em gozo de férias regulamentares e férias prêmio, por unidade prisional ou socioeducativa.</t>
   </si>
   <si>
@@ -1249,6 +1246,9 @@
   </si>
   <si>
     <t>Art. 23, incisos VI, VII e VIII e art. 24, caput, § 1º, inciso I, da Lei Federal nº 12.527/2011 C/C art. 28 do Decreto Estadual nº 45.969/2012</t>
+  </si>
+  <si>
+    <t>Informações relacionadas a nomes, a lotação, a exercício, a quantitativos, a escala de trabalhos, e a postos de serviço de agentes públicos (ativos, inativos ou desligados) das unidades administrativas, das unidades prisionais, das unidades socioeducativas e das Regiões Integradas de Segurança Pública (RISP).</t>
   </si>
 </sst>
 </file>
@@ -1724,31 +1724,31 @@
         <v>60</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>321</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>2</v>
@@ -1774,10 +1774,10 @@
         <v>28</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H2" s="4">
         <v>44298</v>
@@ -1813,10 +1813,10 @@
         <v>28</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H3" s="4">
         <v>44298</v>
@@ -1852,10 +1852,10 @@
         <v>28</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H4" s="4">
         <v>43613</v>
@@ -1893,10 +1893,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H5" s="4">
         <v>43657</v>
@@ -1934,10 +1934,10 @@
         <v>28</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H6" s="4">
         <v>43740</v>
@@ -1975,10 +1975,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H7" s="4">
         <v>43753</v>
@@ -2016,10 +2016,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H8" s="4">
         <v>43948</v>
@@ -2057,10 +2057,10 @@
         <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H9" s="4">
         <v>43945</v>
@@ -2098,10 +2098,10 @@
         <v>28</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H10" s="4">
         <v>43970</v>
@@ -2139,10 +2139,10 @@
         <v>28</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H11" s="4">
         <v>43971</v>
@@ -2180,10 +2180,10 @@
         <v>28</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H12" s="4">
         <v>44082</v>
@@ -2204,158 +2204,154 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G13" t="s">
-        <v>337</v>
-      </c>
-      <c r="H13" s="4">
-        <v>44426</v>
-      </c>
-      <c r="I13" s="4">
-        <v>44473</v>
-      </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="5" t="s">
-        <v>52</v>
+        <v>321</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="H13" s="7">
+        <v>44552</v>
+      </c>
+      <c r="I13" s="7">
+        <v>44552</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="L13" s="2">
         <v>45819</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>25</v>
+      <c r="M13" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G14" t="s">
-        <v>337</v>
-      </c>
-      <c r="H14" s="4">
-        <v>44426</v>
-      </c>
-      <c r="I14" s="4">
-        <v>44473</v>
-      </c>
-      <c r="J14" s="6"/>
-      <c r="K14" s="5" t="s">
-        <v>52</v>
+        <v>321</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="H14" s="7">
+        <v>44552</v>
+      </c>
+      <c r="I14" s="7">
+        <v>44552</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="L14" s="2">
         <v>45819</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>25</v>
+      <c r="M14" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G15" t="s">
-        <v>337</v>
-      </c>
-      <c r="H15" s="4">
-        <v>44426</v>
-      </c>
-      <c r="I15" s="4">
-        <v>44473</v>
-      </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="5" t="s">
-        <v>52</v>
+        <v>321</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="H15" s="9">
+        <v>44780</v>
+      </c>
+      <c r="I15" s="9">
+        <v>44780</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="L15" s="2">
         <v>45819</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>25</v>
+      <c r="M15" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G16" t="s">
-        <v>337</v>
-      </c>
-      <c r="H16" s="4">
-        <v>44679</v>
-      </c>
-      <c r="I16" s="4">
-        <v>45763</v>
-      </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="5" t="s">
-        <v>52</v>
+        <v>321</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="H16" s="9">
+        <v>44780</v>
+      </c>
+      <c r="I16" s="9">
+        <v>44780</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="L16" s="2">
         <v>45819</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>25</v>
+      <c r="M16" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -2366,25 +2362,25 @@
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="H17" s="7">
-        <v>44552</v>
-      </c>
-      <c r="I17" s="7">
-        <v>44552</v>
+        <v>330</v>
+      </c>
+      <c r="H17" s="9">
+        <v>45021</v>
+      </c>
+      <c r="I17" s="9">
+        <v>45021</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>86</v>
@@ -2404,25 +2400,25 @@
         <v>15</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="H18" s="7">
-        <v>44552</v>
-      </c>
-      <c r="I18" s="7">
-        <v>44552</v>
+        <v>330</v>
+      </c>
+      <c r="H18" s="9">
+        <v>45021</v>
+      </c>
+      <c r="I18" s="9">
+        <v>45021</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>86</v>
@@ -2442,25 +2438,25 @@
         <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H19" s="9">
-        <v>44780</v>
+        <v>45292</v>
       </c>
       <c r="I19" s="9">
-        <v>44780</v>
+        <v>45292</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>86</v>
@@ -2480,25 +2476,25 @@
         <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H20" s="9">
-        <v>44780</v>
+        <v>45292</v>
       </c>
       <c r="I20" s="9">
-        <v>44780</v>
+        <v>45292</v>
       </c>
       <c r="K20" s="8" t="s">
         <v>86</v>
@@ -2518,25 +2514,25 @@
         <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>117</v>
+        <v>278</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H21" s="9">
-        <v>45021</v>
+        <v>45658</v>
       </c>
       <c r="I21" s="9">
-        <v>45021</v>
+        <v>45658</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>86</v>
@@ -2556,7 +2552,7 @@
         <v>15</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>118</v>
+        <v>301</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>107</v>
@@ -2565,16 +2561,16 @@
         <v>100</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H22" s="9">
-        <v>45021</v>
+        <v>45658</v>
       </c>
       <c r="I22" s="9">
-        <v>45021</v>
+        <v>45658</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>86</v>
@@ -2594,25 +2590,25 @@
         <v>15</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="H23" s="9">
-        <v>45292</v>
-      </c>
-      <c r="I23" s="9">
-        <v>45292</v>
+        <v>327</v>
+      </c>
+      <c r="G23" t="s">
+        <v>336</v>
+      </c>
+      <c r="H23" s="7">
+        <v>44558</v>
+      </c>
+      <c r="I23" s="7">
+        <v>44558</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>86</v>
@@ -2632,25 +2628,25 @@
         <v>15</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="H24" s="9">
-        <v>45292</v>
-      </c>
-      <c r="I24" s="9">
-        <v>45292</v>
+        <v>327</v>
+      </c>
+      <c r="G24" t="s">
+        <v>336</v>
+      </c>
+      <c r="H24" s="7">
+        <v>44925</v>
+      </c>
+      <c r="I24" s="7">
+        <v>44925</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>86</v>
@@ -2670,25 +2666,25 @@
         <v>15</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>279</v>
+        <v>119</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="H25" s="9">
-        <v>45658</v>
-      </c>
-      <c r="I25" s="9">
-        <v>45658</v>
+        <v>327</v>
+      </c>
+      <c r="G25" t="s">
+        <v>336</v>
+      </c>
+      <c r="H25" s="7">
+        <v>45289</v>
+      </c>
+      <c r="I25" s="7">
+        <v>45289</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>86</v>
@@ -2708,25 +2704,25 @@
         <v>15</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="H26" s="9">
-        <v>45658</v>
-      </c>
-      <c r="I26" s="9">
-        <v>45658</v>
+        <v>327</v>
+      </c>
+      <c r="G26" t="s">
+        <v>336</v>
+      </c>
+      <c r="H26" s="7">
+        <v>45656</v>
+      </c>
+      <c r="I26" s="7">
+        <v>45656</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>86</v>
@@ -2746,25 +2742,25 @@
         <v>15</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H27" s="7">
-        <v>44558</v>
+        <v>44194</v>
       </c>
       <c r="I27" s="7">
-        <v>44558</v>
+        <v>44194</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>86</v>
@@ -2778,154 +2774,154 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>116</v>
+        <v>303</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="G28" t="s">
-        <v>337</v>
-      </c>
-      <c r="H28" s="7">
-        <v>44925</v>
-      </c>
-      <c r="I28" s="7">
-        <v>44925</v>
+        <v>329</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="H28" s="2">
+        <v>45916</v>
+      </c>
+      <c r="I28" s="2">
+        <v>45916</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>86</v>
       </c>
       <c r="L28" s="2">
-        <v>45819</v>
+        <v>46072</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>119</v>
+        <v>306</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G29" t="s">
-        <v>337</v>
-      </c>
-      <c r="H29" s="7">
-        <v>45289</v>
-      </c>
-      <c r="I29" s="7">
-        <v>45289</v>
+        <v>343</v>
+      </c>
+      <c r="H29" s="2">
+        <v>45932</v>
+      </c>
+      <c r="I29" s="2">
+        <v>45932</v>
       </c>
       <c r="K29" s="8" t="s">
         <v>86</v>
       </c>
       <c r="L29" s="2">
-        <v>45819</v>
+        <v>46072</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>122</v>
+        <v>304</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G30" t="s">
-        <v>337</v>
-      </c>
-      <c r="H30" s="7">
-        <v>45656</v>
-      </c>
-      <c r="I30" s="7">
-        <v>45656</v>
+        <v>344</v>
+      </c>
+      <c r="H30" s="2">
+        <v>45932</v>
+      </c>
+      <c r="I30" s="2">
+        <v>45932</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>86</v>
       </c>
       <c r="L30" s="2">
-        <v>45819</v>
+        <v>46072</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>123</v>
+        <v>305</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G31" t="s">
-        <v>337</v>
-      </c>
-      <c r="H31" s="7">
-        <v>44194</v>
-      </c>
-      <c r="I31" s="7">
-        <v>44194</v>
+        <v>344</v>
+      </c>
+      <c r="H31" s="2">
+        <v>45932</v>
+      </c>
+      <c r="I31" s="2">
+        <v>45932</v>
       </c>
       <c r="K31" s="8" t="s">
         <v>86</v>
       </c>
       <c r="L31" s="2">
-        <v>45819</v>
+        <v>46072</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -2939,25 +2935,25 @@
         <v>308</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G32" t="s">
-        <v>342</v>
+        <v>329</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>340</v>
       </c>
       <c r="H32" s="2">
-        <v>45925</v>
+        <v>45923</v>
       </c>
       <c r="I32" s="2">
-        <v>45925</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>72</v>
+        <v>45923</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="L32" s="2">
         <v>46072</v>
@@ -2968,1268 +2964,1321 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="H33" s="2">
-        <v>45916</v>
-      </c>
-      <c r="I33" s="2">
-        <v>45916</v>
-      </c>
-      <c r="K33" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K33" s="3" t="s">
         <v>86</v>
       </c>
       <c r="L33" s="2">
-        <v>46072</v>
+        <v>45814</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="H34" s="2">
-        <v>45925</v>
-      </c>
-      <c r="I34" s="2">
-        <v>45925</v>
+        <v>332</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L34" s="2">
-        <v>46072</v>
+        <v>45814</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="H35" s="2">
-        <v>45925</v>
-      </c>
-      <c r="I35" s="2">
-        <v>45925</v>
+        <v>332</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L35" s="2">
-        <v>46072</v>
+        <v>45814</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>70</v>
+        <v>291</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="H36" s="2">
-        <v>45925</v>
-      </c>
-      <c r="I36" s="2">
-        <v>45925</v>
+        <v>332</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L36" s="2">
-        <v>46072</v>
+        <v>45814</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>65</v>
+        <v>292</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G37" t="s">
-        <v>344</v>
-      </c>
-      <c r="H37" s="2">
-        <v>45932</v>
-      </c>
-      <c r="I37" s="2">
-        <v>45932</v>
-      </c>
-      <c r="K37" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>86</v>
       </c>
       <c r="L37" s="2">
-        <v>46072</v>
+        <v>45814</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>63</v>
+        <v>300</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G38" t="s">
-        <v>345</v>
-      </c>
-      <c r="H38" s="2">
-        <v>45932</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45932</v>
-      </c>
-      <c r="K38" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>86</v>
       </c>
       <c r="L38" s="2">
-        <v>46072</v>
+        <v>45814</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>64</v>
+        <v>299</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G39" t="s">
-        <v>345</v>
-      </c>
-      <c r="H39" s="2">
-        <v>45932</v>
-      </c>
-      <c r="I39" s="2">
-        <v>45932</v>
-      </c>
-      <c r="K39" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>86</v>
       </c>
       <c r="L39" s="2">
-        <v>46072</v>
+        <v>45814</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>67</v>
+        <v>298</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="H40" s="2">
-        <v>45923</v>
-      </c>
-      <c r="I40" s="2">
-        <v>45923</v>
-      </c>
-      <c r="K40" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>86</v>
       </c>
       <c r="L40" s="2">
-        <v>46072</v>
+        <v>45814</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>280</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" t="s">
-        <v>323</v>
-      </c>
-      <c r="H41" s="2">
-        <v>43705</v>
-      </c>
-      <c r="I41" s="2">
-        <v>43705</v>
+        <v>28</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L41" s="2">
-        <v>45911</v>
+        <v>45814</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>286</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F42" t="s">
-        <v>323</v>
-      </c>
-      <c r="H42" s="2">
-        <v>45826</v>
-      </c>
-      <c r="I42" s="2">
-        <v>45826</v>
+        <v>28</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G42" t="s">
+        <v>336</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L42" s="2">
-        <v>45911</v>
+        <v>45814</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>288</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F43" t="s">
-        <v>323</v>
-      </c>
-      <c r="H43" s="2">
-        <v>43705</v>
-      </c>
-      <c r="I43" s="2">
-        <v>43705</v>
+        <v>28</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L43" s="2">
-        <v>45911</v>
+        <v>45814</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>285</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F44" t="s">
-        <v>323</v>
-      </c>
-      <c r="H44" s="2">
-        <v>43705</v>
-      </c>
-      <c r="I44" s="2">
-        <v>43705</v>
+        <v>28</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L44" s="2">
-        <v>45911</v>
+        <v>45814</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>287</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F45" t="s">
-        <v>323</v>
-      </c>
-      <c r="H45" s="2">
-        <v>45833</v>
-      </c>
-      <c r="I45" s="2">
-        <v>45833</v>
+        <v>28</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L45" s="2">
-        <v>45911</v>
+        <v>45814</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>289</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F46" t="s">
-        <v>323</v>
+        <v>28</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G46" t="s">
+        <v>336</v>
       </c>
       <c r="H46" s="2">
-        <v>43705</v>
+        <v>45352</v>
       </c>
       <c r="I46" s="2">
-        <v>43705</v>
+        <v>45352</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L46" s="2">
-        <v>45911</v>
+        <v>45819</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>84</v>
+        <v>302</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>290</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F47" t="s">
-        <v>323</v>
+        <v>28</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G47" t="s">
+        <v>336</v>
       </c>
       <c r="H47" s="2">
-        <v>43705</v>
+        <v>45352</v>
       </c>
       <c r="I47" s="2">
-        <v>43705</v>
+        <v>45352</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L47" s="2">
-        <v>45911</v>
+        <v>45819</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>84</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F48" t="s">
-        <v>323</v>
+        <v>322</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>358</v>
       </c>
       <c r="H48" s="2">
-        <v>43705</v>
+        <v>42191</v>
       </c>
       <c r="I48" s="2">
-        <v>43705</v>
+        <v>44376</v>
+      </c>
+      <c r="J48" s="2">
+        <v>46202</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L48" s="2">
-        <v>45911</v>
+        <v>45817</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>17</v>
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>259</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F49" t="s">
-        <v>323</v>
+        <v>322</v>
+      </c>
+      <c r="G49" t="s">
+        <v>356</v>
       </c>
       <c r="H49" s="2">
-        <v>43697</v>
+        <v>44349</v>
       </c>
       <c r="I49" s="2">
-        <v>43697</v>
+        <v>43486</v>
+      </c>
+      <c r="J49" s="2">
+        <v>45428</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L49" s="2">
-        <v>45911</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="M49" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>17</v>
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>81</v>
+        <v>229</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="F50" t="s">
-        <v>323</v>
+        <v>322</v>
+      </c>
+      <c r="G50" t="s">
+        <v>334</v>
       </c>
       <c r="H50" s="2">
-        <v>43705</v>
+        <v>44617</v>
       </c>
       <c r="I50" s="2">
-        <v>43705</v>
+        <v>45225</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L50" s="2">
-        <v>45911</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="M50" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>18</v>
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
+        <v>21</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>85</v>
+        <v>231</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F51" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>89</v>
+      <c r="F51" t="s">
+        <v>322</v>
+      </c>
+      <c r="G51" t="s">
+        <v>334</v>
+      </c>
+      <c r="H51" s="2">
+        <v>44617</v>
+      </c>
+      <c r="I51" s="2">
+        <v>45225</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L51" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>96</v>
+      <c r="M51" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>88</v>
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" t="s">
+        <v>226</v>
+      </c>
+      <c r="D52" t="s">
+        <v>227</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>326</v>
+      <c r="F52" t="s">
+        <v>322</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>89</v>
-      </c>
+      <c r="H52" s="2">
+        <v>42990</v>
+      </c>
+      <c r="I52" s="2">
+        <v>45967</v>
+      </c>
+      <c r="J52"/>
       <c r="K52" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L52" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>96</v>
+      <c r="L52"/>
+      <c r="M52" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>18</v>
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="s">
+        <v>21</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>285</v>
+        <v>228</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>91</v>
+        <v>229</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>326</v>
+      <c r="F53" t="s">
+        <v>322</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="I53" s="3" t="s">
-        <v>89</v>
+      <c r="H53" s="2">
+        <v>42990</v>
+      </c>
+      <c r="I53" s="2">
+        <v>45230</v>
       </c>
       <c r="K53" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L53" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>96</v>
+      <c r="M53" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>18</v>
+      <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" t="s">
+        <v>21</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>294</v>
+        <v>230</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>326</v>
+      <c r="F54" t="s">
+        <v>322</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>89</v>
+      <c r="H54" s="2">
+        <v>42990</v>
+      </c>
+      <c r="I54" s="2">
+        <v>45230</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L54" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>96</v>
+      <c r="M54" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>18</v>
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="s">
+        <v>21</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>295</v>
+        <v>234</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>293</v>
+        <v>235</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>326</v>
+      <c r="F55" t="s">
+        <v>322</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>89</v>
+      <c r="H55" s="2">
+        <v>44617</v>
+      </c>
+      <c r="I55" s="2">
+        <v>43486</v>
+      </c>
+      <c r="J55" s="2">
+        <v>45432</v>
       </c>
       <c r="K55" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L55" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>96</v>
+      <c r="M55" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>18</v>
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" t="s">
+        <v>21</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>326</v>
+      <c r="F56" t="s">
+        <v>322</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>89</v>
+      <c r="H56" s="2">
+        <v>44734</v>
+      </c>
+      <c r="I56" s="2">
+        <v>43587</v>
+      </c>
+      <c r="J56" s="2">
+        <v>45432</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L56" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>96</v>
+      <c r="M56" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>18</v>
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" t="s">
+        <v>21</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>298</v>
+        <v>262</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>300</v>
+        <v>235</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>326</v>
+      <c r="F57" t="s">
+        <v>322</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>89</v>
+      <c r="H57" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I57" s="2">
+        <v>43511</v>
+      </c>
+      <c r="J57" s="2">
+        <v>45428</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L57" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>96</v>
+      <c r="M57" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>18</v>
+      <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" t="s">
+        <v>21</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>297</v>
+        <v>236</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>299</v>
+        <v>235</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>89</v>
+      <c r="F58" t="s">
+        <v>322</v>
+      </c>
+      <c r="G58" t="s">
+        <v>336</v>
+      </c>
+      <c r="H58" s="2">
+        <v>44617</v>
+      </c>
+      <c r="I58" s="2">
+        <v>43503</v>
+      </c>
+      <c r="J58" s="2">
+        <v>45432</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L58" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>96</v>
+      <c r="M58" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>18</v>
+      <c r="A59" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" t="s">
+        <v>21</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>281</v>
+        <v>238</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>87</v>
+        <v>235</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G59" s="3" t="s">
+      <c r="F59" t="s">
+        <v>322</v>
+      </c>
+      <c r="G59" t="s">
         <v>336</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>89</v>
+      <c r="H59" s="2">
+        <v>45820</v>
+      </c>
+      <c r="I59" s="2">
+        <v>43264</v>
+      </c>
+      <c r="J59" s="2">
+        <v>45432</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L59" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>96</v>
+      <c r="M59" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>18</v>
+      <c r="A60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
+        <v>21</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>287</v>
+        <v>241</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>95</v>
+        <v>235</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="F60" t="s">
         <v>322</v>
       </c>
       <c r="G60" t="s">
-        <v>337</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>89</v>
+        <v>336</v>
+      </c>
+      <c r="H60" s="2">
+        <v>46013</v>
+      </c>
+      <c r="I60" s="2">
+        <v>43294</v>
+      </c>
+      <c r="J60" s="2">
+        <v>45428</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L60" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>96</v>
+      <c r="M60" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>18</v>
+      <c r="A61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B61" t="s">
+        <v>21</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>289</v>
+        <v>242</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>93</v>
+        <v>235</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>89</v>
+      <c r="F61" t="s">
+        <v>322</v>
+      </c>
+      <c r="G61" t="s">
+        <v>336</v>
+      </c>
+      <c r="H61" s="2">
+        <v>44176</v>
+      </c>
+      <c r="I61" s="2">
+        <v>43297</v>
+      </c>
+      <c r="J61" s="2">
+        <v>45428</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L61" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M61" s="3" t="s">
-        <v>96</v>
+      <c r="M61" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>18</v>
+      <c r="A62" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" t="s">
+        <v>21</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>91</v>
+        <v>235</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>89</v>
+        <v>28</v>
+      </c>
+      <c r="F62" t="s">
+        <v>322</v>
+      </c>
+      <c r="G62" t="s">
+        <v>336</v>
+      </c>
+      <c r="H62" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I62" s="2">
+        <v>43308</v>
+      </c>
+      <c r="J62" s="2">
+        <v>45428</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L62" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="M62" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>18</v>
+      <c r="A63" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" t="s">
+        <v>21</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>89</v>
+      <c r="F63" t="s">
+        <v>322</v>
+      </c>
+      <c r="G63" t="s">
+        <v>336</v>
+      </c>
+      <c r="H63" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I63" s="2">
+        <v>43328</v>
+      </c>
+      <c r="J63" s="2">
+        <v>45428</v>
       </c>
       <c r="K63" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L63" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M63" s="3" t="s">
-        <v>96</v>
+      <c r="M63" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>18</v>
+      <c r="A64" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" t="s">
+        <v>21</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>94</v>
+        <v>235</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>89</v>
+      <c r="F64" t="s">
+        <v>322</v>
+      </c>
+      <c r="G64" t="s">
+        <v>336</v>
+      </c>
+      <c r="H64" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I64" s="2">
+        <v>43328</v>
+      </c>
+      <c r="J64" s="2">
+        <v>45428</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L64" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>96</v>
+      <c r="M64" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>18</v>
+      <c r="A65" t="s">
+        <v>10</v>
+      </c>
+      <c r="B65" t="s">
+        <v>21</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>90</v>
+        <v>235</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>89</v>
+        <v>28</v>
+      </c>
+      <c r="F65" t="s">
+        <v>322</v>
+      </c>
+      <c r="G65" t="s">
+        <v>336</v>
+      </c>
+      <c r="H65" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I65" s="2">
+        <v>43329</v>
+      </c>
+      <c r="J65" s="2">
+        <v>45428</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L65" s="2">
-        <v>45814</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="M65" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>19</v>
+      <c r="A66" t="s">
+        <v>10</v>
+      </c>
+      <c r="B66" t="s">
+        <v>21</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>329</v>
+      <c r="F66" t="s">
+        <v>322</v>
       </c>
       <c r="G66" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H66" s="2">
-        <v>45352</v>
+        <v>44349</v>
       </c>
       <c r="I66" s="2">
-        <v>45352</v>
+        <v>43339</v>
+      </c>
+      <c r="J66" s="2">
+        <v>45428</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L66" s="2">
-        <v>45819</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>303</v>
+      <c r="M66" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>19</v>
+      <c r="A67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B67" t="s">
+        <v>21</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>291</v>
+        <v>253</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>97</v>
+        <v>235</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>329</v>
+      <c r="F67" t="s">
+        <v>322</v>
       </c>
       <c r="G67" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H67" s="2">
-        <v>45352</v>
+        <v>44349</v>
       </c>
       <c r="I67" s="2">
-        <v>45352</v>
+        <v>43353</v>
+      </c>
+      <c r="J67" s="2">
+        <v>45428</v>
       </c>
       <c r="K67" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L67" s="2">
-        <v>45819</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>303</v>
+      <c r="M67" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>20</v>
+      <c r="A68" t="s">
+        <v>10</v>
+      </c>
+      <c r="B68" t="s">
+        <v>21</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>124</v>
+        <v>254</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F68" t="s">
-        <v>323</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>359</v>
+        <v>322</v>
+      </c>
+      <c r="G68" t="s">
+        <v>336</v>
       </c>
       <c r="H68" s="2">
-        <v>42191</v>
+        <v>44349</v>
       </c>
       <c r="I68" s="2">
-        <v>44376</v>
+        <v>43415</v>
       </c>
       <c r="J68" s="2">
-        <v>46202</v>
+        <v>45428</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L68" s="2">
-        <v>45817</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>126</v>
+      <c r="M68" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="69" spans="1:13" customFormat="1">
@@ -4240,25 +4289,25 @@
         <v>21</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F69" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G69" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="H69" s="2">
         <v>44349</v>
       </c>
       <c r="I69" s="2">
-        <v>43486</v>
+        <v>43416</v>
       </c>
       <c r="J69" s="2">
         <v>45428</v>
@@ -4268,7 +4317,7 @@
       </c>
       <c r="L69" s="3"/>
       <c r="M69" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -4279,31 +4328,34 @@
         <v>21</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F70" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G70" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H70" s="2">
-        <v>44617</v>
+        <v>44349</v>
       </c>
       <c r="I70" s="2">
-        <v>45225</v>
+        <v>43472</v>
+      </c>
+      <c r="J70" s="2">
+        <v>45428</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>86</v>
       </c>
       <c r="M70" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -4314,31 +4366,34 @@
         <v>21</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F71" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G71" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H71" s="2">
-        <v>44617</v>
+        <v>44349</v>
       </c>
       <c r="I71" s="2">
-        <v>45225</v>
+        <v>43480</v>
+      </c>
+      <c r="J71" s="2">
+        <v>45428</v>
       </c>
       <c r="K71" s="3" t="s">
         <v>86</v>
       </c>
       <c r="M71" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -4348,34 +4403,35 @@
       <c r="B72" t="s">
         <v>21</v>
       </c>
-      <c r="C72" t="s">
-        <v>227</v>
-      </c>
-      <c r="D72" t="s">
-        <v>228</v>
+      <c r="C72" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F72" t="s">
-        <v>323</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
+      </c>
+      <c r="G72" t="s">
+        <v>336</v>
       </c>
       <c r="H72" s="2">
-        <v>42990</v>
+        <v>44349</v>
       </c>
       <c r="I72" s="2">
-        <v>45967</v>
-      </c>
-      <c r="J72"/>
+        <v>43500</v>
+      </c>
+      <c r="J72" s="2">
+        <v>45428</v>
+      </c>
       <c r="K72" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L72"/>
       <c r="M72" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -4386,31 +4442,34 @@
         <v>21</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F73" t="s">
-        <v>323</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
+      </c>
+      <c r="G73" t="s">
+        <v>336</v>
       </c>
       <c r="H73" s="2">
-        <v>42990</v>
+        <v>44349</v>
       </c>
       <c r="I73" s="2">
-        <v>45230</v>
+        <v>43509</v>
+      </c>
+      <c r="J73" s="2">
+        <v>45428</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>86</v>
       </c>
       <c r="M73" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -4421,31 +4480,34 @@
         <v>21</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F74" t="s">
-        <v>323</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
+      </c>
+      <c r="G74" t="s">
+        <v>336</v>
       </c>
       <c r="H74" s="2">
-        <v>42990</v>
+        <v>44349</v>
       </c>
       <c r="I74" s="2">
-        <v>45230</v>
+        <v>43524</v>
+      </c>
+      <c r="J74" s="2">
+        <v>45428</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>86</v>
       </c>
       <c r="M74" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -4456,34 +4518,34 @@
         <v>21</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="E75" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F75" t="s">
-        <v>323</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
+      </c>
+      <c r="G75" t="s">
+        <v>336</v>
       </c>
       <c r="H75" s="2">
-        <v>44617</v>
+        <v>44349</v>
       </c>
       <c r="I75" s="2">
-        <v>43486</v>
+        <v>43545</v>
       </c>
       <c r="J75" s="2">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K75" s="3" t="s">
         <v>86</v>
       </c>
       <c r="M75" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -4494,34 +4556,34 @@
         <v>21</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F76" t="s">
-        <v>323</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
+      </c>
+      <c r="G76" t="s">
+        <v>336</v>
       </c>
       <c r="H76" s="2">
-        <v>44734</v>
+        <v>44349</v>
       </c>
       <c r="I76" s="2">
-        <v>43587</v>
+        <v>43545</v>
       </c>
       <c r="J76" s="2">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>86</v>
       </c>
       <c r="M76" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -4532,25 +4594,25 @@
         <v>21</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F77" t="s">
-        <v>323</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
+      </c>
+      <c r="G77" t="s">
+        <v>336</v>
       </c>
       <c r="H77" s="2">
         <v>44349</v>
       </c>
       <c r="I77" s="2">
-        <v>43511</v>
+        <v>43545</v>
       </c>
       <c r="J77" s="2">
         <v>45428</v>
@@ -4559,7 +4621,7 @@
         <v>86</v>
       </c>
       <c r="M77" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -4570,34 +4632,34 @@
         <v>21</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F78" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G78" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H78" s="2">
-        <v>44617</v>
+        <v>44349</v>
       </c>
       <c r="I78" s="2">
-        <v>43503</v>
+        <v>43549</v>
       </c>
       <c r="J78" s="2">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K78" s="3" t="s">
         <v>86</v>
       </c>
       <c r="M78" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -4608,34 +4670,34 @@
         <v>21</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F79" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G79" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H79" s="2">
-        <v>45820</v>
+        <v>44349</v>
       </c>
       <c r="I79" s="2">
-        <v>43264</v>
+        <v>43551</v>
       </c>
       <c r="J79" s="2">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K79" s="3" t="s">
         <v>86</v>
       </c>
       <c r="M79" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -4646,25 +4708,25 @@
         <v>21</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F80" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G80" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H80" s="2">
-        <v>46013</v>
+        <v>45656</v>
       </c>
       <c r="I80" s="2">
-        <v>43294</v>
+        <v>43559</v>
       </c>
       <c r="J80" s="2">
         <v>45428</v>
@@ -4673,7 +4735,7 @@
         <v>86</v>
       </c>
       <c r="M80" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -4684,25 +4746,25 @@
         <v>21</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F81" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G81" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H81" s="2">
-        <v>44176</v>
+        <v>43500</v>
       </c>
       <c r="I81" s="2">
-        <v>43297</v>
+        <v>43599</v>
       </c>
       <c r="J81" s="2">
         <v>45428</v>
@@ -4711,7 +4773,7 @@
         <v>86</v>
       </c>
       <c r="M81" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -4722,34 +4784,34 @@
         <v>21</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F82" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G82" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="H82" s="2">
-        <v>44349</v>
+        <v>45820</v>
       </c>
       <c r="I82" s="2">
-        <v>43308</v>
+        <v>43271</v>
       </c>
       <c r="J82" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>86</v>
       </c>
       <c r="M82" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -4760,25 +4822,25 @@
         <v>21</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F83" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G83" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="H83" s="2">
         <v>44349</v>
       </c>
       <c r="I83" s="2">
-        <v>43328</v>
+        <v>43461</v>
       </c>
       <c r="J83" s="2">
         <v>45428</v>
@@ -4787,7 +4849,7 @@
         <v>86</v>
       </c>
       <c r="M83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -4798,25 +4860,25 @@
         <v>21</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F84" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G84" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="H84" s="2">
         <v>44349</v>
       </c>
       <c r="I84" s="2">
-        <v>43328</v>
+        <v>43543</v>
       </c>
       <c r="J84" s="2">
         <v>45428</v>
@@ -4825,7 +4887,7 @@
         <v>86</v>
       </c>
       <c r="M84" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -4836,25 +4898,25 @@
         <v>21</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F85" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G85" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="H85" s="2">
-        <v>44349</v>
+        <v>42734</v>
       </c>
       <c r="I85" s="2">
-        <v>43329</v>
+        <v>43571</v>
       </c>
       <c r="J85" s="2">
         <v>45428</v>
@@ -4863,7 +4925,7 @@
         <v>86</v>
       </c>
       <c r="M85" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -4874,25 +4936,25 @@
         <v>21</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G86" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="H86" s="2">
-        <v>44349</v>
+        <v>43132</v>
       </c>
       <c r="I86" s="2">
-        <v>43339</v>
+        <v>43571</v>
       </c>
       <c r="J86" s="2">
         <v>45428</v>
@@ -4901,7 +4963,7 @@
         <v>86</v>
       </c>
       <c r="M86" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -4912,25 +4974,25 @@
         <v>21</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F87" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G87" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="H87" s="2">
-        <v>44349</v>
+        <v>43819</v>
       </c>
       <c r="I87" s="2">
-        <v>43353</v>
+        <v>43609</v>
       </c>
       <c r="J87" s="2">
         <v>45428</v>
@@ -4939,7 +5001,7 @@
         <v>86</v>
       </c>
       <c r="M87" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -4950,25 +5012,25 @@
         <v>21</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F88" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G88" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="H88" s="2">
-        <v>44349</v>
+        <v>44426</v>
       </c>
       <c r="I88" s="2">
-        <v>43415</v>
+        <v>43511</v>
       </c>
       <c r="J88" s="2">
         <v>45428</v>
@@ -4977,7 +5039,7 @@
         <v>86</v>
       </c>
       <c r="M88" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -4988,16 +5050,16 @@
         <v>21</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F89" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G89" t="s">
         <v>337</v>
@@ -5006,7 +5068,7 @@
         <v>44349</v>
       </c>
       <c r="I89" s="2">
-        <v>43416</v>
+        <v>43308</v>
       </c>
       <c r="J89" s="2">
         <v>45428</v>
@@ -5015,7 +5077,7 @@
         <v>86</v>
       </c>
       <c r="M89" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -5026,16 +5088,16 @@
         <v>21</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F90" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G90" t="s">
         <v>337</v>
@@ -5044,7 +5106,7 @@
         <v>44349</v>
       </c>
       <c r="I90" s="2">
-        <v>43472</v>
+        <v>43308</v>
       </c>
       <c r="J90" s="2">
         <v>45428</v>
@@ -5053,7 +5115,7 @@
         <v>86</v>
       </c>
       <c r="M90" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -5064,25 +5126,25 @@
         <v>21</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F91" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G91" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H91" s="2">
         <v>44349</v>
       </c>
       <c r="I91" s="2">
-        <v>43480</v>
+        <v>43304</v>
       </c>
       <c r="J91" s="2">
         <v>45428</v>
@@ -5091,7 +5153,7 @@
         <v>86</v>
       </c>
       <c r="M91" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -5102,25 +5164,25 @@
         <v>21</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F92" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G92" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H92" s="2">
         <v>44349</v>
       </c>
       <c r="I92" s="2">
-        <v>43500</v>
+        <v>43325</v>
       </c>
       <c r="J92" s="2">
         <v>45428</v>
@@ -5129,7 +5191,7 @@
         <v>86</v>
       </c>
       <c r="M92" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -5140,25 +5202,25 @@
         <v>21</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F93" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G93" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H93" s="2">
         <v>44349</v>
       </c>
       <c r="I93" s="2">
-        <v>43509</v>
+        <v>43346</v>
       </c>
       <c r="J93" s="2">
         <v>45428</v>
@@ -5167,7 +5229,7 @@
         <v>86</v>
       </c>
       <c r="M93" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -5178,25 +5240,25 @@
         <v>21</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F94" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G94" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H94" s="2">
         <v>44349</v>
       </c>
       <c r="I94" s="2">
-        <v>43524</v>
+        <v>43551</v>
       </c>
       <c r="J94" s="2">
         <v>45428</v>
@@ -5205,7 +5267,7 @@
         <v>86</v>
       </c>
       <c r="M94" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -5216,25 +5278,25 @@
         <v>21</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F95" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G95" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H95" s="2">
-        <v>44349</v>
+        <v>43712</v>
       </c>
       <c r="I95" s="2">
-        <v>43545</v>
+        <v>43570</v>
       </c>
       <c r="J95" s="2">
         <v>45428</v>
@@ -5243,1576 +5305,1562 @@
         <v>86</v>
       </c>
       <c r="M95" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>21</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>267</v>
+        <v>22</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>236</v>
+        <v>135</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F96" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G96" t="s">
-        <v>337</v>
+      <c r="G96" s="3" t="s">
+        <v>359</v>
       </c>
       <c r="H96" s="2">
-        <v>44349</v>
+        <v>44734</v>
       </c>
       <c r="I96" s="2">
-        <v>43545</v>
-      </c>
-      <c r="J96" s="2">
-        <v>45428</v>
+        <v>44734</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L96" s="1">
+        <v>45820</v>
+      </c>
       <c r="M96" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>21</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>268</v>
+        <v>22</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>236</v>
+        <v>136</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F97" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G97" t="s">
-        <v>337</v>
+      <c r="G97" s="3" t="s">
+        <v>352</v>
       </c>
       <c r="H97" s="2">
-        <v>44349</v>
+        <v>45820</v>
       </c>
       <c r="I97" s="2">
-        <v>43545</v>
-      </c>
-      <c r="J97" s="2">
-        <v>45428</v>
+        <v>45820</v>
       </c>
       <c r="K97" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L97" s="1">
+        <v>45820</v>
+      </c>
       <c r="M97" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>21</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>269</v>
+        <v>22</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>236</v>
+        <v>137</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G98" t="s">
-        <v>337</v>
+      <c r="G98" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="H98" s="2">
-        <v>44349</v>
+        <v>45820</v>
       </c>
       <c r="I98" s="2">
-        <v>43549</v>
-      </c>
-      <c r="J98" s="2">
-        <v>45428</v>
+        <v>45820</v>
       </c>
       <c r="K98" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L98" s="1">
+        <v>45820</v>
+      </c>
       <c r="M98" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>270</v>
+        <v>172</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>236</v>
+        <v>142</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F99" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G99" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H99" s="2">
         <v>44349</v>
       </c>
       <c r="I99" s="2">
-        <v>43551</v>
-      </c>
-      <c r="J99" s="2">
-        <v>45428</v>
+        <v>44349</v>
       </c>
       <c r="K99" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L99" s="1">
+        <v>45656</v>
+      </c>
       <c r="M99" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>272</v>
+        <v>176</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F100" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G100" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H100" s="2">
+        <v>44349</v>
+      </c>
+      <c r="I100" s="2">
+        <v>44349</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L100" s="1">
         <v>45656</v>
       </c>
-      <c r="I100" s="2">
-        <v>43559</v>
-      </c>
-      <c r="J100" s="2">
-        <v>45428</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="M100" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>276</v>
+        <v>177</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>236</v>
+        <v>147</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F101" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G101" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H101" s="2">
-        <v>43500</v>
+        <v>44349</v>
       </c>
       <c r="I101" s="2">
-        <v>43599</v>
-      </c>
-      <c r="J101" s="2">
-        <v>45428</v>
+        <v>44349</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L101" s="1">
+        <v>45656</v>
+      </c>
       <c r="M101" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>236</v>
+        <v>148</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F102" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G102" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="H102" s="2">
-        <v>45820</v>
+        <v>44349</v>
       </c>
       <c r="I102" s="2">
-        <v>43271</v>
-      </c>
-      <c r="J102" s="2">
-        <v>45432</v>
+        <v>44349</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L102" s="1">
+        <v>45656</v>
+      </c>
       <c r="M102" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>257</v>
+        <v>171</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>236</v>
+        <v>141</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F103" t="s">
-        <v>323</v>
-      </c>
-      <c r="G103" t="s">
-        <v>358</v>
+        <v>322</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>333</v>
       </c>
       <c r="H103" s="2">
-        <v>44349</v>
+        <v>44176</v>
       </c>
       <c r="I103" s="2">
-        <v>43461</v>
-      </c>
-      <c r="J103" s="2">
-        <v>45428</v>
+        <v>44176</v>
       </c>
       <c r="K103" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L103" s="1">
+        <v>45656</v>
+      </c>
       <c r="M103" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>265</v>
+        <v>174</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F104" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G104" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="H104" s="2">
         <v>44349</v>
       </c>
       <c r="I104" s="2">
-        <v>43543</v>
-      </c>
-      <c r="J104" s="2">
-        <v>45428</v>
+        <v>44349</v>
       </c>
       <c r="K104" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L104" s="1">
+        <v>45656</v>
+      </c>
       <c r="M104" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>21</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>236</v>
+        <v>23</v>
+      </c>
+      <c r="C105" t="s">
+        <v>175</v>
+      </c>
+      <c r="D105" t="s">
+        <v>145</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F105" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G105" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="H105" s="2">
-        <v>42734</v>
+        <v>44349</v>
       </c>
       <c r="I105" s="2">
-        <v>43571</v>
-      </c>
-      <c r="J105" s="2">
-        <v>45428</v>
+        <v>44349</v>
       </c>
       <c r="K105" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L105" s="1">
+        <v>45656</v>
+      </c>
       <c r="M105" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>275</v>
+        <v>179</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>236</v>
+        <v>149</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F106" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G106" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="H106" s="2">
-        <v>43132</v>
+        <v>44349</v>
       </c>
       <c r="I106" s="2">
-        <v>43571</v>
-      </c>
-      <c r="J106" s="2">
-        <v>45428</v>
+        <v>44349</v>
       </c>
       <c r="K106" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L106" s="1">
+        <v>45656</v>
+      </c>
       <c r="M106" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>21</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>236</v>
+        <v>23</v>
+      </c>
+      <c r="C107" t="s">
+        <v>202</v>
+      </c>
+      <c r="D107" t="s">
+        <v>201</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F107" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G107" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="H107" s="2">
-        <v>43819</v>
+        <v>43712</v>
       </c>
       <c r="I107" s="2">
-        <v>43609</v>
+        <v>43712</v>
       </c>
       <c r="J107" s="2">
-        <v>45428</v>
+        <v>45539</v>
       </c>
       <c r="K107" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L107" s="1">
+        <v>45656</v>
+      </c>
       <c r="M107" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>278</v>
+        <v>173</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>236</v>
+        <v>143</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F108" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G108" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="H108" s="2">
-        <v>44426</v>
+        <v>44349</v>
       </c>
       <c r="I108" s="2">
-        <v>43511</v>
-      </c>
-      <c r="J108" s="2">
-        <v>45428</v>
+        <v>44349</v>
       </c>
       <c r="K108" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L108" s="1">
+        <v>45656</v>
+      </c>
       <c r="M108" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F109" t="s">
-        <v>323</v>
-      </c>
-      <c r="G109" t="s">
-        <v>338</v>
+      <c r="F109" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G109" s="10" t="s">
+        <v>330</v>
       </c>
       <c r="H109" s="2">
-        <v>44349</v>
+        <v>44426</v>
       </c>
       <c r="I109" s="2">
-        <v>43308</v>
-      </c>
-      <c r="J109" s="2">
-        <v>45428</v>
+        <v>44426</v>
       </c>
       <c r="K109" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L109" s="1">
+        <v>45821</v>
+      </c>
       <c r="M109" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B110" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F110" t="s">
-        <v>323</v>
-      </c>
-      <c r="G110" t="s">
-        <v>338</v>
+      <c r="F110" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>330</v>
       </c>
       <c r="H110" s="2">
-        <v>44349</v>
+        <v>44426</v>
       </c>
       <c r="I110" s="2">
-        <v>43308</v>
-      </c>
-      <c r="J110" s="2">
-        <v>45428</v>
+        <v>44426</v>
       </c>
       <c r="K110" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L110" s="1">
+        <v>45821</v>
+      </c>
       <c r="M110" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B111" t="s">
-        <v>21</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>236</v>
+        <v>24</v>
+      </c>
+      <c r="C111" t="s">
+        <v>203</v>
+      </c>
+      <c r="D111" t="s">
+        <v>204</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F111" t="s">
-        <v>323</v>
+      <c r="F111" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="G111" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H111" s="2">
-        <v>44349</v>
+        <v>42734</v>
       </c>
       <c r="I111" s="2">
-        <v>43304</v>
+        <v>42734</v>
       </c>
       <c r="J111" s="2">
-        <v>45428</v>
+        <v>44925</v>
       </c>
       <c r="K111" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L111" s="1">
+        <v>45821</v>
+      </c>
       <c r="M111" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B112" t="s">
-        <v>21</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>236</v>
+        <v>24</v>
+      </c>
+      <c r="C112" t="s">
+        <v>209</v>
+      </c>
+      <c r="D112" t="s">
+        <v>210</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F112" t="s">
-        <v>323</v>
+      <c r="F112" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="G112" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H112" s="2">
-        <v>44349</v>
+        <v>43819</v>
       </c>
       <c r="I112" s="2">
-        <v>43325</v>
+        <v>43819</v>
       </c>
       <c r="J112" s="2">
-        <v>45428</v>
+        <v>45824</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L112" s="1">
+        <v>45821</v>
+      </c>
       <c r="M112" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B113" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F113" t="s">
-        <v>323</v>
+      <c r="F113" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="G113" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H113" s="2">
-        <v>44349</v>
+        <v>44923</v>
       </c>
       <c r="I113" s="2">
-        <v>43346</v>
-      </c>
-      <c r="J113" s="2">
-        <v>45428</v>
+        <v>44923</v>
       </c>
       <c r="K113" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L113" s="1">
+        <v>45821</v>
+      </c>
       <c r="M113" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>271</v>
+        <v>221</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F114" t="s">
-        <v>323</v>
+      <c r="F114" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="G114" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H114" s="2">
-        <v>44349</v>
+        <v>45821</v>
       </c>
       <c r="I114" s="2">
-        <v>43551</v>
-      </c>
-      <c r="J114" s="2">
-        <v>45428</v>
+        <v>45821</v>
       </c>
       <c r="K114" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L114" s="1">
+        <v>45821</v>
+      </c>
       <c r="M114" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>273</v>
+        <v>205</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F115" t="s">
-        <v>323</v>
+      <c r="F115" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="G115" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H115" s="2">
-        <v>43712</v>
+        <v>43132</v>
       </c>
       <c r="I115" s="2">
-        <v>43570</v>
+        <v>43132</v>
       </c>
       <c r="J115" s="2">
-        <v>45428</v>
+        <v>44966</v>
       </c>
       <c r="K115" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="L115" s="1">
+        <v>45821</v>
+      </c>
       <c r="M115" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
     </row>
     <row r="116" spans="1:13" customFormat="1">
       <c r="A116" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B116" t="s">
-        <v>22</v>
-      </c>
-      <c r="C116" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="D116" s="3" t="s">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>350</v>
+        <v>327</v>
+      </c>
+      <c r="G116" t="s">
+        <v>336</v>
       </c>
       <c r="H116" s="2">
+        <v>43500</v>
+      </c>
+      <c r="I116" s="2">
+        <v>43500</v>
+      </c>
+      <c r="J116" s="2">
         <v>45821</v>
       </c>
-      <c r="I116" s="2">
-        <v>44617</v>
-      </c>
-      <c r="J116" s="3"/>
       <c r="K116" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L116" s="1">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="M116" t="s">
-        <v>138</v>
+        <v>225</v>
       </c>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B117" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>355</v>
+        <v>327</v>
+      </c>
+      <c r="G117" t="s">
+        <v>336</v>
       </c>
       <c r="H117" s="2">
-        <v>44617</v>
+        <v>44194</v>
       </c>
       <c r="I117" s="2">
-        <v>44617</v>
+        <v>44194</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L117" s="1">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="M117" t="s">
-        <v>138</v>
+        <v>225</v>
       </c>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B118" t="s">
-        <v>22</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>132</v>
+        <v>24</v>
+      </c>
+      <c r="C118" t="s">
+        <v>219</v>
+      </c>
+      <c r="D118" t="s">
+        <v>220</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G118" s="3" t="s">
-        <v>351</v>
+        <v>327</v>
+      </c>
+      <c r="G118" t="s">
+        <v>336</v>
       </c>
       <c r="H118" s="2">
+        <v>44925</v>
+      </c>
+      <c r="I118" s="2">
+        <v>44925</v>
+      </c>
+      <c r="K118" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L118" s="1">
         <v>45821</v>
       </c>
-      <c r="I118" s="2">
-        <v>44617</v>
-      </c>
-      <c r="K118" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L118" s="1">
-        <v>45820</v>
-      </c>
       <c r="M118" t="s">
-        <v>138</v>
+        <v>225</v>
       </c>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G119" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="H119" s="2">
-        <v>44925</v>
+        <v>45821</v>
       </c>
       <c r="I119" s="2">
-        <v>42990</v>
+        <v>45821</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L119" s="1">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="M119" t="s">
-        <v>138</v>
+        <v>225</v>
       </c>
     </row>
     <row r="120" spans="1:13">
-      <c r="A120" t="s">
-        <v>11</v>
-      </c>
-      <c r="B120" t="s">
-        <v>22</v>
+      <c r="A120" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G120" t="s">
-        <v>343</v>
-      </c>
-      <c r="H120" s="2">
-        <v>44923</v>
-      </c>
-      <c r="I120" s="2">
-        <v>42990</v>
-      </c>
-      <c r="K120" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L120" s="1">
-        <v>45820</v>
-      </c>
-      <c r="M120" t="s">
-        <v>138</v>
+        <v>336</v>
+      </c>
+      <c r="H120" s="4">
+        <v>44426</v>
+      </c>
+      <c r="I120" s="4">
+        <v>44473</v>
+      </c>
+      <c r="J120" s="6"/>
+      <c r="K120" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L120" s="2">
+        <v>45819</v>
+      </c>
+      <c r="M120" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="121" spans="1:13">
-      <c r="A121" t="s">
-        <v>11</v>
-      </c>
-      <c r="B121" t="s">
-        <v>22</v>
+      <c r="A121" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G121" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H121" s="2">
-        <v>44617</v>
-      </c>
-      <c r="I121" s="2">
-        <v>44617</v>
-      </c>
-      <c r="K121" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L121" s="1">
-        <v>45820</v>
-      </c>
-      <c r="M121" t="s">
-        <v>138</v>
+        <v>321</v>
+      </c>
+      <c r="G121" t="s">
+        <v>336</v>
+      </c>
+      <c r="H121" s="4">
+        <v>44426</v>
+      </c>
+      <c r="I121" s="4">
+        <v>44473</v>
+      </c>
+      <c r="J121" s="6"/>
+      <c r="K121" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L121" s="2">
+        <v>45819</v>
+      </c>
+      <c r="M121" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="122" spans="1:13">
-      <c r="A122" t="s">
-        <v>11</v>
-      </c>
-      <c r="B122" t="s">
-        <v>22</v>
+      <c r="A122" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G122" t="s">
-        <v>346</v>
-      </c>
-      <c r="H122" s="2">
-        <v>44194</v>
-      </c>
-      <c r="I122" s="2">
-        <v>42990</v>
-      </c>
-      <c r="K122" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L122" s="1">
-        <v>45820</v>
-      </c>
-      <c r="M122" t="s">
-        <v>138</v>
+        <v>336</v>
+      </c>
+      <c r="H122" s="4">
+        <v>44426</v>
+      </c>
+      <c r="I122" s="4">
+        <v>44473</v>
+      </c>
+      <c r="J122" s="6"/>
+      <c r="K122" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L122" s="2">
+        <v>45819</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="123" spans="1:13">
-      <c r="A123" t="s">
-        <v>11</v>
-      </c>
-      <c r="B123" t="s">
-        <v>22</v>
-      </c>
-      <c r="C123"/>
-      <c r="D123" t="s">
-        <v>127</v>
-      </c>
-      <c r="E123" t="s">
-        <v>82</v>
+      <c r="A123" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G123" t="s">
-        <v>346</v>
-      </c>
-      <c r="H123" s="2">
-        <v>44426</v>
-      </c>
-      <c r="I123" s="2">
-        <v>42191</v>
-      </c>
-      <c r="K123" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L123" s="1">
-        <v>45820</v>
-      </c>
-      <c r="M123" t="s">
-        <v>138</v>
+        <v>336</v>
+      </c>
+      <c r="H123" s="4">
+        <v>44679</v>
+      </c>
+      <c r="I123" s="4">
+        <v>45763</v>
+      </c>
+      <c r="J123" s="6"/>
+      <c r="K123" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L123" s="2">
+        <v>45819</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="124" spans="1:13">
-      <c r="A124" t="s">
-        <v>11</v>
-      </c>
-      <c r="B124" t="s">
-        <v>22</v>
+      <c r="A124" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>307</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>135</v>
+        <v>66</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>360</v>
+        <v>329</v>
+      </c>
+      <c r="G124" t="s">
+        <v>341</v>
       </c>
       <c r="H124" s="2">
-        <v>44734</v>
+        <v>45925</v>
       </c>
       <c r="I124" s="2">
-        <v>44734</v>
+        <v>45925</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L124" s="1">
-        <v>45820</v>
-      </c>
-      <c r="M124" t="s">
-        <v>138</v>
+        <v>72</v>
+      </c>
+      <c r="L124" s="2">
+        <v>46072</v>
+      </c>
+      <c r="M124" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="125" spans="1:13">
-      <c r="A125" t="s">
-        <v>11</v>
-      </c>
-      <c r="B125" t="s">
-        <v>22</v>
+      <c r="A125" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="H125" s="2">
-        <v>45820</v>
+        <v>45925</v>
       </c>
       <c r="I125" s="2">
-        <v>45820</v>
+        <v>45925</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L125" s="1">
-        <v>45820</v>
-      </c>
-      <c r="M125" t="s">
-        <v>138</v>
+        <v>72</v>
+      </c>
+      <c r="L125" s="2">
+        <v>46072</v>
+      </c>
+      <c r="M125" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="126" spans="1:13">
-      <c r="A126" t="s">
-        <v>11</v>
-      </c>
-      <c r="B126" t="s">
-        <v>22</v>
+      <c r="A126" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>310</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>137</v>
+        <v>69</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="H126" s="2">
-        <v>45820</v>
+        <v>45925</v>
       </c>
       <c r="I126" s="2">
-        <v>45820</v>
+        <v>45925</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L126" s="1">
-        <v>45820</v>
-      </c>
-      <c r="M126" t="s">
-        <v>138</v>
+        <v>72</v>
+      </c>
+      <c r="L126" s="2">
+        <v>46072</v>
+      </c>
+      <c r="M126" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="127" spans="1:13" customFormat="1">
-      <c r="A127" t="s">
-        <v>12</v>
-      </c>
-      <c r="B127" t="s">
-        <v>23</v>
-      </c>
-      <c r="C127" t="s">
-        <v>201</v>
-      </c>
-      <c r="D127" t="s">
-        <v>170</v>
+      <c r="A127" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F127" t="s">
-        <v>323</v>
-      </c>
-      <c r="G127" t="s">
-        <v>356</v>
+        <v>51</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>335</v>
       </c>
       <c r="H127" s="2">
-        <v>45656</v>
+        <v>45925</v>
       </c>
       <c r="I127" s="2">
-        <v>45656</v>
+        <v>45925</v>
       </c>
       <c r="J127" s="3"/>
       <c r="K127" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L127" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M127" t="s">
-        <v>139</v>
+        <v>72</v>
+      </c>
+      <c r="L127" s="2">
+        <v>46072</v>
+      </c>
+      <c r="M127" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="128" spans="1:13">
-      <c r="A128" t="s">
-        <v>12</v>
-      </c>
-      <c r="B128" t="s">
-        <v>23</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>173</v>
+      <c r="A128" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F128" t="s">
-        <v>323</v>
-      </c>
-      <c r="G128" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="H128" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="I128" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L128" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M128" t="s">
-        <v>139</v>
+        <v>72</v>
+      </c>
+      <c r="L128" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M128" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="129" spans="1:13">
-      <c r="A129" t="s">
-        <v>12</v>
-      </c>
-      <c r="B129" t="s">
-        <v>23</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>177</v>
+      <c r="A129" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F129" t="s">
-        <v>323</v>
-      </c>
-      <c r="G129" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="H129" s="2">
-        <v>44349</v>
+        <v>45826</v>
       </c>
       <c r="I129" s="2">
-        <v>44349</v>
+        <v>45826</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L129" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M129" t="s">
-        <v>139</v>
+        <v>72</v>
+      </c>
+      <c r="L129" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M129" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="130" spans="1:13">
-      <c r="A130" t="s">
-        <v>12</v>
-      </c>
-      <c r="B130" t="s">
-        <v>23</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>178</v>
+      <c r="A130" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F130" t="s">
-        <v>323</v>
-      </c>
-      <c r="G130" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="H130" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="I130" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L130" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M130" t="s">
-        <v>139</v>
+        <v>72</v>
+      </c>
+      <c r="L130" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M130" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="131" spans="1:13">
-      <c r="A131" t="s">
-        <v>12</v>
-      </c>
-      <c r="B131" t="s">
-        <v>23</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>179</v>
+      <c r="A131" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F131" t="s">
-        <v>323</v>
-      </c>
-      <c r="G131" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="H131" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="I131" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L131" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M131" t="s">
-        <v>139</v>
+        <v>72</v>
+      </c>
+      <c r="L131" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M131" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="132" spans="1:13" customFormat="1">
-      <c r="A132" t="s">
-        <v>12</v>
-      </c>
-      <c r="B132" t="s">
-        <v>23</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>185</v>
-      </c>
+      <c r="A132" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C132" s="3"/>
       <c r="D132" s="3" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F132" t="s">
-        <v>323</v>
-      </c>
-      <c r="G132" t="s">
-        <v>342</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="G132" s="3"/>
       <c r="H132" s="2">
-        <v>44349</v>
+        <v>45833</v>
       </c>
       <c r="I132" s="2">
-        <v>44349</v>
+        <v>45833</v>
       </c>
       <c r="J132" s="3"/>
       <c r="K132" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="L132" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M132" t="s">
-        <v>139</v>
+      <c r="L132" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M132" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="133" spans="1:13">
-      <c r="A133" t="s">
-        <v>12</v>
-      </c>
-      <c r="B133" t="s">
-        <v>23</v>
-      </c>
-      <c r="C133" t="s">
-        <v>196</v>
-      </c>
-      <c r="D133" t="s">
-        <v>165</v>
+      <c r="A133" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F133" t="s">
-        <v>323</v>
-      </c>
-      <c r="G133" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="H133" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="I133" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L133" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M133" t="s">
-        <v>139</v>
+        <v>72</v>
+      </c>
+      <c r="L133" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M133" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="134" spans="1:13">
-      <c r="A134" t="s">
-        <v>12</v>
-      </c>
-      <c r="B134" t="s">
-        <v>23</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>197</v>
+      <c r="A134" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F134" t="s">
-        <v>323</v>
-      </c>
-      <c r="G134" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="H134" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="I134" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L134" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M134" t="s">
-        <v>139</v>
+        <v>72</v>
+      </c>
+      <c r="L134" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M134" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="135" spans="1:13">
-      <c r="A135" t="s">
-        <v>12</v>
-      </c>
-      <c r="B135" t="s">
-        <v>23</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>199</v>
+      <c r="A135" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F135" t="s">
-        <v>323</v>
-      </c>
-      <c r="G135" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="H135" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="I135" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L135" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M135" t="s">
-        <v>139</v>
+        <v>72</v>
+      </c>
+      <c r="L135" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M135" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="136" spans="1:13">
-      <c r="A136" t="s">
-        <v>12</v>
-      </c>
-      <c r="B136" t="s">
-        <v>23</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>200</v>
+      <c r="A136" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F136" t="s">
-        <v>323</v>
-      </c>
-      <c r="G136" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="H136" s="2">
-        <v>44349</v>
+        <v>43697</v>
       </c>
       <c r="I136" s="2">
-        <v>44349</v>
+        <v>43697</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L136" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M136" t="s">
-        <v>139</v>
+        <v>72</v>
+      </c>
+      <c r="L136" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M136" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="137" spans="1:13" customFormat="1">
-      <c r="A137" t="s">
-        <v>12</v>
-      </c>
-      <c r="B137" t="s">
-        <v>23</v>
+      <c r="A137" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>172</v>
+        <v>283</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F137" t="s">
-        <v>323</v>
+        <v>51</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="H137" s="2">
-        <v>44176</v>
-      </c>
-      <c r="I137" s="2">
-        <v>44176</v>
+        <v>331</v>
+      </c>
+      <c r="H137" s="3"/>
+      <c r="I137" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="J137" s="3"/>
       <c r="K137" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L137" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M137" t="s">
-        <v>139</v>
+        <v>72</v>
+      </c>
+      <c r="L137" s="2">
+        <v>45814</v>
+      </c>
+      <c r="M137" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -6823,19 +6871,19 @@
         <v>23</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F138" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G138" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H138" s="2">
         <v>44349</v>
@@ -6861,19 +6909,19 @@
         <v>23</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F139" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G139" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="H139" s="2">
         <v>44349</v>
@@ -6882,7 +6930,7 @@
         <v>44349</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="L139" s="1">
         <v>45656</v>
@@ -6899,19 +6947,19 @@
         <v>23</v>
       </c>
       <c r="C140" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D140" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F140" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G140" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H140" s="2">
         <v>44349</v>
@@ -6920,7 +6968,7 @@
         <v>44349</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="L140" s="1">
         <v>45656</v>
@@ -6937,19 +6985,19 @@
         <v>23</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>149</v>
+        <v>360</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F141" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G141" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H141" s="2">
         <v>44349</v>
@@ -6958,7 +7006,7 @@
         <v>44349</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="L141" s="1">
         <v>45656</v>
@@ -6974,32 +7022,30 @@
       <c r="B142" t="s">
         <v>23</v>
       </c>
-      <c r="C142" t="s">
-        <v>203</v>
-      </c>
-      <c r="D142" t="s">
-        <v>202</v>
+      <c r="C142" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F142" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G142" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H142" s="2">
-        <v>43712</v>
+        <v>44349</v>
       </c>
       <c r="I142" s="2">
-        <v>43712</v>
-      </c>
-      <c r="J142" s="2">
-        <v>45539</v>
-      </c>
+        <v>44349</v>
+      </c>
+      <c r="J142" s="3"/>
       <c r="K142" s="3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="L142" s="1">
         <v>45656</v>
@@ -7015,20 +7061,20 @@
       <c r="B143" t="s">
         <v>23</v>
       </c>
-      <c r="C143" t="s">
-        <v>181</v>
-      </c>
-      <c r="D143" t="s">
-        <v>150</v>
+      <c r="C143" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F143" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G143" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H143" s="2">
         <v>44349</v>
@@ -7053,20 +7099,20 @@
       <c r="B144" t="s">
         <v>23</v>
       </c>
-      <c r="C144" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>151</v>
+      <c r="C144" t="s">
+        <v>185</v>
+      </c>
+      <c r="D144" t="s">
+        <v>154</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F144" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G144" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H144" s="2">
         <v>44349</v>
@@ -7092,19 +7138,19 @@
         <v>23</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F145" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G145" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H145" s="2">
         <v>44349</v>
@@ -7130,19 +7176,19 @@
         <v>23</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F146" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G146" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H146" s="2">
         <v>44349</v>
@@ -7167,20 +7213,20 @@
       <c r="B147" t="s">
         <v>23</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D147" s="3" t="s">
         <v>155</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F147" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G147" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H147" s="2">
         <v>44349</v>
@@ -7206,26 +7252,26 @@
       <c r="B148" t="s">
         <v>23</v>
       </c>
-      <c r="C148" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>157</v>
+      <c r="C148" t="s">
+        <v>170</v>
+      </c>
+      <c r="D148" t="s">
+        <v>140</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F148" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G148" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="H148" s="2">
-        <v>44349</v>
+        <v>46013</v>
       </c>
       <c r="I148" s="2">
-        <v>44349</v>
+        <v>46013</v>
       </c>
       <c r="K148" s="3" t="s">
         <v>72</v>
@@ -7238,818 +7284,776 @@
       </c>
     </row>
     <row r="149" spans="1:13">
-      <c r="A149" t="s">
-        <v>12</v>
-      </c>
-      <c r="B149" t="s">
-        <v>23</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>198</v>
+      <c r="A149" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F149" t="s">
-        <v>323</v>
-      </c>
-      <c r="G149" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="H149" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="I149" s="2">
-        <v>44349</v>
+        <v>43705</v>
       </c>
       <c r="K149" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L149" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M149" t="s">
-        <v>139</v>
+      <c r="L149" s="2">
+        <v>45911</v>
+      </c>
+      <c r="M149" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="150" spans="1:13">
-      <c r="A150" t="s">
-        <v>12</v>
-      </c>
-      <c r="B150" t="s">
-        <v>23</v>
+      <c r="A150" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>190</v>
+        <v>282</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F150" t="s">
-        <v>323</v>
-      </c>
-      <c r="G150" t="s">
-        <v>348</v>
-      </c>
-      <c r="H150" s="2">
-        <v>44349</v>
-      </c>
-      <c r="I150" s="2">
-        <v>44349</v>
+        <v>82</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="K150" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L150" s="1">
-        <v>45656</v>
-      </c>
-      <c r="M150" t="s">
-        <v>139</v>
+        <v>83</v>
+      </c>
+      <c r="L150" s="2">
+        <v>45814</v>
+      </c>
+      <c r="M150" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B151" t="s">
-        <v>23</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>174</v>
+        <v>22</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F151" t="s">
+        <v>82</v>
+      </c>
+      <c r="F151" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G151" t="s">
-        <v>347</v>
+      <c r="G151" s="3" t="s">
+        <v>349</v>
       </c>
       <c r="H151" s="2">
-        <v>44349</v>
+        <v>45821</v>
       </c>
       <c r="I151" s="2">
-        <v>44349</v>
+        <v>44617</v>
       </c>
       <c r="K151" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L151" s="1">
-        <v>45656</v>
+        <v>45820</v>
       </c>
       <c r="M151" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="152" spans="1:13" customFormat="1">
       <c r="A152" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B152" t="s">
-        <v>23</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>187</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C152" s="3"/>
       <c r="D152" s="3" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F152" t="s">
+        <v>82</v>
+      </c>
+      <c r="F152" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G152" t="s">
-        <v>347</v>
+      <c r="G152" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="H152" s="2">
-        <v>44349</v>
+        <v>44617</v>
       </c>
       <c r="I152" s="2">
-        <v>44349</v>
+        <v>44617</v>
       </c>
       <c r="J152" s="3"/>
       <c r="K152" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L152" s="1">
-        <v>45656</v>
+        <v>45820</v>
       </c>
       <c r="M152" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B153" t="s">
-        <v>23</v>
-      </c>
-      <c r="C153" t="s">
-        <v>191</v>
-      </c>
-      <c r="D153" t="s">
-        <v>160</v>
+        <v>22</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F153" t="s">
+      <c r="F153" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G153" t="s">
-        <v>347</v>
+      <c r="G153" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="H153" s="2">
-        <v>44349</v>
+        <v>45821</v>
       </c>
       <c r="I153" s="2">
-        <v>44349</v>
+        <v>44617</v>
       </c>
       <c r="K153" s="3" t="s">
         <v>83</v>
       </c>
       <c r="L153" s="1">
-        <v>45656</v>
+        <v>45820</v>
       </c>
       <c r="M153" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B154" t="s">
-        <v>23</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F154" t="s">
+      <c r="F154" s="3" t="s">
         <v>323</v>
       </c>
       <c r="G154" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="H154" s="2">
-        <v>44349</v>
+        <v>44925</v>
       </c>
       <c r="I154" s="2">
-        <v>44349</v>
+        <v>42990</v>
       </c>
       <c r="K154" s="3" t="s">
         <v>83</v>
       </c>
       <c r="L154" s="1">
-        <v>45656</v>
+        <v>45820</v>
       </c>
       <c r="M154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B155" t="s">
-        <v>23</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>193</v>
+        <v>22</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F155" t="s">
+      <c r="F155" s="3" t="s">
         <v>323</v>
       </c>
       <c r="G155" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="H155" s="2">
-        <v>44349</v>
+        <v>44923</v>
       </c>
       <c r="I155" s="2">
-        <v>44349</v>
+        <v>42990</v>
       </c>
       <c r="K155" s="3" t="s">
         <v>83</v>
       </c>
       <c r="L155" s="1">
-        <v>45656</v>
+        <v>45820</v>
       </c>
       <c r="M155" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B156" t="s">
-        <v>23</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>194</v>
+        <v>22</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F156" t="s">
+      <c r="F156" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G156" t="s">
-        <v>347</v>
+      <c r="G156" s="3" t="s">
+        <v>351</v>
       </c>
       <c r="H156" s="2">
-        <v>44349</v>
+        <v>44617</v>
       </c>
       <c r="I156" s="2">
-        <v>44349</v>
+        <v>44617</v>
       </c>
       <c r="K156" s="3" t="s">
         <v>83</v>
       </c>
       <c r="L156" s="1">
-        <v>45656</v>
+        <v>45820</v>
       </c>
       <c r="M156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="157" spans="1:13" customFormat="1">
       <c r="A157" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B157" t="s">
-        <v>23</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>195</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C157" s="3"/>
       <c r="D157" s="3" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F157" t="s">
+      <c r="F157" s="3" t="s">
         <v>323</v>
       </c>
       <c r="G157" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H157" s="2">
-        <v>44349</v>
+        <v>44194</v>
       </c>
       <c r="I157" s="2">
-        <v>44349</v>
+        <v>42990</v>
       </c>
       <c r="J157" s="3"/>
       <c r="K157" s="3" t="s">
         <v>83</v>
       </c>
       <c r="L157" s="1">
-        <v>45656</v>
+        <v>45820</v>
       </c>
       <c r="M157" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="158" spans="1:13" customFormat="1">
       <c r="A158" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B158" t="s">
-        <v>23</v>
-      </c>
-      <c r="C158" t="s">
-        <v>171</v>
+        <v>22</v>
       </c>
       <c r="D158" t="s">
-        <v>140</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F158" t="s">
+        <v>127</v>
+      </c>
+      <c r="E158" t="s">
+        <v>82</v>
+      </c>
+      <c r="F158" s="3" t="s">
         <v>323</v>
       </c>
       <c r="G158" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="H158" s="2">
-        <v>46013</v>
+        <v>44426</v>
       </c>
       <c r="I158" s="2">
-        <v>46013</v>
+        <v>42191</v>
       </c>
       <c r="J158" s="3"/>
       <c r="K158" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L158" s="1">
-        <v>45656</v>
+        <v>45820</v>
       </c>
       <c r="M158" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="159" spans="1:13" customFormat="1">
       <c r="A159" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>24</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>215</v>
+        <v>23</v>
+      </c>
+      <c r="C159" t="s">
+        <v>200</v>
+      </c>
+      <c r="D159" t="s">
+        <v>169</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F159" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G159" s="10" t="s">
-        <v>331</v>
+        <v>82</v>
+      </c>
+      <c r="F159" t="s">
+        <v>322</v>
+      </c>
+      <c r="G159" t="s">
+        <v>355</v>
       </c>
       <c r="H159" s="2">
-        <v>44426</v>
+        <v>45656</v>
       </c>
       <c r="I159" s="2">
-        <v>44426</v>
+        <v>45656</v>
       </c>
       <c r="J159" s="3"/>
       <c r="K159" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L159" s="1">
-        <v>45821</v>
+        <v>45656</v>
       </c>
       <c r="M159" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>24</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>213</v>
+        <v>23</v>
+      </c>
+      <c r="C160" t="s">
+        <v>195</v>
+      </c>
+      <c r="D160" t="s">
+        <v>164</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G160" s="10" t="s">
-        <v>331</v>
+        <v>82</v>
+      </c>
+      <c r="F160" t="s">
+        <v>322</v>
+      </c>
+      <c r="G160" t="s">
+        <v>341</v>
       </c>
       <c r="H160" s="2">
-        <v>44426</v>
+        <v>44349</v>
       </c>
       <c r="I160" s="2">
-        <v>44426</v>
+        <v>44349</v>
       </c>
       <c r="K160" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L160" s="1">
-        <v>45821</v>
+        <v>45656</v>
       </c>
       <c r="M160" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>24</v>
-      </c>
-      <c r="C161" t="s">
-        <v>204</v>
-      </c>
-      <c r="D161" t="s">
-        <v>205</v>
+        <v>23</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>328</v>
+        <v>82</v>
+      </c>
+      <c r="F161" t="s">
+        <v>322</v>
       </c>
       <c r="G161" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H161" s="2">
-        <v>42734</v>
+        <v>44349</v>
       </c>
       <c r="I161" s="2">
-        <v>42734</v>
-      </c>
-      <c r="J161" s="2">
-        <v>44925</v>
+        <v>44349</v>
       </c>
       <c r="K161" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L161" s="1">
-        <v>45821</v>
+        <v>45656</v>
       </c>
       <c r="M161" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="162" spans="1:13" customFormat="1">
       <c r="A162" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>24</v>
-      </c>
-      <c r="C162" t="s">
-        <v>210</v>
-      </c>
-      <c r="D162" t="s">
-        <v>211</v>
+        <v>23</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>328</v>
+        <v>82</v>
+      </c>
+      <c r="F162" t="s">
+        <v>322</v>
       </c>
       <c r="G162" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H162" s="2">
-        <v>43819</v>
+        <v>44349</v>
       </c>
       <c r="I162" s="2">
-        <v>43819</v>
-      </c>
-      <c r="J162" s="2">
-        <v>45824</v>
-      </c>
+        <v>44349</v>
+      </c>
+      <c r="J162" s="3"/>
       <c r="K162" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L162" s="1">
-        <v>45821</v>
+        <v>45656</v>
       </c>
       <c r="M162" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>328</v>
+        <v>82</v>
+      </c>
+      <c r="F163" t="s">
+        <v>322</v>
       </c>
       <c r="G163" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H163" s="2">
-        <v>44923</v>
+        <v>44349</v>
       </c>
       <c r="I163" s="2">
-        <v>44923</v>
+        <v>44349</v>
       </c>
       <c r="K163" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L163" s="1">
-        <v>45821</v>
+        <v>45656</v>
       </c>
       <c r="M163" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F164" s="3" t="s">
-        <v>328</v>
+        <v>82</v>
+      </c>
+      <c r="F164" t="s">
+        <v>322</v>
       </c>
       <c r="G164" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="H164" s="2">
-        <v>45821</v>
+        <v>44349</v>
       </c>
       <c r="I164" s="2">
-        <v>45821</v>
+        <v>44349</v>
       </c>
       <c r="K164" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L164" s="1">
-        <v>45821</v>
+        <v>45656</v>
       </c>
       <c r="M164" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>24</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>207</v>
+        <v>23</v>
+      </c>
+      <c r="C165" t="s">
+        <v>190</v>
+      </c>
+      <c r="D165" t="s">
+        <v>159</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F165" s="3" t="s">
-        <v>328</v>
+        <v>82</v>
+      </c>
+      <c r="F165" t="s">
+        <v>322</v>
       </c>
       <c r="G165" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="H165" s="2">
-        <v>43132</v>
+        <v>44349</v>
       </c>
       <c r="I165" s="2">
-        <v>43132</v>
-      </c>
-      <c r="J165" s="2">
-        <v>44966</v>
+        <v>44349</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L165" s="1">
-        <v>45821</v>
+        <v>45656</v>
       </c>
       <c r="M165" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F166" s="3" t="s">
-        <v>328</v>
+        <v>82</v>
+      </c>
+      <c r="F166" t="s">
+        <v>322</v>
       </c>
       <c r="G166" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="H166" s="2">
-        <v>43500</v>
+        <v>44349</v>
       </c>
       <c r="I166" s="2">
-        <v>43500</v>
-      </c>
-      <c r="J166" s="2">
-        <v>45821</v>
+        <v>44349</v>
       </c>
       <c r="K166" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L166" s="1">
-        <v>45821</v>
+        <v>45656</v>
       </c>
       <c r="M166" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="167" spans="1:13" customFormat="1">
       <c r="A167" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>217</v>
+        <v>161</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F167" s="3" t="s">
-        <v>328</v>
+        <v>82</v>
+      </c>
+      <c r="F167" t="s">
+        <v>322</v>
       </c>
       <c r="G167" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="H167" s="2">
-        <v>44194</v>
+        <v>44349</v>
       </c>
       <c r="I167" s="2">
-        <v>44194</v>
+        <v>44349</v>
       </c>
       <c r="J167" s="3"/>
       <c r="K167" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L167" s="1">
-        <v>45821</v>
+        <v>45656</v>
       </c>
       <c r="M167" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>24</v>
-      </c>
-      <c r="C168" t="s">
-        <v>220</v>
-      </c>
-      <c r="D168" t="s">
-        <v>221</v>
+        <v>23</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F168" s="3" t="s">
-        <v>328</v>
+        <v>82</v>
+      </c>
+      <c r="F168" t="s">
+        <v>322</v>
       </c>
       <c r="G168" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="H168" s="2">
-        <v>44925</v>
+        <v>44349</v>
       </c>
       <c r="I168" s="2">
-        <v>44925</v>
+        <v>44349</v>
       </c>
       <c r="K168" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L168" s="1">
-        <v>45821</v>
+        <v>45656</v>
       </c>
       <c r="M168" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>225</v>
+        <v>163</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F169" s="3" t="s">
-        <v>328</v>
+        <v>82</v>
+      </c>
+      <c r="F169" t="s">
+        <v>322</v>
       </c>
       <c r="G169" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="H169" s="2">
-        <v>45821</v>
+        <v>44349</v>
       </c>
       <c r="I169" s="2">
-        <v>45821</v>
+        <v>44349</v>
       </c>
       <c r="K169" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L169" s="1">
-        <v>45821</v>
+        <v>45656</v>
       </c>
       <c r="M169" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -8057,8 +8061,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M169" xr:uid="{CC06B792-B278-4FD9-89F7-02F8181B0784}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M170">
-      <sortCondition ref="A1:A169"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M169">
+      <sortCondition ref="E1:E169"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/upload/informacoes_classificadas_desclassificadas.xlsx
+++ b/upload/informacoes_classificadas_desclassificadas.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha2!$A$1:$M$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha2!$A$1:$N$170</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="355">
   <si>
     <t>orgao_entidade</t>
   </si>
@@ -1221,6 +1221,15 @@
   </si>
   <si>
     <t>Decreto 46.983/2016; Decreto 45.357/2010; Art. 31, Decreto 45.969/12</t>
+  </si>
+  <si>
+    <t>tipo_classificacao</t>
+  </si>
+  <si>
+    <t>Classificada</t>
+  </si>
+  <si>
+    <t>Desclassificada</t>
   </si>
 </sst>
 </file>
@@ -1670,7 +1679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:N171"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9.125" style="2"/>
@@ -1682,12 +1691,13 @@
     <col min="8" max="8" width="19.125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.125" style="2"/>
+    <col min="11" max="11" width="22.625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="23.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="10.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1719,16 +1729,19 @@
         <v>314</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1757,17 +1770,20 @@
         <v>44473</v>
       </c>
       <c r="J2" s="5"/>
-      <c r="K2" s="4">
+      <c r="K2" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L2" s="4">
         <v>10</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>45819</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1796,17 +1812,20 @@
         <v>44473</v>
       </c>
       <c r="J3" s="5"/>
-      <c r="K3" s="4">
+      <c r="K3" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L3" s="4">
         <v>10</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>45819</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1835,17 +1854,20 @@
         <v>44473</v>
       </c>
       <c r="J4" s="5"/>
-      <c r="K4" s="4">
+      <c r="K4" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L4" s="4">
         <v>10</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>45819</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1874,17 +1896,20 @@
         <v>45763</v>
       </c>
       <c r="J5" s="5"/>
-      <c r="K5" s="4">
+      <c r="K5" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L5" s="4">
         <v>10</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>45819</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1913,17 +1938,20 @@
         <v>44298</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="2">
-        <v>5</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="K6" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L6" s="2">
+        <v>5</v>
+      </c>
+      <c r="M6" s="1">
         <v>45819</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -1952,17 +1980,20 @@
         <v>44298</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="2">
-        <v>5</v>
-      </c>
-      <c r="L7" s="1">
+      <c r="K7" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L7" s="2">
+        <v>5</v>
+      </c>
+      <c r="M7" s="1">
         <v>45819</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1993,17 +2024,20 @@
       <c r="J8" s="3">
         <v>45440</v>
       </c>
-      <c r="K8" s="7">
-        <v>5</v>
-      </c>
-      <c r="L8" s="1">
+      <c r="K8" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L8" s="7">
+        <v>5</v>
+      </c>
+      <c r="M8" s="1">
         <v>45819</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -2034,17 +2068,20 @@
       <c r="J9" s="3">
         <v>45484</v>
       </c>
-      <c r="K9" s="2">
-        <v>5</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="K9" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L9" s="2">
+        <v>5</v>
+      </c>
+      <c r="M9" s="1">
         <v>45819</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -2075,17 +2112,20 @@
       <c r="J10" s="3">
         <v>45567</v>
       </c>
-      <c r="K10" s="2">
-        <v>5</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K10" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L10" s="2">
+        <v>5</v>
+      </c>
+      <c r="M10" s="1">
         <v>45819</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -2116,17 +2156,20 @@
       <c r="J11" s="3">
         <v>45580</v>
       </c>
-      <c r="K11" s="7">
-        <v>5</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="K11" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L11" s="7">
+        <v>5</v>
+      </c>
+      <c r="M11" s="1">
         <v>45819</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -2157,17 +2200,20 @@
       <c r="J12" s="3">
         <v>45774</v>
       </c>
-      <c r="K12" s="7">
-        <v>5</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="K12" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L12" s="7">
+        <v>5</v>
+      </c>
+      <c r="M12" s="1">
         <v>45819</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:14">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
@@ -2198,17 +2244,20 @@
       <c r="J13" s="3">
         <v>45771</v>
       </c>
-      <c r="K13" s="2">
-        <v>5</v>
-      </c>
-      <c r="L13" s="1">
+      <c r="K13" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L13" s="2">
+        <v>5</v>
+      </c>
+      <c r="M13" s="1">
         <v>45819</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:14">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
@@ -2239,17 +2288,20 @@
       <c r="J14" s="3">
         <v>45796</v>
       </c>
-      <c r="K14" s="2">
-        <v>5</v>
-      </c>
-      <c r="L14" s="1">
+      <c r="K14" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L14" s="2">
+        <v>5</v>
+      </c>
+      <c r="M14" s="1">
         <v>45819</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:14">
       <c r="A15" s="2" t="s">
         <v>3</v>
       </c>
@@ -2280,17 +2332,20 @@
       <c r="J15" s="3">
         <v>45797</v>
       </c>
-      <c r="K15" s="7">
-        <v>5</v>
-      </c>
-      <c r="L15" s="1">
+      <c r="K15" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L15" s="7">
+        <v>5</v>
+      </c>
+      <c r="M15" s="1">
         <v>45819</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:14">
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
@@ -2319,17 +2374,20 @@
         <v>44298</v>
       </c>
       <c r="J16" s="5"/>
-      <c r="K16" s="7">
-        <v>5</v>
-      </c>
-      <c r="L16" s="1">
+      <c r="K16" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L16" s="7">
+        <v>5</v>
+      </c>
+      <c r="M16" s="1">
         <v>45819</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:14">
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
@@ -2357,17 +2415,20 @@
       <c r="I17" s="6">
         <v>44552</v>
       </c>
-      <c r="K17" s="7">
-        <v>5</v>
-      </c>
-      <c r="L17" s="1">
+      <c r="K17" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L17" s="7">
+        <v>5</v>
+      </c>
+      <c r="M17" s="1">
         <v>45819</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:14">
       <c r="A18" s="2" t="s">
         <v>4</v>
       </c>
@@ -2395,17 +2456,20 @@
       <c r="I18" s="6">
         <v>44552</v>
       </c>
-      <c r="K18" s="7">
-        <v>5</v>
-      </c>
-      <c r="L18" s="1">
+      <c r="K18" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L18" s="7">
+        <v>5</v>
+      </c>
+      <c r="M18" s="1">
         <v>45819</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:14">
       <c r="A19" s="2" t="s">
         <v>4</v>
       </c>
@@ -2433,17 +2497,20 @@
       <c r="I19" s="8">
         <v>44780</v>
       </c>
-      <c r="K19" s="2">
-        <v>5</v>
-      </c>
-      <c r="L19" s="1">
+      <c r="K19" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L19" s="2">
+        <v>5</v>
+      </c>
+      <c r="M19" s="1">
         <v>45819</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:14">
       <c r="A20" s="2" t="s">
         <v>4</v>
       </c>
@@ -2471,17 +2538,20 @@
       <c r="I20" s="8">
         <v>44780</v>
       </c>
-      <c r="K20" s="2">
-        <v>5</v>
-      </c>
-      <c r="L20" s="1">
+      <c r="K20" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L20" s="2">
+        <v>5</v>
+      </c>
+      <c r="M20" s="1">
         <v>45819</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:14">
       <c r="A21" s="2" t="s">
         <v>4</v>
       </c>
@@ -2509,17 +2579,20 @@
       <c r="I21" s="8">
         <v>45021</v>
       </c>
-      <c r="K21" s="7">
-        <v>5</v>
-      </c>
-      <c r="L21" s="1">
+      <c r="K21" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L21" s="7">
+        <v>5</v>
+      </c>
+      <c r="M21" s="1">
         <v>45819</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:14">
       <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
@@ -2547,17 +2620,20 @@
       <c r="I22" s="8">
         <v>45021</v>
       </c>
-      <c r="K22" s="7">
-        <v>5</v>
-      </c>
-      <c r="L22" s="1">
+      <c r="K22" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L22" s="7">
+        <v>5</v>
+      </c>
+      <c r="M22" s="1">
         <v>45819</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:14">
       <c r="A23" s="2" t="s">
         <v>4</v>
       </c>
@@ -2585,17 +2661,20 @@
       <c r="I23" s="8">
         <v>45292</v>
       </c>
-      <c r="K23" s="2">
-        <v>5</v>
-      </c>
-      <c r="L23" s="1">
+      <c r="K23" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L23" s="2">
+        <v>5</v>
+      </c>
+      <c r="M23" s="1">
         <v>45819</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:14">
       <c r="A24" s="2" t="s">
         <v>4</v>
       </c>
@@ -2623,17 +2702,20 @@
       <c r="I24" s="8">
         <v>45292</v>
       </c>
-      <c r="K24" s="2">
-        <v>5</v>
-      </c>
-      <c r="L24" s="1">
+      <c r="K24" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L24" s="2">
+        <v>5</v>
+      </c>
+      <c r="M24" s="1">
         <v>45819</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:14">
       <c r="A25" s="2" t="s">
         <v>4</v>
       </c>
@@ -2661,17 +2743,20 @@
       <c r="I25" s="8">
         <v>45658</v>
       </c>
-      <c r="K25" s="7">
-        <v>5</v>
-      </c>
-      <c r="L25" s="1">
+      <c r="K25" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L25" s="7">
+        <v>5</v>
+      </c>
+      <c r="M25" s="1">
         <v>45819</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:14">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
@@ -2699,17 +2784,20 @@
       <c r="I26" s="8">
         <v>45658</v>
       </c>
-      <c r="K26" s="7">
-        <v>5</v>
-      </c>
-      <c r="L26" s="1">
+      <c r="K26" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L26" s="7">
+        <v>5</v>
+      </c>
+      <c r="M26" s="1">
         <v>45819</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="N26" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:14">
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
@@ -2737,17 +2825,20 @@
       <c r="I27" s="6">
         <v>44558</v>
       </c>
-      <c r="K27" s="2">
-        <v>5</v>
-      </c>
-      <c r="L27" s="1">
+      <c r="K27" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L27" s="2">
+        <v>5</v>
+      </c>
+      <c r="M27" s="1">
         <v>45819</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:14">
       <c r="A28" s="2" t="s">
         <v>4</v>
       </c>
@@ -2775,17 +2866,20 @@
       <c r="I28" s="6">
         <v>44925</v>
       </c>
-      <c r="K28" s="2">
-        <v>5</v>
-      </c>
-      <c r="L28" s="1">
+      <c r="K28" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L28" s="2">
+        <v>5</v>
+      </c>
+      <c r="M28" s="1">
         <v>45819</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="N28" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:14">
       <c r="A29" s="2" t="s">
         <v>4</v>
       </c>
@@ -2813,17 +2907,20 @@
       <c r="I29" s="6">
         <v>45289</v>
       </c>
-      <c r="K29" s="7">
-        <v>5</v>
-      </c>
-      <c r="L29" s="1">
+      <c r="K29" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L29" s="7">
+        <v>5</v>
+      </c>
+      <c r="M29" s="1">
         <v>45819</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:14">
       <c r="A30" s="2" t="s">
         <v>4</v>
       </c>
@@ -2851,17 +2948,20 @@
       <c r="I30" s="6">
         <v>45656</v>
       </c>
-      <c r="K30" s="7">
-        <v>5</v>
-      </c>
-      <c r="L30" s="1">
+      <c r="K30" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L30" s="7">
+        <v>5</v>
+      </c>
+      <c r="M30" s="1">
         <v>45819</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:14">
       <c r="A31" s="2" t="s">
         <v>4</v>
       </c>
@@ -2889,17 +2989,20 @@
       <c r="I31" s="6">
         <v>44194</v>
       </c>
-      <c r="K31" s="2">
-        <v>5</v>
-      </c>
-      <c r="L31" s="1">
+      <c r="K31" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L31" s="2">
+        <v>5</v>
+      </c>
+      <c r="M31" s="1">
         <v>45819</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:14">
       <c r="A32" s="2" t="s">
         <v>5</v>
       </c>
@@ -2927,17 +3030,20 @@
       <c r="I32" s="1">
         <v>45925</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K32" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L32" s="2">
         <v>15</v>
       </c>
-      <c r="L32" s="1">
+      <c r="M32" s="1">
         <v>46072</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="N32" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:14">
       <c r="A33" s="2" t="s">
         <v>5</v>
       </c>
@@ -2965,17 +3071,20 @@
       <c r="I33" s="1">
         <v>45925</v>
       </c>
-      <c r="K33" s="2">
+      <c r="K33" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L33" s="2">
         <v>15</v>
       </c>
-      <c r="L33" s="1">
+      <c r="M33" s="1">
         <v>46072</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="N33" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:14">
       <c r="A34" s="2" t="s">
         <v>5</v>
       </c>
@@ -3003,17 +3112,20 @@
       <c r="I34" s="1">
         <v>45925</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K34" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L34" s="2">
         <v>15</v>
       </c>
-      <c r="L34" s="1">
+      <c r="M34" s="1">
         <v>46072</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="N34" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:14">
       <c r="A35" s="2" t="s">
         <v>5</v>
       </c>
@@ -3041,17 +3153,20 @@
       <c r="I35" s="1">
         <v>45925</v>
       </c>
-      <c r="K35" s="2">
+      <c r="K35" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L35" s="2">
         <v>15</v>
       </c>
-      <c r="L35" s="1">
+      <c r="M35" s="1">
         <v>46072</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="N35" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:14">
       <c r="A36" s="2" t="s">
         <v>5</v>
       </c>
@@ -3079,17 +3194,20 @@
       <c r="I36" s="1">
         <v>45916</v>
       </c>
-      <c r="K36" s="2">
-        <v>5</v>
-      </c>
-      <c r="L36" s="1">
+      <c r="K36" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L36" s="2">
+        <v>5</v>
+      </c>
+      <c r="M36" s="1">
         <v>46072</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="N36" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:14">
       <c r="A37" s="2" t="s">
         <v>5</v>
       </c>
@@ -3117,17 +3235,20 @@
       <c r="I37" s="1">
         <v>45932</v>
       </c>
-      <c r="K37" s="7">
-        <v>5</v>
-      </c>
-      <c r="L37" s="1">
+      <c r="K37" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L37" s="7">
+        <v>5</v>
+      </c>
+      <c r="M37" s="1">
         <v>46072</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="N37" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:14">
       <c r="A38" s="2" t="s">
         <v>5</v>
       </c>
@@ -3155,17 +3276,20 @@
       <c r="I38" s="1">
         <v>45932</v>
       </c>
-      <c r="K38" s="7">
-        <v>5</v>
-      </c>
-      <c r="L38" s="1">
+      <c r="K38" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L38" s="7">
+        <v>5</v>
+      </c>
+      <c r="M38" s="1">
         <v>46072</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="N38" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:14">
       <c r="A39" s="2" t="s">
         <v>5</v>
       </c>
@@ -3193,17 +3317,20 @@
       <c r="I39" s="1">
         <v>45932</v>
       </c>
-      <c r="K39" s="7">
-        <v>5</v>
-      </c>
-      <c r="L39" s="1">
+      <c r="K39" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L39" s="7">
+        <v>5</v>
+      </c>
+      <c r="M39" s="1">
         <v>46072</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="N39" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:14">
       <c r="A40" s="2" t="s">
         <v>5</v>
       </c>
@@ -3231,17 +3358,20 @@
       <c r="I40" s="1">
         <v>45923</v>
       </c>
-      <c r="K40" s="7">
-        <v>5</v>
-      </c>
-      <c r="L40" s="1">
+      <c r="K40" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L40" s="7">
+        <v>5</v>
+      </c>
+      <c r="M40" s="1">
         <v>46072</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="N40" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:14">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
@@ -3266,17 +3396,20 @@
       <c r="I41" s="1">
         <v>43705</v>
       </c>
-      <c r="K41" s="2">
+      <c r="K41" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L41" s="2">
         <v>15</v>
       </c>
-      <c r="L41" s="1">
+      <c r="M41" s="1">
         <v>45911</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="N41" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:14">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
@@ -3301,17 +3434,20 @@
       <c r="I42" s="1">
         <v>45826</v>
       </c>
-      <c r="K42" s="2">
+      <c r="K42" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L42" s="2">
         <v>15</v>
       </c>
-      <c r="L42" s="1">
+      <c r="M42" s="1">
         <v>45911</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="N42" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:14">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
@@ -3336,17 +3472,20 @@
       <c r="I43" s="1">
         <v>43705</v>
       </c>
-      <c r="K43" s="2">
+      <c r="K43" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L43" s="2">
         <v>15</v>
       </c>
-      <c r="L43" s="1">
+      <c r="M43" s="1">
         <v>45911</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="N43" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:14">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
@@ -3371,17 +3510,20 @@
       <c r="I44" s="1">
         <v>43705</v>
       </c>
-      <c r="K44" s="2">
+      <c r="K44" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L44" s="2">
         <v>15</v>
       </c>
-      <c r="L44" s="1">
+      <c r="M44" s="1">
         <v>45911</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="N44" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:14">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
@@ -3406,17 +3548,20 @@
       <c r="I45" s="1">
         <v>45833</v>
       </c>
-      <c r="K45" s="2">
+      <c r="K45" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L45" s="2">
         <v>15</v>
       </c>
-      <c r="L45" s="1">
+      <c r="M45" s="1">
         <v>45911</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="N45" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:14">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
@@ -3441,17 +3586,20 @@
       <c r="I46" s="1">
         <v>43705</v>
       </c>
-      <c r="K46" s="2">
+      <c r="K46" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L46" s="2">
         <v>15</v>
       </c>
-      <c r="L46" s="1">
+      <c r="M46" s="1">
         <v>45911</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:14">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
@@ -3476,17 +3624,20 @@
       <c r="I47" s="1">
         <v>43705</v>
       </c>
-      <c r="K47" s="2">
+      <c r="K47" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L47" s="2">
         <v>15</v>
       </c>
-      <c r="L47" s="1">
+      <c r="M47" s="1">
         <v>45911</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="N47" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:14">
       <c r="A48" s="2" t="s">
         <v>6</v>
       </c>
@@ -3511,17 +3662,20 @@
       <c r="I48" s="1">
         <v>43705</v>
       </c>
-      <c r="K48" s="2">
+      <c r="K48" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L48" s="2">
         <v>15</v>
       </c>
-      <c r="L48" s="1">
+      <c r="M48" s="1">
         <v>45911</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="N48" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:14">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
@@ -3546,17 +3700,20 @@
       <c r="I49" s="1">
         <v>43697</v>
       </c>
-      <c r="K49" s="2">
+      <c r="K49" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L49" s="2">
         <v>15</v>
       </c>
-      <c r="L49" s="1">
+      <c r="M49" s="1">
         <v>45911</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="N49" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:14">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
@@ -3581,17 +3738,20 @@
       <c r="I50" s="1">
         <v>43697</v>
       </c>
-      <c r="K50" s="2">
+      <c r="K50" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L50" s="2">
         <v>25</v>
       </c>
-      <c r="L50" s="1">
+      <c r="M50" s="1">
         <v>45911</v>
       </c>
-      <c r="M50" s="2" t="s">
+      <c r="N50" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:14">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
@@ -3613,17 +3773,20 @@
       <c r="I51" s="1">
         <v>43705</v>
       </c>
-      <c r="K51" s="2">
+      <c r="K51" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L51" s="2">
         <v>25</v>
       </c>
-      <c r="L51" s="1">
+      <c r="M51" s="1">
         <v>45911</v>
       </c>
-      <c r="M51" s="2" t="s">
+      <c r="N51" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:14">
       <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
@@ -3651,17 +3814,20 @@
       <c r="I52" s="1">
         <v>45303</v>
       </c>
-      <c r="K52" s="2">
+      <c r="K52" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L52" s="2">
         <v>15</v>
       </c>
-      <c r="L52" s="1">
+      <c r="M52" s="1">
         <v>45814</v>
       </c>
-      <c r="M52" s="2" t="s">
+      <c r="N52" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:14">
       <c r="A53" s="2" t="s">
         <v>7</v>
       </c>
@@ -3689,17 +3855,20 @@
       <c r="I53" s="1">
         <v>45303</v>
       </c>
-      <c r="K53" s="2">
+      <c r="K53" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L53" s="2">
         <v>25</v>
       </c>
-      <c r="L53" s="1">
+      <c r="M53" s="1">
         <v>45814</v>
       </c>
-      <c r="M53" s="2" t="s">
+      <c r="N53" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:14">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
@@ -3727,17 +3896,20 @@
       <c r="I54" s="1">
         <v>45303</v>
       </c>
-      <c r="K54" s="7">
-        <v>5</v>
-      </c>
-      <c r="L54" s="1">
+      <c r="K54" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L54" s="7">
+        <v>5</v>
+      </c>
+      <c r="M54" s="1">
         <v>45814</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="N54" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:14">
       <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
@@ -3765,17 +3937,20 @@
       <c r="I55" s="1">
         <v>45303</v>
       </c>
-      <c r="K55" s="7">
-        <v>5</v>
-      </c>
-      <c r="L55" s="1">
+      <c r="K55" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L55" s="7">
+        <v>5</v>
+      </c>
+      <c r="M55" s="1">
         <v>45814</v>
       </c>
-      <c r="M55" s="2" t="s">
+      <c r="N55" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:14">
       <c r="A56" s="2" t="s">
         <v>7</v>
       </c>
@@ -3803,17 +3978,20 @@
       <c r="I56" s="1">
         <v>45303</v>
       </c>
-      <c r="K56" s="2">
-        <v>5</v>
-      </c>
-      <c r="L56" s="1">
+      <c r="K56" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L56" s="2">
+        <v>5</v>
+      </c>
+      <c r="M56" s="1">
         <v>45814</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="N56" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:14">
       <c r="A57" s="2" t="s">
         <v>7</v>
       </c>
@@ -3841,17 +4019,20 @@
       <c r="I57" s="1">
         <v>45303</v>
       </c>
-      <c r="K57" s="2">
-        <v>5</v>
-      </c>
-      <c r="L57" s="1">
+      <c r="K57" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L57" s="2">
+        <v>5</v>
+      </c>
+      <c r="M57" s="1">
         <v>45814</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="N57" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:14">
       <c r="A58" s="2" t="s">
         <v>7</v>
       </c>
@@ -3879,17 +4060,20 @@
       <c r="I58" s="1">
         <v>45303</v>
       </c>
-      <c r="K58" s="7">
-        <v>5</v>
-      </c>
-      <c r="L58" s="1">
+      <c r="K58" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L58" s="7">
+        <v>5</v>
+      </c>
+      <c r="M58" s="1">
         <v>45814</v>
       </c>
-      <c r="M58" s="2" t="s">
+      <c r="N58" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:14">
       <c r="A59" s="2" t="s">
         <v>7</v>
       </c>
@@ -3917,17 +4101,20 @@
       <c r="I59" s="1">
         <v>45303</v>
       </c>
-      <c r="K59" s="7">
-        <v>5</v>
-      </c>
-      <c r="L59" s="1">
+      <c r="K59" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L59" s="7">
+        <v>5</v>
+      </c>
+      <c r="M59" s="1">
         <v>45814</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="N59" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:14">
       <c r="A60" s="2" t="s">
         <v>7</v>
       </c>
@@ -3955,17 +4142,20 @@
       <c r="I60" s="1">
         <v>45303</v>
       </c>
-      <c r="K60" s="2">
-        <v>5</v>
-      </c>
-      <c r="L60" s="1">
+      <c r="K60" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L60" s="2">
+        <v>5</v>
+      </c>
+      <c r="M60" s="1">
         <v>45814</v>
       </c>
-      <c r="M60" s="2" t="s">
+      <c r="N60" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:14">
       <c r="A61" s="2" t="s">
         <v>7</v>
       </c>
@@ -3993,17 +4183,20 @@
       <c r="I61" s="1">
         <v>45303</v>
       </c>
-      <c r="K61" s="2">
-        <v>5</v>
-      </c>
-      <c r="L61" s="1">
+      <c r="K61" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L61" s="2">
+        <v>5</v>
+      </c>
+      <c r="M61" s="1">
         <v>45814</v>
       </c>
-      <c r="M61" s="2" t="s">
+      <c r="N61" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:14">
       <c r="A62" s="2" t="s">
         <v>7</v>
       </c>
@@ -4031,17 +4224,20 @@
       <c r="I62" s="1">
         <v>45303</v>
       </c>
-      <c r="K62" s="7">
-        <v>5</v>
-      </c>
-      <c r="L62" s="1">
+      <c r="K62" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L62" s="7">
+        <v>5</v>
+      </c>
+      <c r="M62" s="1">
         <v>45814</v>
       </c>
-      <c r="M62" s="2" t="s">
+      <c r="N62" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:14">
       <c r="A63" s="2" t="s">
         <v>7</v>
       </c>
@@ -4069,17 +4265,20 @@
       <c r="I63" s="1">
         <v>45303</v>
       </c>
-      <c r="K63" s="2">
-        <v>5</v>
-      </c>
-      <c r="L63" s="1">
+      <c r="K63" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L63" s="2">
+        <v>5</v>
+      </c>
+      <c r="M63" s="1">
         <v>45814</v>
       </c>
-      <c r="M63" s="2" t="s">
+      <c r="N63" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:14">
       <c r="A64" s="2" t="s">
         <v>7</v>
       </c>
@@ -4107,17 +4306,20 @@
       <c r="I64" s="1">
         <v>45303</v>
       </c>
-      <c r="K64" s="7">
-        <v>5</v>
-      </c>
-      <c r="L64" s="1">
+      <c r="K64" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L64" s="7">
+        <v>5</v>
+      </c>
+      <c r="M64" s="1">
         <v>45814</v>
       </c>
-      <c r="M64" s="2" t="s">
+      <c r="N64" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:14">
       <c r="A65" s="2" t="s">
         <v>7</v>
       </c>
@@ -4145,17 +4347,20 @@
       <c r="I65" s="1">
         <v>45303</v>
       </c>
-      <c r="K65" s="2">
-        <v>5</v>
-      </c>
-      <c r="L65" s="1">
+      <c r="K65" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L65" s="2">
+        <v>5</v>
+      </c>
+      <c r="M65" s="1">
         <v>45814</v>
       </c>
-      <c r="M65" s="2" t="s">
+      <c r="N65" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:14">
       <c r="A66" s="2" t="s">
         <v>7</v>
       </c>
@@ -4183,17 +4388,20 @@
       <c r="I66" s="1">
         <v>45303</v>
       </c>
-      <c r="K66" s="2">
-        <v>5</v>
-      </c>
-      <c r="L66" s="1">
+      <c r="K66" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L66" s="2">
+        <v>5</v>
+      </c>
+      <c r="M66" s="1">
         <v>45814</v>
       </c>
-      <c r="M66" s="2" t="s">
+      <c r="N66" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:14">
       <c r="A67" s="2" t="s">
         <v>8</v>
       </c>
@@ -4221,17 +4429,20 @@
       <c r="I67" s="1">
         <v>45352</v>
       </c>
-      <c r="K67" s="7">
-        <v>5</v>
-      </c>
-      <c r="L67" s="1">
+      <c r="K67" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L67" s="7">
+        <v>5</v>
+      </c>
+      <c r="M67" s="1">
         <v>45819</v>
       </c>
-      <c r="M67" s="2" t="s">
+      <c r="N67" s="2" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:14">
       <c r="A68" s="2" t="s">
         <v>8</v>
       </c>
@@ -4259,17 +4470,20 @@
       <c r="I68" s="1">
         <v>45352</v>
       </c>
-      <c r="K68" s="7">
-        <v>5</v>
-      </c>
-      <c r="L68" s="1">
+      <c r="K68" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L68" s="7">
+        <v>5</v>
+      </c>
+      <c r="M68" s="1">
         <v>45819</v>
       </c>
-      <c r="M68" s="2" t="s">
+      <c r="N68" s="2" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:14">
       <c r="A69" s="2" t="s">
         <v>9</v>
       </c>
@@ -4300,17 +4514,20 @@
       <c r="J69" s="1">
         <v>46202</v>
       </c>
-      <c r="K69" s="2">
-        <v>5</v>
-      </c>
-      <c r="L69" s="1">
+      <c r="K69" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L69" s="2">
+        <v>5</v>
+      </c>
+      <c r="M69" s="1">
         <v>45817</v>
       </c>
-      <c r="M69" s="2" t="s">
+      <c r="N69" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="70" spans="1:13" customFormat="1">
+    <row r="70" spans="1:14" customFormat="1">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -4341,15 +4558,18 @@
       <c r="J70" s="1">
         <v>45428</v>
       </c>
-      <c r="K70" s="7">
-        <v>5</v>
-      </c>
-      <c r="L70" s="2"/>
-      <c r="M70" t="s">
+      <c r="K70" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L70" s="7">
+        <v>5</v>
+      </c>
+      <c r="M70" s="2"/>
+      <c r="N70" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:14">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -4377,14 +4597,17 @@
       <c r="I71" s="1">
         <v>45225</v>
       </c>
-      <c r="K71" s="7">
-        <v>5</v>
-      </c>
-      <c r="M71" t="s">
+      <c r="K71" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L71" s="7">
+        <v>5</v>
+      </c>
+      <c r="N71" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:14">
       <c r="A72" t="s">
         <v>10</v>
       </c>
@@ -4412,14 +4635,17 @@
       <c r="I72" s="1">
         <v>45225</v>
       </c>
-      <c r="K72" s="2">
-        <v>5</v>
-      </c>
-      <c r="M72" t="s">
+      <c r="K72" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L72" s="2">
+        <v>5</v>
+      </c>
+      <c r="N72" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:14">
       <c r="A73" t="s">
         <v>10</v>
       </c>
@@ -4448,15 +4674,18 @@
         <v>45967</v>
       </c>
       <c r="J73"/>
-      <c r="K73" s="2">
-        <v>5</v>
-      </c>
-      <c r="L73"/>
-      <c r="M73" t="s">
+      <c r="K73" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L73" s="2">
+        <v>5</v>
+      </c>
+      <c r="M73"/>
+      <c r="N73" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:14">
       <c r="A74" t="s">
         <v>10</v>
       </c>
@@ -4484,14 +4713,17 @@
       <c r="I74" s="1">
         <v>45230</v>
       </c>
-      <c r="K74" s="2">
-        <v>5</v>
-      </c>
-      <c r="M74" t="s">
+      <c r="K74" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L74" s="2">
+        <v>5</v>
+      </c>
+      <c r="N74" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:14">
       <c r="A75" t="s">
         <v>10</v>
       </c>
@@ -4519,14 +4751,17 @@
       <c r="I75" s="1">
         <v>45230</v>
       </c>
-      <c r="K75" s="7">
-        <v>5</v>
-      </c>
-      <c r="M75" t="s">
+      <c r="K75" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L75" s="7">
+        <v>5</v>
+      </c>
+      <c r="N75" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:14">
       <c r="A76" t="s">
         <v>10</v>
       </c>
@@ -4557,14 +4792,17 @@
       <c r="J76" s="1">
         <v>45432</v>
       </c>
-      <c r="K76" s="7">
-        <v>5</v>
-      </c>
-      <c r="M76" t="s">
+      <c r="K76" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L76" s="7">
+        <v>5</v>
+      </c>
+      <c r="N76" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:14">
       <c r="A77" t="s">
         <v>10</v>
       </c>
@@ -4595,14 +4833,17 @@
       <c r="J77" s="1">
         <v>45432</v>
       </c>
-      <c r="K77" s="2">
-        <v>5</v>
-      </c>
-      <c r="M77" t="s">
+      <c r="K77" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L77" s="2">
+        <v>5</v>
+      </c>
+      <c r="N77" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:14">
       <c r="A78" t="s">
         <v>10</v>
       </c>
@@ -4633,14 +4874,17 @@
       <c r="J78" s="1">
         <v>45428</v>
       </c>
-      <c r="K78" s="2">
-        <v>5</v>
-      </c>
-      <c r="M78" t="s">
+      <c r="K78" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L78" s="2">
+        <v>5</v>
+      </c>
+      <c r="N78" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:14">
       <c r="A79" t="s">
         <v>10</v>
       </c>
@@ -4671,14 +4915,17 @@
       <c r="J79" s="1">
         <v>45432</v>
       </c>
-      <c r="K79" s="2">
-        <v>5</v>
-      </c>
-      <c r="M79" t="s">
+      <c r="K79" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L79" s="2">
+        <v>5</v>
+      </c>
+      <c r="N79" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:14">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -4709,14 +4956,17 @@
       <c r="J80" s="1">
         <v>45432</v>
       </c>
-      <c r="K80" s="7">
-        <v>5</v>
-      </c>
-      <c r="M80" t="s">
+      <c r="K80" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L80" s="7">
+        <v>5</v>
+      </c>
+      <c r="N80" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:14">
       <c r="A81" t="s">
         <v>10</v>
       </c>
@@ -4747,14 +4997,17 @@
       <c r="J81" s="1">
         <v>45428</v>
       </c>
-      <c r="K81" s="7">
-        <v>5</v>
-      </c>
-      <c r="M81" t="s">
+      <c r="K81" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L81" s="7">
+        <v>5</v>
+      </c>
+      <c r="N81" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:14">
       <c r="A82" t="s">
         <v>10</v>
       </c>
@@ -4785,14 +5038,17 @@
       <c r="J82" s="1">
         <v>45428</v>
       </c>
-      <c r="K82" s="2">
-        <v>5</v>
-      </c>
-      <c r="M82" t="s">
+      <c r="K82" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L82" s="2">
+        <v>5</v>
+      </c>
+      <c r="N82" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:14">
       <c r="A83" t="s">
         <v>10</v>
       </c>
@@ -4823,14 +5079,17 @@
       <c r="J83" s="1">
         <v>45428</v>
       </c>
-      <c r="K83" s="2">
-        <v>5</v>
-      </c>
-      <c r="M83" t="s">
+      <c r="K83" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L83" s="2">
+        <v>5</v>
+      </c>
+      <c r="N83" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:14">
       <c r="A84" t="s">
         <v>10</v>
       </c>
@@ -4861,14 +5120,17 @@
       <c r="J84" s="1">
         <v>45428</v>
       </c>
-      <c r="K84" s="7">
-        <v>5</v>
-      </c>
-      <c r="M84" t="s">
+      <c r="K84" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L84" s="7">
+        <v>5</v>
+      </c>
+      <c r="N84" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:14">
       <c r="A85" t="s">
         <v>10</v>
       </c>
@@ -4899,14 +5161,17 @@
       <c r="J85" s="1">
         <v>45428</v>
       </c>
-      <c r="K85" s="7">
-        <v>5</v>
-      </c>
-      <c r="M85" t="s">
+      <c r="K85" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L85" s="7">
+        <v>5</v>
+      </c>
+      <c r="N85" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:14">
       <c r="A86" t="s">
         <v>10</v>
       </c>
@@ -4937,14 +5202,17 @@
       <c r="J86" s="1">
         <v>45428</v>
       </c>
-      <c r="K86" s="2">
-        <v>5</v>
-      </c>
-      <c r="M86" t="s">
+      <c r="K86" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L86" s="2">
+        <v>5</v>
+      </c>
+      <c r="N86" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:14">
       <c r="A87" t="s">
         <v>10</v>
       </c>
@@ -4975,14 +5243,17 @@
       <c r="J87" s="1">
         <v>45428</v>
       </c>
-      <c r="K87" s="2">
-        <v>5</v>
-      </c>
-      <c r="M87" t="s">
+      <c r="K87" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L87" s="2">
+        <v>5</v>
+      </c>
+      <c r="N87" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:14">
       <c r="A88" t="s">
         <v>10</v>
       </c>
@@ -5013,14 +5284,17 @@
       <c r="J88" s="1">
         <v>45428</v>
       </c>
-      <c r="K88" s="7">
-        <v>5</v>
-      </c>
-      <c r="M88" t="s">
+      <c r="K88" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L88" s="7">
+        <v>5</v>
+      </c>
+      <c r="N88" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:14">
       <c r="A89" t="s">
         <v>10</v>
       </c>
@@ -5051,14 +5325,17 @@
       <c r="J89" s="1">
         <v>45428</v>
       </c>
-      <c r="K89" s="7">
-        <v>5</v>
-      </c>
-      <c r="M89" t="s">
+      <c r="K89" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L89" s="7">
+        <v>5</v>
+      </c>
+      <c r="N89" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:14">
       <c r="A90" t="s">
         <v>10</v>
       </c>
@@ -5089,14 +5366,17 @@
       <c r="J90" s="1">
         <v>45428</v>
       </c>
-      <c r="K90" s="2">
-        <v>5</v>
-      </c>
-      <c r="M90" t="s">
+      <c r="K90" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L90" s="2">
+        <v>5</v>
+      </c>
+      <c r="N90" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:14">
       <c r="A91" t="s">
         <v>10</v>
       </c>
@@ -5127,14 +5407,17 @@
       <c r="J91" s="1">
         <v>45428</v>
       </c>
-      <c r="K91" s="2">
-        <v>5</v>
-      </c>
-      <c r="M91" t="s">
+      <c r="K91" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L91" s="2">
+        <v>5</v>
+      </c>
+      <c r="N91" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:14">
       <c r="A92" t="s">
         <v>10</v>
       </c>
@@ -5165,14 +5448,17 @@
       <c r="J92" s="1">
         <v>45428</v>
       </c>
-      <c r="K92" s="7">
-        <v>5</v>
-      </c>
-      <c r="M92" t="s">
+      <c r="K92" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L92" s="7">
+        <v>5</v>
+      </c>
+      <c r="N92" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:14">
       <c r="A93" t="s">
         <v>10</v>
       </c>
@@ -5203,14 +5489,17 @@
       <c r="J93" s="1">
         <v>45428</v>
       </c>
-      <c r="K93" s="7">
-        <v>5</v>
-      </c>
-      <c r="M93" t="s">
+      <c r="K93" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L93" s="7">
+        <v>5</v>
+      </c>
+      <c r="N93" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:14">
       <c r="A94" t="s">
         <v>10</v>
       </c>
@@ -5241,14 +5530,17 @@
       <c r="J94" s="1">
         <v>45428</v>
       </c>
-      <c r="K94" s="2">
-        <v>5</v>
-      </c>
-      <c r="M94" t="s">
+      <c r="K94" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L94" s="2">
+        <v>5</v>
+      </c>
+      <c r="N94" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:14">
       <c r="A95" t="s">
         <v>10</v>
       </c>
@@ -5279,14 +5571,17 @@
       <c r="J95" s="1">
         <v>45428</v>
       </c>
-      <c r="K95" s="2">
-        <v>5</v>
-      </c>
-      <c r="M95" t="s">
+      <c r="K95" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L95" s="2">
+        <v>5</v>
+      </c>
+      <c r="N95" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:14">
       <c r="A96" t="s">
         <v>10</v>
       </c>
@@ -5317,14 +5612,17 @@
       <c r="J96" s="1">
         <v>45428</v>
       </c>
-      <c r="K96" s="7">
-        <v>5</v>
-      </c>
-      <c r="M96" t="s">
+      <c r="K96" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L96" s="7">
+        <v>5</v>
+      </c>
+      <c r="N96" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:14">
       <c r="A97" t="s">
         <v>10</v>
       </c>
@@ -5355,14 +5653,17 @@
       <c r="J97" s="1">
         <v>45428</v>
       </c>
-      <c r="K97" s="7">
-        <v>5</v>
-      </c>
-      <c r="M97" t="s">
+      <c r="K97" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L97" s="7">
+        <v>5</v>
+      </c>
+      <c r="N97" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:14">
       <c r="A98" t="s">
         <v>10</v>
       </c>
@@ -5393,14 +5694,17 @@
       <c r="J98" s="1">
         <v>45428</v>
       </c>
-      <c r="K98" s="2">
-        <v>5</v>
-      </c>
-      <c r="M98" t="s">
+      <c r="K98" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L98" s="2">
+        <v>5</v>
+      </c>
+      <c r="N98" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:14">
       <c r="A99" t="s">
         <v>10</v>
       </c>
@@ -5431,14 +5735,17 @@
       <c r="J99" s="1">
         <v>45428</v>
       </c>
-      <c r="K99" s="2">
-        <v>5</v>
-      </c>
-      <c r="M99" t="s">
+      <c r="K99" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L99" s="2">
+        <v>5</v>
+      </c>
+      <c r="N99" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:14">
       <c r="A100" t="s">
         <v>10</v>
       </c>
@@ -5469,14 +5776,17 @@
       <c r="J100" s="1">
         <v>45428</v>
       </c>
-      <c r="K100" s="7">
-        <v>5</v>
-      </c>
-      <c r="M100" t="s">
+      <c r="K100" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L100" s="7">
+        <v>5</v>
+      </c>
+      <c r="N100" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:14">
       <c r="A101" t="s">
         <v>10</v>
       </c>
@@ -5507,14 +5817,17 @@
       <c r="J101" s="1">
         <v>45428</v>
       </c>
-      <c r="K101" s="7">
-        <v>5</v>
-      </c>
-      <c r="M101" t="s">
+      <c r="K101" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L101" s="7">
+        <v>5</v>
+      </c>
+      <c r="N101" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:14">
       <c r="A102" t="s">
         <v>10</v>
       </c>
@@ -5545,14 +5858,17 @@
       <c r="J102" s="1">
         <v>45428</v>
       </c>
-      <c r="K102" s="2">
-        <v>5</v>
-      </c>
-      <c r="M102" t="s">
+      <c r="K102" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L102" s="2">
+        <v>5</v>
+      </c>
+      <c r="N102" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:14">
       <c r="A103" t="s">
         <v>10</v>
       </c>
@@ -5583,14 +5899,17 @@
       <c r="J103" s="1">
         <v>45432</v>
       </c>
-      <c r="K103" s="2">
-        <v>5</v>
-      </c>
-      <c r="M103" t="s">
+      <c r="K103" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L103" s="2">
+        <v>5</v>
+      </c>
+      <c r="N103" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:14">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -5621,14 +5940,17 @@
       <c r="J104" s="1">
         <v>45428</v>
       </c>
-      <c r="K104" s="7">
-        <v>5</v>
-      </c>
-      <c r="M104" t="s">
+      <c r="K104" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L104" s="7">
+        <v>5</v>
+      </c>
+      <c r="N104" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:14">
       <c r="A105" t="s">
         <v>10</v>
       </c>
@@ -5659,14 +5981,17 @@
       <c r="J105" s="1">
         <v>45428</v>
       </c>
-      <c r="K105" s="7">
-        <v>5</v>
-      </c>
-      <c r="M105" t="s">
+      <c r="K105" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L105" s="7">
+        <v>5</v>
+      </c>
+      <c r="N105" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:14">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -5697,14 +6022,17 @@
       <c r="J106" s="1">
         <v>45428</v>
       </c>
-      <c r="K106" s="2">
-        <v>5</v>
-      </c>
-      <c r="M106" t="s">
+      <c r="K106" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L106" s="2">
+        <v>5</v>
+      </c>
+      <c r="N106" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:14">
       <c r="A107" t="s">
         <v>10</v>
       </c>
@@ -5735,14 +6063,17 @@
       <c r="J107" s="1">
         <v>45428</v>
       </c>
-      <c r="K107" s="2">
-        <v>5</v>
-      </c>
-      <c r="M107" t="s">
+      <c r="K107" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L107" s="2">
+        <v>5</v>
+      </c>
+      <c r="N107" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:14">
       <c r="A108" t="s">
         <v>10</v>
       </c>
@@ -5773,14 +6104,17 @@
       <c r="J108" s="1">
         <v>45428</v>
       </c>
-      <c r="K108" s="7">
-        <v>5</v>
-      </c>
-      <c r="M108" t="s">
+      <c r="K108" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L108" s="7">
+        <v>5</v>
+      </c>
+      <c r="N108" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:14">
       <c r="A109" t="s">
         <v>10</v>
       </c>
@@ -5811,14 +6145,17 @@
       <c r="J109" s="1">
         <v>45428</v>
       </c>
-      <c r="K109" s="7">
-        <v>5</v>
-      </c>
-      <c r="M109" t="s">
+      <c r="K109" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L109" s="7">
+        <v>5</v>
+      </c>
+      <c r="N109" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:14">
       <c r="A110" t="s">
         <v>10</v>
       </c>
@@ -5849,14 +6186,17 @@
       <c r="J110" s="1">
         <v>45428</v>
       </c>
-      <c r="K110" s="2">
-        <v>5</v>
-      </c>
-      <c r="M110" t="s">
+      <c r="K110" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L110" s="2">
+        <v>5</v>
+      </c>
+      <c r="N110" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:14">
       <c r="A111" t="s">
         <v>10</v>
       </c>
@@ -5887,14 +6227,17 @@
       <c r="J111" s="1">
         <v>45428</v>
       </c>
-      <c r="K111" s="7">
-        <v>5</v>
-      </c>
-      <c r="M111" t="s">
+      <c r="K111" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L111" s="7">
+        <v>5</v>
+      </c>
+      <c r="N111" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:14">
       <c r="A112" t="s">
         <v>10</v>
       </c>
@@ -5925,15 +6268,18 @@
       <c r="J112" s="1">
         <v>45428</v>
       </c>
-      <c r="K112" s="2">
-        <v>5</v>
-      </c>
-      <c r="L112" s="1"/>
-      <c r="M112" t="s">
+      <c r="K112" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L112" s="2">
+        <v>5</v>
+      </c>
+      <c r="M112" s="1"/>
+      <c r="N112" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:14">
       <c r="A113" t="s">
         <v>10</v>
       </c>
@@ -5964,15 +6310,18 @@
       <c r="J113" s="1">
         <v>45428</v>
       </c>
-      <c r="K113" s="7">
-        <v>5</v>
-      </c>
-      <c r="L113" s="1"/>
-      <c r="M113" t="s">
+      <c r="K113" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L113" s="7">
+        <v>5</v>
+      </c>
+      <c r="M113" s="1"/>
+      <c r="N113" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:14">
       <c r="A114" t="s">
         <v>10</v>
       </c>
@@ -6003,15 +6352,18 @@
       <c r="J114" s="1">
         <v>45428</v>
       </c>
-      <c r="K114" s="7">
-        <v>5</v>
-      </c>
-      <c r="L114" s="1"/>
-      <c r="M114" t="s">
+      <c r="K114" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L114" s="7">
+        <v>5</v>
+      </c>
+      <c r="M114" s="1"/>
+      <c r="N114" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:14">
       <c r="A115" t="s">
         <v>10</v>
       </c>
@@ -6042,15 +6394,18 @@
       <c r="J115" s="1">
         <v>45428</v>
       </c>
-      <c r="K115" s="2">
-        <v>5</v>
-      </c>
-      <c r="L115" s="1"/>
-      <c r="M115" t="s">
+      <c r="K115" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L115" s="2">
+        <v>5</v>
+      </c>
+      <c r="M115" s="1"/>
+      <c r="N115" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:14">
       <c r="A116" t="s">
         <v>10</v>
       </c>
@@ -6081,15 +6436,18 @@
       <c r="J116" s="1">
         <v>45428</v>
       </c>
-      <c r="K116" s="2">
-        <v>5</v>
-      </c>
-      <c r="L116" s="1"/>
-      <c r="M116" t="s">
+      <c r="K116" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L116" s="2">
+        <v>5</v>
+      </c>
+      <c r="M116" s="1"/>
+      <c r="N116" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="117" spans="1:13" customFormat="1">
+    <row r="117" spans="1:14" customFormat="1">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -6116,17 +6474,20 @@
         <v>44617</v>
       </c>
       <c r="J117" s="2"/>
-      <c r="K117" s="2">
+      <c r="K117" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L117" s="2">
         <v>25</v>
       </c>
-      <c r="L117" s="1">
+      <c r="M117" s="1">
         <v>45820</v>
       </c>
-      <c r="M117" t="s">
+      <c r="N117" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:14">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -6151,17 +6512,20 @@
       <c r="I118" s="1">
         <v>44617</v>
       </c>
-      <c r="K118" s="2">
+      <c r="K118" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L118" s="2">
         <v>25</v>
       </c>
-      <c r="L118" s="1">
+      <c r="M118" s="1">
         <v>45820</v>
       </c>
-      <c r="M118" t="s">
+      <c r="N118" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:14">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -6186,17 +6550,20 @@
       <c r="I119" s="1">
         <v>44617</v>
       </c>
-      <c r="K119" s="2">
+      <c r="K119" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L119" s="2">
         <v>25</v>
       </c>
-      <c r="L119" s="1">
+      <c r="M119" s="1">
         <v>45820</v>
       </c>
-      <c r="M119" t="s">
+      <c r="N119" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:14">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -6221,17 +6588,20 @@
       <c r="I120" s="1">
         <v>42990</v>
       </c>
-      <c r="K120" s="2">
+      <c r="K120" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L120" s="2">
         <v>25</v>
       </c>
-      <c r="L120" s="1">
+      <c r="M120" s="1">
         <v>45820</v>
       </c>
-      <c r="M120" t="s">
+      <c r="N120" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:14">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -6256,17 +6626,20 @@
       <c r="I121" s="1">
         <v>42990</v>
       </c>
-      <c r="K121" s="2">
+      <c r="K121" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L121" s="2">
         <v>25</v>
       </c>
-      <c r="L121" s="1">
+      <c r="M121" s="1">
         <v>45820</v>
       </c>
-      <c r="M121" t="s">
+      <c r="N121" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:14">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -6291,17 +6664,20 @@
       <c r="I122" s="1">
         <v>44617</v>
       </c>
-      <c r="K122" s="2">
+      <c r="K122" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L122" s="2">
         <v>25</v>
       </c>
-      <c r="L122" s="1">
+      <c r="M122" s="1">
         <v>45820</v>
       </c>
-      <c r="M122" t="s">
+      <c r="N122" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:14">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -6326,17 +6702,20 @@
       <c r="I123" s="1">
         <v>42990</v>
       </c>
-      <c r="K123" s="2">
+      <c r="K123" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L123" s="2">
         <v>25</v>
       </c>
-      <c r="L123" s="1">
+      <c r="M123" s="1">
         <v>45820</v>
       </c>
-      <c r="M123" t="s">
+      <c r="N123" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:14">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -6362,17 +6741,20 @@
       <c r="I124" s="1">
         <v>42191</v>
       </c>
-      <c r="K124" s="2">
+      <c r="K124" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L124" s="2">
         <v>25</v>
       </c>
-      <c r="L124" s="1">
+      <c r="M124" s="1">
         <v>45820</v>
       </c>
-      <c r="M124" t="s">
+      <c r="N124" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:14">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -6397,17 +6779,20 @@
       <c r="I125" s="1">
         <v>45820</v>
       </c>
-      <c r="K125" s="7">
-        <v>5</v>
-      </c>
-      <c r="L125" s="1">
+      <c r="K125" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L125" s="7">
+        <v>5</v>
+      </c>
+      <c r="M125" s="1">
         <v>45820</v>
       </c>
-      <c r="M125" t="s">
+      <c r="N125" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:14">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -6432,17 +6817,20 @@
       <c r="I126" s="1">
         <v>45820</v>
       </c>
-      <c r="K126" s="2">
-        <v>5</v>
-      </c>
-      <c r="L126" s="1">
+      <c r="K126" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L126" s="2">
+        <v>5</v>
+      </c>
+      <c r="M126" s="1">
         <v>45820</v>
       </c>
-      <c r="M126" t="s">
+      <c r="N126" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:14">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -6467,17 +6855,20 @@
       <c r="I127" s="1">
         <v>44734</v>
       </c>
-      <c r="K127" s="2">
-        <v>5</v>
-      </c>
-      <c r="L127" s="1">
+      <c r="K127" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L127" s="2">
+        <v>5</v>
+      </c>
+      <c r="M127" s="1">
         <v>45820</v>
       </c>
-      <c r="M127" t="s">
+      <c r="N127" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="128" spans="1:13" customFormat="1">
+    <row r="128" spans="1:14" customFormat="1">
       <c r="A128" t="s">
         <v>12</v>
       </c>
@@ -6506,17 +6897,20 @@
         <v>44349</v>
       </c>
       <c r="J128" s="2"/>
-      <c r="K128" s="2">
+      <c r="K128" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L128" s="2">
         <v>15</v>
       </c>
-      <c r="L128" s="1">
+      <c r="M128" s="1">
         <v>45656</v>
       </c>
-      <c r="M128" t="s">
+      <c r="N128" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:14">
       <c r="A129" t="s">
         <v>12</v>
       </c>
@@ -6544,17 +6938,20 @@
       <c r="I129" s="1">
         <v>44349</v>
       </c>
-      <c r="K129" s="2">
+      <c r="K129" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L129" s="2">
         <v>15</v>
       </c>
-      <c r="L129" s="1">
+      <c r="M129" s="1">
         <v>45656</v>
       </c>
-      <c r="M129" t="s">
+      <c r="N129" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:14">
       <c r="A130" t="s">
         <v>12</v>
       </c>
@@ -6582,17 +6979,20 @@
       <c r="I130" s="1">
         <v>44349</v>
       </c>
-      <c r="K130" s="2">
+      <c r="K130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L130" s="2">
         <v>15</v>
       </c>
-      <c r="L130" s="1">
+      <c r="M130" s="1">
         <v>45656</v>
       </c>
-      <c r="M130" t="s">
+      <c r="N130" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:14">
       <c r="A131" t="s">
         <v>12</v>
       </c>
@@ -6620,17 +7020,20 @@
       <c r="I131" s="1">
         <v>44349</v>
       </c>
-      <c r="K131" s="2">
+      <c r="K131" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L131" s="2">
         <v>15</v>
       </c>
-      <c r="L131" s="1">
+      <c r="M131" s="1">
         <v>45656</v>
       </c>
-      <c r="M131" t="s">
+      <c r="N131" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:14">
       <c r="A132" t="s">
         <v>12</v>
       </c>
@@ -6658,17 +7061,20 @@
       <c r="I132" s="1">
         <v>44349</v>
       </c>
-      <c r="K132" s="2">
+      <c r="K132" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L132" s="2">
         <v>15</v>
       </c>
-      <c r="L132" s="1">
+      <c r="M132" s="1">
         <v>45656</v>
       </c>
-      <c r="M132" t="s">
+      <c r="N132" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="133" spans="1:13" customFormat="1">
+    <row r="133" spans="1:14" customFormat="1">
       <c r="A133" t="s">
         <v>12</v>
       </c>
@@ -6697,17 +7103,20 @@
         <v>44349</v>
       </c>
       <c r="J133" s="2"/>
-      <c r="K133" s="2">
+      <c r="K133" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L133" s="2">
         <v>15</v>
       </c>
-      <c r="L133" s="1">
+      <c r="M133" s="1">
         <v>45656</v>
       </c>
-      <c r="M133" t="s">
+      <c r="N133" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:14">
       <c r="A134" t="s">
         <v>12</v>
       </c>
@@ -6735,17 +7144,20 @@
       <c r="I134" s="1">
         <v>44349</v>
       </c>
-      <c r="K134" s="2">
+      <c r="K134" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L134" s="2">
         <v>15</v>
       </c>
-      <c r="L134" s="1">
+      <c r="M134" s="1">
         <v>45656</v>
       </c>
-      <c r="M134" t="s">
+      <c r="N134" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:14">
       <c r="A135" t="s">
         <v>12</v>
       </c>
@@ -6773,17 +7185,20 @@
       <c r="I135" s="1">
         <v>44349</v>
       </c>
-      <c r="K135" s="2">
+      <c r="K135" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L135" s="2">
         <v>15</v>
       </c>
-      <c r="L135" s="1">
+      <c r="M135" s="1">
         <v>45656</v>
       </c>
-      <c r="M135" t="s">
+      <c r="N135" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:14">
       <c r="A136" t="s">
         <v>12</v>
       </c>
@@ -6811,17 +7226,20 @@
       <c r="I136" s="1">
         <v>44349</v>
       </c>
-      <c r="K136" s="2">
+      <c r="K136" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L136" s="2">
         <v>15</v>
       </c>
-      <c r="L136" s="1">
+      <c r="M136" s="1">
         <v>45656</v>
       </c>
-      <c r="M136" t="s">
+      <c r="N136" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:14">
       <c r="A137" t="s">
         <v>12</v>
       </c>
@@ -6849,17 +7267,20 @@
       <c r="I137" s="1">
         <v>44349</v>
       </c>
-      <c r="K137" s="2">
+      <c r="K137" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L137" s="2">
         <v>15</v>
       </c>
-      <c r="L137" s="1">
+      <c r="M137" s="1">
         <v>45656</v>
       </c>
-      <c r="M137" t="s">
+      <c r="N137" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="138" spans="1:13" customFormat="1">
+    <row r="138" spans="1:14" customFormat="1">
       <c r="A138" t="s">
         <v>12</v>
       </c>
@@ -6888,17 +7309,20 @@
         <v>46013</v>
       </c>
       <c r="J138" s="2"/>
-      <c r="K138" s="2">
+      <c r="K138" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L138" s="2">
         <v>15</v>
       </c>
-      <c r="L138" s="1">
+      <c r="M138" s="1">
         <v>45656</v>
       </c>
-      <c r="M138" t="s">
+      <c r="N138" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:14">
       <c r="A139" t="s">
         <v>12</v>
       </c>
@@ -6926,17 +7350,20 @@
       <c r="I139" s="1">
         <v>45656</v>
       </c>
-      <c r="K139" s="2">
+      <c r="K139" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L139" s="2">
         <v>25</v>
       </c>
-      <c r="L139" s="1">
+      <c r="M139" s="1">
         <v>45656</v>
       </c>
-      <c r="M139" t="s">
+      <c r="N139" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:14">
       <c r="A140" t="s">
         <v>12</v>
       </c>
@@ -6964,17 +7391,20 @@
       <c r="I140" s="1">
         <v>44349</v>
       </c>
-      <c r="K140" s="2">
+      <c r="K140" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L140" s="2">
         <v>25</v>
       </c>
-      <c r="L140" s="1">
+      <c r="M140" s="1">
         <v>45656</v>
       </c>
-      <c r="M140" t="s">
+      <c r="N140" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:14">
       <c r="A141" t="s">
         <v>12</v>
       </c>
@@ -7002,17 +7432,20 @@
       <c r="I141" s="1">
         <v>44349</v>
       </c>
-      <c r="K141" s="2">
+      <c r="K141" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L141" s="2">
         <v>25</v>
       </c>
-      <c r="L141" s="1">
+      <c r="M141" s="1">
         <v>45656</v>
       </c>
-      <c r="M141" t="s">
+      <c r="N141" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:14">
       <c r="A142" t="s">
         <v>12</v>
       </c>
@@ -7040,17 +7473,20 @@
       <c r="I142" s="1">
         <v>44349</v>
       </c>
-      <c r="K142" s="2">
+      <c r="K142" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L142" s="2">
         <v>25</v>
       </c>
-      <c r="L142" s="1">
+      <c r="M142" s="1">
         <v>45656</v>
       </c>
-      <c r="M142" t="s">
+      <c r="N142" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="143" spans="1:13" customFormat="1">
+    <row r="143" spans="1:14" customFormat="1">
       <c r="A143" t="s">
         <v>12</v>
       </c>
@@ -7079,17 +7515,20 @@
         <v>44349</v>
       </c>
       <c r="J143" s="2"/>
-      <c r="K143" s="2">
+      <c r="K143" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L143" s="2">
         <v>25</v>
       </c>
-      <c r="L143" s="1">
+      <c r="M143" s="1">
         <v>45656</v>
       </c>
-      <c r="M143" t="s">
+      <c r="N143" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:14">
       <c r="A144" t="s">
         <v>12</v>
       </c>
@@ -7117,17 +7556,20 @@
       <c r="I144" s="1">
         <v>44349</v>
       </c>
-      <c r="K144" s="2">
+      <c r="K144" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L144" s="2">
         <v>25</v>
       </c>
-      <c r="L144" s="1">
+      <c r="M144" s="1">
         <v>45656</v>
       </c>
-      <c r="M144" t="s">
+      <c r="N144" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="145" spans="1:13">
+    <row r="145" spans="1:14">
       <c r="A145" t="s">
         <v>12</v>
       </c>
@@ -7155,17 +7597,20 @@
       <c r="I145" s="1">
         <v>44349</v>
       </c>
-      <c r="K145" s="2">
+      <c r="K145" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L145" s="2">
         <v>25</v>
       </c>
-      <c r="L145" s="1">
+      <c r="M145" s="1">
         <v>45656</v>
       </c>
-      <c r="M145" t="s">
+      <c r="N145" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:14">
       <c r="A146" t="s">
         <v>12</v>
       </c>
@@ -7193,17 +7638,20 @@
       <c r="I146" s="1">
         <v>44349</v>
       </c>
-      <c r="K146" s="2">
+      <c r="K146" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L146" s="2">
         <v>25</v>
       </c>
-      <c r="L146" s="1">
+      <c r="M146" s="1">
         <v>45656</v>
       </c>
-      <c r="M146" t="s">
+      <c r="N146" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:14">
       <c r="A147" t="s">
         <v>12</v>
       </c>
@@ -7231,17 +7679,20 @@
       <c r="I147" s="1">
         <v>44349</v>
       </c>
-      <c r="K147" s="2">
+      <c r="K147" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L147" s="2">
         <v>25</v>
       </c>
-      <c r="L147" s="1">
+      <c r="M147" s="1">
         <v>45656</v>
       </c>
-      <c r="M147" t="s">
+      <c r="N147" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="148" spans="1:13" customFormat="1">
+    <row r="148" spans="1:14" customFormat="1">
       <c r="A148" t="s">
         <v>12</v>
       </c>
@@ -7270,17 +7721,20 @@
         <v>44349</v>
       </c>
       <c r="J148" s="2"/>
-      <c r="K148" s="2">
+      <c r="K148" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L148" s="2">
         <v>25</v>
       </c>
-      <c r="L148" s="1">
+      <c r="M148" s="1">
         <v>45656</v>
       </c>
-      <c r="M148" t="s">
+      <c r="N148" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="149" spans="1:13">
+    <row r="149" spans="1:14">
       <c r="A149" t="s">
         <v>12</v>
       </c>
@@ -7308,17 +7762,20 @@
       <c r="I149" s="1">
         <v>44349</v>
       </c>
-      <c r="K149" s="2">
+      <c r="K149" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L149" s="2">
         <v>25</v>
       </c>
-      <c r="L149" s="1">
+      <c r="M149" s="1">
         <v>45656</v>
       </c>
-      <c r="M149" t="s">
+      <c r="N149" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:14">
       <c r="A150" t="s">
         <v>12</v>
       </c>
@@ -7346,17 +7803,20 @@
       <c r="I150" s="1">
         <v>44349</v>
       </c>
-      <c r="K150" s="7">
-        <v>5</v>
-      </c>
-      <c r="L150" s="1">
+      <c r="K150" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L150" s="7">
+        <v>5</v>
+      </c>
+      <c r="M150" s="1">
         <v>45656</v>
       </c>
-      <c r="M150" t="s">
+      <c r="N150" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:14">
       <c r="A151" t="s">
         <v>12</v>
       </c>
@@ -7384,17 +7844,20 @@
       <c r="I151" s="1">
         <v>44349</v>
       </c>
-      <c r="K151" s="2">
-        <v>5</v>
-      </c>
-      <c r="L151" s="1">
+      <c r="K151" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L151" s="2">
+        <v>5</v>
+      </c>
+      <c r="M151" s="1">
         <v>45656</v>
       </c>
-      <c r="M151" t="s">
+      <c r="N151" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:14">
       <c r="A152" t="s">
         <v>12</v>
       </c>
@@ -7422,17 +7885,20 @@
       <c r="I152" s="1">
         <v>44349</v>
       </c>
-      <c r="K152" s="2">
-        <v>5</v>
-      </c>
-      <c r="L152" s="1">
+      <c r="K152" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L152" s="2">
+        <v>5</v>
+      </c>
+      <c r="M152" s="1">
         <v>45656</v>
       </c>
-      <c r="M152" t="s">
+      <c r="N152" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="153" spans="1:13" customFormat="1">
+    <row r="153" spans="1:14" customFormat="1">
       <c r="A153" t="s">
         <v>12</v>
       </c>
@@ -7461,17 +7927,20 @@
         <v>44349</v>
       </c>
       <c r="J153" s="2"/>
-      <c r="K153" s="7">
-        <v>5</v>
-      </c>
-      <c r="L153" s="1">
+      <c r="K153" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L153" s="7">
+        <v>5</v>
+      </c>
+      <c r="M153" s="1">
         <v>45656</v>
       </c>
-      <c r="M153" t="s">
+      <c r="N153" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="154" spans="1:13">
+    <row r="154" spans="1:14">
       <c r="A154" t="s">
         <v>12</v>
       </c>
@@ -7499,17 +7968,20 @@
       <c r="I154" s="1">
         <v>44176</v>
       </c>
-      <c r="K154" s="7">
-        <v>5</v>
-      </c>
-      <c r="L154" s="1">
+      <c r="K154" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L154" s="7">
+        <v>5</v>
+      </c>
+      <c r="M154" s="1">
         <v>45656</v>
       </c>
-      <c r="M154" t="s">
+      <c r="N154" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="155" spans="1:13">
+    <row r="155" spans="1:14">
       <c r="A155" t="s">
         <v>12</v>
       </c>
@@ -7537,17 +8009,20 @@
       <c r="I155" s="1">
         <v>44349</v>
       </c>
-      <c r="K155" s="2">
-        <v>5</v>
-      </c>
-      <c r="L155" s="1">
+      <c r="K155" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L155" s="2">
+        <v>5</v>
+      </c>
+      <c r="M155" s="1">
         <v>45656</v>
       </c>
-      <c r="M155" t="s">
+      <c r="N155" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:14">
       <c r="A156" t="s">
         <v>12</v>
       </c>
@@ -7575,17 +8050,20 @@
       <c r="I156" s="1">
         <v>44349</v>
       </c>
-      <c r="K156" s="2">
-        <v>5</v>
-      </c>
-      <c r="L156" s="1">
+      <c r="K156" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L156" s="2">
+        <v>5</v>
+      </c>
+      <c r="M156" s="1">
         <v>45656</v>
       </c>
-      <c r="M156" t="s">
+      <c r="N156" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="157" spans="1:13">
+    <row r="157" spans="1:14">
       <c r="A157" t="s">
         <v>12</v>
       </c>
@@ -7613,17 +8091,20 @@
       <c r="I157" s="1">
         <v>44349</v>
       </c>
-      <c r="K157" s="7">
-        <v>5</v>
-      </c>
-      <c r="L157" s="1">
+      <c r="K157" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L157" s="7">
+        <v>5</v>
+      </c>
+      <c r="M157" s="1">
         <v>45656</v>
       </c>
-      <c r="M157" t="s">
+      <c r="N157" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="158" spans="1:13" customFormat="1">
+    <row r="158" spans="1:14" customFormat="1">
       <c r="A158" t="s">
         <v>12</v>
       </c>
@@ -7654,17 +8135,20 @@
       <c r="J158" s="1">
         <v>45539</v>
       </c>
-      <c r="K158" s="7">
-        <v>5</v>
-      </c>
-      <c r="L158" s="1">
+      <c r="K158" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L158" s="7">
+        <v>5</v>
+      </c>
+      <c r="M158" s="1">
         <v>45656</v>
       </c>
-      <c r="M158" t="s">
+      <c r="N158" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="159" spans="1:13" customFormat="1">
+    <row r="159" spans="1:14" customFormat="1">
       <c r="A159" t="s">
         <v>12</v>
       </c>
@@ -7693,17 +8177,20 @@
         <v>44349</v>
       </c>
       <c r="J159" s="2"/>
-      <c r="K159" s="2">
-        <v>5</v>
-      </c>
-      <c r="L159" s="1">
+      <c r="K159" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L159" s="2">
+        <v>5</v>
+      </c>
+      <c r="M159" s="1">
         <v>45656</v>
       </c>
-      <c r="M159" t="s">
+      <c r="N159" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="160" spans="1:13" customFormat="1">
+    <row r="160" spans="1:14" customFormat="1">
       <c r="A160" t="s">
         <v>13</v>
       </c>
@@ -7732,17 +8219,20 @@
         <v>44426</v>
       </c>
       <c r="J160" s="2"/>
-      <c r="K160" s="2">
-        <v>5</v>
-      </c>
-      <c r="L160" s="1">
+      <c r="K160" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L160" s="2">
+        <v>5</v>
+      </c>
+      <c r="M160" s="1">
         <v>45821</v>
       </c>
-      <c r="M160" t="s">
+      <c r="N160" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161" spans="1:14">
       <c r="A161" t="s">
         <v>13</v>
       </c>
@@ -7770,17 +8260,20 @@
       <c r="I161" s="1">
         <v>44426</v>
       </c>
-      <c r="K161" s="2">
-        <v>5</v>
-      </c>
-      <c r="L161" s="1">
+      <c r="K161" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L161" s="2">
+        <v>5</v>
+      </c>
+      <c r="M161" s="1">
         <v>45821</v>
       </c>
-      <c r="M161" t="s">
+      <c r="N161" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162" spans="1:14">
       <c r="A162" t="s">
         <v>13</v>
       </c>
@@ -7811,17 +8304,20 @@
       <c r="J162" s="1">
         <v>44925</v>
       </c>
-      <c r="K162" s="2">
-        <v>5</v>
-      </c>
-      <c r="L162" s="1">
+      <c r="K162" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L162" s="2">
+        <v>5</v>
+      </c>
+      <c r="M162" s="1">
         <v>45821</v>
       </c>
-      <c r="M162" t="s">
+      <c r="N162" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="163" spans="1:13" customFormat="1">
+    <row r="163" spans="1:14" customFormat="1">
       <c r="A163" t="s">
         <v>13</v>
       </c>
@@ -7852,17 +8348,20 @@
       <c r="J163" s="1">
         <v>45824</v>
       </c>
-      <c r="K163" s="2">
-        <v>5</v>
-      </c>
-      <c r="L163" s="1">
+      <c r="K163" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L163" s="2">
+        <v>5</v>
+      </c>
+      <c r="M163" s="1">
         <v>45821</v>
       </c>
-      <c r="M163" t="s">
+      <c r="N163" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" spans="1:14">
       <c r="A164" t="s">
         <v>13</v>
       </c>
@@ -7890,17 +8389,20 @@
       <c r="I164" s="1">
         <v>44923</v>
       </c>
-      <c r="K164" s="7">
-        <v>5</v>
-      </c>
-      <c r="L164" s="1">
+      <c r="K164" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L164" s="7">
+        <v>5</v>
+      </c>
+      <c r="M164" s="1">
         <v>45821</v>
       </c>
-      <c r="M164" t="s">
+      <c r="N164" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:14">
       <c r="A165" t="s">
         <v>13</v>
       </c>
@@ -7928,17 +8430,20 @@
       <c r="I165" s="1">
         <v>45821</v>
       </c>
-      <c r="K165" s="7">
-        <v>5</v>
-      </c>
-      <c r="L165" s="1">
+      <c r="K165" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L165" s="7">
+        <v>5</v>
+      </c>
+      <c r="M165" s="1">
         <v>45821</v>
       </c>
-      <c r="M165" t="s">
+      <c r="N165" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:14">
       <c r="A166" t="s">
         <v>13</v>
       </c>
@@ -7969,17 +8474,20 @@
       <c r="J166" s="1">
         <v>44966</v>
       </c>
-      <c r="K166" s="2">
-        <v>5</v>
-      </c>
-      <c r="L166" s="1">
+      <c r="K166" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L166" s="2">
+        <v>5</v>
+      </c>
+      <c r="M166" s="1">
         <v>45821</v>
       </c>
-      <c r="M166" t="s">
+      <c r="N166" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:14">
       <c r="A167" t="s">
         <v>13</v>
       </c>
@@ -8010,17 +8518,20 @@
       <c r="J167" s="1">
         <v>45821</v>
       </c>
-      <c r="K167" s="2">
-        <v>5</v>
-      </c>
-      <c r="L167" s="1">
+      <c r="K167" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L167" s="2">
+        <v>5</v>
+      </c>
+      <c r="M167" s="1">
         <v>45821</v>
       </c>
-      <c r="M167" t="s">
+      <c r="N167" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="168" spans="1:13" customFormat="1">
+    <row r="168" spans="1:14" customFormat="1">
       <c r="A168" t="s">
         <v>13</v>
       </c>
@@ -8049,17 +8560,20 @@
         <v>44194</v>
       </c>
       <c r="J168" s="2"/>
-      <c r="K168" s="7">
-        <v>5</v>
-      </c>
-      <c r="L168" s="1">
+      <c r="K168" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L168" s="7">
+        <v>5</v>
+      </c>
+      <c r="M168" s="1">
         <v>45821</v>
       </c>
-      <c r="M168" t="s">
+      <c r="N168" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:14">
       <c r="A169" t="s">
         <v>13</v>
       </c>
@@ -8087,17 +8601,20 @@
       <c r="I169" s="1">
         <v>44925</v>
       </c>
-      <c r="K169" s="7">
-        <v>5</v>
-      </c>
-      <c r="L169" s="1">
+      <c r="K169" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L169" s="7">
+        <v>5</v>
+      </c>
+      <c r="M169" s="1">
         <v>45821</v>
       </c>
-      <c r="M169" t="s">
+      <c r="N169" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:14">
       <c r="A170" t="s">
         <v>13</v>
       </c>
@@ -8125,21 +8642,24 @@
       <c r="I170" s="1">
         <v>45821</v>
       </c>
-      <c r="K170" s="2">
-        <v>5</v>
-      </c>
-      <c r="L170" s="1">
+      <c r="K170" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L170" s="2">
+        <v>5</v>
+      </c>
+      <c r="M170" s="1">
         <v>45821</v>
       </c>
-      <c r="M170" t="s">
+      <c r="N170" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:14">
       <c r="F171"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M170">
+  <autoFilter ref="A1:N170">
     <sortState ref="A2:M170">
       <sortCondition ref="A1:A170"/>
     </sortState>

--- a/upload/informacoes_classificadas_desclassificadas.xlsx
+++ b/upload/informacoes_classificadas_desclassificadas.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="6420"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -1220,9 +1220,6 @@
     <t>prazo_classificacao_anos</t>
   </si>
   <si>
-    <t>Decreto 46.983/2016; Decreto 45.357/2010; Art. 31, Decreto 45.969/12</t>
-  </si>
-  <si>
     <t>tipo_classificacao</t>
   </si>
   <si>
@@ -1230,6 +1227,9 @@
   </si>
   <si>
     <t>Desclassificada</t>
+  </si>
+  <si>
+    <t>Art. 31, Decreto 45.969/12</t>
   </si>
 </sst>
 </file>
@@ -1729,7 +1729,7 @@
         <v>314</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>350</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L2" s="4">
         <v>10</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L3" s="4">
         <v>10</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L4" s="4">
         <v>10</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L5" s="4">
         <v>10</v>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L6" s="2">
         <v>5</v>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L7" s="2">
         <v>5</v>
@@ -2025,7 +2025,7 @@
         <v>45440</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L8" s="7">
         <v>5</v>
@@ -2069,7 +2069,7 @@
         <v>45484</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L9" s="2">
         <v>5</v>
@@ -2113,7 +2113,7 @@
         <v>45567</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L10" s="2">
         <v>5</v>
@@ -2157,7 +2157,7 @@
         <v>45580</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L11" s="7">
         <v>5</v>
@@ -2201,7 +2201,7 @@
         <v>45774</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L12" s="7">
         <v>5</v>
@@ -2245,7 +2245,7 @@
         <v>45771</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L13" s="2">
         <v>5</v>
@@ -2289,7 +2289,7 @@
         <v>45796</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L14" s="2">
         <v>5</v>
@@ -2333,7 +2333,7 @@
         <v>45797</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L15" s="7">
         <v>5</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L16" s="7">
         <v>5</v>
@@ -2416,7 +2416,7 @@
         <v>44552</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L17" s="7">
         <v>5</v>
@@ -2457,7 +2457,7 @@
         <v>44552</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L18" s="7">
         <v>5</v>
@@ -2498,7 +2498,7 @@
         <v>44780</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L19" s="2">
         <v>5</v>
@@ -2539,7 +2539,7 @@
         <v>44780</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L20" s="2">
         <v>5</v>
@@ -2580,7 +2580,7 @@
         <v>45021</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L21" s="7">
         <v>5</v>
@@ -2621,7 +2621,7 @@
         <v>45021</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L22" s="7">
         <v>5</v>
@@ -2662,7 +2662,7 @@
         <v>45292</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L23" s="2">
         <v>5</v>
@@ -2703,7 +2703,7 @@
         <v>45292</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L24" s="2">
         <v>5</v>
@@ -2744,7 +2744,7 @@
         <v>45658</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L25" s="7">
         <v>5</v>
@@ -2785,7 +2785,7 @@
         <v>45658</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L26" s="7">
         <v>5</v>
@@ -2826,7 +2826,7 @@
         <v>44558</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L27" s="2">
         <v>5</v>
@@ -2867,7 +2867,7 @@
         <v>44925</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L28" s="2">
         <v>5</v>
@@ -2908,7 +2908,7 @@
         <v>45289</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L29" s="7">
         <v>5</v>
@@ -2949,7 +2949,7 @@
         <v>45656</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L30" s="7">
         <v>5</v>
@@ -2990,7 +2990,7 @@
         <v>44194</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L31" s="2">
         <v>5</v>
@@ -3031,7 +3031,7 @@
         <v>45925</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L32" s="2">
         <v>15</v>
@@ -3072,7 +3072,7 @@
         <v>45925</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L33" s="2">
         <v>15</v>
@@ -3113,7 +3113,7 @@
         <v>45925</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L34" s="2">
         <v>15</v>
@@ -3154,7 +3154,7 @@
         <v>45925</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L35" s="2">
         <v>15</v>
@@ -3195,7 +3195,7 @@
         <v>45916</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L36" s="2">
         <v>5</v>
@@ -3236,7 +3236,7 @@
         <v>45932</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L37" s="7">
         <v>5</v>
@@ -3277,7 +3277,7 @@
         <v>45932</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L38" s="7">
         <v>5</v>
@@ -3318,7 +3318,7 @@
         <v>45932</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L39" s="7">
         <v>5</v>
@@ -3359,7 +3359,7 @@
         <v>45923</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L40" s="7">
         <v>5</v>
@@ -3397,7 +3397,7 @@
         <v>43705</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L41" s="2">
         <v>15</v>
@@ -3435,7 +3435,7 @@
         <v>45826</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L42" s="2">
         <v>15</v>
@@ -3473,7 +3473,7 @@
         <v>43705</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L43" s="2">
         <v>15</v>
@@ -3511,7 +3511,7 @@
         <v>43705</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L44" s="2">
         <v>15</v>
@@ -3549,7 +3549,7 @@
         <v>45833</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L45" s="2">
         <v>15</v>
@@ -3587,7 +3587,7 @@
         <v>43705</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L46" s="2">
         <v>15</v>
@@ -3625,7 +3625,7 @@
         <v>43705</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L47" s="2">
         <v>15</v>
@@ -3663,7 +3663,7 @@
         <v>43705</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L48" s="2">
         <v>15</v>
@@ -3701,7 +3701,7 @@
         <v>43697</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L49" s="2">
         <v>15</v>
@@ -3730,7 +3730,7 @@
         <v>316</v>
       </c>
       <c r="G50" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="H50" s="1">
         <v>43697</v>
@@ -3739,7 +3739,7 @@
         <v>43697</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L50" s="2">
         <v>25</v>
@@ -3774,7 +3774,7 @@
         <v>43705</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L51" s="2">
         <v>25</v>
@@ -3815,7 +3815,7 @@
         <v>45303</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L52" s="2">
         <v>15</v>
@@ -3856,7 +3856,7 @@
         <v>45303</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L53" s="2">
         <v>25</v>
@@ -3897,7 +3897,7 @@
         <v>45303</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L54" s="7">
         <v>5</v>
@@ -3938,7 +3938,7 @@
         <v>45303</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L55" s="7">
         <v>5</v>
@@ -3979,7 +3979,7 @@
         <v>45303</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L56" s="2">
         <v>5</v>
@@ -4020,7 +4020,7 @@
         <v>45303</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L57" s="2">
         <v>5</v>
@@ -4061,7 +4061,7 @@
         <v>45303</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L58" s="7">
         <v>5</v>
@@ -4102,7 +4102,7 @@
         <v>45303</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L59" s="7">
         <v>5</v>
@@ -4143,7 +4143,7 @@
         <v>45303</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L60" s="2">
         <v>5</v>
@@ -4184,7 +4184,7 @@
         <v>45303</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L61" s="2">
         <v>5</v>
@@ -4225,7 +4225,7 @@
         <v>45303</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L62" s="7">
         <v>5</v>
@@ -4266,7 +4266,7 @@
         <v>45303</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L63" s="2">
         <v>5</v>
@@ -4307,7 +4307,7 @@
         <v>45303</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L64" s="7">
         <v>5</v>
@@ -4348,7 +4348,7 @@
         <v>45303</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L65" s="2">
         <v>5</v>
@@ -4389,7 +4389,7 @@
         <v>45303</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L66" s="2">
         <v>5</v>
@@ -4430,7 +4430,7 @@
         <v>45352</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L67" s="7">
         <v>5</v>
@@ -4471,7 +4471,7 @@
         <v>45352</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L68" s="7">
         <v>5</v>
@@ -4515,7 +4515,7 @@
         <v>46202</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L69" s="2">
         <v>5</v>
@@ -4559,7 +4559,7 @@
         <v>45428</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L70" s="7">
         <v>5</v>
@@ -4598,7 +4598,7 @@
         <v>45225</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L71" s="7">
         <v>5</v>
@@ -4636,7 +4636,7 @@
         <v>45225</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L72" s="2">
         <v>5</v>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="J73"/>
       <c r="K73" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L73" s="2">
         <v>5</v>
@@ -4714,7 +4714,7 @@
         <v>45230</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L74" s="2">
         <v>5</v>
@@ -4752,7 +4752,7 @@
         <v>45230</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L75" s="7">
         <v>5</v>
@@ -4793,7 +4793,7 @@
         <v>45432</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L76" s="7">
         <v>5</v>
@@ -4834,7 +4834,7 @@
         <v>45432</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L77" s="2">
         <v>5</v>
@@ -4875,7 +4875,7 @@
         <v>45428</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L78" s="2">
         <v>5</v>
@@ -4916,7 +4916,7 @@
         <v>45432</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L79" s="2">
         <v>5</v>
@@ -4957,7 +4957,7 @@
         <v>45432</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L80" s="7">
         <v>5</v>
@@ -4998,7 +4998,7 @@
         <v>45428</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L81" s="7">
         <v>5</v>
@@ -5039,7 +5039,7 @@
         <v>45428</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L82" s="2">
         <v>5</v>
@@ -5080,7 +5080,7 @@
         <v>45428</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L83" s="2">
         <v>5</v>
@@ -5121,7 +5121,7 @@
         <v>45428</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L84" s="7">
         <v>5</v>
@@ -5162,7 +5162,7 @@
         <v>45428</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L85" s="7">
         <v>5</v>
@@ -5203,7 +5203,7 @@
         <v>45428</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L86" s="2">
         <v>5</v>
@@ -5244,7 +5244,7 @@
         <v>45428</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L87" s="2">
         <v>5</v>
@@ -5285,7 +5285,7 @@
         <v>45428</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L88" s="7">
         <v>5</v>
@@ -5326,7 +5326,7 @@
         <v>45428</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L89" s="7">
         <v>5</v>
@@ -5367,7 +5367,7 @@
         <v>45428</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L90" s="2">
         <v>5</v>
@@ -5408,7 +5408,7 @@
         <v>45428</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L91" s="2">
         <v>5</v>
@@ -5449,7 +5449,7 @@
         <v>45428</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L92" s="7">
         <v>5</v>
@@ -5490,7 +5490,7 @@
         <v>45428</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L93" s="7">
         <v>5</v>
@@ -5531,7 +5531,7 @@
         <v>45428</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L94" s="2">
         <v>5</v>
@@ -5572,7 +5572,7 @@
         <v>45428</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L95" s="2">
         <v>5</v>
@@ -5613,7 +5613,7 @@
         <v>45428</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L96" s="7">
         <v>5</v>
@@ -5654,7 +5654,7 @@
         <v>45428</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L97" s="7">
         <v>5</v>
@@ -5695,7 +5695,7 @@
         <v>45428</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L98" s="2">
         <v>5</v>
@@ -5736,7 +5736,7 @@
         <v>45428</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L99" s="2">
         <v>5</v>
@@ -5777,7 +5777,7 @@
         <v>45428</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L100" s="7">
         <v>5</v>
@@ -5818,7 +5818,7 @@
         <v>45428</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L101" s="7">
         <v>5</v>
@@ -5859,7 +5859,7 @@
         <v>45428</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L102" s="2">
         <v>5</v>
@@ -5900,7 +5900,7 @@
         <v>45432</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L103" s="2">
         <v>5</v>
@@ -5941,7 +5941,7 @@
         <v>45428</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L104" s="7">
         <v>5</v>
@@ -5982,7 +5982,7 @@
         <v>45428</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L105" s="7">
         <v>5</v>
@@ -6023,7 +6023,7 @@
         <v>45428</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L106" s="2">
         <v>5</v>
@@ -6064,7 +6064,7 @@
         <v>45428</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L107" s="2">
         <v>5</v>
@@ -6105,7 +6105,7 @@
         <v>45428</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L108" s="7">
         <v>5</v>
@@ -6146,7 +6146,7 @@
         <v>45428</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L109" s="7">
         <v>5</v>
@@ -6187,7 +6187,7 @@
         <v>45428</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L110" s="2">
         <v>5</v>
@@ -6228,7 +6228,7 @@
         <v>45428</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L111" s="7">
         <v>5</v>
@@ -6269,7 +6269,7 @@
         <v>45428</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L112" s="2">
         <v>5</v>
@@ -6311,7 +6311,7 @@
         <v>45428</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L113" s="7">
         <v>5</v>
@@ -6353,7 +6353,7 @@
         <v>45428</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L114" s="7">
         <v>5</v>
@@ -6395,7 +6395,7 @@
         <v>45428</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L115" s="2">
         <v>5</v>
@@ -6437,7 +6437,7 @@
         <v>45428</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L116" s="2">
         <v>5</v>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="J117" s="2"/>
       <c r="K117" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L117" s="2">
         <v>25</v>
@@ -6513,7 +6513,7 @@
         <v>44617</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L118" s="2">
         <v>25</v>
@@ -6551,7 +6551,7 @@
         <v>44617</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L119" s="2">
         <v>25</v>
@@ -6589,7 +6589,7 @@
         <v>42990</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L120" s="2">
         <v>25</v>
@@ -6627,7 +6627,7 @@
         <v>42990</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L121" s="2">
         <v>25</v>
@@ -6665,7 +6665,7 @@
         <v>44617</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L122" s="2">
         <v>25</v>
@@ -6703,7 +6703,7 @@
         <v>42990</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L123" s="2">
         <v>25</v>
@@ -6742,7 +6742,7 @@
         <v>42191</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L124" s="2">
         <v>25</v>
@@ -6780,7 +6780,7 @@
         <v>45820</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L125" s="7">
         <v>5</v>
@@ -6818,7 +6818,7 @@
         <v>45820</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L126" s="2">
         <v>5</v>
@@ -6856,7 +6856,7 @@
         <v>44734</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L127" s="2">
         <v>5</v>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="J128" s="2"/>
       <c r="K128" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L128" s="2">
         <v>15</v>
@@ -6939,7 +6939,7 @@
         <v>44349</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L129" s="2">
         <v>15</v>
@@ -6980,7 +6980,7 @@
         <v>44349</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L130" s="2">
         <v>15</v>
@@ -7021,7 +7021,7 @@
         <v>44349</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L131" s="2">
         <v>15</v>
@@ -7062,7 +7062,7 @@
         <v>44349</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L132" s="2">
         <v>15</v>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="J133" s="2"/>
       <c r="K133" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L133" s="2">
         <v>15</v>
@@ -7145,7 +7145,7 @@
         <v>44349</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L134" s="2">
         <v>15</v>
@@ -7186,7 +7186,7 @@
         <v>44349</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L135" s="2">
         <v>15</v>
@@ -7227,7 +7227,7 @@
         <v>44349</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L136" s="2">
         <v>15</v>
@@ -7268,7 +7268,7 @@
         <v>44349</v>
       </c>
       <c r="K137" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L137" s="2">
         <v>15</v>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="J138" s="2"/>
       <c r="K138" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L138" s="2">
         <v>15</v>
@@ -7351,7 +7351,7 @@
         <v>45656</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L139" s="2">
         <v>25</v>
@@ -7392,7 +7392,7 @@
         <v>44349</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L140" s="2">
         <v>25</v>
@@ -7433,7 +7433,7 @@
         <v>44349</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L141" s="2">
         <v>25</v>
@@ -7474,7 +7474,7 @@
         <v>44349</v>
       </c>
       <c r="K142" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L142" s="2">
         <v>25</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="J143" s="2"/>
       <c r="K143" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L143" s="2">
         <v>25</v>
@@ -7557,7 +7557,7 @@
         <v>44349</v>
       </c>
       <c r="K144" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L144" s="2">
         <v>25</v>
@@ -7598,7 +7598,7 @@
         <v>44349</v>
       </c>
       <c r="K145" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L145" s="2">
         <v>25</v>
@@ -7639,7 +7639,7 @@
         <v>44349</v>
       </c>
       <c r="K146" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L146" s="2">
         <v>25</v>
@@ -7680,7 +7680,7 @@
         <v>44349</v>
       </c>
       <c r="K147" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L147" s="2">
         <v>25</v>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="J148" s="2"/>
       <c r="K148" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L148" s="2">
         <v>25</v>
@@ -7763,7 +7763,7 @@
         <v>44349</v>
       </c>
       <c r="K149" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L149" s="2">
         <v>25</v>
@@ -7804,7 +7804,7 @@
         <v>44349</v>
       </c>
       <c r="K150" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L150" s="7">
         <v>5</v>
@@ -7845,7 +7845,7 @@
         <v>44349</v>
       </c>
       <c r="K151" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L151" s="2">
         <v>5</v>
@@ -7886,7 +7886,7 @@
         <v>44349</v>
       </c>
       <c r="K152" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L152" s="2">
         <v>5</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="J153" s="2"/>
       <c r="K153" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L153" s="7">
         <v>5</v>
@@ -7969,7 +7969,7 @@
         <v>44176</v>
       </c>
       <c r="K154" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L154" s="7">
         <v>5</v>
@@ -8010,7 +8010,7 @@
         <v>44349</v>
       </c>
       <c r="K155" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L155" s="2">
         <v>5</v>
@@ -8051,7 +8051,7 @@
         <v>44349</v>
       </c>
       <c r="K156" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L156" s="2">
         <v>5</v>
@@ -8092,7 +8092,7 @@
         <v>44349</v>
       </c>
       <c r="K157" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L157" s="7">
         <v>5</v>
@@ -8136,7 +8136,7 @@
         <v>45539</v>
       </c>
       <c r="K158" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L158" s="7">
         <v>5</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="J159" s="2"/>
       <c r="K159" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L159" s="2">
         <v>5</v>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="J160" s="2"/>
       <c r="K160" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L160" s="2">
         <v>5</v>
@@ -8261,7 +8261,7 @@
         <v>44426</v>
       </c>
       <c r="K161" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L161" s="2">
         <v>5</v>
@@ -8305,7 +8305,7 @@
         <v>44925</v>
       </c>
       <c r="K162" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L162" s="2">
         <v>5</v>
@@ -8349,7 +8349,7 @@
         <v>45824</v>
       </c>
       <c r="K163" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L163" s="2">
         <v>5</v>
@@ -8390,7 +8390,7 @@
         <v>44923</v>
       </c>
       <c r="K164" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L164" s="7">
         <v>5</v>
@@ -8431,7 +8431,7 @@
         <v>45821</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L165" s="7">
         <v>5</v>
@@ -8475,7 +8475,7 @@
         <v>44966</v>
       </c>
       <c r="K166" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L166" s="2">
         <v>5</v>
@@ -8519,7 +8519,7 @@
         <v>45821</v>
       </c>
       <c r="K167" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L167" s="2">
         <v>5</v>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="J168" s="2"/>
       <c r="K168" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L168" s="7">
         <v>5</v>
@@ -8602,7 +8602,7 @@
         <v>44925</v>
       </c>
       <c r="K169" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L169" s="7">
         <v>5</v>
@@ -8643,7 +8643,7 @@
         <v>45821</v>
       </c>
       <c r="K170" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L170" s="2">
         <v>5</v>

--- a/upload/informacoes_classificadas_desclassificadas.xlsx
+++ b/upload/informacoes_classificadas_desclassificadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2551F1AC-1E58-4ED5-9B92-6372DB6473E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89899A28-3574-4B80-9134-4F3ABD059DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="6420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="439">
   <si>
     <t>orgao_entidade</t>
   </si>
@@ -194,21 +194,45 @@
     <t>CODEMGE</t>
   </si>
   <si>
+    <t>020.07.5011</t>
+  </si>
+  <si>
+    <t>Ata da reunião CODEMGE - FIEMG de 11/06/21 e documentos subsequentes sobre o tema (Ata de reunião de diretoria e Assembleia Geral)</t>
+  </si>
+  <si>
+    <t>7 - Economia e Finanças</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Art. 86, §4º Lei 13.303/2016 </t>
+  </si>
+  <si>
+    <t>https://codemge.com.br/classificacao-da-informacao/</t>
+  </si>
+  <si>
+    <t>019.15.5011</t>
+  </si>
+  <si>
+    <t>Informações relativas aos relatórios entregues pela consultoria Ceres Inteligência no âmbito do contrato nº 10110</t>
+  </si>
+  <si>
+    <t>15 -  Relações Institucionais</t>
+  </si>
+  <si>
+    <t>022.07.5011</t>
+  </si>
+  <si>
+    <t>Informações referentes ao Contrato Social da Sociedade em Conta de Participação – SCP Água Mineral, firmado em 17/01/2018 entre  Máximus Prestação de Serviços Eireli – EPP e a Codemge. Aditivo em 15/02/2021 com a MINASBEV Águas do Brasil Ltda</t>
+  </si>
+  <si>
     <t>003.07.5011</t>
   </si>
   <si>
     <t>Informações relativas à parceria existente entre a CODEMIG,  UFMG e CDTN para desenvolvimento do projeto MG Grafeno</t>
   </si>
   <si>
-    <t>7 - Economia e Finanças</t>
-  </si>
-  <si>
     <t>Art. 23, inciso II, da Lei Federal nº 12.527/2011</t>
   </si>
   <si>
-    <t>https://codemge.com.br/classificacao-da-informacao/</t>
-  </si>
-  <si>
     <t>004.07.5011</t>
   </si>
   <si>
@@ -230,18 +254,6 @@
     <t>5 - Convênios e Transferências</t>
   </si>
   <si>
-    <t>016.02.5011</t>
-  </si>
-  <si>
-    <t>Informações que constam no contrato de nº: 10382 relativas à parceria existente entre a CODEMGE e UFMG para desenvolvimento de Nanoespetrômetro (Na@mo)</t>
-  </si>
-  <si>
-    <t>2 - Ciência e Tecnologoa</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso VI, da Lei Federal nº 12.527/2011</t>
-  </si>
-  <si>
     <t>006.07.5011</t>
   </si>
   <si>
@@ -264,51 +276,6 @@
   </si>
   <si>
     <t xml:space="preserve">Relatórios Técnicos / Estudos, pesquisas e testes relativos ao Projeto de Calcinação Flash </t>
-  </si>
-  <si>
-    <t>020.07.5011</t>
-  </si>
-  <si>
-    <t>Ata da reunião CODEMGE - FIEMG de 11/06/21 e documentos subsequentes sobre o tema (Ata de reunião de diretoria e Assembleia Geral)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Art. 86, §4º Lei 13.303/2016 </t>
-  </si>
-  <si>
-    <t>019.15.5011</t>
-  </si>
-  <si>
-    <t>Informações relativas aos relatórios entregues pela consultoria Ceres Inteligência no âmbito do contrato nº 10110</t>
-  </si>
-  <si>
-    <t>15 -  Relações Institucionais</t>
-  </si>
-  <si>
-    <t>013.02.5011</t>
-  </si>
-  <si>
-    <t>Informações que constam no contrato de nº 11010 relativas à parceria existente entre a CODEMGE e UFMG para desenvolvimento de testes diagnósticos para Covid-19 a partir de amostra de soro de pacientes</t>
-  </si>
-  <si>
-    <t>014.02.5011</t>
-  </si>
-  <si>
-    <t>Informações que constam no contrato de nº 11009 relativas à parceria existente entre a CODEMGE e Detechta para capacitar a empresa para produzir testes diagnósticos de COVID-19 (ELISA e Teste rápido), que estão sendo desenvolvidos e validados na empresa</t>
-  </si>
-  <si>
-    <t>017.02.5011</t>
-  </si>
-  <si>
-    <t>Informações que constam no contrato de nº 10365 relativas à parceria existente entre a CODEMGE e UFMG ampliação e complementação da infraestrutura do Laboratório de Ensaios e Combustíveis da UFMG (LEC)</t>
-  </si>
-  <si>
-    <t>018.07.5011</t>
-  </si>
-  <si>
-    <t>Informações relativas ao Projeto Tiger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Art. 23, inciso VI, da Lei Federal nº 12.527/2011 e  Art. 86, §4º Lei 13.303/2016 </t>
   </si>
   <si>
     <t>021.07.5011</t>
@@ -318,10 +285,64 @@
 prestação dos serviços de saúde à população a ser beneficiada pelo projeto</t>
   </si>
   <si>
-    <t>022.07.5011</t>
-  </si>
-  <si>
-    <t>Informações referentes ao Contrato Social da Sociedade em Conta de Participação – SCP Água Mineral, firmado em 17/01/2018 entre  Máximus Prestação de Serviços Eireli – EPP e a Codemge. Aditivo em 15/02/2021 com a MINASBEV Águas do Brasil Ltda</t>
+    <t>026.07.5011</t>
+  </si>
+  <si>
+    <t>Informações, referente ao contrato nº 11.517/2024 - Contratação do BNDES para a prestação de serviços técnicos especializados para a estruturação e implementação de projeto de parceria com a iniciativa privada, destinado à reforma ou reconstrução, construção, manutenção conservação, gestão e operação de serviços não pedagógicos de até 123 escolas da rede estadual de Minas Gerais ("Projeto Educação")</t>
+  </si>
+  <si>
+    <t>027.10.5011</t>
+  </si>
+  <si>
+    <t>Informações sobre o acordo de parceria 11.254/2022 - Contratação do IFC (International Finance Corporation) para execução dos estudos que incluirão a análise de viabilidade técnica, econômico-financeira, ambiental e jurídica para concessão, com apoio do Governo do Estado de MInas Gerais, dos serviços de saneamento básico em municípios da região nordeste de Minas Gerais</t>
+  </si>
+  <si>
+    <t>10 - Habitação, Saneamento e Urbanismo</t>
+  </si>
+  <si>
+    <t>016.02.5011</t>
+  </si>
+  <si>
+    <t>Informações que constam no contrato de nº: 10382 relativas à parceria existente entre a CODEMGE e UFMG para desenvolvimento de Nanoespetrômetro (Na@mo)</t>
+  </si>
+  <si>
+    <t>2 - Ciência e Tecnologoa</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso VI, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>013.02.5011</t>
+  </si>
+  <si>
+    <t>Informações que constam no contrato de nº 11010 relativas à parceria existente entre a CODEMGE e UFMG para desenvolvimento de testes diagnósticos para Covid-19 a partir de amostra de soro de pacientes</t>
+  </si>
+  <si>
+    <t>014.02.5011</t>
+  </si>
+  <si>
+    <t>Informações que constam no contrato de nº 11009 relativas à parceria existente entre a CODEMGE e Detechta para capacitar a empresa para produzir testes diagnósticos de COVID-19 (ELISA e Teste rápido), que estão sendo desenvolvidos e validados na empresa</t>
+  </si>
+  <si>
+    <t>017.02.5011</t>
+  </si>
+  <si>
+    <t>Informações que constam no contrato de nº 10365 relativas à parceria existente entre a CODEMGE e UFMG ampliação e complementação da infraestrutura do Laboratório de Ensaios e Combustíveis da UFMG (LEC)</t>
+  </si>
+  <si>
+    <t>015.02.5011</t>
+  </si>
+  <si>
+    <t>Informações relativas à atuação do BiotechTown, conforme contidas no Acordo de Acionistas assinado em 06 de fevereiro de 2018, no Estatuto Social consolidado na AGE de 21 de maio de 2018 do BiotechTown e nas escrituras da 1ª e 2ª emissão de debêntures firmadas em 06 de fevereiro de 2018</t>
+  </si>
+  <si>
+    <t>018.07.5011</t>
+  </si>
+  <si>
+    <t>Informações relativas ao Projeto Tiger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art. 23, inciso VI, da Lei Federal nº 12.527/2011 e  Art. 86, §4º Lei 13.303/2016 </t>
   </si>
   <si>
     <t>024.02.5011</t>
@@ -336,27 +357,6 @@
     <t>Estudos e pesquisas relacionados ao Projeto Reminas, bem como acordos, memorandos de entendimento e demais documentos associados ao projeto Re-Minas</t>
   </si>
   <si>
-    <t>026.07.5011</t>
-  </si>
-  <si>
-    <t>Informações, referente ao contrato nº 11.517/2024 - Contratação do BNDES para a prestação de serviços técnicos especializados para a estruturação e implementação de projeto de parceria com a iniciativa privada, destinado à reforma ou reconstrução, construção, manutenção conservação, gestão e operação de serviços não pedagógicos de até 123 escolas da rede estadual de Minas Gerais ("Projeto Educação")</t>
-  </si>
-  <si>
-    <t>027.10.5011</t>
-  </si>
-  <si>
-    <t>Informações sobre o acordo de parceria 11.254/2022 - Contratação do IFC (International Finance Corporation) para execução dos estudos que incluirão a análise de viabilidade técnica, econômico-financeira, ambiental e jurídica para concessão, com apoio do Governo do Estado de MInas Gerais, dos serviços de saneamento básico em municípios da região nordeste de Minas Gerais</t>
-  </si>
-  <si>
-    <t>10 - Habitação, Saneamento e Urbanismo</t>
-  </si>
-  <si>
-    <t>015.02.5011</t>
-  </si>
-  <si>
-    <t>Informações relativas à atuação do BiotechTown, conforme contidas no Acordo de Acionistas assinado em 06 de fevereiro de 2018, no Estatuto Social consolidado na AGE de 21 de maio de 2018 do BiotechTown e nas escrituras da 1ª e 2ª emissão de debêntures firmadas em 06 de fevereiro de 2018</t>
-  </si>
-  <si>
     <t>Companhia de Desenvolvimento Econômico de Minas Gerais</t>
   </si>
   <si>
@@ -457,37 +457,6 @@
   </si>
   <si>
     <t>FEAM</t>
-  </si>
-  <si>
-    <t>001.13.2091</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Plano Anual de Fiscalização 2021</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Reservado</t>
-    </r>
-  </si>
-  <si>
-    <t>13 - Meio Ambiente</t>
-  </si>
-  <si>
-    <t>https://www.feam.br/informa%C3%A7%C3%B5es-classificadas-e-desclassificadas</t>
   </si>
   <si>
     <t>002.04.2091</t>
@@ -505,7 +474,21 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reservado</t>
+    </r>
+  </si>
+  <si>
     <t>Art 23, caput da Lei Federal 12.527/2011</t>
+  </si>
+  <si>
+    <t>https://www.feam.br/informa%C3%A7%C3%B5es-classificadas-e-desclassificadas</t>
   </si>
   <si>
     <t>003.04.2091</t>
@@ -523,20 +506,6 @@
     </r>
   </si>
   <si>
-    <t>004.13.2091</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Plano Anual de Fiscalização 2022</t>
-    </r>
-  </si>
-  <si>
     <t>005.04.2091</t>
   </si>
   <si>
@@ -567,6 +536,77 @@
     </r>
   </si>
   <si>
+    <t>008.04.2091</t>
+  </si>
+  <si>
+    <t>009.04.2091</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Produtos de auditoria – Relatórios, Pareceres, Notas de Auditoria relativos à avaliação e à consultoria de gestão de riscos</t>
+    </r>
+  </si>
+  <si>
+    <t>011.04.2091</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Papéis de Trabalho produzidos para subsidiar a opinião e convicção do Controlador Seccional</t>
+    </r>
+  </si>
+  <si>
+    <t>012.04.2091</t>
+  </si>
+  <si>
+    <t>014.04.2091</t>
+  </si>
+  <si>
+    <t>015.04.2091</t>
+  </si>
+  <si>
+    <t>001.13.2091</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Plano Anual de Fiscalização 2021</t>
+    </r>
+  </si>
+  <si>
+    <t>13 - Meio Ambiente</t>
+  </si>
+  <si>
+    <t>004.13.2091</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Plano Anual de Fiscalização 2022</t>
+    </r>
+  </si>
+  <si>
     <t>007.13.2091</t>
   </si>
   <si>
@@ -581,23 +621,6 @@
     </r>
   </si>
   <si>
-    <t>008.04.2091</t>
-  </si>
-  <si>
-    <t>009.04.2091</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Produtos de auditoria – Relatórios, Pareceres, Notas de Auditoria relativos à avaliação e à consultoria de gestão de riscos</t>
-    </r>
-  </si>
-  <si>
     <t>010.13.2091</t>
   </si>
   <si>
@@ -612,23 +635,6 @@
     </r>
   </si>
   <si>
-    <t>011.04.2091</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Papéis de Trabalho produzidos para subsidiar a opinião e convicção do Controlador Seccional</t>
-    </r>
-  </si>
-  <si>
-    <t>012.04.2091</t>
-  </si>
-  <si>
     <t>013.13.2091</t>
   </si>
   <si>
@@ -643,49 +649,34 @@
     </r>
   </si>
   <si>
-    <t>014.04.2091</t>
-  </si>
-  <si>
-    <t>015.04.2091</t>
-  </si>
-  <si>
     <t>Fundação Ezequiel Dias - FUNED</t>
   </si>
   <si>
     <t>FUNED</t>
   </si>
   <si>
+    <t>005.16.2261</t>
+  </si>
+  <si>
+    <t>Relatórios de Auditorias Internas</t>
+  </si>
+  <si>
+    <t>16 - Saúde</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso III, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>https://www.funed.mg.gov.br/informacoes-classificadas-e-desclassificadas/</t>
+  </si>
+  <si>
     <t>001.16.2261</t>
   </si>
   <si>
     <t>Informações relacionadas à biossegurança nos laboratórios de pesquisa</t>
   </si>
   <si>
-    <t>16 - Saúde</t>
-  </si>
-  <si>
     <t>Art. 23, inciso VI da Lei Federal nº 12.527/2011</t>
-  </si>
-  <si>
-    <t>https://www.funed.mg.gov.br/informacoes-classificadas-e-desclassificadas/</t>
-  </si>
-  <si>
-    <t>006.16.2261</t>
-  </si>
-  <si>
-    <t>Informações utilizadas como fundamento da tomada de decisão ou de ato administrativo.</t>
-  </si>
-  <si>
-    <t>Art. 7º, § 3º da Lei Federal nº 12.527</t>
-  </si>
-  <si>
-    <t>005.16.2261</t>
-  </si>
-  <si>
-    <t>Relatórios de Auditorias Internas</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso III, da Lei Federal nº 12.527/2011</t>
   </si>
   <si>
     <t>007.16.2261</t>
@@ -728,6 +719,15 @@
     <t>Ofício externo - Documentos recebidos de órgãos externos como Polícia Civil, Federal, Ministério Público ou congênere, com finalidade de elucidação de crimes contra Saúde Pública ou Estado</t>
   </si>
   <si>
+    <t>006.16.2261</t>
+  </si>
+  <si>
+    <t>Informações utilizadas como fundamento da tomada de decisão ou de ato administrativo.</t>
+  </si>
+  <si>
+    <t>Art. 7º, § 3º da Lei Federal nº 12.527</t>
+  </si>
+  <si>
     <t>Gabinete Militar do Governador do Estado de Minas Gerais - GMG</t>
   </si>
   <si>
@@ -764,19 +764,19 @@
     <t>Relação dos veículos disponibilizados para o escritório de representação em Brasília</t>
   </si>
   <si>
+    <t>Informações sobre viaturas do Gabinete Militar do Governador, bem como veículos colocados à disposição do órgão.</t>
+  </si>
+  <si>
+    <t>Registros dos serviços prestados ao GMG de agenciamento de viagens (passagens, hotéis, fretamentos e serviços correlatos) envolvendo a agenda do Governador ou do Vice-Governador</t>
+  </si>
+  <si>
     <t>Plantas e Projetos das edificações onde o Governador, Vice-Governador e Chefe do Gabinete Militar exercerem as suas funções e das respectivas residências oficiais</t>
   </si>
   <si>
     <t>Ultrassecreto</t>
   </si>
   <si>
-    <t>Art. 31, Decreto 45.969/12;Decreto 46.983/2016; Decreto 45.357/2010;</t>
-  </si>
-  <si>
-    <t>Informações sobre viaturas do Gabinete Militar do Governador, bem como veículos colocados à disposição do órgão.</t>
-  </si>
-  <si>
-    <t>Registros dos serviços prestados ao GMG de agenciamento de viagens (passagens, hotéis, fretamentos e serviços correlatos) envolvendo a agenda do Governador ou do Vice-Governador</t>
+    <t>Art. 31, Decreto 45.969/12, Decreto 46.983/2016, Decreto 45.357/2010</t>
   </si>
   <si>
     <t>Instituto de Desenvolvimento Integrado de Minas Gerais - InvestMinas</t>
@@ -785,34 +785,28 @@
     <t>InvestMinas</t>
   </si>
   <si>
-    <t>005.11.5130</t>
+    <t>001.11.5130</t>
+  </si>
+  <si>
+    <t>Estudos regionais e setoriais (direcionados às empresas e investidores), quando encomendados</t>
+  </si>
+  <si>
+    <t>11 - Indústria</t>
+  </si>
+  <si>
+    <t>https://investminas.mg.gov.br/pt/sobre/</t>
+  </si>
+  <si>
+    <t>003.11.5130</t>
+  </si>
+  <si>
+    <t>Informações consolidadas em Notas Técnicas sobre detalhes de projetos empresariais, como valor do investimento, localização, descrição do projeto, produtos, geração de empregos, pleitos das empresas, necessidades de licenciamento ambiental e infraestrutura</t>
+  </si>
+  <si>
+    <t>006.11.5130</t>
   </si>
   <si>
     <t>Íntegra de Acordos de cooperação técnica</t>
-  </si>
-  <si>
-    <t>11 - Indústria</t>
-  </si>
-  <si>
-    <t>Art. 23, incisos II e IV, da Lei Federal  nº 12.527/2011</t>
-  </si>
-  <si>
-    <t>https://investminas.mg.gov.br/pt/sobre/</t>
-  </si>
-  <si>
-    <t>001.11.5130</t>
-  </si>
-  <si>
-    <t>Estudos regionais e setoriais (direcionados às empresas e investidores), quando encomendados</t>
-  </si>
-  <si>
-    <t>003.11.5130</t>
-  </si>
-  <si>
-    <t>Informações consolidadas em Notas Técnicas sobre detalhes de projetos empresariais, como valor do investimento, localização, descrição do projeto, produtos, geração de empregos, pleitos das empresas, necessidades de licenciamento ambiental e infraestrutura</t>
-  </si>
-  <si>
-    <t>006.11.5130</t>
   </si>
   <si>
     <t>011.11.5130</t>
@@ -854,6 +848,18 @@
     <t>Relatórios de investimentos e projetos ativos/inativos para os mantenedores</t>
   </si>
   <si>
+    <t>008.04.5130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processos, informações e documentos de auditoria interna, como relatórios trimestrais e anuais enviados ao conselho superior </t>
+  </si>
+  <si>
+    <t>005.11.5130</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos II e IV, da Lei Federal  nº 12.527/2011</t>
+  </si>
+  <si>
     <t>010.09.5130</t>
   </si>
   <si>
@@ -869,12 +875,6 @@
     <t>12 - Justição e Legislação</t>
   </si>
   <si>
-    <t>008.04.5130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Processos, informações e documentos de auditoria interna, como relatórios trimestrais e anuais enviados ao conselho superior </t>
-  </si>
-  <si>
     <t>004.09.5130</t>
   </si>
   <si>
@@ -926,10 +926,6 @@
     <t>Equipamento e Especificações Técnicas</t>
   </si>
   <si>
-    <t>Art. 23, inciso VIII, da Lei Federal nº 12.527/2011; Art.25, inciso IX, Decreto
-no 7724/2012</t>
-  </si>
-  <si>
     <t>https://www.policiacivil.mg.gov.br/pagina/transparencia</t>
   </si>
   <si>
@@ -939,129 +935,162 @@
     <t>PMMG</t>
   </si>
   <si>
+    <t>7460.112422/2019-85</t>
+  </si>
+  <si>
+    <t>Inserir o assunto sobre o qual versa a informação</t>
+  </si>
+  <si>
+    <t>https://www.policiamilitar.mg.gov.br/site/externo/pagina/10081/lei-de-acesso-%C3%A0-informa%C3%A7%C3%A3o</t>
+  </si>
+  <si>
+    <t>7460.112493/2023-63</t>
+  </si>
+  <si>
+    <t>Resposta ao Requerimento de informações 557/2023</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso V, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>7460.112494/2023-53</t>
+  </si>
+  <si>
+    <t>Resposta ao Requerimento de informações 1602/2023</t>
+  </si>
+  <si>
+    <t>7460.112497/2023-52</t>
+  </si>
+  <si>
+    <t>Postos de combustível Orgânico da PMMG</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso VII da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>7460.112495/2023-52</t>
+  </si>
+  <si>
+    <t>7460.112496/2023-52</t>
+  </si>
+  <si>
+    <t>7460.112429/2019-64</t>
+  </si>
+  <si>
+    <t>0718.112421/2019-85</t>
+  </si>
+  <si>
+    <t>0718.112444/2019-74</t>
+  </si>
+  <si>
     <t>7460.112442/2019-75</t>
   </si>
   <si>
-    <t>Inserir o assunto sobre o qual versa a informação</t>
-  </si>
-  <si>
-    <t>https://www.policiamilitar.mg.gov.br/site/externo/pagina/10081/lei-de-acesso-%C3%A0-informa%C3%A7%C3%A3o</t>
-  </si>
-  <si>
-    <t>7460.112497/2023-52</t>
-  </si>
-  <si>
-    <t>Postos de combustível Orgânico da PMMG</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso VII da Lei Federal nº 12.527/2011</t>
-  </si>
-  <si>
-    <t>7460.112495/2023-52</t>
-  </si>
-  <si>
-    <t>Resposta ao Requerimento de informações 557/2023</t>
-  </si>
-  <si>
-    <t>7460.112496/2023-52</t>
-  </si>
-  <si>
-    <t>Resposta ao Requerimento de informações 1602/2023</t>
-  </si>
-  <si>
     <t>7460.112443/2019-74</t>
   </si>
   <si>
     <t>7460.112445/2019-74</t>
   </si>
   <si>
+    <t>7460.112447/2019-63</t>
+  </si>
+  <si>
+    <t>7460.112400/2018-96</t>
+  </si>
+  <si>
+    <t>7460.112403/2018-86</t>
+  </si>
+  <si>
+    <t>7460.112409/2018-74</t>
+  </si>
+  <si>
+    <t>7460.112410/2018-86</t>
+  </si>
+  <si>
+    <t>7460.112411/2018-86</t>
+  </si>
+  <si>
+    <t>7460.112412/2018-86</t>
+  </si>
+  <si>
+    <t>7460.112414/2018-85</t>
+  </si>
+  <si>
+    <t>7460.112415/2018-75</t>
+  </si>
+  <si>
+    <t>7460.112416/2018-75</t>
+  </si>
+  <si>
+    <t>7460.112419/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112420/2019-86</t>
+  </si>
+  <si>
+    <t>7460.112426/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112428/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112431/2019-85</t>
+  </si>
+  <si>
+    <t>7460.112434/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112435/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112436/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112437/2019-64</t>
+  </si>
+  <si>
+    <t>7460.112438/2019-64</t>
+  </si>
+  <si>
+    <t>7460.112418/2018-74</t>
+  </si>
+  <si>
+    <t>7460.112432/2019-75</t>
+  </si>
+  <si>
+    <t>7460.112457/2019-63</t>
+  </si>
+  <si>
+    <t>2903.112427/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112440/2019-75</t>
+  </si>
+  <si>
+    <t>7460.112397/2018-52</t>
+  </si>
+  <si>
+    <t>7460.112398/2018-52</t>
+  </si>
+  <si>
+    <t>7460.112399/2018-52</t>
+  </si>
+  <si>
+    <t>7460.112404/2018-85</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso(s) VIII, III, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>7460.112405/2018-85</t>
+  </si>
+  <si>
     <t>7460.112441/2019-75</t>
   </si>
   <si>
     <t>Art. 29, inciso I, do Decreto Estadual nº 45.969/2011</t>
   </si>
   <si>
-    <t>7460.112447/2019-63</t>
-  </si>
-  <si>
-    <t>7460.112400/2018-96</t>
-  </si>
-  <si>
-    <t>7460.112422/2019-85</t>
-  </si>
-  <si>
-    <t>7460.112429/2019-64</t>
-  </si>
-  <si>
-    <t>7460.112403/2018-86</t>
-  </si>
-  <si>
-    <t>7460.112409/2018-74</t>
-  </si>
-  <si>
-    <t>7460.112410/2018-86</t>
-  </si>
-  <si>
-    <t>7460.112411/2018-86</t>
-  </si>
-  <si>
-    <t>7460.112412/2018-86</t>
-  </si>
-  <si>
-    <t>7460.112414/2018-85</t>
-  </si>
-  <si>
-    <t>7460.112415/2018-75</t>
-  </si>
-  <si>
-    <t>7460.112416/2018-75</t>
-  </si>
-  <si>
-    <t>7460.112419/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112420/2019-86</t>
-  </si>
-  <si>
-    <t>7460.112426/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112428/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112431/2019-85</t>
-  </si>
-  <si>
-    <t>7460.112434/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112435/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112436/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112437/2019-64</t>
-  </si>
-  <si>
-    <t>7460.112438/2019-64</t>
-  </si>
-  <si>
-    <t>7460.112418/2018-74</t>
-  </si>
-  <si>
-    <t>7460.112432/2019-75</t>
-  </si>
-  <si>
-    <t>7460.112404/2018-85</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso(s) VIII, III, da Lei Federal nº 12.527/2011</t>
-  </si>
-  <si>
-    <t>7460.112405/2018-85</t>
-  </si>
-  <si>
     <t>7460.112401/2018-86</t>
   </si>
   <si>
@@ -1074,100 +1103,67 @@
     <t>7460.112439/2019-63</t>
   </si>
   <si>
-    <t>7460.112457/2019-63</t>
-  </si>
-  <si>
-    <t>7460.112493/2023-63</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso V, da Lei Federal nº 12.527/2011</t>
-  </si>
-  <si>
-    <t>7460.112494/2023-53</t>
-  </si>
-  <si>
-    <t>0718.112421/2019-85</t>
-  </si>
-  <si>
-    <t>2903.112427/2019-74</t>
-  </si>
-  <si>
-    <t>0718.112444/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112440/2019-75</t>
-  </si>
-  <si>
-    <t>7460.112397/2018-52</t>
-  </si>
-  <si>
-    <t>7460.112398/2018-52</t>
-  </si>
-  <si>
-    <t>7460.112399/2018-52</t>
-  </si>
-  <si>
     <t>Secretaria de Estado de Fazenda - SEF</t>
   </si>
   <si>
     <t>SEF</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Processos   e documentos referentes à imunidade, isenções e demais benefícios fiscais do   IPVA, ITCD e Taxas Estaduais, exceto as consultas sobre aplicação da   Legislação Tributária</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso IV e art. 24, caput, § 1º, inciso I e § 5º, inciso I, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>https://www.fazenda.mg.gov.br/transparencia/informacoes-classificadas-e-desclassificadas/</t>
+  </si>
+  <si>
+    <t>Regimes   especiais que dispõem sobre obrigações principais e acessórias, e respectivos   pareceres e estudos que os embasaram</t>
+  </si>
+  <si>
+    <t>Processos e documentos referentes à aplicação   de benefícios fiscais de que tratam o RICMS/02 e seus anexos I, II, IV, IX e   XVI, exceto as consultas sobre aplicação da Legislação Tributária</t>
+  </si>
+  <si>
+    <t>Informações   sobre acesso, perfil e rastreabilidade de usuários e registros de transações   executadas no Sistema Integrado de Administração Financeira (SIAFI/MG)</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso IV, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Informações contábeis custodiadas pela   Superintendência Central de Contadoria-Geral (SCCG) específicas de unidades   orçamentárias e/ou executoras</t>
+  </si>
+  <si>
+    <t>Regimes especiais que dispõem sobre benefícios   fiscais e respectivos pareceres, estudo que embasaram e consultas de   contribuintes a eles referentes</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso VI e art. 24, caput, § 1º, inciso I e § 5º, inciso I, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
     <t>Protocolos de Intenções</t>
   </si>
   <si>
     <t>Art. 23, incisos II, IV e VI, da Lei Federal nº 12.527/2011</t>
   </si>
   <si>
-    <t>https://www.fazenda.mg.gov.br/transparencia/informacoes-classificadas-e-desclassificadas/</t>
-  </si>
-  <si>
     <t>Extrato   de contas e movimentações financeiras</t>
   </si>
   <si>
-    <t>Processos   e documentos referentes à imunidade, isenções e demais benefícios fiscais do   IPVA, ITCD e Taxas Estaduais, exceto as consultas sobre aplicação da   Legislação Tributária</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso IV e art. 24, caput, § 1º, inciso I e § 5º, inciso I, da Lei Federal nº 12.527/2011; Decreto Estadual nº 45.969, de 24/05/2012; Art. 1º, Caput, 4º, 7º, 8º, III, 9º e 13 da Resolução nº 4.671, de 13/06/2014</t>
-  </si>
-  <si>
-    <t>Regimes especiais que dispõem sobre benefícios   fiscais e respectivos pareceres, estudo que embasaram e consultas de   contribuintes a eles referentes</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso VI e art. 24, caput, § 1º, inciso I e § 5º, inciso I, da Lei Federal nº 12.527/2011; Art.29, I, 30, e 36 do Decreto   Estadual nº 45.969/2012; Artigos 1º, Caput, 4º, 7º, III, 8º, I, 9º   e 13 da Resolução nº 4.671, de 13/06/2014</t>
+    <t>Disponibilidade de Caixa - Contrato de Prestação de Serviços   Financeiros e outras Avenças, N.º 1900010998, que entre si celebram o Estado   de Minas Gerais e o Banco do Brasil S.A., de 21/12/2021, exceto as   informações publicadas no Diário Oficial do Estado de Minas Gerais em   22/12/2021</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso IV e art. 24, caput e § 1º, inciso III e § 5º, inciso I, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>Folha de Pagamento - CONTRATO Nº 1900010957/2021, DE PRESTAÇÃO   DE SERVIÇOS, QUE ENTRE SI CELEBRAM O ESTADO DE MINAS GERAIS, POR INTERMÉDIO   DA SECRETARIA DE ESTADO DE FAZENDA - SEF/MG E O ITAÚ UNIBANCO S/A, de   02/08/2021, exceto as informações publicadas no Diário Oficial do Estado de   Minas Gerais em em 03/08/2021</t>
   </si>
   <si>
     <t>Acordo   de Cooperação Técnica nº 1910003054/SEF-MG. Processo SEI nº   1190.01.0006287/2022-26 Estado de Minas Gerais / Secretaria de Estado de   Fazenda e União / Superintendência da Polícia Rodoviária Federal do Estado de   Minas Gerais</t>
   </si>
   <si>
-    <t>Art. 23, incisos VI, VII e VIII e art. 24, caput, § 1º, inciso I, da Lei Federal nº 12.527/2011 C/C art. 28 do Decreto Estadual nº 45.969/2012</t>
-  </si>
-  <si>
-    <t>Informações   sobre acesso, perfil e rastreabilidade de usuários e registros de transações   executadas no Sistema Integrado de Administração Financeira (SIAFI/MG)</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso IV, da Lei Federal nº 12.527/2011</t>
-  </si>
-  <si>
-    <t>Informações contábeis custodiadas pela   Superintendência Central de Contadoria-Geral (SCCG) específicas de unidades   orçamentárias e/ou executoras</t>
-  </si>
-  <si>
-    <t>Disponibilidade de Caixa - Contrato de Prestação de Serviços   Financeiros e outras Avenças, N.º 1900010998, que entre si celebram o Estado   de Minas Gerais e o Banco do Brasil S.A., de 21/12/2021, exceto as   informações publicadas no Diário Oficial do Estado de Minas Gerais em   22/12/2021</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso IV e art. 24, caput e § 1º, inciso III e § 5º, inciso I, da Lei Federal nº 12.527/2011 C/C art. 29, inciso I, art. 30, inciso III e art. 36 do Decreto Estadual nº 45.969/2012, art. 1º , Caput, art. 4º, art. 7º, inciso I, art.  8º, inciso III, art. 9º e art. 13 da Resolução nº 4.671/2014, do Secretário de Estado de Fazenda de Minas Gerais</t>
-  </si>
-  <si>
-    <t>Folha de Pagamento - CONTRATO Nº 1900010957/2021, DE PRESTAÇÃO   DE SERVIÇOS, QUE ENTRE SI CELEBRAM O ESTADO DE MINAS GERAIS, POR INTERMÉDIO   DA SECRETARIA DE ESTADO DE FAZENDA - SEF/MG E O ITAÚ UNIBANCO S/A, de   02/08/2021, exceto as informações publicadas no Diário Oficial do Estado de   Minas Gerais em em 03/08/2021</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso IV e art. 24, caput e § 1º, inciso III e § 5º, inciso I, da Lei Federal nº 12.527/2011 C/C art. 29, inciso I, art. 30,inciso III e art. 36 do Decreto Estadual nº 45.969/2012, art 1º, Caput, art. 4º, art. 7º, inciso I, art. 8º, inciso III, art. 9º e art. 13 da Resolução nº4.671/2014, do Secretário de Estado de Fazenda de Minas Gerais</t>
-  </si>
-  <si>
-    <t>Regimes   especiais que dispõem sobre obrigações principais e acessórias, e respectivos   pareceres e estudos que os embasaram</t>
-  </si>
-  <si>
-    <t>Processos e documentos referentes à aplicação   de benefícios fiscais de que tratam o RICMS/02 e seus anexos I, II, IV, IX e   XVI, exceto as consultas sobre aplicação da Legislação Tributária</t>
+    <t>Art. 23, incisos VI, VII e VIII e art. 24, caput, § 1º, inciso I, da Lei Federal nº 12.527/2011</t>
   </si>
   <si>
     <t>Secretaria de Estado de Justiça e Segurança Pública - SEJUSP</t>
@@ -1176,66 +1172,18 @@
     <t>SEJUSP</t>
   </si>
   <si>
-    <t>031.06.1450</t>
-  </si>
-  <si>
-    <t>Dados das violências autoprovocadas (suicídio consumado e tentativa de suicídio) e de homicídios seguidos de violências autoprovocadas de policiais penais e de agentes socioeducativos ativos e inativos.</t>
-  </si>
-  <si>
-    <t>Art. 23, incisos III e VII, da Lei Federal nº 12.527/2011</t>
+    <t>032.06.1450</t>
+  </si>
+  <si>
+    <t>Informações contidas em processos do sistema SEI! que tratam especificamente do Termo de Compromisso firmado entre a Sejusp, Vale e Ministério Público.</t>
+  </si>
+  <si>
+    <t>Art. 22 e art. 23, incisos III, VI e VII da Lei Federal nº 12.527/2011</t>
   </si>
   <si>
     <t>https://www.seguranca.mg.gov.br/index.php/transparencia/informacoes-classificadas-e-desclassificadas2</t>
   </si>
   <si>
-    <t>001.06.1450</t>
-  </si>
-  <si>
-    <t>Relatório de auditoria interna - Nº Processo SIGA 1450.145.31.0101.20.</t>
-  </si>
-  <si>
-    <t>Art. 23, incisos VII e VIII, da Lei Federal nº 12.527/2011 e Art. 29, inciso I, do Decreto Estadual nº 45.969/2012</t>
-  </si>
-  <si>
-    <t>032.06.1450</t>
-  </si>
-  <si>
-    <t>Informações contidas em processos do sistema SEI! que tratam especificamente do Termo de Compromisso firmado entre a Sejusp, Vale e Ministério Público.</t>
-  </si>
-  <si>
-    <t>Art. 22 e art. 23, incisos III, VI e VII da Lei Federal nº 12.527/2011</t>
-  </si>
-  <si>
-    <t>018.06.1450</t>
-  </si>
-  <si>
-    <t>Informações contidas em estudos e diagnósticos envolvendo opiniões, rotinas, qualidade de trabalho, treinamento, saúde e perfil de agentes públicos de segurança pública e defesa social de Minas Gerais. [7]</t>
-  </si>
-  <si>
-    <t>021.06.1450</t>
-  </si>
-  <si>
-    <t>Informações das abas Homicídios / Vulnerabilidade Criminal / Dinâmica das Vulnerabilidades dos Relatórios de Gestão Estratégica (RGE).</t>
-  </si>
-  <si>
-    <t>Art. 23, incisos III, VII e VIII, da Lei Federal nº 12.527/2011</t>
-  </si>
-  <si>
-    <t>022.06.1450</t>
-  </si>
-  <si>
-    <t>Informações dos Relatórios Analíticos de Dinâmica Criminal.</t>
-  </si>
-  <si>
-    <t>020.06.1450</t>
-  </si>
-  <si>
-    <t>Informações contidas em bancos de dados internos e soluções tecnológicas adotadas pela SEJUSP: descrições, configurações, projetos, códigos fonte e os produtos de soluções tecnológicas, incluindo todos os seus componentes de hardware, software e rede. [8]</t>
-  </si>
-  <si>
-    <t>Art. 23, incisos III e VIII, da Lei Federal nº 12.527/2011</t>
-  </si>
-  <si>
     <t>026.06.1450</t>
   </si>
   <si>
@@ -1252,12 +1200,6 @@
   </si>
   <si>
     <t>Informações referentes aos componentes e registros de armamentos, explosivos, equipamentos de segurança, apetrechos de uso policial, dispositivos de dispersão e munições gerenciados e utilizados pela SEJUSP. [9]</t>
-  </si>
-  <si>
-    <t>028.06.1450</t>
-  </si>
-  <si>
-    <t>Informações relacionadas a integrantes e líderes de facções criminosas acautelados em unidades prisionais.</t>
   </si>
   <si>
     <t>003.06.1450</t>
@@ -1304,6 +1246,51 @@
     <t>Dados de frequência e codificação do sistema de radiocomunicação das unidades prisionais, socioeducativas e administrativas da Sejusp. [3]</t>
   </si>
   <si>
+    <t>015.06.1450</t>
+  </si>
+  <si>
+    <t>Informações relacionadas à análise de provisionamento e à vagas  livres de cargo ofertado em concurso público ou em processo seletivo.</t>
+  </si>
+  <si>
+    <t>027.06.1450</t>
+  </si>
+  <si>
+    <t>Informações contidas nos planos de segurança no âmbito do DEPEN/SEJUSP.</t>
+  </si>
+  <si>
+    <t>002.06.1450</t>
+  </si>
+  <si>
+    <t>Dados de ocorrências no âmbito das unidades prisionais.</t>
+  </si>
+  <si>
+    <t>019.06.1450</t>
+  </si>
+  <si>
+    <t>Informações contidas em relatórios de auditoria consolidados pela inteligência.</t>
+  </si>
+  <si>
+    <t>031.06.1450</t>
+  </si>
+  <si>
+    <t>Dados das violências autoprovocadas (suicídio consumado e tentativa de suicídio) e de homicídios seguidos de violências autoprovocadas de policiais penais e de agentes socioeducativos ativos e inativos.</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos III e VII, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>018.06.1450</t>
+  </si>
+  <si>
+    <t>Informações contidas em estudos e diagnósticos envolvendo opiniões, rotinas, qualidade de trabalho, treinamento, saúde e perfil de agentes públicos de segurança pública e defesa social de Minas Gerais. [7]</t>
+  </si>
+  <si>
+    <t>028.06.1450</t>
+  </si>
+  <si>
+    <t>Informações relacionadas a integrantes e líderes de facções criminosas acautelados em unidades prisionais.</t>
+  </si>
+  <si>
     <t>005.06.1450</t>
   </si>
   <si>
@@ -1328,30 +1315,60 @@
     <t>Informações referentes a estudo de dimensionamento da força de trabalho do Sistema Prisional.</t>
   </si>
   <si>
-    <t>015.06.1450</t>
-  </si>
-  <si>
-    <t>Informações relacionadas à análise de provisionamento e à vagas  livres de cargo ofertado em concurso público ou em processo seletivo.</t>
-  </si>
-  <si>
     <t>014.06.1450</t>
   </si>
   <si>
     <t>Informações relacionadas à gestão da segurança prisional e socioeducativa envolvendo o quadro de pessoal.</t>
   </si>
   <si>
+    <t>012.06.1450</t>
+  </si>
+  <si>
+    <t>Informações relacionadas a nomes, a lotação, a exercício, a quantitativos, a escala de trabalhos, e a postos de serviço de agentes públicos (ativos, inativos ou desligados) das unidades administrativas, das unidades prisionais, das unidades socioeducativas e das Regiões Integradas de Segurança Pública (RISP). [5]</t>
+  </si>
+  <si>
+    <t>013.06.1450</t>
+  </si>
+  <si>
+    <t>Lista e quantitativo de servidores afastados e em gozo de férias regulamentares e férias prêmio, por unidade prisional ou socioeducativa.</t>
+  </si>
+  <si>
+    <t>016.06.1450</t>
+  </si>
+  <si>
+    <t>Informações sobre absenteísmo nas unidades prisionais e socioeducativas.</t>
+  </si>
+  <si>
+    <t>020.06.1450</t>
+  </si>
+  <si>
+    <t>Informações contidas em bancos de dados internos e soluções tecnológicas adotadas pela SEJUSP: descrições, configurações, projetos, códigos fonte e os produtos de soluções tecnológicas, incluindo todos os seus componentes de hardware, software e rede. [8]</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos III e VIII, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>021.06.1450</t>
+  </si>
+  <si>
+    <t>Informações das abas Homicídios / Vulnerabilidade Criminal / Dinâmica das Vulnerabilidades dos Relatórios de Gestão Estratégica (RGE).</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos III, VII e VIII, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>022.06.1450</t>
+  </si>
+  <si>
+    <t>Informações dos Relatórios Analíticos de Dinâmica Criminal.</t>
+  </si>
+  <si>
     <t>017.06.1450</t>
   </si>
   <si>
     <t>Informações referentes ao conteúdo das chamadas ao teleatendimento emergencial, via 190, 193 e 197. [6]</t>
   </si>
   <si>
-    <t>002.06.1450</t>
-  </si>
-  <si>
-    <t>Dados de ocorrências no âmbito das unidades prisionais.</t>
-  </si>
-  <si>
     <t>023.06.1450</t>
   </si>
   <si>
@@ -1370,79 +1387,25 @@
     <t>Informações das atas das reuniões do eixo Núcleo Integrado de monitoramento à violência contra a mulher do programa MG Mulher.</t>
   </si>
   <si>
-    <t>012.06.1450</t>
-  </si>
-  <si>
-    <t>Informações relacionadas a nomes, a lotação, a exercício, a quantitativos, a escala de trabalhos, e a postos de serviço de agentes públicos (ativos, inativos ou desligados) das unidades administrativas, das unidades prisionais, das unidades socioeducativas e das Regiões Integradas de Segurança Pública (RISP). [5]</t>
-  </si>
-  <si>
-    <t>013.06.1450</t>
-  </si>
-  <si>
-    <t>Lista e quantitativo de servidores afastados e em gozo de férias regulamentares e férias prêmio, por unidade prisional ou socioeducativa.</t>
-  </si>
-  <si>
-    <t>016.06.1450</t>
-  </si>
-  <si>
-    <t>Informações sobre absenteísmo nas unidades prisionais e socioeducativas.</t>
-  </si>
-  <si>
-    <t>019.06.1450</t>
-  </si>
-  <si>
-    <t>Informações contidas em relatórios de auditoria consolidados pela inteligência.</t>
-  </si>
-  <si>
-    <t>027.06.1450</t>
-  </si>
-  <si>
-    <t>Informações contidas nos planos de segurança no âmbito do DEPEN/SEJUSP.</t>
-  </si>
-  <si>
     <t>024.06.1450</t>
   </si>
   <si>
     <t>Selo Prevenção Minas - Informações das entrevistas do Diagnóstico Municipal de Segurança Cidadã.</t>
   </si>
   <si>
+    <t>001.06.1450</t>
+  </si>
+  <si>
+    <t>Relatório de auditoria interna - Nº Processo SIGA 1450.145.31.0101.20.</t>
+  </si>
+  <si>
+    <t>Art. 23, incisos VII e VIII, da Lei Federal nº 12.527/2011 e Art. 29, inciso I, do Decreto Estadual nº 45.969/2012</t>
+  </si>
+  <si>
     <t>Secretaria de Estado de Meio Ambiente e Desenvolvimento Sustentável - SEMAD</t>
   </si>
   <si>
     <t>SEMAD</t>
-  </si>
-  <si>
-    <t>001.13.1371</t>
-  </si>
-  <si>
-    <t>Planejamento Anual de Fiscalização 2017</t>
-  </si>
-  <si>
-    <t>https://meioambiente.mg.gov.br/informacoes-classificadas-e-desclassificadas?p_l_back_url=%2Fbusca%3Fq%3Dclassificadas</t>
-  </si>
-  <si>
-    <t>002.13.1371</t>
-  </si>
-  <si>
-    <t>Plano de Fiscalização Ambiental 2018</t>
-  </si>
-  <si>
-    <t>003.13.1371</t>
-  </si>
-  <si>
-    <t>Planejamento Anual de Fiscalização 2019</t>
-  </si>
-  <si>
-    <t>004.13.1371</t>
-  </si>
-  <si>
-    <t>Planejamento Anual de Fiscalização Ambiental 2020</t>
-  </si>
-  <si>
-    <t>007.13.1371</t>
-  </si>
-  <si>
-    <t>Plano Anual de Fiscalização 2021</t>
   </si>
   <si>
     <t>006.04.1371</t>
@@ -1453,11 +1416,44 @@
 à consultoria de gestão de riscos</t>
   </si>
   <si>
+    <t>https://meioambiente.mg.gov.br/informacoes-classificadas-e-desclassificadas?p_l_back_url=%2Fbusca%3Fq%3Dclassificadas</t>
+  </si>
+  <si>
     <t>005.04.1371</t>
   </si>
   <si>
     <t>Papéis de Trabalho produzidos para subsidiar
 a opinião e convicção do auditor</t>
+  </si>
+  <si>
+    <t>001.13.1371</t>
+  </si>
+  <si>
+    <t>Planejamento Anual de Fiscalização 2017</t>
+  </si>
+  <si>
+    <t>002.13.1371</t>
+  </si>
+  <si>
+    <t>Plano de Fiscalização Ambiental 2018</t>
+  </si>
+  <si>
+    <t>003.13.1371</t>
+  </si>
+  <si>
+    <t>Planejamento Anual de Fiscalização 2019</t>
+  </si>
+  <si>
+    <t>004.13.1371</t>
+  </si>
+  <si>
+    <t>Planejamento Anual de Fiscalização Ambiental 2020</t>
+  </si>
+  <si>
+    <t>007.13.1371</t>
+  </si>
+  <si>
+    <t>Plano Anual de Fiscalização 2021</t>
   </si>
   <si>
     <t>008.13.1371</t>
@@ -2026,7 +2022,7 @@
     <col min="4" max="4" width="38.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="44.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="121.140625" style="2" customWidth="1"/>
     <col min="8" max="8" width="19.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26" style="2" bestFit="1" customWidth="1"/>
@@ -2661,18 +2657,19 @@
       <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" t="s">
         <v>53</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>54</v>
       </c>
       <c r="H15" s="1">
-        <v>43131</v>
+        <v>44372</v>
       </c>
       <c r="I15" s="1">
-        <v>43131</v>
-      </c>
+        <v>44372</v>
+      </c>
+      <c r="J15" s="10"/>
       <c r="K15" s="3" t="s">
         <v>42</v>
       </c>
@@ -2700,26 +2697,26 @@
         <v>57</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>58</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>54</v>
       </c>
       <c r="H16" s="1">
-        <v>43221</v>
+        <v>44713</v>
       </c>
       <c r="I16" s="1">
-        <v>43221</v>
+        <v>44713</v>
       </c>
       <c r="J16" s="10"/>
       <c r="K16" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L16" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M16" s="1">
         <v>46142</v>
@@ -2736,10 +2733,10 @@
         <v>50</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>41</v>
@@ -2751,10 +2748,10 @@
         <v>54</v>
       </c>
       <c r="H17" s="1">
-        <v>43221</v>
+        <v>45344</v>
       </c>
       <c r="I17" s="1">
-        <v>43221</v>
+        <v>45344</v>
       </c>
       <c r="J17" s="10"/>
       <c r="K17" s="3" t="s">
@@ -2778,27 +2775,26 @@
         <v>50</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F18" t="s">
-        <v>62</v>
+      <c r="F18" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H18" s="1">
-        <v>43252</v>
+        <v>43131</v>
       </c>
       <c r="I18" s="1">
-        <v>43252</v>
-      </c>
-      <c r="J18" s="10"/>
+        <v>43131</v>
+      </c>
       <c r="K18" s="3" t="s">
         <v>42</v>
       </c>
@@ -2820,25 +2816,25 @@
         <v>50</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>65</v>
+      <c r="F19" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H19" s="1">
-        <v>43304</v>
+        <v>43221</v>
       </c>
       <c r="I19" s="1">
-        <v>43304</v>
+        <v>43221</v>
       </c>
       <c r="J19" s="10"/>
       <c r="K19" s="3" t="s">
@@ -2862,10 +2858,10 @@
         <v>50</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>41</v>
@@ -2874,13 +2870,13 @@
         <v>53</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H20" s="1">
-        <v>43374</v>
+        <v>43221</v>
       </c>
       <c r="I20" s="1">
-        <v>43374</v>
+        <v>43221</v>
       </c>
       <c r="J20" s="10"/>
       <c r="K20" s="3" t="s">
@@ -2904,25 +2900,25 @@
         <v>50</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H21" s="1">
-        <v>43569</v>
+        <v>43252</v>
       </c>
       <c r="I21" s="1">
-        <v>43569</v>
+        <v>43252</v>
       </c>
       <c r="J21" s="10"/>
       <c r="K21" s="3" t="s">
@@ -2958,13 +2954,13 @@
         <v>53</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H22" s="1">
-        <v>43831</v>
+        <v>43374</v>
       </c>
       <c r="I22" s="1">
-        <v>43831</v>
+        <v>43374</v>
       </c>
       <c r="J22" s="10"/>
       <c r="K22" s="3" t="s">
@@ -3000,13 +2996,13 @@
         <v>53</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H23" s="1">
-        <v>43831</v>
+        <v>43569</v>
       </c>
       <c r="I23" s="1">
-        <v>43831</v>
+        <v>43569</v>
       </c>
       <c r="J23" s="10"/>
       <c r="K23" s="3" t="s">
@@ -3042,13 +3038,13 @@
         <v>53</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H24" s="1">
-        <v>44372</v>
+        <v>43831</v>
       </c>
       <c r="I24" s="1">
-        <v>44372</v>
+        <v>43831</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="3" t="s">
@@ -3072,32 +3068,32 @@
         <v>50</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H25" s="1">
-        <v>44713</v>
+        <v>43831</v>
       </c>
       <c r="I25" s="1">
-        <v>44713</v>
+        <v>43831</v>
       </c>
       <c r="J25" s="10"/>
       <c r="K25" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L25" s="7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M25" s="1">
         <v>46142</v>
@@ -3114,25 +3110,25 @@
         <v>50</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="12" t="s">
-        <v>65</v>
+      <c r="F26" t="s">
+        <v>53</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H26" s="1">
-        <v>44713</v>
+        <v>45330</v>
       </c>
       <c r="I26" s="1">
-        <v>44713</v>
+        <v>45330</v>
       </c>
       <c r="J26" s="10"/>
       <c r="K26" s="3" t="s">
@@ -3156,25 +3152,25 @@
         <v>50</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="12" t="s">
-        <v>65</v>
+      <c r="F27" t="s">
+        <v>53</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H27" s="1">
-        <v>44713</v>
+        <v>45565</v>
       </c>
       <c r="I27" s="1">
-        <v>44713</v>
+        <v>45565</v>
       </c>
       <c r="J27" s="10"/>
       <c r="K27" s="3" t="s">
@@ -3198,25 +3194,25 @@
         <v>50</v>
       </c>
       <c r="C28" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>65</v>
-      </c>
       <c r="G28" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H28" s="1">
-        <v>44713</v>
+        <v>45793</v>
       </c>
       <c r="I28" s="1">
-        <v>44713</v>
+        <v>45793</v>
       </c>
       <c r="J28" s="10"/>
       <c r="K28" s="3" t="s">
@@ -3240,32 +3236,32 @@
         <v>50</v>
       </c>
       <c r="C29" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="12" t="s">
         <v>88</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H29" s="1">
-        <v>44713</v>
+        <v>43304</v>
       </c>
       <c r="I29" s="1">
-        <v>44713</v>
+        <v>43304</v>
       </c>
       <c r="J29" s="10"/>
       <c r="K29" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L29" s="7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M29" s="1">
         <v>46142</v>
@@ -3290,17 +3286,17 @@
       <c r="E30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F30" t="s">
-        <v>53</v>
+      <c r="F30" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="H30" s="1">
-        <v>45330</v>
+        <v>44713</v>
       </c>
       <c r="I30" s="1">
-        <v>45330</v>
+        <v>44713</v>
       </c>
       <c r="J30" s="10"/>
       <c r="K30" s="3" t="s">
@@ -3330,26 +3326,26 @@
         <v>93</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
+        <v>18</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H31" s="1">
-        <v>45344</v>
+        <v>44713</v>
       </c>
       <c r="I31" s="1">
-        <v>45344</v>
+        <v>44713</v>
       </c>
       <c r="J31" s="10"/>
       <c r="K31" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L31" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M31" s="1">
         <v>46142</v>
@@ -3372,26 +3368,26 @@
         <v>95</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H32" s="1">
-        <v>45441</v>
+        <v>44713</v>
       </c>
       <c r="I32" s="1">
-        <v>45441</v>
+        <v>44713</v>
       </c>
       <c r="J32" s="10"/>
       <c r="K32" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L32" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M32" s="1">
         <v>46142</v>
@@ -3414,26 +3410,26 @@
         <v>97</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
+        <v>41</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H33" s="1">
-        <v>45441</v>
+        <v>46789</v>
       </c>
       <c r="I33" s="1">
-        <v>45441</v>
+        <v>46789</v>
       </c>
       <c r="J33" s="10"/>
       <c r="K33" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L33" s="7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M33" s="1">
         <v>46142</v>
@@ -3462,13 +3458,13 @@
         <v>53</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="H34" s="1">
-        <v>45565</v>
+        <v>44713</v>
       </c>
       <c r="I34" s="1">
-        <v>45565</v>
+        <v>44713</v>
       </c>
       <c r="J34" s="10"/>
       <c r="K34" s="3" t="s">
@@ -3492,32 +3488,32 @@
         <v>50</v>
       </c>
       <c r="C35" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" t="s">
-        <v>102</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="H35" s="1">
-        <v>45793</v>
+        <v>45441</v>
       </c>
       <c r="I35" s="1">
-        <v>45793</v>
+        <v>45441</v>
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L35" s="7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M35" s="1">
         <v>46142</v>
@@ -3540,26 +3536,26 @@
         <v>104</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>65</v>
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>53</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="H36" s="1">
-        <v>46789</v>
+        <v>45441</v>
       </c>
       <c r="I36" s="1">
-        <v>46789</v>
+        <v>45441</v>
       </c>
       <c r="J36" s="10"/>
       <c r="K36" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L36" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M36" s="1">
         <v>46142</v>
@@ -3588,7 +3584,7 @@
         <v>53</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H37" s="3">
         <v>42795</v>
@@ -3618,10 +3614,10 @@
         <v>106</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>41</v>
@@ -3630,7 +3626,7 @@
         <v>53</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H38" s="3">
         <v>43131</v>
@@ -3672,7 +3668,7 @@
         <v>53</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H39" s="3">
         <v>45441</v>
@@ -3714,7 +3710,7 @@
         <v>53</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H40" s="3">
         <v>45937</v>
@@ -3756,7 +3752,7 @@
         <v>53</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H41" s="3">
         <v>45937</v>
@@ -3798,7 +3794,7 @@
         <v>53</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H42" s="3">
         <v>45937</v>
@@ -3840,7 +3836,7 @@
         <v>53</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H43" s="3">
         <v>45937</v>
@@ -3882,7 +3878,7 @@
         <v>53</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H44" s="3">
         <v>45937</v>
@@ -3924,7 +3920,7 @@
         <v>53</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H45" s="3">
         <v>45937</v>
@@ -3966,7 +3962,7 @@
         <v>53</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H46" s="3">
         <v>45937</v>
@@ -4008,7 +4004,7 @@
         <v>53</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H47" s="3">
         <v>45937</v>
@@ -4050,7 +4046,7 @@
         <v>53</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H48" s="3">
         <v>45937</v>
@@ -4092,7 +4088,7 @@
         <v>53</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H49" s="3">
         <v>45937</v>
@@ -4134,7 +4130,7 @@
         <v>53</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H50" s="3">
         <v>45937</v>
@@ -4176,7 +4172,7 @@
         <v>53</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H51" s="3">
         <v>45937</v>
@@ -4218,7 +4214,7 @@
         <v>53</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H52" s="1">
         <v>45937</v>
@@ -4257,24 +4253,21 @@
         <v>141</v>
       </c>
       <c r="F53" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="G53" t="s">
-        <v>20</v>
-      </c>
       <c r="H53" s="6">
-        <v>44194</v>
+        <v>44552</v>
       </c>
       <c r="I53" s="6">
-        <v>44194</v>
-      </c>
-      <c r="J53" s="1">
-        <v>46090</v>
+        <v>44552</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L53" s="2">
+        <v>42</v>
+      </c>
+      <c r="L53" s="7">
         <v>5</v>
       </c>
       <c r="M53" s="1">
@@ -4304,7 +4297,7 @@
         <v>19</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H54" s="6">
         <v>44552</v>
@@ -4333,10 +4326,10 @@
         <v>138</v>
       </c>
       <c r="C55" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>141</v>
@@ -4345,18 +4338,18 @@
         <v>19</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H55" s="6">
-        <v>44552</v>
-      </c>
-      <c r="I55" s="6">
-        <v>44552</v>
+        <v>142</v>
+      </c>
+      <c r="H55" s="8">
+        <v>44780</v>
+      </c>
+      <c r="I55" s="8">
+        <v>44780</v>
       </c>
       <c r="K55" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L55" s="7">
+      <c r="L55" s="2">
         <v>5</v>
       </c>
       <c r="M55" s="1">
@@ -4374,25 +4367,25 @@
         <v>138</v>
       </c>
       <c r="C56" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="G56" t="s">
-        <v>20</v>
-      </c>
-      <c r="H56" s="6">
-        <v>44558</v>
-      </c>
-      <c r="I56" s="6">
-        <v>44558</v>
+      <c r="H56" s="8">
+        <v>44780</v>
+      </c>
+      <c r="I56" s="8">
+        <v>44780</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>42</v>
@@ -4415,10 +4408,10 @@
         <v>138</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>141</v>
@@ -4427,18 +4420,18 @@
         <v>19</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H57" s="8">
-        <v>44780</v>
+        <v>45021</v>
       </c>
       <c r="I57" s="8">
-        <v>44780</v>
+        <v>45021</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L57" s="2">
+      <c r="L57" s="7">
         <v>5</v>
       </c>
       <c r="M57" s="1">
@@ -4456,10 +4449,10 @@
         <v>138</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>141</v>
@@ -4468,18 +4461,18 @@
         <v>19</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H58" s="8">
-        <v>44780</v>
+        <v>45021</v>
       </c>
       <c r="I58" s="8">
-        <v>44780</v>
+        <v>45021</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L58" s="2">
+      <c r="L58" s="7">
         <v>5</v>
       </c>
       <c r="M58" s="1">
@@ -4497,25 +4490,25 @@
         <v>138</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F59" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="G59" t="s">
-        <v>20</v>
-      </c>
-      <c r="H59" s="6">
-        <v>44925</v>
-      </c>
-      <c r="I59" s="6">
-        <v>44925</v>
+      <c r="H59" s="8">
+        <v>45292</v>
+      </c>
+      <c r="I59" s="8">
+        <v>45292</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>42</v>
@@ -4538,7 +4531,7 @@
         <v>138</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>152</v>
@@ -4550,18 +4543,18 @@
         <v>19</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H60" s="8">
-        <v>45021</v>
+        <v>45292</v>
       </c>
       <c r="I60" s="8">
-        <v>45021</v>
+        <v>45292</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L60" s="7">
+      <c r="L60" s="2">
         <v>5</v>
       </c>
       <c r="M60" s="1">
@@ -4579,10 +4572,10 @@
         <v>138</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>141</v>
@@ -4591,13 +4584,13 @@
         <v>19</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H61" s="8">
-        <v>45021</v>
+        <v>45658</v>
       </c>
       <c r="I61" s="8">
-        <v>45021</v>
+        <v>45658</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>42</v>
@@ -4620,25 +4613,25 @@
         <v>138</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F62" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="G62" t="s">
-        <v>20</v>
-      </c>
-      <c r="H62" s="6">
-        <v>45289</v>
-      </c>
-      <c r="I62" s="6">
-        <v>45289</v>
+      <c r="H62" s="8">
+        <v>45658</v>
+      </c>
+      <c r="I62" s="8">
+        <v>45658</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>42</v>
@@ -4661,28 +4654,31 @@
         <v>138</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H63" s="8">
-        <v>45292</v>
-      </c>
-      <c r="I63" s="8">
-        <v>45292</v>
+        <v>160</v>
+      </c>
+      <c r="G63" t="s">
+        <v>20</v>
+      </c>
+      <c r="H63" s="6">
+        <v>44194</v>
+      </c>
+      <c r="I63" s="6">
+        <v>44194</v>
+      </c>
+      <c r="J63" s="1">
+        <v>46090</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L63" s="2">
         <v>5</v>
@@ -4702,25 +4698,25 @@
         <v>138</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H64" s="8">
-        <v>45292</v>
-      </c>
-      <c r="I64" s="8">
-        <v>45292</v>
+        <v>160</v>
+      </c>
+      <c r="G64" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64" s="6">
+        <v>44558</v>
+      </c>
+      <c r="I64" s="6">
+        <v>44558</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>42</v>
@@ -4743,30 +4739,30 @@
         <v>138</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
         <v>20</v>
       </c>
       <c r="H65" s="6">
-        <v>45656</v>
+        <v>44925</v>
       </c>
       <c r="I65" s="6">
-        <v>45656</v>
+        <v>44925</v>
       </c>
       <c r="K65" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L65" s="7">
+      <c r="L65" s="2">
         <v>5</v>
       </c>
       <c r="M65" s="1">
@@ -4784,25 +4780,25 @@
         <v>138</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H66" s="8">
-        <v>45658</v>
-      </c>
-      <c r="I66" s="8">
-        <v>45658</v>
+        <v>160</v>
+      </c>
+      <c r="G66" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" s="6">
+        <v>45289</v>
+      </c>
+      <c r="I66" s="6">
+        <v>45289</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>42</v>
@@ -4825,25 +4821,25 @@
         <v>138</v>
       </c>
       <c r="C67" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H67" s="8">
-        <v>45658</v>
-      </c>
-      <c r="I67" s="8">
-        <v>45658</v>
+        <v>160</v>
+      </c>
+      <c r="G67" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" s="6">
+        <v>45656</v>
+      </c>
+      <c r="I67" s="6">
+        <v>45656</v>
       </c>
       <c r="K67" s="3" t="s">
         <v>42</v>
@@ -4865,32 +4861,32 @@
       <c r="B68" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="14" t="s">
         <v>171</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>172</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="G68" t="s">
         <v>174</v>
       </c>
       <c r="H68" s="1">
-        <v>45916</v>
+        <v>45925</v>
       </c>
       <c r="I68" s="1">
-        <v>45916</v>
+        <v>45925</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L68" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M68" s="1">
         <v>46072</v>
@@ -4922,15 +4918,15 @@
         <v>178</v>
       </c>
       <c r="H69" s="1">
-        <v>45923</v>
+        <v>45916</v>
       </c>
       <c r="I69" s="1">
-        <v>45923</v>
+        <v>45916</v>
       </c>
       <c r="K69" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L69" s="7">
+      <c r="L69" s="2">
         <v>5</v>
       </c>
       <c r="M69" s="1">
@@ -4947,7 +4943,7 @@
       <c r="B70" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="2" t="s">
         <v>179</v>
       </c>
       <c r="D70" s="2" t="s">
@@ -4959,8 +4955,8 @@
       <c r="F70" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G70" t="s">
-        <v>181</v>
+      <c r="G70" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="H70" s="1">
         <v>45925</v>
@@ -4989,10 +4985,10 @@
         <v>170</v>
       </c>
       <c r="C71" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>41</v>
@@ -5001,7 +4997,7 @@
         <v>173</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H71" s="1">
         <v>45925</v>
@@ -5030,10 +5026,10 @@
         <v>170</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>41</v>
@@ -5042,7 +5038,7 @@
         <v>173</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H72" s="1">
         <v>45925</v>
@@ -5071,31 +5067,31 @@
         <v>170</v>
       </c>
       <c r="C73" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="E73" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>174</v>
+      <c r="G73" t="s">
+        <v>89</v>
       </c>
       <c r="H73" s="1">
-        <v>45925</v>
+        <v>45932</v>
       </c>
       <c r="I73" s="1">
-        <v>45925</v>
+        <v>45932</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L73" s="2">
-        <v>15</v>
+      <c r="L73" s="7">
+        <v>5</v>
       </c>
       <c r="M73" s="1">
         <v>46072</v>
@@ -5112,10 +5108,10 @@
         <v>170</v>
       </c>
       <c r="C74" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>18</v>
@@ -5124,7 +5120,7 @@
         <v>173</v>
       </c>
       <c r="G74" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="H74" s="1">
         <v>45932</v>
@@ -5165,7 +5161,7 @@
         <v>173</v>
       </c>
       <c r="G75" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H75" s="1">
         <v>45932</v>
@@ -5194,10 +5190,10 @@
         <v>170</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>18</v>
@@ -5205,14 +5201,14 @@
       <c r="F76" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G76" t="s">
-        <v>192</v>
+      <c r="G76" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="H76" s="1">
-        <v>45932</v>
+        <v>45923</v>
       </c>
       <c r="I76" s="1">
-        <v>45932</v>
+        <v>45923</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>42</v>
@@ -5504,25 +5500,25 @@
         <v>207</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>208</v>
+        <v>41</v>
       </c>
       <c r="F84" t="s">
         <v>198</v>
       </c>
       <c r="G84" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="H84" s="1">
-        <v>43705</v>
+        <v>45826</v>
       </c>
       <c r="I84" s="1">
-        <v>43705</v>
+        <v>45826</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L84" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M84" s="1">
         <v>46128</v>
@@ -5539,7 +5535,7 @@
         <v>196</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>41</v>
@@ -5551,10 +5547,10 @@
         <v>199</v>
       </c>
       <c r="H85" s="1">
-        <v>45826</v>
+        <v>45833</v>
       </c>
       <c r="I85" s="1">
-        <v>45826</v>
+        <v>45833</v>
       </c>
       <c r="K85" s="3" t="s">
         <v>42</v>
@@ -5577,28 +5573,28 @@
         <v>196</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="F86" t="s">
         <v>198</v>
       </c>
       <c r="G86" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="H86" s="1">
-        <v>45833</v>
+        <v>43705</v>
       </c>
       <c r="I86" s="1">
-        <v>45833</v>
+        <v>43705</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L86" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M86" s="1">
         <v>46128</v>
@@ -5608,7 +5604,7 @@
       </c>
     </row>
     <row r="87" spans="1:14">
-      <c r="A87" s="15" t="s">
+      <c r="A87" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B87" s="2" t="s">
@@ -5621,13 +5617,13 @@
         <v>215</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>216</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>217</v>
+        <v>63</v>
       </c>
       <c r="H87" s="1">
         <v>45303</v>
@@ -5638,14 +5634,14 @@
       <c r="K87" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L87" s="2">
-        <v>15</v>
+      <c r="L87" s="7">
+        <v>5</v>
       </c>
       <c r="M87" s="1">
         <v>45814</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -5656,10 +5652,10 @@
         <v>213</v>
       </c>
       <c r="C88" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>18</v>
@@ -5668,7 +5664,7 @@
         <v>216</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H88" s="1">
         <v>45303</v>
@@ -5686,7 +5682,7 @@
         <v>45814</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -5697,10 +5693,10 @@
         <v>213</v>
       </c>
       <c r="C89" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>18</v>
@@ -5709,7 +5705,7 @@
         <v>216</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H89" s="1">
         <v>45303</v>
@@ -5720,14 +5716,14 @@
       <c r="K89" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L89" s="7">
+      <c r="L89" s="2">
         <v>5</v>
       </c>
       <c r="M89" s="1">
         <v>45814</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -5738,10 +5734,10 @@
         <v>213</v>
       </c>
       <c r="C90" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>18</v>
@@ -5750,7 +5746,7 @@
         <v>216</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H90" s="1">
         <v>45303</v>
@@ -5768,7 +5764,7 @@
         <v>45814</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -5791,7 +5787,7 @@
         <v>216</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H91" s="1">
         <v>45303</v>
@@ -5802,14 +5798,14 @@
       <c r="K91" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L91" s="2">
+      <c r="L91" s="7">
         <v>5</v>
       </c>
       <c r="M91" s="1">
         <v>45814</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -5832,7 +5828,7 @@
         <v>216</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H92" s="1">
         <v>45303</v>
@@ -5850,7 +5846,7 @@
         <v>45814</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -5873,7 +5869,7 @@
         <v>216</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H93" s="1">
         <v>45303</v>
@@ -5884,14 +5880,14 @@
       <c r="K93" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L93" s="7">
+      <c r="L93" s="2">
         <v>5</v>
       </c>
       <c r="M93" s="1">
         <v>45814</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -5914,7 +5910,7 @@
         <v>216</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H94" s="1">
         <v>45303</v>
@@ -5932,7 +5928,7 @@
         <v>45814</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -5955,7 +5951,7 @@
         <v>216</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="H95" s="1">
         <v>45303</v>
@@ -5966,14 +5962,14 @@
       <c r="K95" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L95" s="2">
+      <c r="L95" s="7">
         <v>5</v>
       </c>
       <c r="M95" s="1">
         <v>45814</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -5993,10 +5989,10 @@
         <v>18</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>174</v>
+        <v>19</v>
+      </c>
+      <c r="G96" t="s">
+        <v>20</v>
       </c>
       <c r="H96" s="1">
         <v>45303</v>
@@ -6007,18 +6003,18 @@
       <c r="K96" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L96" s="7">
+      <c r="L96" s="2">
         <v>5</v>
       </c>
       <c r="M96" s="1">
         <v>45814</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="1:14">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="15" t="s">
         <v>212</v>
       </c>
       <c r="B97" s="2" t="s">
@@ -6028,16 +6024,16 @@
         <v>236</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>216</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="H97" s="1">
         <v>45303</v>
@@ -6048,14 +6044,14 @@
       <c r="K97" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L97" s="7">
-        <v>5</v>
+      <c r="L97" s="2">
+        <v>15</v>
       </c>
       <c r="M97" s="1">
         <v>45814</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -6075,10 +6071,10 @@
         <v>18</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="H98" s="1">
         <v>45303</v>
@@ -6089,14 +6085,14 @@
       <c r="K98" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L98" s="2">
+      <c r="L98" s="7">
         <v>5</v>
       </c>
       <c r="M98" s="1">
         <v>45814</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -6107,19 +6103,19 @@
         <v>213</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="E99" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G99" t="s">
-        <v>20</v>
+      <c r="G99" s="2" t="s">
+        <v>237</v>
       </c>
       <c r="H99" s="1">
         <v>45303</v>
@@ -6137,7 +6133,7 @@
         <v>45814</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -6154,13 +6150,13 @@
         <v>244</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>245</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="H100" s="1">
         <v>45303</v>
@@ -6178,7 +6174,7 @@
         <v>45814</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -6201,7 +6197,7 @@
         <v>245</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="H101" s="1">
         <v>45303</v>
@@ -6219,7 +6215,7 @@
         <v>45814</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -6324,7 +6320,7 @@
         <v>198</v>
       </c>
       <c r="G104" t="s">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="H104" s="1">
         <v>44375</v>
@@ -6343,21 +6339,21 @@
         <v>46122</v>
       </c>
       <c r="N104" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" customFormat="1">
+      <c r="A105" s="17" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" customFormat="1">
-      <c r="A105" t="s">
+      <c r="B105" t="s">
         <v>262</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="D105" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>18</v>
@@ -6366,13 +6362,13 @@
         <v>198</v>
       </c>
       <c r="G105" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="H105" s="1">
-        <v>42734</v>
+        <v>44349</v>
       </c>
       <c r="I105" s="1">
-        <v>43571</v>
+        <v>43486</v>
       </c>
       <c r="J105" s="1">
         <v>45428</v>
@@ -6380,26 +6376,26 @@
       <c r="K105" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L105" s="2">
+      <c r="L105" s="7">
         <v>5</v>
       </c>
       <c r="M105" s="2"/>
       <c r="N105" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" t="s">
+        <v>261</v>
+      </c>
+      <c r="B106" t="s">
         <v>262</v>
       </c>
-      <c r="B106" t="s">
-        <v>263</v>
-      </c>
-      <c r="C106" t="s">
+      <c r="C106" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="D106" t="s">
-        <v>268</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>18</v>
@@ -6407,39 +6403,40 @@
       <c r="F106" t="s">
         <v>198</v>
       </c>
-      <c r="G106" s="2" t="s">
-        <v>269</v>
+      <c r="G106" t="s">
+        <v>268</v>
       </c>
       <c r="H106" s="1">
-        <v>42990</v>
+        <v>44617</v>
       </c>
       <c r="I106" s="1">
-        <v>45967</v>
-      </c>
-      <c r="J106"/>
+        <v>45225</v>
+      </c>
       <c r="K106" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L106" s="2">
-        <v>5</v>
-      </c>
-      <c r="M106"/>
+      <c r="L106" s="7">
+        <v>5</v>
+      </c>
+      <c r="M106" s="1">
+        <v>45817</v>
+      </c>
       <c r="N106" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" t="s">
+        <v>261</v>
+      </c>
+      <c r="B107" t="s">
         <v>262</v>
       </c>
-      <c r="B107" t="s">
-        <v>263</v>
-      </c>
       <c r="C107" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>18</v>
@@ -6447,14 +6444,14 @@
       <c r="F107" t="s">
         <v>198</v>
       </c>
-      <c r="G107" s="2" t="s">
-        <v>269</v>
+      <c r="G107" t="s">
+        <v>268</v>
       </c>
       <c r="H107" s="1">
-        <v>42990</v>
+        <v>44617</v>
       </c>
       <c r="I107" s="1">
-        <v>45230</v>
+        <v>45225</v>
       </c>
       <c r="K107" s="3" t="s">
         <v>42</v>
@@ -6463,21 +6460,21 @@
         <v>5</v>
       </c>
       <c r="N107" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" t="s">
+        <v>261</v>
+      </c>
+      <c r="B108" t="s">
         <v>262</v>
       </c>
-      <c r="B108" t="s">
-        <v>263</v>
-      </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" t="s">
+        <v>271</v>
+      </c>
+      <c r="D108" t="s">
         <v>272</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>18</v>
@@ -6486,36 +6483,38 @@
         <v>198</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H108" s="1">
         <v>42990</v>
       </c>
       <c r="I108" s="1">
-        <v>45230</v>
-      </c>
+        <v>45967</v>
+      </c>
+      <c r="J108"/>
       <c r="K108" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L108" s="7">
-        <v>5</v>
-      </c>
+      <c r="L108" s="2">
+        <v>5</v>
+      </c>
+      <c r="M108"/>
       <c r="N108" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" t="s">
+        <v>261</v>
+      </c>
+      <c r="B109" t="s">
         <v>262</v>
-      </c>
-      <c r="B109" t="s">
-        <v>263</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>274</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>18</v>
@@ -6523,40 +6522,37 @@
       <c r="F109" t="s">
         <v>198</v>
       </c>
-      <c r="G109" t="s">
-        <v>20</v>
+      <c r="G109" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="H109" s="1">
-        <v>43132</v>
+        <v>42990</v>
       </c>
       <c r="I109" s="1">
-        <v>43571</v>
-      </c>
-      <c r="J109" s="1">
-        <v>45428</v>
+        <v>45230</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L109" s="2">
         <v>5</v>
       </c>
       <c r="N109" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" t="s">
+        <v>261</v>
+      </c>
+      <c r="B110" t="s">
         <v>262</v>
-      </c>
-      <c r="B110" t="s">
-        <v>263</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>275</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>18</v>
@@ -6564,40 +6560,37 @@
       <c r="F110" t="s">
         <v>198</v>
       </c>
-      <c r="G110" t="s">
-        <v>20</v>
+      <c r="G110" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="H110" s="1">
-        <v>43500</v>
+        <v>42990</v>
       </c>
       <c r="I110" s="1">
-        <v>43599</v>
-      </c>
-      <c r="J110" s="1">
-        <v>45428</v>
+        <v>45230</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L110" s="2">
+        <v>42</v>
+      </c>
+      <c r="L110" s="7">
         <v>5</v>
       </c>
       <c r="N110" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" t="s">
+        <v>261</v>
+      </c>
+      <c r="B111" t="s">
         <v>262</v>
-      </c>
-      <c r="B111" t="s">
-        <v>263</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>276</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>18</v>
@@ -6605,14 +6598,14 @@
       <c r="F111" t="s">
         <v>198</v>
       </c>
-      <c r="G111" t="s">
-        <v>277</v>
+      <c r="G111" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="H111" s="1">
-        <v>43712</v>
+        <v>44349</v>
       </c>
       <c r="I111" s="1">
-        <v>43570</v>
+        <v>43511</v>
       </c>
       <c r="J111" s="1">
         <v>45428</v>
@@ -6623,23 +6616,22 @@
       <c r="L111" s="2">
         <v>5</v>
       </c>
-      <c r="M111" s="1"/>
       <c r="N111" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" t="s">
+        <v>261</v>
+      </c>
+      <c r="B112" t="s">
         <v>262</v>
       </c>
-      <c r="B112" t="s">
-        <v>263</v>
-      </c>
       <c r="C112" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>18</v>
@@ -6647,17 +6639,17 @@
       <c r="F112" t="s">
         <v>198</v>
       </c>
-      <c r="G112" t="s">
-        <v>20</v>
+      <c r="G112" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="H112" s="1">
-        <v>43819</v>
+        <v>44617</v>
       </c>
       <c r="I112" s="1">
-        <v>43609</v>
+        <v>43486</v>
       </c>
       <c r="J112" s="1">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>21</v>
@@ -6666,21 +6658,21 @@
         <v>5</v>
       </c>
       <c r="N112" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" t="s">
+        <v>261</v>
+      </c>
+      <c r="B113" t="s">
         <v>262</v>
       </c>
-      <c r="B113" t="s">
-        <v>263</v>
-      </c>
       <c r="C113" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>18</v>
@@ -6688,17 +6680,17 @@
       <c r="F113" t="s">
         <v>198</v>
       </c>
-      <c r="G113" t="s">
-        <v>20</v>
+      <c r="G113" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="H113" s="1">
-        <v>44176</v>
+        <v>44734</v>
       </c>
       <c r="I113" s="1">
-        <v>43297</v>
+        <v>43587</v>
       </c>
       <c r="J113" s="1">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="K113" s="3" t="s">
         <v>21</v>
@@ -6707,21 +6699,21 @@
         <v>5</v>
       </c>
       <c r="N113" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="114" spans="1:14">
-      <c r="A114" s="17" t="s">
+      <c r="A114" t="s">
+        <v>261</v>
+      </c>
+      <c r="B114" t="s">
         <v>262</v>
       </c>
-      <c r="B114" t="s">
-        <v>263</v>
-      </c>
       <c r="C114" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>18</v>
@@ -6730,13 +6722,13 @@
         <v>198</v>
       </c>
       <c r="G114" t="s">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="H114" s="1">
-        <v>44349</v>
+        <v>42734</v>
       </c>
       <c r="I114" s="1">
-        <v>43486</v>
+        <v>43571</v>
       </c>
       <c r="J114" s="1">
         <v>45428</v>
@@ -6744,25 +6736,25 @@
       <c r="K114" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L114" s="7">
+      <c r="L114" s="2">
         <v>5</v>
       </c>
       <c r="N114" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" t="s">
+        <v>261</v>
+      </c>
+      <c r="B115" t="s">
         <v>262</v>
       </c>
-      <c r="B115" t="s">
-        <v>263</v>
-      </c>
       <c r="C115" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>18</v>
@@ -6770,14 +6762,14 @@
       <c r="F115" t="s">
         <v>198</v>
       </c>
-      <c r="G115" s="2" t="s">
-        <v>269</v>
+      <c r="G115" t="s">
+        <v>20</v>
       </c>
       <c r="H115" s="1">
-        <v>44349</v>
+        <v>43132</v>
       </c>
       <c r="I115" s="1">
-        <v>43511</v>
+        <v>43571</v>
       </c>
       <c r="J115" s="1">
         <v>45428</v>
@@ -6789,21 +6781,21 @@
         <v>5</v>
       </c>
       <c r="N115" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" t="s">
+        <v>261</v>
+      </c>
+      <c r="B116" t="s">
         <v>262</v>
       </c>
-      <c r="B116" t="s">
-        <v>263</v>
-      </c>
       <c r="C116" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>18</v>
@@ -6815,10 +6807,10 @@
         <v>20</v>
       </c>
       <c r="H116" s="1">
-        <v>44349</v>
+        <v>43500</v>
       </c>
       <c r="I116" s="1">
-        <v>43308</v>
+        <v>43599</v>
       </c>
       <c r="J116" s="1">
         <v>45428</v>
@@ -6830,21 +6822,21 @@
         <v>5</v>
       </c>
       <c r="N116" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" t="s">
+        <v>261</v>
+      </c>
+      <c r="B117" t="s">
         <v>262</v>
       </c>
-      <c r="B117" t="s">
-        <v>263</v>
-      </c>
       <c r="C117" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>18</v>
@@ -6856,10 +6848,10 @@
         <v>20</v>
       </c>
       <c r="H117" s="1">
-        <v>44349</v>
+        <v>43819</v>
       </c>
       <c r="I117" s="1">
-        <v>43328</v>
+        <v>43609</v>
       </c>
       <c r="J117" s="1">
         <v>45428</v>
@@ -6871,21 +6863,21 @@
         <v>5</v>
       </c>
       <c r="N117" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" t="s">
+        <v>261</v>
+      </c>
+      <c r="B118" t="s">
         <v>262</v>
       </c>
-      <c r="B118" t="s">
-        <v>263</v>
-      </c>
       <c r="C118" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>18</v>
@@ -6897,10 +6889,10 @@
         <v>20</v>
       </c>
       <c r="H118" s="1">
-        <v>44349</v>
+        <v>44176</v>
       </c>
       <c r="I118" s="1">
-        <v>43328</v>
+        <v>43297</v>
       </c>
       <c r="J118" s="1">
         <v>45428</v>
@@ -6908,25 +6900,25 @@
       <c r="K118" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L118" s="7">
+      <c r="L118" s="2">
         <v>5</v>
       </c>
       <c r="N118" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" t="s">
+        <v>261</v>
+      </c>
+      <c r="B119" t="s">
         <v>262</v>
       </c>
-      <c r="B119" t="s">
-        <v>263</v>
-      </c>
       <c r="C119" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>18</v>
@@ -6941,7 +6933,7 @@
         <v>44349</v>
       </c>
       <c r="I119" s="1">
-        <v>43329</v>
+        <v>43308</v>
       </c>
       <c r="J119" s="1">
         <v>45428</v>
@@ -6953,21 +6945,21 @@
         <v>5</v>
       </c>
       <c r="N119" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" t="s">
+        <v>261</v>
+      </c>
+      <c r="B120" t="s">
         <v>262</v>
       </c>
-      <c r="B120" t="s">
-        <v>263</v>
-      </c>
       <c r="C120" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>18</v>
@@ -6982,7 +6974,7 @@
         <v>44349</v>
       </c>
       <c r="I120" s="1">
-        <v>43339</v>
+        <v>43328</v>
       </c>
       <c r="J120" s="1">
         <v>45428</v>
@@ -6990,25 +6982,25 @@
       <c r="K120" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L120" s="2">
+      <c r="L120" s="7">
         <v>5</v>
       </c>
       <c r="N120" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" t="s">
+        <v>261</v>
+      </c>
+      <c r="B121" t="s">
         <v>262</v>
       </c>
-      <c r="B121" t="s">
-        <v>263</v>
-      </c>
       <c r="C121" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>18</v>
@@ -7023,7 +7015,7 @@
         <v>44349</v>
       </c>
       <c r="I121" s="1">
-        <v>43353</v>
+        <v>43328</v>
       </c>
       <c r="J121" s="1">
         <v>45428</v>
@@ -7035,21 +7027,21 @@
         <v>5</v>
       </c>
       <c r="N121" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" t="s">
+        <v>261</v>
+      </c>
+      <c r="B122" t="s">
         <v>262</v>
       </c>
-      <c r="B122" t="s">
-        <v>263</v>
-      </c>
       <c r="C122" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>18</v>
@@ -7064,7 +7056,7 @@
         <v>44349</v>
       </c>
       <c r="I122" s="1">
-        <v>43415</v>
+        <v>43329</v>
       </c>
       <c r="J122" s="1">
         <v>45428</v>
@@ -7072,25 +7064,25 @@
       <c r="K122" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L122" s="7">
+      <c r="L122" s="2">
         <v>5</v>
       </c>
       <c r="N122" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" t="s">
+        <v>261</v>
+      </c>
+      <c r="B123" t="s">
         <v>262</v>
       </c>
-      <c r="B123" t="s">
-        <v>263</v>
-      </c>
       <c r="C123" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>18</v>
@@ -7105,7 +7097,7 @@
         <v>44349</v>
       </c>
       <c r="I123" s="1">
-        <v>43416</v>
+        <v>43339</v>
       </c>
       <c r="J123" s="1">
         <v>45428</v>
@@ -7117,21 +7109,21 @@
         <v>5</v>
       </c>
       <c r="N123" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" t="s">
+        <v>261</v>
+      </c>
+      <c r="B124" t="s">
         <v>262</v>
       </c>
-      <c r="B124" t="s">
-        <v>263</v>
-      </c>
       <c r="C124" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>18</v>
@@ -7146,7 +7138,7 @@
         <v>44349</v>
       </c>
       <c r="I124" s="1">
-        <v>43472</v>
+        <v>43353</v>
       </c>
       <c r="J124" s="1">
         <v>45428</v>
@@ -7154,25 +7146,25 @@
       <c r="K124" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L124" s="2">
+      <c r="L124" s="7">
         <v>5</v>
       </c>
       <c r="N124" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" t="s">
+        <v>261</v>
+      </c>
+      <c r="B125" t="s">
         <v>262</v>
       </c>
-      <c r="B125" t="s">
-        <v>263</v>
-      </c>
       <c r="C125" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>18</v>
@@ -7187,7 +7179,7 @@
         <v>44349</v>
       </c>
       <c r="I125" s="1">
-        <v>43480</v>
+        <v>43415</v>
       </c>
       <c r="J125" s="1">
         <v>45428</v>
@@ -7199,21 +7191,21 @@
         <v>5</v>
       </c>
       <c r="N125" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" t="s">
+        <v>261</v>
+      </c>
+      <c r="B126" t="s">
         <v>262</v>
       </c>
-      <c r="B126" t="s">
-        <v>263</v>
-      </c>
       <c r="C126" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>18</v>
@@ -7228,7 +7220,7 @@
         <v>44349</v>
       </c>
       <c r="I126" s="1">
-        <v>43500</v>
+        <v>43416</v>
       </c>
       <c r="J126" s="1">
         <v>45428</v>
@@ -7236,25 +7228,25 @@
       <c r="K126" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L126" s="7">
+      <c r="L126" s="2">
         <v>5</v>
       </c>
       <c r="N126" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" t="s">
+        <v>261</v>
+      </c>
+      <c r="B127" t="s">
         <v>262</v>
       </c>
-      <c r="B127" t="s">
-        <v>263</v>
-      </c>
       <c r="C127" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>18</v>
@@ -7269,7 +7261,7 @@
         <v>44349</v>
       </c>
       <c r="I127" s="1">
-        <v>43509</v>
+        <v>43472</v>
       </c>
       <c r="J127" s="1">
         <v>45428</v>
@@ -7281,21 +7273,21 @@
         <v>5</v>
       </c>
       <c r="N127" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" t="s">
+        <v>261</v>
+      </c>
+      <c r="B128" t="s">
         <v>262</v>
       </c>
-      <c r="B128" t="s">
-        <v>263</v>
-      </c>
       <c r="C128" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>18</v>
@@ -7310,7 +7302,7 @@
         <v>44349</v>
       </c>
       <c r="I128" s="1">
-        <v>43524</v>
+        <v>43480</v>
       </c>
       <c r="J128" s="1">
         <v>45428</v>
@@ -7318,25 +7310,25 @@
       <c r="K128" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L128" s="2">
+      <c r="L128" s="7">
         <v>5</v>
       </c>
       <c r="N128" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" t="s">
+        <v>261</v>
+      </c>
+      <c r="B129" t="s">
         <v>262</v>
       </c>
-      <c r="B129" t="s">
-        <v>263</v>
-      </c>
       <c r="C129" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>18</v>
@@ -7351,7 +7343,7 @@
         <v>44349</v>
       </c>
       <c r="I129" s="1">
-        <v>43545</v>
+        <v>43500</v>
       </c>
       <c r="J129" s="1">
         <v>45428</v>
@@ -7363,21 +7355,21 @@
         <v>5</v>
       </c>
       <c r="N129" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" t="s">
+        <v>261</v>
+      </c>
+      <c r="B130" t="s">
         <v>262</v>
       </c>
-      <c r="B130" t="s">
-        <v>263</v>
-      </c>
       <c r="C130" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>18</v>
@@ -7392,7 +7384,7 @@
         <v>44349</v>
       </c>
       <c r="I130" s="1">
-        <v>43545</v>
+        <v>43509</v>
       </c>
       <c r="J130" s="1">
         <v>45428</v>
@@ -7400,25 +7392,25 @@
       <c r="K130" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L130" s="7">
+      <c r="L130" s="2">
         <v>5</v>
       </c>
       <c r="N130" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" t="s">
+        <v>261</v>
+      </c>
+      <c r="B131" t="s">
         <v>262</v>
       </c>
-      <c r="B131" t="s">
-        <v>263</v>
-      </c>
       <c r="C131" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>18</v>
@@ -7433,7 +7425,7 @@
         <v>44349</v>
       </c>
       <c r="I131" s="1">
-        <v>43545</v>
+        <v>43524</v>
       </c>
       <c r="J131" s="1">
         <v>45428</v>
@@ -7445,21 +7437,21 @@
         <v>5</v>
       </c>
       <c r="N131" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" t="s">
+        <v>261</v>
+      </c>
+      <c r="B132" t="s">
         <v>262</v>
       </c>
-      <c r="B132" t="s">
-        <v>263</v>
-      </c>
       <c r="C132" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>18</v>
@@ -7474,7 +7466,7 @@
         <v>44349</v>
       </c>
       <c r="I132" s="1">
-        <v>43549</v>
+        <v>43545</v>
       </c>
       <c r="J132" s="1">
         <v>45428</v>
@@ -7482,25 +7474,25 @@
       <c r="K132" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L132" s="2">
+      <c r="L132" s="7">
         <v>5</v>
       </c>
       <c r="N132" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" t="s">
+        <v>261</v>
+      </c>
+      <c r="B133" t="s">
         <v>262</v>
       </c>
-      <c r="B133" t="s">
-        <v>263</v>
-      </c>
       <c r="C133" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>18</v>
@@ -7515,7 +7507,7 @@
         <v>44349</v>
       </c>
       <c r="I133" s="1">
-        <v>43551</v>
+        <v>43545</v>
       </c>
       <c r="J133" s="1">
         <v>45428</v>
@@ -7527,21 +7519,21 @@
         <v>5</v>
       </c>
       <c r="N133" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" t="s">
+        <v>261</v>
+      </c>
+      <c r="B134" t="s">
         <v>262</v>
       </c>
-      <c r="B134" t="s">
-        <v>263</v>
-      </c>
       <c r="C134" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>18</v>
@@ -7556,7 +7548,7 @@
         <v>44349</v>
       </c>
       <c r="I134" s="1">
-        <v>43461</v>
+        <v>43545</v>
       </c>
       <c r="J134" s="1">
         <v>45428</v>
@@ -7564,25 +7556,25 @@
       <c r="K134" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L134" s="7">
+      <c r="L134" s="2">
         <v>5</v>
       </c>
       <c r="N134" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" t="s">
+        <v>261</v>
+      </c>
+      <c r="B135" t="s">
         <v>262</v>
       </c>
-      <c r="B135" t="s">
-        <v>263</v>
-      </c>
       <c r="C135" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>18</v>
@@ -7597,7 +7589,7 @@
         <v>44349</v>
       </c>
       <c r="I135" s="1">
-        <v>43543</v>
+        <v>43549</v>
       </c>
       <c r="J135" s="1">
         <v>45428</v>
@@ -7605,25 +7597,25 @@
       <c r="K135" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L135" s="7">
+      <c r="L135" s="2">
         <v>5</v>
       </c>
       <c r="N135" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" t="s">
+        <v>261</v>
+      </c>
+      <c r="B136" t="s">
         <v>262</v>
       </c>
-      <c r="B136" t="s">
-        <v>263</v>
-      </c>
       <c r="C136" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>18</v>
@@ -7632,13 +7624,13 @@
         <v>198</v>
       </c>
       <c r="G136" t="s">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="H136" s="1">
         <v>44349</v>
       </c>
       <c r="I136" s="1">
-        <v>43308</v>
+        <v>43551</v>
       </c>
       <c r="J136" s="1">
         <v>45428</v>
@@ -7646,25 +7638,25 @@
       <c r="K136" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L136" s="2">
+      <c r="L136" s="7">
         <v>5</v>
       </c>
       <c r="N136" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" t="s">
+        <v>261</v>
+      </c>
+      <c r="B137" t="s">
         <v>262</v>
       </c>
-      <c r="B137" t="s">
-        <v>263</v>
-      </c>
       <c r="C137" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>18</v>
@@ -7673,13 +7665,13 @@
         <v>198</v>
       </c>
       <c r="G137" t="s">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="H137" s="1">
         <v>44349</v>
       </c>
       <c r="I137" s="1">
-        <v>43308</v>
+        <v>43461</v>
       </c>
       <c r="J137" s="1">
         <v>45428</v>
@@ -7691,21 +7683,21 @@
         <v>5</v>
       </c>
       <c r="N137" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" t="s">
+        <v>261</v>
+      </c>
+      <c r="B138" t="s">
         <v>262</v>
       </c>
-      <c r="B138" t="s">
-        <v>263</v>
-      </c>
       <c r="C138" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>18</v>
@@ -7714,13 +7706,13 @@
         <v>198</v>
       </c>
       <c r="G138" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="H138" s="1">
         <v>44349</v>
       </c>
       <c r="I138" s="1">
-        <v>43304</v>
+        <v>43543</v>
       </c>
       <c r="J138" s="1">
         <v>45428</v>
@@ -7728,26 +7720,25 @@
       <c r="K138" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L138" s="2">
-        <v>5</v>
-      </c>
-      <c r="M138" s="1"/>
+      <c r="L138" s="7">
+        <v>5</v>
+      </c>
       <c r="N138" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" t="s">
+        <v>261</v>
+      </c>
+      <c r="B139" t="s">
         <v>262</v>
       </c>
-      <c r="B139" t="s">
-        <v>263</v>
-      </c>
       <c r="C139" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>18</v>
@@ -7756,13 +7747,13 @@
         <v>198</v>
       </c>
       <c r="G139" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="H139" s="1">
-        <v>44349</v>
+        <v>44426</v>
       </c>
       <c r="I139" s="1">
-        <v>43325</v>
+        <v>43511</v>
       </c>
       <c r="J139" s="1">
         <v>45428</v>
@@ -7773,23 +7764,22 @@
       <c r="L139" s="7">
         <v>5</v>
       </c>
-      <c r="M139" s="1"/>
       <c r="N139" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" t="s">
+        <v>261</v>
+      </c>
+      <c r="B140" t="s">
         <v>262</v>
       </c>
-      <c r="B140" t="s">
-        <v>263</v>
-      </c>
       <c r="C140" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>18</v>
@@ -7798,40 +7788,39 @@
         <v>198</v>
       </c>
       <c r="G140" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="H140" s="1">
-        <v>44349</v>
+        <v>44617</v>
       </c>
       <c r="I140" s="1">
-        <v>43346</v>
+        <v>43503</v>
       </c>
       <c r="J140" s="1">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="K140" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L140" s="7">
-        <v>5</v>
-      </c>
-      <c r="M140" s="1"/>
+      <c r="L140" s="2">
+        <v>5</v>
+      </c>
       <c r="N140" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" t="s">
+        <v>261</v>
+      </c>
+      <c r="B141" t="s">
         <v>262</v>
       </c>
-      <c r="B141" t="s">
-        <v>263</v>
-      </c>
       <c r="C141" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>18</v>
@@ -7840,13 +7829,13 @@
         <v>198</v>
       </c>
       <c r="G141" t="s">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="H141" s="1">
-        <v>44349</v>
+        <v>45656</v>
       </c>
       <c r="I141" s="1">
-        <v>43551</v>
+        <v>43559</v>
       </c>
       <c r="J141" s="1">
         <v>45428</v>
@@ -7854,26 +7843,25 @@
       <c r="K141" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L141" s="2">
-        <v>5</v>
-      </c>
-      <c r="M141" s="1"/>
+      <c r="L141" s="7">
+        <v>5</v>
+      </c>
       <c r="N141" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" t="s">
+        <v>261</v>
+      </c>
+      <c r="B142" t="s">
         <v>262</v>
       </c>
-      <c r="B142" t="s">
-        <v>263</v>
-      </c>
       <c r="C142" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>18</v>
@@ -7885,13 +7873,13 @@
         <v>20</v>
       </c>
       <c r="H142" s="1">
-        <v>44426</v>
+        <v>45820</v>
       </c>
       <c r="I142" s="1">
-        <v>43511</v>
+        <v>43264</v>
       </c>
       <c r="J142" s="1">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="K142" s="3" t="s">
         <v>21</v>
@@ -7900,21 +7888,21 @@
         <v>5</v>
       </c>
       <c r="N142" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" t="s">
+        <v>261</v>
+      </c>
+      <c r="B143" t="s">
         <v>262</v>
       </c>
-      <c r="B143" t="s">
-        <v>263</v>
-      </c>
       <c r="C143" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>18</v>
@@ -7923,39 +7911,39 @@
         <v>198</v>
       </c>
       <c r="G143" t="s">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="H143" s="1">
-        <v>44617</v>
+        <v>45820</v>
       </c>
       <c r="I143" s="1">
-        <v>45225</v>
+        <v>43271</v>
+      </c>
+      <c r="J143" s="1">
+        <v>45432</v>
       </c>
       <c r="K143" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L143" s="7">
-        <v>5</v>
-      </c>
-      <c r="M143" s="1">
-        <v>45817</v>
+        <v>21</v>
+      </c>
+      <c r="L143" s="2">
+        <v>5</v>
       </c>
       <c r="N143" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" t="s">
+        <v>261</v>
+      </c>
+      <c r="B144" t="s">
         <v>262</v>
       </c>
-      <c r="B144" t="s">
-        <v>263</v>
-      </c>
       <c r="C144" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>18</v>
@@ -7964,36 +7952,39 @@
         <v>198</v>
       </c>
       <c r="G144" t="s">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="H144" s="1">
-        <v>44617</v>
+        <v>46013</v>
       </c>
       <c r="I144" s="1">
-        <v>45225</v>
+        <v>43294</v>
+      </c>
+      <c r="J144" s="1">
+        <v>45428</v>
       </c>
       <c r="K144" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L144" s="2">
+        <v>21</v>
+      </c>
+      <c r="L144" s="7">
         <v>5</v>
       </c>
       <c r="N144" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" t="s">
+        <v>261</v>
+      </c>
+      <c r="B145" t="s">
         <v>262</v>
       </c>
-      <c r="B145" t="s">
-        <v>263</v>
-      </c>
       <c r="C145" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>18</v>
@@ -8001,40 +7992,40 @@
       <c r="F145" t="s">
         <v>198</v>
       </c>
-      <c r="G145" s="2" t="s">
-        <v>269</v>
+      <c r="G145" t="s">
+        <v>311</v>
       </c>
       <c r="H145" s="1">
-        <v>44617</v>
+        <v>44349</v>
       </c>
       <c r="I145" s="1">
-        <v>43486</v>
+        <v>43308</v>
       </c>
       <c r="J145" s="1">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K145" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L145" s="7">
+      <c r="L145" s="2">
         <v>5</v>
       </c>
       <c r="N145" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" t="s">
+        <v>261</v>
+      </c>
+      <c r="B146" t="s">
         <v>262</v>
       </c>
-      <c r="B146" t="s">
-        <v>263</v>
-      </c>
       <c r="C146" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>18</v>
@@ -8043,39 +8034,39 @@
         <v>198</v>
       </c>
       <c r="G146" t="s">
-        <v>20</v>
+        <v>311</v>
       </c>
       <c r="H146" s="1">
-        <v>44617</v>
+        <v>44349</v>
       </c>
       <c r="I146" s="1">
-        <v>43503</v>
+        <v>43308</v>
       </c>
       <c r="J146" s="1">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K146" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L146" s="2">
+      <c r="L146" s="7">
         <v>5</v>
       </c>
       <c r="N146" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" t="s">
+        <v>261</v>
+      </c>
+      <c r="B147" t="s">
         <v>262</v>
       </c>
-      <c r="B147" t="s">
-        <v>263</v>
-      </c>
       <c r="C147" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>18</v>
@@ -8083,17 +8074,17 @@
       <c r="F147" t="s">
         <v>198</v>
       </c>
-      <c r="G147" s="2" t="s">
-        <v>269</v>
+      <c r="G147" t="s">
+        <v>314</v>
       </c>
       <c r="H147" s="1">
-        <v>44734</v>
+        <v>43712</v>
       </c>
       <c r="I147" s="1">
-        <v>43587</v>
+        <v>43570</v>
       </c>
       <c r="J147" s="1">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K147" s="3" t="s">
         <v>21</v>
@@ -8101,22 +8092,23 @@
       <c r="L147" s="2">
         <v>5</v>
       </c>
+      <c r="M147" s="1"/>
       <c r="N147" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" t="s">
+        <v>261</v>
+      </c>
+      <c r="B148" t="s">
         <v>262</v>
       </c>
-      <c r="B148" t="s">
-        <v>263</v>
-      </c>
       <c r="C148" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>18</v>
@@ -8125,13 +8117,13 @@
         <v>198</v>
       </c>
       <c r="G148" t="s">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="H148" s="1">
-        <v>45656</v>
+        <v>44349</v>
       </c>
       <c r="I148" s="1">
-        <v>43559</v>
+        <v>43304</v>
       </c>
       <c r="J148" s="1">
         <v>45428</v>
@@ -8139,25 +8131,26 @@
       <c r="K148" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L148" s="7">
-        <v>5</v>
-      </c>
+      <c r="L148" s="2">
+        <v>5</v>
+      </c>
+      <c r="M148" s="1"/>
       <c r="N148" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" t="s">
+        <v>261</v>
+      </c>
+      <c r="B149" t="s">
         <v>262</v>
       </c>
-      <c r="B149" t="s">
-        <v>263</v>
-      </c>
       <c r="C149" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>18</v>
@@ -8166,16 +8159,16 @@
         <v>198</v>
       </c>
       <c r="G149" t="s">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="H149" s="1">
-        <v>45820</v>
+        <v>44349</v>
       </c>
       <c r="I149" s="1">
-        <v>43264</v>
+        <v>43325</v>
       </c>
       <c r="J149" s="1">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K149" s="3" t="s">
         <v>21</v>
@@ -8183,22 +8176,23 @@
       <c r="L149" s="7">
         <v>5</v>
       </c>
+      <c r="M149" s="1"/>
       <c r="N149" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" t="s">
+        <v>261</v>
+      </c>
+      <c r="B150" t="s">
         <v>262</v>
       </c>
-      <c r="B150" t="s">
-        <v>263</v>
-      </c>
       <c r="C150" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>18</v>
@@ -8207,39 +8201,40 @@
         <v>198</v>
       </c>
       <c r="G150" t="s">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="H150" s="1">
-        <v>45820</v>
+        <v>44349</v>
       </c>
       <c r="I150" s="1">
-        <v>43271</v>
+        <v>43346</v>
       </c>
       <c r="J150" s="1">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K150" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L150" s="2">
-        <v>5</v>
-      </c>
+      <c r="L150" s="7">
+        <v>5</v>
+      </c>
+      <c r="M150" s="1"/>
       <c r="N150" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" t="s">
+        <v>261</v>
+      </c>
+      <c r="B151" t="s">
         <v>262</v>
       </c>
-      <c r="B151" t="s">
-        <v>263</v>
-      </c>
       <c r="C151" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>18</v>
@@ -8248,13 +8243,13 @@
         <v>198</v>
       </c>
       <c r="G151" t="s">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="H151" s="1">
-        <v>46013</v>
+        <v>44349</v>
       </c>
       <c r="I151" s="1">
-        <v>43294</v>
+        <v>43551</v>
       </c>
       <c r="J151" s="1">
         <v>45428</v>
@@ -8262,38 +8257,41 @@
       <c r="K151" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L151" s="7">
-        <v>5</v>
-      </c>
+      <c r="L151" s="2">
+        <v>5</v>
+      </c>
+      <c r="M151" s="1"/>
       <c r="N151" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:14" customFormat="1">
       <c r="A152" t="s">
+        <v>319</v>
+      </c>
+      <c r="B152" t="s">
         <v>320</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C152" s="2"/>
       <c r="D152" s="11" t="s">
         <v>322</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G152" t="s">
+      <c r="G152" s="2" t="s">
         <v>323</v>
       </c>
       <c r="H152" s="1">
-        <v>44194</v>
+        <v>44617</v>
       </c>
       <c r="I152" s="1">
-        <v>42990</v>
+        <v>44617</v>
       </c>
       <c r="J152" s="2"/>
       <c r="K152" s="3" t="s">
@@ -8311,29 +8309,31 @@
     </row>
     <row r="153" spans="1:14">
       <c r="A153" t="s">
+        <v>319</v>
+      </c>
+      <c r="B153" t="s">
         <v>320</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C153" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C153"/>
-      <c r="D153" s="18" t="s">
+      <c r="D153" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="E153" t="s">
-        <v>208</v>
+      <c r="E153" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G153" t="s">
+      <c r="G153" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="H153" s="19">
-        <v>44426</v>
+      <c r="H153" s="1">
+        <v>45821</v>
       </c>
       <c r="I153" s="1">
-        <v>42191</v>
+        <v>44617</v>
       </c>
       <c r="K153" s="3" t="s">
         <v>42</v>
@@ -8350,25 +8350,28 @@
     </row>
     <row r="154" spans="1:14">
       <c r="A154" t="s">
+        <v>319</v>
+      </c>
+      <c r="B154" t="s">
         <v>320</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D154" s="11" t="s">
         <v>326</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H154" s="1">
-        <v>44617</v>
+        <v>45821</v>
       </c>
       <c r="I154" s="1">
         <v>44617</v>
@@ -8388,28 +8391,31 @@
     </row>
     <row r="155" spans="1:14">
       <c r="A155" t="s">
+        <v>319</v>
+      </c>
+      <c r="B155" t="s">
         <v>320</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G155" s="2" t="s">
-        <v>329</v>
+      <c r="G155" t="s">
+        <v>328</v>
       </c>
       <c r="H155" s="1">
-        <v>44617</v>
+        <v>44923</v>
       </c>
       <c r="I155" s="1">
-        <v>44617</v>
+        <v>42990</v>
       </c>
       <c r="K155" s="3" t="s">
         <v>42</v>
@@ -8426,34 +8432,37 @@
     </row>
     <row r="156" spans="1:14">
       <c r="A156" t="s">
+        <v>319</v>
+      </c>
+      <c r="B156" t="s">
         <v>320</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G156" s="2" t="s">
-        <v>331</v>
+      <c r="G156" t="s">
+        <v>328</v>
       </c>
       <c r="H156" s="1">
-        <v>44734</v>
+        <v>44925</v>
       </c>
       <c r="I156" s="1">
-        <v>44734</v>
+        <v>42990</v>
       </c>
       <c r="K156" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L156" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M156" s="1">
         <v>46128</v>
@@ -8464,28 +8473,31 @@
     </row>
     <row r="157" spans="1:14">
       <c r="A157" t="s">
+        <v>319</v>
+      </c>
+      <c r="B157" t="s">
         <v>320</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G157" t="s">
-        <v>333</v>
+      <c r="G157" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="H157" s="1">
-        <v>44923</v>
+        <v>44617</v>
       </c>
       <c r="I157" s="1">
-        <v>42990</v>
+        <v>44617</v>
       </c>
       <c r="K157" s="3" t="s">
         <v>42</v>
@@ -8502,16 +8514,19 @@
     </row>
     <row r="158" spans="1:14">
       <c r="A158" t="s">
+        <v>319</v>
+      </c>
+      <c r="B158" t="s">
         <v>320</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>53</v>
@@ -8520,7 +8535,7 @@
         <v>333</v>
       </c>
       <c r="H158" s="1">
-        <v>44925</v>
+        <v>44194</v>
       </c>
       <c r="I158" s="1">
         <v>42990</v>
@@ -8540,34 +8555,37 @@
     </row>
     <row r="159" spans="1:14">
       <c r="A159" t="s">
+        <v>319</v>
+      </c>
+      <c r="B159" t="s">
         <v>320</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
         <v>321</v>
       </c>
-      <c r="D159" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>18</v>
+      <c r="D159" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="E159" t="s">
+        <v>210</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G159" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="H159" s="1">
-        <v>45820</v>
+      <c r="G159" t="s">
+        <v>333</v>
+      </c>
+      <c r="H159" s="19">
+        <v>44426</v>
       </c>
       <c r="I159" s="1">
-        <v>45820</v>
+        <v>42191</v>
       </c>
       <c r="K159" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L159" s="7">
-        <v>5</v>
+      <c r="L159" s="2">
+        <v>25</v>
       </c>
       <c r="M159" s="1">
         <v>46128</v>
@@ -8578,13 +8596,16 @@
     </row>
     <row r="160" spans="1:14">
       <c r="A160" t="s">
+        <v>319</v>
+      </c>
+      <c r="B160" t="s">
         <v>320</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C160" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>18</v>
@@ -8593,7 +8614,7 @@
         <v>53</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H160" s="1">
         <v>45820</v>
@@ -8604,7 +8625,7 @@
       <c r="K160" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L160" s="2">
+      <c r="L160" s="7">
         <v>5</v>
       </c>
       <c r="M160" s="1">
@@ -8616,34 +8637,37 @@
     </row>
     <row r="161" spans="1:14">
       <c r="A161" t="s">
+        <v>319</v>
+      </c>
+      <c r="B161" t="s">
         <v>320</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="H161" s="1">
-        <v>45821</v>
+        <v>45820</v>
       </c>
       <c r="I161" s="1">
-        <v>44617</v>
+        <v>45820</v>
       </c>
       <c r="K161" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L161" s="2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M161" s="1">
         <v>46128</v>
@@ -8654,34 +8678,37 @@
     </row>
     <row r="162" spans="1:14">
       <c r="A162" t="s">
+        <v>319</v>
+      </c>
+      <c r="B162" t="s">
         <v>320</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="H162" s="1">
-        <v>45821</v>
+        <v>44734</v>
       </c>
       <c r="I162" s="1">
-        <v>44617</v>
+        <v>44734</v>
       </c>
       <c r="K162" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L162" s="2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M162" s="1">
         <v>46128</v>
@@ -8692,116 +8719,114 @@
     </row>
     <row r="163" spans="1:14" customFormat="1">
       <c r="A163" t="s">
+        <v>340</v>
+      </c>
+      <c r="B163" t="s">
         <v>341</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C163" s="18" t="s">
         <v>342</v>
       </c>
-      <c r="C163" s="18" t="s">
+      <c r="D163" t="s">
         <v>343</v>
       </c>
-      <c r="D163" t="s">
-        <v>344</v>
-      </c>
       <c r="E163" s="2" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="F163" t="s">
         <v>198</v>
       </c>
       <c r="G163" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H163" s="1">
-        <v>43712</v>
+        <v>44027</v>
       </c>
       <c r="I163" s="1">
-        <v>43712</v>
-      </c>
-      <c r="J163" s="1">
-        <v>45539</v>
-      </c>
+        <v>45656</v>
+      </c>
+      <c r="J163" s="2"/>
       <c r="K163" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L163" s="7">
-        <v>5</v>
+        <v>42</v>
+      </c>
+      <c r="L163" s="2">
+        <v>25</v>
       </c>
       <c r="M163" s="1">
         <v>46141</v>
       </c>
       <c r="N163" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" t="s">
+        <v>340</v>
+      </c>
+      <c r="B164" t="s">
         <v>341</v>
       </c>
-      <c r="B164" t="s">
-        <v>342</v>
-      </c>
       <c r="C164" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="D164" t="s">
         <v>347</v>
       </c>
-      <c r="D164" t="s">
-        <v>348</v>
-      </c>
       <c r="E164" s="2" t="s">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="F164" t="s">
         <v>198</v>
       </c>
       <c r="G164" t="s">
-        <v>349</v>
+        <v>174</v>
       </c>
       <c r="H164" s="1">
-        <v>43910</v>
+        <v>44348</v>
       </c>
       <c r="I164" s="1">
-        <v>46013</v>
+        <v>44349</v>
       </c>
       <c r="K164" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L164" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M164" s="1">
         <v>46141</v>
       </c>
       <c r="N164" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" t="s">
+        <v>340</v>
+      </c>
+      <c r="B165" t="s">
         <v>341</v>
       </c>
-      <c r="B165" t="s">
-        <v>342</v>
-      </c>
-      <c r="C165" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="D165" t="s">
-        <v>351</v>
+      <c r="C165" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F165" t="s">
         <v>198</v>
       </c>
       <c r="G165" t="s">
-        <v>352</v>
+        <v>174</v>
       </c>
       <c r="H165" s="1">
-        <v>44027</v>
+        <v>44348</v>
       </c>
       <c r="I165" s="1">
-        <v>45656</v>
+        <v>44349</v>
       </c>
       <c r="K165" s="3" t="s">
         <v>42</v>
@@ -8813,30 +8838,30 @@
         <v>46141</v>
       </c>
       <c r="N165" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" t="s">
+        <v>340</v>
+      </c>
+      <c r="B166" t="s">
         <v>341</v>
       </c>
-      <c r="B166" t="s">
-        <v>342</v>
-      </c>
       <c r="C166" s="11" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="F166" t="s">
         <v>198</v>
       </c>
       <c r="G166" t="s">
-        <v>345</v>
+        <v>174</v>
       </c>
       <c r="H166" s="1">
         <v>44348</v>
@@ -8848,36 +8873,36 @@
         <v>42</v>
       </c>
       <c r="L166" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M166" s="1">
         <v>46141</v>
       </c>
       <c r="N166" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" t="s">
+        <v>340</v>
+      </c>
+      <c r="B167" t="s">
         <v>341</v>
       </c>
-      <c r="B167" t="s">
-        <v>342</v>
-      </c>
-      <c r="C167" s="18" t="s">
-        <v>355</v>
-      </c>
-      <c r="D167" t="s">
-        <v>356</v>
+      <c r="C167" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="F167" t="s">
         <v>198</v>
       </c>
       <c r="G167" t="s">
-        <v>357</v>
+        <v>174</v>
       </c>
       <c r="H167" s="1">
         <v>44348</v>
@@ -8888,37 +8913,37 @@
       <c r="K167" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L167" s="2">
-        <v>25</v>
+      <c r="L167" s="7">
+        <v>5</v>
       </c>
       <c r="M167" s="1">
         <v>46141</v>
       </c>
       <c r="N167" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="168" spans="1:14" customFormat="1">
       <c r="A168" t="s">
+        <v>340</v>
+      </c>
+      <c r="B168" t="s">
         <v>341</v>
       </c>
-      <c r="B168" t="s">
-        <v>342</v>
-      </c>
       <c r="C168" s="11" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="F168" t="s">
         <v>198</v>
       </c>
       <c r="G168" t="s">
-        <v>357</v>
+        <v>174</v>
       </c>
       <c r="H168" s="1">
         <v>44348</v>
@@ -8931,36 +8956,36 @@
         <v>42</v>
       </c>
       <c r="L168" s="2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M168" s="1">
         <v>46141</v>
       </c>
       <c r="N168" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" t="s">
+        <v>340</v>
+      </c>
+      <c r="B169" t="s">
         <v>341</v>
       </c>
-      <c r="B169" t="s">
-        <v>342</v>
-      </c>
       <c r="C169" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F169" t="s">
         <v>198</v>
       </c>
       <c r="G169" t="s">
-        <v>362</v>
+        <v>174</v>
       </c>
       <c r="H169" s="1">
         <v>44348</v>
@@ -8972,36 +8997,36 @@
         <v>42</v>
       </c>
       <c r="L169" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M169" s="1">
         <v>46141</v>
       </c>
       <c r="N169" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" t="s">
+        <v>340</v>
+      </c>
+      <c r="B170" t="s">
         <v>341</v>
       </c>
-      <c r="B170" t="s">
-        <v>342</v>
-      </c>
-      <c r="C170" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="D170" t="s">
-        <v>364</v>
+      <c r="C170" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="F170" t="s">
         <v>198</v>
       </c>
       <c r="G170" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H170" s="1">
         <v>44348</v>
@@ -9012,37 +9037,37 @@
       <c r="K170" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L170" s="2">
-        <v>25</v>
+      <c r="L170" s="7">
+        <v>5</v>
       </c>
       <c r="M170" s="1">
         <v>46141</v>
       </c>
       <c r="N170" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" t="s">
+        <v>340</v>
+      </c>
+      <c r="B171" t="s">
         <v>341</v>
       </c>
-      <c r="B171" t="s">
-        <v>342</v>
-      </c>
       <c r="C171" s="11" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>208</v>
+        <v>41</v>
       </c>
       <c r="F171" t="s">
         <v>198</v>
       </c>
       <c r="G171" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H171" s="1">
         <v>44348</v>
@@ -9054,36 +9079,36 @@
         <v>42</v>
       </c>
       <c r="L171" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M171" s="1">
         <v>46141</v>
       </c>
       <c r="N171" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" t="s">
+        <v>340</v>
+      </c>
+      <c r="B172" t="s">
         <v>341</v>
       </c>
-      <c r="B172" t="s">
-        <v>342</v>
-      </c>
       <c r="C172" s="11" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F172" t="s">
         <v>198</v>
       </c>
       <c r="G172" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H172" s="1">
         <v>44348</v>
@@ -9101,30 +9126,30 @@
         <v>46141</v>
       </c>
       <c r="N172" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="173" spans="1:14" customFormat="1">
       <c r="A173" t="s">
+        <v>340</v>
+      </c>
+      <c r="B173" t="s">
         <v>341</v>
       </c>
-      <c r="B173" t="s">
-        <v>342</v>
-      </c>
       <c r="C173" s="11" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="F173" t="s">
         <v>198</v>
       </c>
-      <c r="G173" t="s">
-        <v>345</v>
+      <c r="G173" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="H173" s="1">
         <v>44348</v>
@@ -9136,37 +9161,37 @@
       <c r="K173" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L173" s="2">
-        <v>25</v>
+      <c r="L173" s="7">
+        <v>5</v>
       </c>
       <c r="M173" s="1">
         <v>46141</v>
       </c>
       <c r="N173" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" t="s">
+        <v>340</v>
+      </c>
+      <c r="B174" t="s">
         <v>341</v>
       </c>
-      <c r="B174" t="s">
-        <v>342</v>
-      </c>
       <c r="C174" s="11" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F174" t="s">
         <v>198</v>
       </c>
       <c r="G174" t="s">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="H174" s="1">
         <v>44348</v>
@@ -9177,28 +9202,28 @@
       <c r="K174" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L174" s="7">
-        <v>5</v>
+      <c r="L174" s="2">
+        <v>15</v>
       </c>
       <c r="M174" s="1">
         <v>46141</v>
       </c>
       <c r="N174" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" t="s">
+        <v>340</v>
+      </c>
+      <c r="B175" t="s">
         <v>341</v>
       </c>
-      <c r="B175" t="s">
-        <v>342</v>
-      </c>
-      <c r="C175" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>374</v>
+      <c r="C175" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="D175" t="s">
+        <v>369</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>18</v>
@@ -9207,48 +9232,51 @@
         <v>198</v>
       </c>
       <c r="G175" t="s">
-        <v>181</v>
+        <v>370</v>
       </c>
       <c r="H175" s="1">
-        <v>44348</v>
+        <v>43712</v>
       </c>
       <c r="I175" s="1">
-        <v>44349</v>
+        <v>43712</v>
+      </c>
+      <c r="J175" s="1">
+        <v>45539</v>
       </c>
       <c r="K175" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L175" s="2">
+        <v>21</v>
+      </c>
+      <c r="L175" s="7">
         <v>5</v>
       </c>
       <c r="M175" s="1">
         <v>46141</v>
       </c>
       <c r="N175" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" t="s">
+        <v>340</v>
+      </c>
+      <c r="B176" t="s">
         <v>341</v>
       </c>
-      <c r="B176" t="s">
-        <v>342</v>
-      </c>
       <c r="C176" s="11" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F176" t="s">
         <v>198</v>
       </c>
       <c r="G176" t="s">
-        <v>181</v>
+        <v>370</v>
       </c>
       <c r="H176" s="1">
         <v>44348</v>
@@ -9260,36 +9288,36 @@
         <v>42</v>
       </c>
       <c r="L176" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M176" s="1">
         <v>46141</v>
       </c>
       <c r="N176" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" t="s">
+        <v>340</v>
+      </c>
+      <c r="B177" t="s">
         <v>341</v>
       </c>
-      <c r="B177" t="s">
-        <v>342</v>
-      </c>
       <c r="C177" s="11" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="F177" t="s">
         <v>198</v>
       </c>
       <c r="G177" t="s">
-        <v>181</v>
+        <v>370</v>
       </c>
       <c r="H177" s="1">
         <v>44348</v>
@@ -9300,28 +9328,28 @@
       <c r="K177" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L177" s="7">
-        <v>5</v>
+      <c r="L177" s="2">
+        <v>25</v>
       </c>
       <c r="M177" s="1">
         <v>46141</v>
       </c>
       <c r="N177" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="178" spans="1:14" customFormat="1">
       <c r="A178" t="s">
+        <v>340</v>
+      </c>
+      <c r="B178" t="s">
         <v>341</v>
       </c>
-      <c r="B178" t="s">
-        <v>342</v>
-      </c>
       <c r="C178" s="11" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>18</v>
@@ -9330,7 +9358,7 @@
         <v>198</v>
       </c>
       <c r="G178" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="H178" s="1">
         <v>44348</v>
@@ -9349,21 +9377,21 @@
         <v>46141</v>
       </c>
       <c r="N178" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" t="s">
+        <v>340</v>
+      </c>
+      <c r="B179" t="s">
         <v>341</v>
       </c>
-      <c r="B179" t="s">
-        <v>342</v>
-      </c>
       <c r="C179" s="18" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D179" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>18</v>
@@ -9372,7 +9400,7 @@
         <v>198</v>
       </c>
       <c r="G179" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="H179" s="1">
         <v>44348</v>
@@ -9390,21 +9418,21 @@
         <v>46141</v>
       </c>
       <c r="N179" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" t="s">
+        <v>340</v>
+      </c>
+      <c r="B180" t="s">
         <v>341</v>
       </c>
-      <c r="B180" t="s">
-        <v>342</v>
-      </c>
       <c r="C180" s="11" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>18</v>
@@ -9413,7 +9441,7 @@
         <v>198</v>
       </c>
       <c r="G180" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="H180" s="1">
         <v>44348</v>
@@ -9431,21 +9459,21 @@
         <v>46141</v>
       </c>
       <c r="N180" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="181" spans="1:14">
       <c r="A181" t="s">
+        <v>340</v>
+      </c>
+      <c r="B181" t="s">
         <v>341</v>
       </c>
-      <c r="B181" t="s">
-        <v>342</v>
-      </c>
       <c r="C181" s="18" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D181" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>41</v>
@@ -9454,7 +9482,7 @@
         <v>198</v>
       </c>
       <c r="G181" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="H181" s="1">
         <v>44348</v>
@@ -9472,21 +9500,21 @@
         <v>46141</v>
       </c>
       <c r="N181" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="182" spans="1:14">
       <c r="A182" t="s">
+        <v>340</v>
+      </c>
+      <c r="B182" t="s">
         <v>341</v>
       </c>
-      <c r="B182" t="s">
-        <v>342</v>
-      </c>
       <c r="C182" s="11" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>41</v>
@@ -9495,7 +9523,7 @@
         <v>198</v>
       </c>
       <c r="G182" t="s">
-        <v>181</v>
+        <v>370</v>
       </c>
       <c r="H182" s="1">
         <v>44348</v>
@@ -9513,21 +9541,21 @@
         <v>46141</v>
       </c>
       <c r="N182" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="183" spans="1:14" customFormat="1">
       <c r="A183" t="s">
+        <v>340</v>
+      </c>
+      <c r="B183" t="s">
         <v>341</v>
       </c>
-      <c r="B183" t="s">
-        <v>342</v>
-      </c>
       <c r="C183" s="11" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>41</v>
@@ -9536,7 +9564,7 @@
         <v>198</v>
       </c>
       <c r="G183" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="H183" s="1">
         <v>44348</v>
@@ -9555,21 +9583,21 @@
         <v>46141</v>
       </c>
       <c r="N183" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" t="s">
+        <v>340</v>
+      </c>
+      <c r="B184" t="s">
         <v>341</v>
       </c>
-      <c r="B184" t="s">
-        <v>342</v>
-      </c>
       <c r="C184" s="11" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>41</v>
@@ -9578,7 +9606,7 @@
         <v>198</v>
       </c>
       <c r="G184" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="H184" s="1">
         <v>44348</v>
@@ -9596,30 +9624,30 @@
         <v>46141</v>
       </c>
       <c r="N184" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="185" spans="1:14">
       <c r="A185" t="s">
+        <v>340</v>
+      </c>
+      <c r="B185" t="s">
         <v>341</v>
       </c>
-      <c r="B185" t="s">
-        <v>342</v>
-      </c>
-      <c r="C185" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>394</v>
+      <c r="C185" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="D185" t="s">
+        <v>390</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F185" t="s">
         <v>198</v>
       </c>
-      <c r="G185" s="2" t="s">
-        <v>269</v>
+      <c r="G185" t="s">
+        <v>370</v>
       </c>
       <c r="H185" s="1">
         <v>44348</v>
@@ -9630,37 +9658,37 @@
       <c r="K185" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L185" s="7">
-        <v>5</v>
+      <c r="L185" s="2">
+        <v>15</v>
       </c>
       <c r="M185" s="1">
         <v>46141</v>
       </c>
       <c r="N185" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" t="s">
+        <v>340</v>
+      </c>
+      <c r="B186" t="s">
         <v>341</v>
       </c>
-      <c r="B186" t="s">
-        <v>342</v>
-      </c>
       <c r="C186" s="11" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>208</v>
+        <v>41</v>
       </c>
       <c r="F186" t="s">
         <v>198</v>
       </c>
       <c r="G186" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="H186" s="1">
         <v>44348</v>
@@ -9672,36 +9700,36 @@
         <v>42</v>
       </c>
       <c r="L186" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M186" s="1">
         <v>46141</v>
       </c>
       <c r="N186" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" t="s">
+        <v>340</v>
+      </c>
+      <c r="B187" t="s">
         <v>341</v>
       </c>
-      <c r="B187" t="s">
-        <v>342</v>
-      </c>
-      <c r="C187" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>398</v>
+      <c r="C187" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="D187" t="s">
+        <v>395</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F187" t="s">
         <v>198</v>
       </c>
       <c r="G187" t="s">
-        <v>357</v>
+        <v>396</v>
       </c>
       <c r="H187" s="1">
         <v>44348</v>
@@ -9719,30 +9747,30 @@
         <v>46141</v>
       </c>
       <c r="N187" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="188" spans="1:14" customFormat="1">
       <c r="A188" t="s">
+        <v>340</v>
+      </c>
+      <c r="B188" t="s">
         <v>341</v>
       </c>
-      <c r="B188" t="s">
-        <v>342</v>
-      </c>
       <c r="C188" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="F188" t="s">
         <v>198</v>
       </c>
       <c r="G188" t="s">
-        <v>357</v>
+        <v>396</v>
       </c>
       <c r="H188" s="1">
         <v>44348</v>
@@ -9755,27 +9783,27 @@
         <v>42</v>
       </c>
       <c r="L188" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M188" s="1">
         <v>46141</v>
       </c>
       <c r="N188" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" t="s">
+        <v>340</v>
+      </c>
+      <c r="B189" t="s">
         <v>341</v>
       </c>
-      <c r="B189" t="s">
-        <v>342</v>
-      </c>
       <c r="C189" s="11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>41</v>
@@ -9784,7 +9812,7 @@
         <v>198</v>
       </c>
       <c r="G189" t="s">
-        <v>345</v>
+        <v>396</v>
       </c>
       <c r="H189" s="1">
         <v>44348</v>
@@ -9802,30 +9830,30 @@
         <v>46141</v>
       </c>
       <c r="N189" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" t="s">
+        <v>340</v>
+      </c>
+      <c r="B190" t="s">
         <v>341</v>
       </c>
-      <c r="B190" t="s">
-        <v>342</v>
-      </c>
       <c r="C190" s="11" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="F190" t="s">
         <v>198</v>
       </c>
       <c r="G190" t="s">
-        <v>345</v>
+        <v>396</v>
       </c>
       <c r="H190" s="1">
         <v>44348</v>
@@ -9837,36 +9865,36 @@
         <v>42</v>
       </c>
       <c r="L190" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M190" s="1">
         <v>46141</v>
       </c>
       <c r="N190" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="191" spans="1:14">
       <c r="A191" t="s">
+        <v>340</v>
+      </c>
+      <c r="B191" t="s">
         <v>341</v>
       </c>
-      <c r="B191" t="s">
-        <v>342</v>
-      </c>
-      <c r="C191" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="D191" t="s">
-        <v>406</v>
+      <c r="C191" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>404</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="F191" t="s">
         <v>198</v>
       </c>
       <c r="G191" t="s">
-        <v>345</v>
+        <v>396</v>
       </c>
       <c r="H191" s="1">
         <v>44348</v>
@@ -9878,36 +9906,36 @@
         <v>42</v>
       </c>
       <c r="L191" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M191" s="1">
         <v>46141</v>
       </c>
       <c r="N191" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="192" spans="1:14">
       <c r="A192" t="s">
+        <v>340</v>
+      </c>
+      <c r="B192" t="s">
         <v>341</v>
       </c>
-      <c r="B192" t="s">
-        <v>342</v>
-      </c>
       <c r="C192" s="11" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F192" t="s">
         <v>198</v>
       </c>
       <c r="G192" t="s">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="H192" s="1">
         <v>44348</v>
@@ -9919,36 +9947,36 @@
         <v>42</v>
       </c>
       <c r="L192" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M192" s="1">
         <v>46141</v>
       </c>
       <c r="N192" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="193" spans="1:14" customFormat="1">
       <c r="A193" t="s">
+        <v>340</v>
+      </c>
+      <c r="B193" t="s">
         <v>341</v>
       </c>
-      <c r="B193" t="s">
-        <v>342</v>
-      </c>
       <c r="C193" s="11" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F193" t="s">
         <v>198</v>
       </c>
       <c r="G193" t="s">
-        <v>181</v>
+        <v>396</v>
       </c>
       <c r="H193" s="1">
         <v>44348</v>
@@ -9967,84 +9995,82 @@
         <v>46141</v>
       </c>
       <c r="N193" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="194" spans="1:14" customFormat="1">
       <c r="A194" t="s">
+        <v>340</v>
+      </c>
+      <c r="B194" t="s">
         <v>341</v>
       </c>
-      <c r="B194" t="s">
-        <v>342</v>
-      </c>
-      <c r="C194" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>412</v>
+      <c r="C194" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="D194" t="s">
+        <v>410</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>208</v>
+        <v>41</v>
       </c>
       <c r="F194" t="s">
         <v>198</v>
       </c>
       <c r="G194" t="s">
-        <v>357</v>
+        <v>411</v>
       </c>
       <c r="H194" s="1">
-        <v>44348</v>
+        <v>43910</v>
       </c>
       <c r="I194" s="1">
-        <v>44349</v>
+        <v>46013</v>
       </c>
       <c r="J194" s="2"/>
       <c r="K194" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L194" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M194" s="1">
         <v>46141</v>
       </c>
       <c r="N194" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="195" spans="1:14" customFormat="1">
       <c r="A195" t="s">
+        <v>412</v>
+      </c>
+      <c r="B195" t="s">
         <v>413</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" s="21" t="s">
         <v>414</v>
       </c>
-      <c r="C195" s="20" t="s">
+      <c r="D195" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D195" t="s">
-        <v>416</v>
-      </c>
       <c r="E195" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F195" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G195" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="G195" t="s">
-        <v>20</v>
-      </c>
       <c r="H195" s="1">
-        <v>42734</v>
+        <v>44426</v>
       </c>
       <c r="I195" s="1">
-        <v>42734</v>
-      </c>
-      <c r="J195" s="1">
-        <v>44925</v>
-      </c>
+        <v>44426</v>
+      </c>
+      <c r="J195" s="2"/>
       <c r="K195" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L195" s="2">
         <v>5</v>
@@ -10053,42 +10079,39 @@
         <v>46125</v>
       </c>
       <c r="N195" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="196" spans="1:14">
       <c r="A196" t="s">
+        <v>412</v>
+      </c>
+      <c r="B196" t="s">
         <v>413</v>
       </c>
-      <c r="B196" t="s">
-        <v>414</v>
-      </c>
       <c r="C196" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="D196" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D196" s="2" t="s">
-        <v>419</v>
-      </c>
       <c r="E196" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F196" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G196" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="G196" t="s">
-        <v>20</v>
-      </c>
       <c r="H196" s="1">
-        <v>43132</v>
+        <v>44426</v>
       </c>
       <c r="I196" s="1">
-        <v>43132</v>
-      </c>
-      <c r="J196" s="1">
-        <v>44966</v>
+        <v>44426</v>
       </c>
       <c r="K196" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L196" s="2">
         <v>5</v>
@@ -10097,39 +10120,39 @@
         <v>46125</v>
       </c>
       <c r="N196" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="197" spans="1:14">
       <c r="A197" t="s">
+        <v>412</v>
+      </c>
+      <c r="B197" t="s">
         <v>413</v>
       </c>
-      <c r="B197" t="s">
-        <v>414</v>
-      </c>
-      <c r="C197" s="21" t="s">
+      <c r="C197" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="D197" t="s">
         <v>420</v>
       </c>
-      <c r="D197" s="2" t="s">
-        <v>421</v>
-      </c>
       <c r="E197" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G197" t="s">
         <v>20</v>
       </c>
       <c r="H197" s="1">
-        <v>43500</v>
+        <v>42734</v>
       </c>
       <c r="I197" s="1">
-        <v>43500</v>
+        <v>42734</v>
       </c>
       <c r="J197" s="1">
-        <v>45821</v>
+        <v>44925</v>
       </c>
       <c r="K197" s="3" t="s">
         <v>21</v>
@@ -10141,39 +10164,39 @@
         <v>46125</v>
       </c>
       <c r="N197" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="198" spans="1:14" customFormat="1">
       <c r="A198" t="s">
+        <v>412</v>
+      </c>
+      <c r="B198" t="s">
         <v>413</v>
       </c>
-      <c r="B198" t="s">
-        <v>414</v>
-      </c>
-      <c r="C198" s="20" t="s">
+      <c r="C198" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="D198" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D198" t="s">
-        <v>423</v>
-      </c>
       <c r="E198" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G198" t="s">
         <v>20</v>
       </c>
       <c r="H198" s="1">
-        <v>43819</v>
+        <v>43132</v>
       </c>
       <c r="I198" s="1">
-        <v>43819</v>
+        <v>43132</v>
       </c>
       <c r="J198" s="1">
-        <v>45821</v>
+        <v>44966</v>
       </c>
       <c r="K198" s="3" t="s">
         <v>21</v>
@@ -10185,83 +10208,86 @@
         <v>46125</v>
       </c>
       <c r="N198" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="199" spans="1:14">
       <c r="A199" t="s">
+        <v>412</v>
+      </c>
+      <c r="B199" t="s">
         <v>413</v>
       </c>
-      <c r="B199" t="s">
-        <v>414</v>
-      </c>
       <c r="C199" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="D199" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D199" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="E199" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G199" t="s">
         <v>20</v>
       </c>
       <c r="H199" s="1">
-        <v>44194</v>
+        <v>43500</v>
       </c>
       <c r="I199" s="1">
-        <v>44194</v>
+        <v>43500</v>
       </c>
       <c r="J199" s="1">
-        <v>44994</v>
+        <v>45821</v>
       </c>
       <c r="K199" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L199" s="7">
+      <c r="L199" s="2">
         <v>5</v>
       </c>
       <c r="M199" s="1">
         <v>46125</v>
       </c>
       <c r="N199" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" t="s">
+        <v>412</v>
+      </c>
+      <c r="B200" t="s">
         <v>413</v>
       </c>
-      <c r="B200" t="s">
-        <v>414</v>
-      </c>
-      <c r="C200" s="21" t="s">
+      <c r="C200" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="D200" t="s">
         <v>426</v>
       </c>
-      <c r="D200" s="2" t="s">
-        <v>427</v>
-      </c>
       <c r="E200" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G200" s="9" t="s">
-        <v>146</v>
+        <v>160</v>
+      </c>
+      <c r="G200" t="s">
+        <v>20</v>
       </c>
       <c r="H200" s="1">
-        <v>44426</v>
+        <v>43819</v>
       </c>
       <c r="I200" s="1">
-        <v>44426</v>
+        <v>43819</v>
+      </c>
+      <c r="J200" s="1">
+        <v>45821</v>
       </c>
       <c r="K200" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L200" s="2">
         <v>5</v>
@@ -10270,68 +10296,71 @@
         <v>46125</v>
       </c>
       <c r="N200" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="201" spans="1:14">
       <c r="A201" t="s">
+        <v>412</v>
+      </c>
+      <c r="B201" t="s">
         <v>413</v>
       </c>
-      <c r="B201" t="s">
-        <v>414</v>
-      </c>
       <c r="C201" s="21" t="s">
+        <v>427</v>
+      </c>
+      <c r="D201" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D201" s="2" t="s">
-        <v>429</v>
-      </c>
       <c r="E201" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G201" s="9" t="s">
-        <v>146</v>
+        <v>160</v>
+      </c>
+      <c r="G201" t="s">
+        <v>20</v>
       </c>
       <c r="H201" s="1">
-        <v>44426</v>
+        <v>44194</v>
       </c>
       <c r="I201" s="1">
-        <v>44426</v>
+        <v>44194</v>
+      </c>
+      <c r="J201" s="1">
+        <v>44994</v>
       </c>
       <c r="K201" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L201" s="2">
+        <v>21</v>
+      </c>
+      <c r="L201" s="7">
         <v>5</v>
       </c>
       <c r="M201" s="1">
         <v>46125</v>
       </c>
       <c r="N201" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="202" spans="1:14">
       <c r="A202" t="s">
+        <v>412</v>
+      </c>
+      <c r="B202" t="s">
         <v>413</v>
       </c>
-      <c r="B202" t="s">
-        <v>414</v>
-      </c>
       <c r="C202" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="D202" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D202" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="E202" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G202" t="s">
         <v>20</v>
@@ -10352,27 +10381,27 @@
         <v>46125</v>
       </c>
       <c r="N202" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="203" spans="1:14" customFormat="1">
       <c r="A203" t="s">
+        <v>412</v>
+      </c>
+      <c r="B203" t="s">
         <v>413</v>
       </c>
-      <c r="B203" t="s">
-        <v>414</v>
-      </c>
       <c r="C203" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="D203" t="s">
         <v>432</v>
       </c>
-      <c r="D203" t="s">
-        <v>433</v>
-      </c>
       <c r="E203" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G203" t="s">
         <v>20</v>
@@ -10394,27 +10423,27 @@
         <v>46125</v>
       </c>
       <c r="N203" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="204" spans="1:14">
       <c r="A204" t="s">
+        <v>412</v>
+      </c>
+      <c r="B204" t="s">
         <v>413</v>
       </c>
-      <c r="B204" t="s">
-        <v>414</v>
-      </c>
       <c r="C204" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="D204" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D204" s="2" t="s">
-        <v>435</v>
-      </c>
       <c r="E204" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G204" t="s">
         <v>20</v>
@@ -10435,27 +10464,27 @@
         <v>46125</v>
       </c>
       <c r="N204" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="205" spans="1:14">
       <c r="A205" t="s">
+        <v>412</v>
+      </c>
+      <c r="B205" t="s">
         <v>413</v>
       </c>
-      <c r="B205" t="s">
-        <v>414</v>
-      </c>
       <c r="C205" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="D205" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D205" s="2" t="s">
-        <v>437</v>
-      </c>
       <c r="E205" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G205" t="s">
         <v>20</v>
@@ -10476,27 +10505,27 @@
         <v>46125</v>
       </c>
       <c r="N205" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="206" spans="1:14">
       <c r="A206" t="s">
+        <v>412</v>
+      </c>
+      <c r="B206" t="s">
         <v>413</v>
       </c>
-      <c r="B206" t="s">
-        <v>414</v>
-      </c>
       <c r="C206" s="21" t="s">
+        <v>437</v>
+      </c>
+      <c r="D206" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="D206" s="2" t="s">
-        <v>439</v>
-      </c>
       <c r="E206" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G206" t="s">
         <v>20</v>
@@ -10529,8 +10558,8 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="N16" r:id="rId1" xr:uid="{8220B955-B269-49BB-BD6D-AD834FA30E13}"/>
-    <hyperlink ref="N15" r:id="rId2" xr:uid="{B401B411-58A7-4BCC-B48B-D8DA63942597}"/>
+    <hyperlink ref="N19" r:id="rId1" xr:uid="{8220B955-B269-49BB-BD6D-AD834FA30E13}"/>
+    <hyperlink ref="N18" r:id="rId2" xr:uid="{B401B411-58A7-4BCC-B48B-D8DA63942597}"/>
     <hyperlink ref="N37" r:id="rId3" xr:uid="{F7481F57-E642-473E-825B-2A3D484E1C5E}"/>
     <hyperlink ref="N38" r:id="rId4" xr:uid="{79505A78-76AD-446F-8895-A9AAE6ED4D85}"/>
     <hyperlink ref="N39" r:id="rId5" xr:uid="{D7BD8461-1283-4F76-A6D3-0EBF106113F2}"/>
@@ -10547,26 +10576,26 @@
     <hyperlink ref="N50" r:id="rId16" xr:uid="{B1A14EE6-E586-475E-A004-A0A7974021EA}"/>
     <hyperlink ref="N51" r:id="rId17" xr:uid="{DC7AB8ED-12FF-4553-902F-ABF0C0AA87A0}"/>
     <hyperlink ref="N52" r:id="rId18" xr:uid="{47B117F6-4AAA-40CE-BA3D-920E867CC01C}"/>
-    <hyperlink ref="N18" r:id="rId19" xr:uid="{173DBD48-C21A-4E6D-AABD-EEB40694EDD0}"/>
-    <hyperlink ref="N20" r:id="rId20" xr:uid="{1274BBA3-6669-4546-A4EA-1D2DFCA1CD9D}"/>
-    <hyperlink ref="N17" r:id="rId21" xr:uid="{264B87E2-07DE-4863-92C2-A75554151B1E}"/>
-    <hyperlink ref="N21" r:id="rId22" xr:uid="{A4B00B57-A4BA-406A-A2E6-3A571C1DE925}"/>
-    <hyperlink ref="N22" r:id="rId23" xr:uid="{30E19A6E-5A66-4CE2-9D18-2AA9292884BD}"/>
-    <hyperlink ref="N23" r:id="rId24" xr:uid="{205ADC83-FAAB-416D-AEFD-829E624A64BF}"/>
-    <hyperlink ref="N26" r:id="rId25" xr:uid="{8E131B5C-9A03-4606-AD38-DC03B6780539}"/>
-    <hyperlink ref="N27" r:id="rId26" xr:uid="{7D50EF81-D643-49A2-9F32-6CA2C7E17DC2}"/>
-    <hyperlink ref="N36" r:id="rId27" xr:uid="{2F2FCB70-920A-46DB-9936-996BFD6F1E44}"/>
-    <hyperlink ref="N19" r:id="rId28" xr:uid="{E67F4C0B-E78E-4885-9DE5-921A1E05F79D}"/>
-    <hyperlink ref="N28" r:id="rId29" xr:uid="{EB8AF4B8-ADA3-4865-8664-DD5D247A2B2E}"/>
-    <hyperlink ref="N29" r:id="rId30" xr:uid="{590BF203-1E3B-473B-9560-1E7AC342850F}"/>
-    <hyperlink ref="N25" r:id="rId31" xr:uid="{707DFEE0-F031-49F2-B879-F29BDE9CC8CE}"/>
-    <hyperlink ref="N24" r:id="rId32" xr:uid="{F30819C5-2CE1-480A-AD45-85D77369AF7A}"/>
-    <hyperlink ref="N30" r:id="rId33" xr:uid="{E0356CEA-79E2-4F83-BBD4-0FC36F3F51F0}"/>
-    <hyperlink ref="N31" r:id="rId34" xr:uid="{FD33E1CA-F48E-47A5-8C92-A9A529CCCE36}"/>
-    <hyperlink ref="N32" r:id="rId35" xr:uid="{0B6CD7D4-5B10-4C12-804A-B828752BAD78}"/>
-    <hyperlink ref="N33" r:id="rId36" xr:uid="{4C6E4D41-53B9-40C4-8A52-DEC4CF7AEC69}"/>
-    <hyperlink ref="N34" r:id="rId37" xr:uid="{3C1E0CD2-AB6A-4CD8-8320-CAC9C1EA81F2}"/>
-    <hyperlink ref="N35" r:id="rId38" xr:uid="{DB27BD91-88FA-44E1-A326-DE5A8086A60F}"/>
+    <hyperlink ref="N21" r:id="rId19" xr:uid="{173DBD48-C21A-4E6D-AABD-EEB40694EDD0}"/>
+    <hyperlink ref="N22" r:id="rId20" xr:uid="{1274BBA3-6669-4546-A4EA-1D2DFCA1CD9D}"/>
+    <hyperlink ref="N20" r:id="rId21" xr:uid="{264B87E2-07DE-4863-92C2-A75554151B1E}"/>
+    <hyperlink ref="N23" r:id="rId22" xr:uid="{A4B00B57-A4BA-406A-A2E6-3A571C1DE925}"/>
+    <hyperlink ref="N24" r:id="rId23" xr:uid="{30E19A6E-5A66-4CE2-9D18-2AA9292884BD}"/>
+    <hyperlink ref="N25" r:id="rId24" xr:uid="{205ADC83-FAAB-416D-AEFD-829E624A64BF}"/>
+    <hyperlink ref="N30" r:id="rId25" xr:uid="{8E131B5C-9A03-4606-AD38-DC03B6780539}"/>
+    <hyperlink ref="N31" r:id="rId26" xr:uid="{7D50EF81-D643-49A2-9F32-6CA2C7E17DC2}"/>
+    <hyperlink ref="N33" r:id="rId27" xr:uid="{2F2FCB70-920A-46DB-9936-996BFD6F1E44}"/>
+    <hyperlink ref="N29" r:id="rId28" xr:uid="{E67F4C0B-E78E-4885-9DE5-921A1E05F79D}"/>
+    <hyperlink ref="N32" r:id="rId29" xr:uid="{EB8AF4B8-ADA3-4865-8664-DD5D247A2B2E}"/>
+    <hyperlink ref="N34" r:id="rId30" xr:uid="{590BF203-1E3B-473B-9560-1E7AC342850F}"/>
+    <hyperlink ref="N16" r:id="rId31" xr:uid="{707DFEE0-F031-49F2-B879-F29BDE9CC8CE}"/>
+    <hyperlink ref="N15" r:id="rId32" xr:uid="{F30819C5-2CE1-480A-AD45-85D77369AF7A}"/>
+    <hyperlink ref="N26" r:id="rId33" xr:uid="{E0356CEA-79E2-4F83-BBD4-0FC36F3F51F0}"/>
+    <hyperlink ref="N17" r:id="rId34" xr:uid="{FD33E1CA-F48E-47A5-8C92-A9A529CCCE36}"/>
+    <hyperlink ref="N35" r:id="rId35" xr:uid="{0B6CD7D4-5B10-4C12-804A-B828752BAD78}"/>
+    <hyperlink ref="N36" r:id="rId36" xr:uid="{4C6E4D41-53B9-40C4-8A52-DEC4CF7AEC69}"/>
+    <hyperlink ref="N27" r:id="rId37" xr:uid="{3C1E0CD2-AB6A-4CD8-8320-CAC9C1EA81F2}"/>
+    <hyperlink ref="N28" r:id="rId38" xr:uid="{DB27BD91-88FA-44E1-A326-DE5A8086A60F}"/>
     <hyperlink ref="N104" r:id="rId39" xr:uid="{D8AC412C-8BF0-4534-BEB6-9FEE3561C22D}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/upload/informacoes_classificadas_desclassificadas.xlsx
+++ b/upload/informacoes_classificadas_desclassificadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89899A28-3574-4B80-9134-4F3ABD059DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B7B51A6-1032-4855-B24C-06298208BC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="6420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="448">
   <si>
     <t>orgao_entidade</t>
   </si>
@@ -1484,6 +1484,35 @@
   </si>
   <si>
     <t>Planejamento Anual de Fiscalização 2026</t>
+  </si>
+  <si>
+    <t>Secretaria dePlanejamento e Gestão - SEPLAG</t>
+  </si>
+  <si>
+    <t>SEPLAG</t>
+  </si>
+  <si>
+    <t>Atas de reuniões do Comitê de Orçamento e Finanças (Cofin)</t>
+  </si>
+  <si>
+    <t>Data da 
+realização
+da reunião</t>
+  </si>
+  <si>
+    <t>Atas das reuniões da Câmara de Coordenação da Ação Governamental (CCGov)</t>
+  </si>
+  <si>
+    <t>Produtos de auditoria – Relatórios, Pareceres, Notas de Auditoria relativos à avaliação e à consultoria de gestão de riscos</t>
+  </si>
+  <si>
+    <t>Data de conclusão da produção</t>
+  </si>
+  <si>
+    <t>Papéis de Trabalho produzidos para subsidiar a opinião e convicção do auditor</t>
+  </si>
+  <si>
+    <t>data de conclusão da produção</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1589,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1603,6 +1632,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1619,7 +1654,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1664,9 +1699,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1674,6 +1706,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2606,7 +2644,7 @@
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="11" t="s">
         <v>47</v>
       </c>
       <c r="D14" s="2" t="s">
@@ -6219,13 +6257,13 @@
       </c>
     </row>
     <row r="102" spans="1:14">
-      <c r="A102" s="16" t="s">
+      <c r="A102" s="22" t="s">
         <v>248</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="21" t="s">
         <v>250</v>
       </c>
       <c r="D102" s="2" t="s">
@@ -6253,7 +6291,7 @@
         <v>5</v>
       </c>
       <c r="M102" s="1">
-        <v>45819</v>
+        <v>46156</v>
       </c>
       <c r="N102" s="2" t="s">
         <v>253</v>
@@ -6266,7 +6304,7 @@
       <c r="B103" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="21" t="s">
         <v>254</v>
       </c>
       <c r="D103" s="2" t="s">
@@ -6294,7 +6332,7 @@
         <v>5</v>
       </c>
       <c r="M103" s="1">
-        <v>45819</v>
+        <v>46156</v>
       </c>
       <c r="N103" s="2" t="s">
         <v>253</v>
@@ -6343,7 +6381,7 @@
       </c>
     </row>
     <row r="105" spans="1:14" customFormat="1">
-      <c r="A105" s="17" t="s">
+      <c r="A105" s="16" t="s">
         <v>261</v>
       </c>
       <c r="B105" t="s">
@@ -8563,7 +8601,7 @@
       <c r="C159" t="s">
         <v>321</v>
       </c>
-      <c r="D159" s="18" t="s">
+      <c r="D159" s="17" t="s">
         <v>334</v>
       </c>
       <c r="E159" t="s">
@@ -8575,7 +8613,7 @@
       <c r="G159" t="s">
         <v>333</v>
       </c>
-      <c r="H159" s="19">
+      <c r="H159" s="18">
         <v>44426</v>
       </c>
       <c r="I159" s="1">
@@ -8724,7 +8762,7 @@
       <c r="B163" t="s">
         <v>341</v>
       </c>
-      <c r="C163" s="18" t="s">
+      <c r="C163" s="17" t="s">
         <v>342</v>
       </c>
       <c r="D163" t="s">
@@ -8766,7 +8804,7 @@
       <c r="B164" t="s">
         <v>341</v>
       </c>
-      <c r="C164" s="18" t="s">
+      <c r="C164" s="17" t="s">
         <v>346</v>
       </c>
       <c r="D164" t="s">
@@ -9219,7 +9257,7 @@
       <c r="B175" t="s">
         <v>341</v>
       </c>
-      <c r="C175" s="18" t="s">
+      <c r="C175" s="17" t="s">
         <v>368</v>
       </c>
       <c r="D175" t="s">
@@ -9387,7 +9425,7 @@
       <c r="B179" t="s">
         <v>341</v>
       </c>
-      <c r="C179" s="18" t="s">
+      <c r="C179" s="17" t="s">
         <v>377</v>
       </c>
       <c r="D179" t="s">
@@ -9469,7 +9507,7 @@
       <c r="B181" t="s">
         <v>341</v>
       </c>
-      <c r="C181" s="18" t="s">
+      <c r="C181" s="17" t="s">
         <v>381</v>
       </c>
       <c r="D181" t="s">
@@ -9634,7 +9672,7 @@
       <c r="B185" t="s">
         <v>341</v>
       </c>
-      <c r="C185" s="18" t="s">
+      <c r="C185" s="17" t="s">
         <v>389</v>
       </c>
       <c r="D185" t="s">
@@ -9716,7 +9754,7 @@
       <c r="B187" t="s">
         <v>341</v>
       </c>
-      <c r="C187" s="18" t="s">
+      <c r="C187" s="17" t="s">
         <v>394</v>
       </c>
       <c r="D187" t="s">
@@ -10005,7 +10043,7 @@
       <c r="B194" t="s">
         <v>341</v>
       </c>
-      <c r="C194" s="18" t="s">
+      <c r="C194" s="17" t="s">
         <v>409</v>
       </c>
       <c r="D194" t="s">
@@ -10047,7 +10085,7 @@
       <c r="B195" t="s">
         <v>413</v>
       </c>
-      <c r="C195" s="21" t="s">
+      <c r="C195" s="20" t="s">
         <v>414</v>
       </c>
       <c r="D195" s="2" t="s">
@@ -10089,7 +10127,7 @@
       <c r="B196" t="s">
         <v>413</v>
       </c>
-      <c r="C196" s="21" t="s">
+      <c r="C196" s="20" t="s">
         <v>417</v>
       </c>
       <c r="D196" s="2" t="s">
@@ -10130,7 +10168,7 @@
       <c r="B197" t="s">
         <v>413</v>
       </c>
-      <c r="C197" s="20" t="s">
+      <c r="C197" s="19" t="s">
         <v>419</v>
       </c>
       <c r="D197" t="s">
@@ -10174,7 +10212,7 @@
       <c r="B198" t="s">
         <v>413</v>
       </c>
-      <c r="C198" s="21" t="s">
+      <c r="C198" s="20" t="s">
         <v>421</v>
       </c>
       <c r="D198" s="2" t="s">
@@ -10218,7 +10256,7 @@
       <c r="B199" t="s">
         <v>413</v>
       </c>
-      <c r="C199" s="21" t="s">
+      <c r="C199" s="20" t="s">
         <v>423</v>
       </c>
       <c r="D199" s="2" t="s">
@@ -10262,7 +10300,7 @@
       <c r="B200" t="s">
         <v>413</v>
       </c>
-      <c r="C200" s="20" t="s">
+      <c r="C200" s="19" t="s">
         <v>425</v>
       </c>
       <c r="D200" t="s">
@@ -10306,7 +10344,7 @@
       <c r="B201" t="s">
         <v>413</v>
       </c>
-      <c r="C201" s="21" t="s">
+      <c r="C201" s="20" t="s">
         <v>427</v>
       </c>
       <c r="D201" s="2" t="s">
@@ -10350,7 +10388,7 @@
       <c r="B202" t="s">
         <v>413</v>
       </c>
-      <c r="C202" s="21" t="s">
+      <c r="C202" s="20" t="s">
         <v>429</v>
       </c>
       <c r="D202" s="2" t="s">
@@ -10391,7 +10429,7 @@
       <c r="B203" t="s">
         <v>413</v>
       </c>
-      <c r="C203" s="20" t="s">
+      <c r="C203" s="19" t="s">
         <v>431</v>
       </c>
       <c r="D203" t="s">
@@ -10433,7 +10471,7 @@
       <c r="B204" t="s">
         <v>413</v>
       </c>
-      <c r="C204" s="21" t="s">
+      <c r="C204" s="20" t="s">
         <v>433</v>
       </c>
       <c r="D204" s="2" t="s">
@@ -10474,7 +10512,7 @@
       <c r="B205" t="s">
         <v>413</v>
       </c>
-      <c r="C205" s="21" t="s">
+      <c r="C205" s="20" t="s">
         <v>435</v>
       </c>
       <c r="D205" s="2" t="s">
@@ -10515,7 +10553,7 @@
       <c r="B206" t="s">
         <v>413</v>
       </c>
-      <c r="C206" s="21" t="s">
+      <c r="C206" s="20" t="s">
         <v>437</v>
       </c>
       <c r="D206" s="2" t="s">
@@ -10546,10 +10584,164 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="207" spans="1:14"/>
-    <row r="208" spans="1:14"/>
-    <row r="209"/>
-    <row r="210"/>
+    <row r="207" spans="1:14">
+      <c r="A207" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C207" s="2">
+        <v>1071501</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G207" t="s">
+        <v>328</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="I207" s="1">
+        <v>45842</v>
+      </c>
+      <c r="K207" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L207" s="2">
+        <v>15</v>
+      </c>
+      <c r="M207" s="1">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14">
+      <c r="A208" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C208" s="2">
+        <v>2091501</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G208" t="s">
+        <v>328</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="I208" s="1">
+        <v>45842</v>
+      </c>
+      <c r="K208" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L208" s="2">
+        <v>15</v>
+      </c>
+      <c r="M208" s="1">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13">
+      <c r="A209" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C209" s="2">
+        <v>5041501</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="I209" s="1">
+        <v>45820</v>
+      </c>
+      <c r="J209" s="1">
+        <v>46161</v>
+      </c>
+      <c r="K209" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L209" s="2">
+        <v>5</v>
+      </c>
+      <c r="M209" s="1">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13">
+      <c r="A210" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C210" s="2">
+        <v>6041501</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="I210" s="1">
+        <v>45820</v>
+      </c>
+      <c r="J210" s="1">
+        <v>46161</v>
+      </c>
+      <c r="K210" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L210" s="2">
+        <v>5</v>
+      </c>
+      <c r="M210" s="1">
+        <v>46169</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N206" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N206">

--- a/upload/informacoes_classificadas_desclassificadas.xlsx
+++ b/upload/informacoes_classificadas_desclassificadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B7B51A6-1032-4855-B24C-06298208BC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A675BCE2-E29A-4CB7-8727-780731FBA8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="6420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha2!$A$1:$N$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha2!$A$1:$N$235</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="503">
   <si>
     <t>orgao_entidade</t>
   </si>
@@ -794,7 +794,7 @@
     <t>11 - Indústria</t>
   </si>
   <si>
-    <t>https://investminas.mg.gov.br/pt/sobre/</t>
+    <t>https://investminas.mg.gov.br/sobre#transparencia</t>
   </si>
   <si>
     <t>003.11.5130</t>
@@ -857,6 +857,9 @@
     <t>005.11.5130</t>
   </si>
   <si>
+    <t>Acordos de confidencialidade</t>
+  </si>
+  <si>
     <t>Art. 23, incisos II e IV, da Lei Federal  nº 12.527/2011</t>
   </si>
   <si>
@@ -935,13 +938,148 @@
     <t>PMMG</t>
   </si>
   <si>
+    <t>0718.112421/2019-85</t>
+  </si>
+  <si>
+    <t>Inserir o assunto sobre o qual versa a informação</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso VII da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>https://www.policiamilitar.mg.gov.br/site/externo/pagina/10081/lei-de-acesso-%C3%A0-informa%C3%A7%C3%A3o</t>
+  </si>
+  <si>
+    <t>0718.112444/2019-74</t>
+  </si>
+  <si>
+    <t>2903.112427/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112397/2018-52</t>
+  </si>
+  <si>
+    <t>7460.112398/2018-52</t>
+  </si>
+  <si>
+    <t>7460.112399/2018-52</t>
+  </si>
+  <si>
+    <t>7460.112400/2018-96</t>
+  </si>
+  <si>
+    <t>7460.112401/2018-86</t>
+  </si>
+  <si>
+    <t>Art. 29, inciso I, do Decreto Estadual nº 45.969/2011</t>
+  </si>
+  <si>
+    <t>7460.112403/2018-86</t>
+  </si>
+  <si>
+    <t>7460.112404/2018-85</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso(s) VIII, III, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>7460.112405/2018-85</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso(s) VII, III, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>7460.112407/2018-75</t>
+  </si>
+  <si>
+    <t>7460.112409/2018-74</t>
+  </si>
+  <si>
+    <t>7460.112410/2018-86</t>
+  </si>
+  <si>
+    <t>7460.112411/2018-86</t>
+  </si>
+  <si>
+    <t>7460.112412/2018-86</t>
+  </si>
+  <si>
+    <t>7460.112413/2018-85</t>
+  </si>
+  <si>
+    <t>7460.112414/2018-85</t>
+  </si>
+  <si>
+    <t>7460.112415/2018-75</t>
+  </si>
+  <si>
+    <t>7460.112416/2018-75</t>
+  </si>
+  <si>
+    <t>7460.112418/2018-74</t>
+  </si>
+  <si>
+    <t>7460.112419/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112420/2019-86</t>
+  </si>
+  <si>
     <t>7460.112422/2019-85</t>
   </si>
   <si>
-    <t>Inserir o assunto sobre o qual versa a informação</t>
-  </si>
-  <si>
-    <t>https://www.policiamilitar.mg.gov.br/site/externo/pagina/10081/lei-de-acesso-%C3%A0-informa%C3%A7%C3%A3o</t>
+    <t>7460.112426/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112428/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112429/2019-64</t>
+  </si>
+  <si>
+    <t>7460.112431/2019-85</t>
+  </si>
+  <si>
+    <t>7460.112432/2019-75</t>
+  </si>
+  <si>
+    <t>7460.112434/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112435/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112436/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112437/2019-64</t>
+  </si>
+  <si>
+    <t>7460.112438/2019-64</t>
+  </si>
+  <si>
+    <t>7460.112439/2019-63</t>
+  </si>
+  <si>
+    <t>7460.112440/2019-75</t>
+  </si>
+  <si>
+    <t>7460.112441/2019-75</t>
+  </si>
+  <si>
+    <t>7460.112442/2019-75</t>
+  </si>
+  <si>
+    <t>7460.112443/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112445/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112447/2019-63</t>
+  </si>
+  <si>
+    <t>7460.112457/2019-63</t>
   </si>
   <si>
     <t>7460.112493/2023-63</t>
@@ -959,148 +1097,175 @@
     <t>Resposta ao Requerimento de informações 1602/2023</t>
   </si>
   <si>
+    <t>7460.112495/2023-52</t>
+  </si>
+  <si>
+    <t>7460.112496/2023-52</t>
+  </si>
+  <si>
     <t>7460.112497/2023-52</t>
   </si>
   <si>
     <t>Postos de combustível Orgânico da PMMG</t>
   </si>
   <si>
-    <t>Art. 23, inciso VII da Lei Federal nº 12.527/2011</t>
-  </si>
-  <si>
-    <t>7460.112495/2023-52</t>
-  </si>
-  <si>
-    <t>7460.112496/2023-52</t>
-  </si>
-  <si>
-    <t>7460.112429/2019-64</t>
-  </si>
-  <si>
-    <t>0718.112421/2019-85</t>
-  </si>
-  <si>
-    <t>0718.112444/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112442/2019-75</t>
-  </si>
-  <si>
-    <t>7460.112443/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112445/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112447/2019-63</t>
-  </si>
-  <si>
-    <t>7460.112400/2018-96</t>
-  </si>
-  <si>
-    <t>7460.112403/2018-86</t>
-  </si>
-  <si>
-    <t>7460.112409/2018-74</t>
-  </si>
-  <si>
-    <t>7460.112410/2018-86</t>
-  </si>
-  <si>
-    <t>7460.112411/2018-86</t>
-  </si>
-  <si>
-    <t>7460.112412/2018-86</t>
-  </si>
-  <si>
-    <t>7460.112414/2018-85</t>
-  </si>
-  <si>
-    <t>7460.112415/2018-75</t>
-  </si>
-  <si>
-    <t>7460.112416/2018-75</t>
-  </si>
-  <si>
-    <t>7460.112419/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112420/2019-86</t>
-  </si>
-  <si>
-    <t>7460.112426/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112428/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112431/2019-85</t>
-  </si>
-  <si>
-    <t>7460.112434/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112435/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112436/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112437/2019-64</t>
-  </si>
-  <si>
-    <t>7460.112438/2019-64</t>
-  </si>
-  <si>
-    <t>7460.112418/2018-74</t>
-  </si>
-  <si>
-    <t>7460.112432/2019-75</t>
-  </si>
-  <si>
-    <t>7460.112457/2019-63</t>
-  </si>
-  <si>
-    <t>2903.112427/2019-74</t>
-  </si>
-  <si>
-    <t>7460.112440/2019-75</t>
-  </si>
-  <si>
-    <t>7460.112397/2018-52</t>
-  </si>
-  <si>
-    <t>7460.112398/2018-52</t>
-  </si>
-  <si>
-    <t>7460.112399/2018-52</t>
-  </si>
-  <si>
-    <t>7460.112404/2018-85</t>
-  </si>
-  <si>
-    <t>Art. 23, inciso(s) VIII, III, da Lei Federal nº 12.527/2011</t>
-  </si>
-  <si>
-    <t>7460.112405/2018-85</t>
-  </si>
-  <si>
-    <t>7460.112441/2019-75</t>
-  </si>
-  <si>
-    <t>Art. 29, inciso I, do Decreto Estadual nº 45.969/2011</t>
-  </si>
-  <si>
-    <t>7460.112401/2018-86</t>
-  </si>
-  <si>
-    <t>7460.112407/2018-75</t>
-  </si>
-  <si>
-    <t>7460.112413/2018-85</t>
-  </si>
-  <si>
-    <t>7460.112439/2019-63</t>
+    <t>9760.112464/2019-64</t>
+  </si>
+  <si>
+    <t>Contém informações sobre a estrutura, composição e funcionamento das agências que compõem a 9ª RPM</t>
+  </si>
+  <si>
+    <t>0016.112468/2019-53</t>
+  </si>
+  <si>
+    <t>0016.112469/2019-52</t>
+  </si>
+  <si>
+    <t>Autorização para aquisição de armas de fogo de uso restrito</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso(s) III ,VII, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>0016.112470/2019-74</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso(s)  VII,III da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>6876.112478/2020-52</t>
+  </si>
+  <si>
+    <t>Plano de Defesa Territorial do 47 BPM da PMMG</t>
+  </si>
+  <si>
+    <t>2401.112477/2020-53</t>
+  </si>
+  <si>
+    <t>O documento é um plano de atuação do 21 BPM, em caso de ataques a instituições financeiras.</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso(s)  VII, VIII, III da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>7460.112448/2019-63</t>
+  </si>
+  <si>
+    <t>Informações sobre ORCRIM</t>
+  </si>
+  <si>
+    <t>7460.112449/2019-63</t>
+  </si>
+  <si>
+    <t>Informações sobre ataque a UFMG</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso(s) III ,VI, VII, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>7460.112451/2019-75</t>
+  </si>
+  <si>
+    <t>Informações sobre criminalidade em lagoa Santa</t>
+  </si>
+  <si>
+    <t>7460.112452/2019-74</t>
+  </si>
+  <si>
+    <t>Informações sobre explosivos em Uberaba</t>
+  </si>
+  <si>
+    <t>7460.112453/2019-74</t>
+  </si>
+  <si>
+    <t>Ataque a instituição financeira</t>
+  </si>
+  <si>
+    <t>7460.112454/2019-64</t>
+  </si>
+  <si>
+    <t>Abordagem de suspeito</t>
+  </si>
+  <si>
+    <t>7460.112455/2019-64</t>
+  </si>
+  <si>
+    <t>Operação caixa forte</t>
+  </si>
+  <si>
+    <t>7460.112456/2019-63</t>
+  </si>
+  <si>
+    <t>Organização criminosa</t>
+  </si>
+  <si>
+    <t>7460.112458/2019-63</t>
+  </si>
+  <si>
+    <t>7460.112459/2019-63</t>
+  </si>
+  <si>
+    <t>7460.112460/2019-74</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso I, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>7460.112461/2019-74</t>
+  </si>
+  <si>
+    <t>Infomações crime organizado</t>
+  </si>
+  <si>
+    <t>7460.112462/2019-74</t>
+  </si>
+  <si>
+    <t>7460.112466/2019-63</t>
+  </si>
+  <si>
+    <t>Operação policial</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso(s) III ,VIII, da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>7460.112467/2019-63</t>
+  </si>
+  <si>
+    <t>Operação Integração das Policias Bahia e Minas Gerais</t>
+  </si>
+  <si>
+    <t>7460.112471/2020-64</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>7460.112472/2020-64</t>
+  </si>
+  <si>
+    <t>0063.112265/2017-74</t>
+  </si>
+  <si>
+    <t>0063.112357/2018-64</t>
+  </si>
+  <si>
+    <t>0063.112406/2018-75</t>
+  </si>
+  <si>
+    <t>0063.112423/2019-75</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso(s) III ,VII,V  da Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>0063.112424/2019-75</t>
+  </si>
+  <si>
+    <t>0063.112425/2019-75</t>
+  </si>
+  <si>
+    <t>Art. 23, inciso(s) V ,VIII, III, II  da Lei Federal nº 12.527/2011</t>
   </si>
   <si>
     <t>Secretaria de Estado de Fazenda - SEF</t>
@@ -1589,7 +1754,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1616,12 +1781,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1635,6 +1794,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1654,7 +1837,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1696,24 +1879,36 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="3" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1723,6 +1918,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF87D448"/>
+      <color rgb="FF4FD448"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2051,14 +2252,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N210"/>
+  <dimension ref="A1:N240"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="2" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="2"/>
     <col min="3" max="3" width="71" style="2" customWidth="1"/>
     <col min="4" max="4" width="38.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="121.140625" style="2" customWidth="1"/>
     <col min="8" max="8" width="19.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2066,7 +2267,7 @@
     <col min="10" max="10" width="26" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.5703125" style="2" customWidth="1"/>
     <col min="12" max="12" width="23.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="2"/>
   </cols>
@@ -5648,7 +5849,7 @@
       <c r="B87" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="23" t="s">
         <v>214</v>
       </c>
       <c r="D87" s="2" t="s">
@@ -5663,10 +5864,10 @@
       <c r="G87" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H87" s="1">
+      <c r="H87" s="22">
         <v>45303</v>
       </c>
-      <c r="I87" s="1">
+      <c r="I87" s="22">
         <v>45303</v>
       </c>
       <c r="K87" s="3" t="s">
@@ -5676,7 +5877,7 @@
         <v>5</v>
       </c>
       <c r="M87" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>217</v>
@@ -5689,7 +5890,7 @@
       <c r="B88" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="23" t="s">
         <v>218</v>
       </c>
       <c r="D88" s="2" t="s">
@@ -5704,10 +5905,10 @@
       <c r="G88" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H88" s="1">
+      <c r="H88" s="22">
         <v>45303</v>
       </c>
-      <c r="I88" s="1">
+      <c r="I88" s="22">
         <v>45303</v>
       </c>
       <c r="K88" s="3" t="s">
@@ -5717,7 +5918,7 @@
         <v>5</v>
       </c>
       <c r="M88" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>217</v>
@@ -5730,7 +5931,7 @@
       <c r="B89" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="23" t="s">
         <v>220</v>
       </c>
       <c r="D89" s="2" t="s">
@@ -5745,10 +5946,10 @@
       <c r="G89" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H89" s="1">
+      <c r="H89" s="22">
         <v>45303</v>
       </c>
-      <c r="I89" s="1">
+      <c r="I89" s="22">
         <v>45303</v>
       </c>
       <c r="K89" s="3" t="s">
@@ -5758,7 +5959,7 @@
         <v>5</v>
       </c>
       <c r="M89" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>217</v>
@@ -5771,7 +5972,7 @@
       <c r="B90" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="23" t="s">
         <v>222</v>
       </c>
       <c r="D90" s="2" t="s">
@@ -5786,10 +5987,10 @@
       <c r="G90" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H90" s="1">
+      <c r="H90" s="22">
         <v>45303</v>
       </c>
-      <c r="I90" s="1">
+      <c r="I90" s="22">
         <v>45303</v>
       </c>
       <c r="K90" s="3" t="s">
@@ -5799,7 +6000,7 @@
         <v>5</v>
       </c>
       <c r="M90" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>217</v>
@@ -5812,7 +6013,7 @@
       <c r="B91" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="23" t="s">
         <v>224</v>
       </c>
       <c r="D91" s="2" t="s">
@@ -5827,10 +6028,10 @@
       <c r="G91" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H91" s="1">
+      <c r="H91" s="22">
         <v>45303</v>
       </c>
-      <c r="I91" s="1">
+      <c r="I91" s="22">
         <v>45303</v>
       </c>
       <c r="K91" s="3" t="s">
@@ -5840,7 +6041,7 @@
         <v>5</v>
       </c>
       <c r="M91" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>217</v>
@@ -5853,7 +6054,7 @@
       <c r="B92" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="23" t="s">
         <v>226</v>
       </c>
       <c r="D92" s="2" t="s">
@@ -5868,10 +6069,10 @@
       <c r="G92" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H92" s="1">
+      <c r="H92" s="22">
         <v>45303</v>
       </c>
-      <c r="I92" s="1">
+      <c r="I92" s="22">
         <v>45303</v>
       </c>
       <c r="K92" s="3" t="s">
@@ -5881,7 +6082,7 @@
         <v>5</v>
       </c>
       <c r="M92" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>217</v>
@@ -5894,7 +6095,7 @@
       <c r="B93" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="23" t="s">
         <v>228</v>
       </c>
       <c r="D93" s="2" t="s">
@@ -5909,10 +6110,10 @@
       <c r="G93" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H93" s="1">
+      <c r="H93" s="22">
         <v>45303</v>
       </c>
-      <c r="I93" s="1">
+      <c r="I93" s="22">
         <v>45303</v>
       </c>
       <c r="K93" s="3" t="s">
@@ -5922,7 +6123,7 @@
         <v>5</v>
       </c>
       <c r="M93" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>217</v>
@@ -5935,7 +6136,7 @@
       <c r="B94" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="23" t="s">
         <v>230</v>
       </c>
       <c r="D94" s="2" t="s">
@@ -5950,10 +6151,10 @@
       <c r="G94" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H94" s="1">
+      <c r="H94" s="22">
         <v>45303</v>
       </c>
-      <c r="I94" s="1">
+      <c r="I94" s="22">
         <v>45303</v>
       </c>
       <c r="K94" s="3" t="s">
@@ -5963,7 +6164,7 @@
         <v>5</v>
       </c>
       <c r="M94" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N94" s="2" t="s">
         <v>217</v>
@@ -5976,7 +6177,7 @@
       <c r="B95" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="23" t="s">
         <v>232</v>
       </c>
       <c r="D95" s="2" t="s">
@@ -5991,10 +6192,10 @@
       <c r="G95" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H95" s="1">
+      <c r="H95" s="22">
         <v>45303</v>
       </c>
-      <c r="I95" s="1">
+      <c r="I95" s="22">
         <v>45303</v>
       </c>
       <c r="K95" s="3" t="s">
@@ -6004,7 +6205,7 @@
         <v>5</v>
       </c>
       <c r="M95" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>217</v>
@@ -6017,7 +6218,7 @@
       <c r="B96" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="23" t="s">
         <v>234</v>
       </c>
       <c r="D96" s="2" t="s">
@@ -6032,10 +6233,10 @@
       <c r="G96" t="s">
         <v>20</v>
       </c>
-      <c r="H96" s="1">
+      <c r="H96" s="22">
         <v>45303</v>
       </c>
-      <c r="I96" s="1">
+      <c r="I96" s="22">
         <v>45303</v>
       </c>
       <c r="K96" s="3" t="s">
@@ -6045,24 +6246,24 @@
         <v>5</v>
       </c>
       <c r="M96" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="97" spans="1:14">
-      <c r="A97" s="15" t="s">
+      <c r="A97" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="23" t="s">
         <v>236</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>41</v>
@@ -6071,12 +6272,12 @@
         <v>216</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H97" s="1">
+        <v>238</v>
+      </c>
+      <c r="H97" s="22">
         <v>45303</v>
       </c>
-      <c r="I97" s="1">
+      <c r="I97" s="22">
         <v>45303</v>
       </c>
       <c r="K97" s="3" t="s">
@@ -6086,7 +6287,7 @@
         <v>15</v>
       </c>
       <c r="M97" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>217</v>
@@ -6099,11 +6300,11 @@
       <c r="B98" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>238</v>
+      <c r="C98" s="23" t="s">
+        <v>239</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>18</v>
@@ -6112,12 +6313,12 @@
         <v>216</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H98" s="1">
+        <v>238</v>
+      </c>
+      <c r="H98" s="22">
         <v>45303</v>
       </c>
-      <c r="I98" s="1">
+      <c r="I98" s="22">
         <v>45303</v>
       </c>
       <c r="K98" s="3" t="s">
@@ -6127,7 +6328,7 @@
         <v>5</v>
       </c>
       <c r="M98" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>217</v>
@@ -6140,25 +6341,25 @@
       <c r="B99" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>240</v>
+      <c r="C99" s="23" t="s">
+        <v>241</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H99" s="1">
+        <v>238</v>
+      </c>
+      <c r="H99" s="22">
         <v>45303</v>
       </c>
-      <c r="I99" s="1">
+      <c r="I99" s="22">
         <v>45303</v>
       </c>
       <c r="K99" s="3" t="s">
@@ -6168,7 +6369,7 @@
         <v>5</v>
       </c>
       <c r="M99" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N99" s="2" t="s">
         <v>217</v>
@@ -6181,25 +6382,25 @@
       <c r="B100" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>243</v>
+      <c r="C100" s="23" t="s">
+        <v>244</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>210</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H100" s="1">
+        <v>238</v>
+      </c>
+      <c r="H100" s="22">
         <v>45303</v>
       </c>
-      <c r="I100" s="1">
+      <c r="I100" s="22">
         <v>45303</v>
       </c>
       <c r="K100" s="3" t="s">
@@ -6209,7 +6410,7 @@
         <v>25</v>
       </c>
       <c r="M100" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N100" s="2" t="s">
         <v>217</v>
@@ -6222,25 +6423,25 @@
       <c r="B101" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="G101" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H101" s="1">
+        <v>238</v>
+      </c>
+      <c r="H101" s="22">
         <v>45303</v>
       </c>
-      <c r="I101" s="1">
+      <c r="I101" s="22">
         <v>45303</v>
       </c>
       <c r="K101" s="3" t="s">
@@ -6250,30 +6451,30 @@
         <v>5</v>
       </c>
       <c r="M101" s="1">
-        <v>45814</v>
+        <v>46171</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="102" spans="1:14">
-      <c r="A102" s="22" t="s">
-        <v>248</v>
+      <c r="A102" s="20" t="s">
+        <v>249</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C102" s="21" t="s">
         <v>250</v>
       </c>
+      <c r="C102" s="19" t="s">
+        <v>251</v>
+      </c>
       <c r="D102" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G102" t="s">
         <v>20</v>
@@ -6294,27 +6495,27 @@
         <v>46156</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C103" s="21" t="s">
-        <v>254</v>
+        <v>250</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>255</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G103" t="s">
         <v>20</v>
@@ -6335,21 +6536,21 @@
         <v>46156</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>18</v>
@@ -6377,21 +6578,21 @@
         <v>46122</v>
       </c>
       <c r="N104" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="105" spans="1:14" customFormat="1">
-      <c r="A105" s="16" t="s">
-        <v>261</v>
+      <c r="A105" t="s">
+        <v>262</v>
       </c>
       <c r="B105" t="s">
-        <v>262</v>
-      </c>
-      <c r="C105" s="2" t="s">
         <v>263</v>
       </c>
+      <c r="C105" s="27" t="s">
+        <v>264</v>
+      </c>
       <c r="D105" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>18</v>
@@ -6399,17 +6600,17 @@
       <c r="F105" t="s">
         <v>198</v>
       </c>
-      <c r="G105" t="s">
-        <v>174</v>
+      <c r="G105" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="H105" s="1">
-        <v>44349</v>
+        <v>43486</v>
       </c>
       <c r="I105" s="1">
         <v>43486</v>
       </c>
       <c r="J105" s="1">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="K105" s="3" t="s">
         <v>21</v>
@@ -6419,21 +6620,21 @@
       </c>
       <c r="M105" s="2"/>
       <c r="N105" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B106" t="s">
-        <v>262</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
+      </c>
+      <c r="C106" s="27" t="s">
+        <v>268</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>18</v>
@@ -6441,40 +6642,40 @@
       <c r="F106" t="s">
         <v>198</v>
       </c>
-      <c r="G106" t="s">
-        <v>268</v>
+      <c r="G106" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="H106" s="1">
-        <v>44617</v>
+        <v>43587</v>
       </c>
       <c r="I106" s="1">
-        <v>45225</v>
+        <v>43587</v>
+      </c>
+      <c r="J106" s="1">
+        <v>45432</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L106" s="7">
-        <v>5</v>
-      </c>
-      <c r="M106" s="1">
-        <v>45817</v>
+        <v>21</v>
+      </c>
+      <c r="L106" s="2">
+        <v>5</v>
       </c>
       <c r="N106" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B107" t="s">
-        <v>262</v>
-      </c>
-      <c r="C107" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C107" s="27" t="s">
         <v>269</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>18</v>
@@ -6483,36 +6684,39 @@
         <v>198</v>
       </c>
       <c r="G107" t="s">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="H107" s="1">
-        <v>44617</v>
+        <v>43503</v>
       </c>
       <c r="I107" s="1">
-        <v>45225</v>
+        <v>43503</v>
+      </c>
+      <c r="J107" s="1">
+        <v>45432</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L107" s="2">
         <v>5</v>
       </c>
       <c r="N107" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B108" t="s">
-        <v>262</v>
-      </c>
-      <c r="C108" t="s">
-        <v>271</v>
-      </c>
-      <c r="D108" t="s">
-        <v>272</v>
+        <v>263</v>
+      </c>
+      <c r="C108" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>18</v>
@@ -6520,39 +6724,40 @@
       <c r="F108" t="s">
         <v>198</v>
       </c>
-      <c r="G108" s="2" t="s">
-        <v>273</v>
+      <c r="G108" t="s">
+        <v>20</v>
       </c>
       <c r="H108" s="1">
-        <v>42990</v>
+        <v>43264</v>
       </c>
       <c r="I108" s="1">
-        <v>45967</v>
-      </c>
-      <c r="J108"/>
+        <v>43264</v>
+      </c>
+      <c r="J108" s="1">
+        <v>45428</v>
+      </c>
       <c r="K108" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L108" s="2">
-        <v>5</v>
-      </c>
-      <c r="M108"/>
+        <v>21</v>
+      </c>
+      <c r="L108" s="7">
+        <v>5</v>
+      </c>
       <c r="N108" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B109" t="s">
-        <v>262</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>274</v>
+        <v>263</v>
+      </c>
+      <c r="C109" s="27" t="s">
+        <v>271</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>18</v>
@@ -6560,37 +6765,40 @@
       <c r="F109" t="s">
         <v>198</v>
       </c>
-      <c r="G109" s="2" t="s">
-        <v>273</v>
+      <c r="G109" t="s">
+        <v>20</v>
       </c>
       <c r="H109" s="1">
-        <v>42990</v>
+        <v>43271</v>
       </c>
       <c r="I109" s="1">
-        <v>45230</v>
+        <v>43271</v>
+      </c>
+      <c r="J109" s="1">
+        <v>45428</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L109" s="2">
         <v>5</v>
       </c>
       <c r="N109" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B110" t="s">
-        <v>262</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>275</v>
+        <v>263</v>
+      </c>
+      <c r="C110" s="27" t="s">
+        <v>272</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>18</v>
@@ -6598,37 +6806,40 @@
       <c r="F110" t="s">
         <v>198</v>
       </c>
-      <c r="G110" s="2" t="s">
-        <v>273</v>
+      <c r="G110" t="s">
+        <v>20</v>
       </c>
       <c r="H110" s="1">
-        <v>42990</v>
+        <v>43294</v>
       </c>
       <c r="I110" s="1">
-        <v>45230</v>
+        <v>43294</v>
+      </c>
+      <c r="J110" s="1">
+        <v>45428</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L110" s="7">
         <v>5</v>
       </c>
       <c r="N110" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B111" t="s">
-        <v>262</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>276</v>
+        <v>263</v>
+      </c>
+      <c r="C111" s="27" t="s">
+        <v>273</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>18</v>
@@ -6636,14 +6847,14 @@
       <c r="F111" t="s">
         <v>198</v>
       </c>
-      <c r="G111" s="2" t="s">
-        <v>273</v>
+      <c r="G111" t="s">
+        <v>20</v>
       </c>
       <c r="H111" s="1">
-        <v>44349</v>
+        <v>43297</v>
       </c>
       <c r="I111" s="1">
-        <v>43511</v>
+        <v>43297</v>
       </c>
       <c r="J111" s="1">
         <v>45428</v>
@@ -6655,21 +6866,21 @@
         <v>5</v>
       </c>
       <c r="N111" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B112" t="s">
-        <v>262</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>277</v>
+        <v>263</v>
+      </c>
+      <c r="C112" s="27" t="s">
+        <v>274</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>18</v>
@@ -6677,40 +6888,41 @@
       <c r="F112" t="s">
         <v>198</v>
       </c>
-      <c r="G112" s="2" t="s">
-        <v>273</v>
+      <c r="G112" t="s">
+        <v>275</v>
       </c>
       <c r="H112" s="1">
-        <v>44617</v>
+        <v>43304</v>
       </c>
       <c r="I112" s="1">
-        <v>43486</v>
+        <v>43304</v>
       </c>
       <c r="J112" s="1">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L112" s="7">
-        <v>5</v>
-      </c>
+      <c r="L112" s="2">
+        <v>5</v>
+      </c>
+      <c r="M112" s="1"/>
       <c r="N112" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B113" t="s">
-        <v>262</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>278</v>
+        <v>263</v>
+      </c>
+      <c r="C113" s="27" t="s">
+        <v>276</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>18</v>
@@ -6718,17 +6930,17 @@
       <c r="F113" t="s">
         <v>198</v>
       </c>
-      <c r="G113" s="2" t="s">
-        <v>273</v>
+      <c r="G113" t="s">
+        <v>20</v>
       </c>
       <c r="H113" s="1">
-        <v>44734</v>
+        <v>43308</v>
       </c>
       <c r="I113" s="1">
-        <v>43587</v>
+        <v>43308</v>
       </c>
       <c r="J113" s="1">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K113" s="3" t="s">
         <v>21</v>
@@ -6737,21 +6949,21 @@
         <v>5</v>
       </c>
       <c r="N113" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B114" t="s">
-        <v>262</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>279</v>
+        <v>263</v>
+      </c>
+      <c r="C114" s="27" t="s">
+        <v>277</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>18</v>
@@ -6760,13 +6972,13 @@
         <v>198</v>
       </c>
       <c r="G114" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="H114" s="1">
-        <v>42734</v>
+        <v>43308</v>
       </c>
       <c r="I114" s="1">
-        <v>43571</v>
+        <v>43308</v>
       </c>
       <c r="J114" s="1">
         <v>45428</v>
@@ -6778,21 +6990,21 @@
         <v>5</v>
       </c>
       <c r="N114" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B115" t="s">
-        <v>262</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>280</v>
+        <v>263</v>
+      </c>
+      <c r="C115" s="27" t="s">
+        <v>279</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>18</v>
@@ -6801,13 +7013,13 @@
         <v>198</v>
       </c>
       <c r="G115" t="s">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="H115" s="1">
-        <v>43132</v>
+        <v>43308</v>
       </c>
       <c r="I115" s="1">
-        <v>43571</v>
+        <v>43308</v>
       </c>
       <c r="J115" s="1">
         <v>45428</v>
@@ -6815,25 +7027,25 @@
       <c r="K115" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L115" s="2">
+      <c r="L115" s="7">
         <v>5</v>
       </c>
       <c r="N115" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B116" t="s">
-        <v>262</v>
-      </c>
-      <c r="C116" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C116" s="27" t="s">
         <v>281</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>18</v>
@@ -6842,13 +7054,13 @@
         <v>198</v>
       </c>
       <c r="G116" t="s">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="H116" s="1">
-        <v>43500</v>
+        <v>43325</v>
       </c>
       <c r="I116" s="1">
-        <v>43599</v>
+        <v>43325</v>
       </c>
       <c r="J116" s="1">
         <v>45428</v>
@@ -6856,25 +7068,26 @@
       <c r="K116" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L116" s="2">
-        <v>5</v>
-      </c>
-      <c r="N116" t="s">
-        <v>265</v>
+      <c r="L116" s="7">
+        <v>5</v>
+      </c>
+      <c r="M116" s="1"/>
+      <c r="N116" s="21" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B117" t="s">
-        <v>262</v>
-      </c>
-      <c r="C117" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C117" s="27" t="s">
         <v>282</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>18</v>
@@ -6886,10 +7099,10 @@
         <v>20</v>
       </c>
       <c r="H117" s="1">
-        <v>43819</v>
+        <v>43328</v>
       </c>
       <c r="I117" s="1">
-        <v>43609</v>
+        <v>43328</v>
       </c>
       <c r="J117" s="1">
         <v>45428</v>
@@ -6901,21 +7114,21 @@
         <v>5</v>
       </c>
       <c r="N117" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B118" t="s">
-        <v>262</v>
-      </c>
-      <c r="C118" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C118" s="27" t="s">
         <v>283</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>18</v>
@@ -6927,10 +7140,10 @@
         <v>20</v>
       </c>
       <c r="H118" s="1">
-        <v>44176</v>
+        <v>43328</v>
       </c>
       <c r="I118" s="1">
-        <v>43297</v>
+        <v>43328</v>
       </c>
       <c r="J118" s="1">
         <v>45428</v>
@@ -6938,25 +7151,25 @@
       <c r="K118" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L118" s="2">
+      <c r="L118" s="7">
         <v>5</v>
       </c>
       <c r="N118" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B119" t="s">
-        <v>262</v>
-      </c>
-      <c r="C119" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C119" s="27" t="s">
         <v>284</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>18</v>
@@ -6968,10 +7181,10 @@
         <v>20</v>
       </c>
       <c r="H119" s="1">
-        <v>44349</v>
+        <v>43329</v>
       </c>
       <c r="I119" s="1">
-        <v>43308</v>
+        <v>43329</v>
       </c>
       <c r="J119" s="1">
         <v>45428</v>
@@ -6983,21 +7196,21 @@
         <v>5</v>
       </c>
       <c r="N119" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B120" t="s">
-        <v>262</v>
-      </c>
-      <c r="C120" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C120" s="27" t="s">
         <v>285</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>18</v>
@@ -7009,10 +7222,10 @@
         <v>20</v>
       </c>
       <c r="H120" s="1">
-        <v>44349</v>
+        <v>43339</v>
       </c>
       <c r="I120" s="1">
-        <v>43328</v>
+        <v>43339</v>
       </c>
       <c r="J120" s="1">
         <v>45428</v>
@@ -7020,25 +7233,25 @@
       <c r="K120" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L120" s="7">
+      <c r="L120" s="2">
         <v>5</v>
       </c>
       <c r="N120" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B121" t="s">
-        <v>262</v>
-      </c>
-      <c r="C121" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C121" s="27" t="s">
         <v>286</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>18</v>
@@ -7047,13 +7260,13 @@
         <v>198</v>
       </c>
       <c r="G121" t="s">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="H121" s="1">
-        <v>44349</v>
+        <v>43346</v>
       </c>
       <c r="I121" s="1">
-        <v>43328</v>
+        <v>43346</v>
       </c>
       <c r="J121" s="1">
         <v>45428</v>
@@ -7064,22 +7277,23 @@
       <c r="L121" s="7">
         <v>5</v>
       </c>
+      <c r="M121" s="1"/>
       <c r="N121" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B122" t="s">
-        <v>262</v>
-      </c>
-      <c r="C122" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C122" s="27" t="s">
         <v>287</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>18</v>
@@ -7091,10 +7305,10 @@
         <v>20</v>
       </c>
       <c r="H122" s="1">
-        <v>44349</v>
+        <v>43353</v>
       </c>
       <c r="I122" s="1">
-        <v>43329</v>
+        <v>43353</v>
       </c>
       <c r="J122" s="1">
         <v>45428</v>
@@ -7102,25 +7316,25 @@
       <c r="K122" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L122" s="2">
+      <c r="L122" s="7">
         <v>5</v>
       </c>
       <c r="N122" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B123" t="s">
-        <v>262</v>
-      </c>
-      <c r="C123" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C123" s="27" t="s">
         <v>288</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>18</v>
@@ -7132,10 +7346,10 @@
         <v>20</v>
       </c>
       <c r="H123" s="1">
-        <v>44349</v>
+        <v>43415</v>
       </c>
       <c r="I123" s="1">
-        <v>43339</v>
+        <v>43415</v>
       </c>
       <c r="J123" s="1">
         <v>45428</v>
@@ -7143,25 +7357,25 @@
       <c r="K123" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L123" s="2">
+      <c r="L123" s="7">
         <v>5</v>
       </c>
       <c r="N123" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B124" t="s">
-        <v>262</v>
-      </c>
-      <c r="C124" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C124" s="27" t="s">
         <v>289</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>18</v>
@@ -7173,10 +7387,10 @@
         <v>20</v>
       </c>
       <c r="H124" s="1">
-        <v>44349</v>
+        <v>43416</v>
       </c>
       <c r="I124" s="1">
-        <v>43353</v>
+        <v>43416</v>
       </c>
       <c r="J124" s="1">
         <v>45428</v>
@@ -7184,25 +7398,25 @@
       <c r="K124" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L124" s="7">
+      <c r="L124" s="2">
         <v>5</v>
       </c>
       <c r="N124" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B125" t="s">
-        <v>262</v>
-      </c>
-      <c r="C125" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C125" s="27" t="s">
         <v>290</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>18</v>
@@ -7214,10 +7428,10 @@
         <v>20</v>
       </c>
       <c r="H125" s="1">
-        <v>44349</v>
+        <v>43461</v>
       </c>
       <c r="I125" s="1">
-        <v>43415</v>
+        <v>43461</v>
       </c>
       <c r="J125" s="1">
         <v>45428</v>
@@ -7229,21 +7443,21 @@
         <v>5</v>
       </c>
       <c r="N125" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B126" t="s">
-        <v>262</v>
-      </c>
-      <c r="C126" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C126" s="27" t="s">
         <v>291</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>18</v>
@@ -7255,10 +7469,10 @@
         <v>20</v>
       </c>
       <c r="H126" s="1">
-        <v>44349</v>
+        <v>43472</v>
       </c>
       <c r="I126" s="1">
-        <v>43416</v>
+        <v>43472</v>
       </c>
       <c r="J126" s="1">
         <v>45428</v>
@@ -7270,21 +7484,21 @@
         <v>5</v>
       </c>
       <c r="N126" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>262</v>
-      </c>
-      <c r="C127" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C127" s="27" t="s">
         <v>292</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>18</v>
@@ -7296,10 +7510,10 @@
         <v>20</v>
       </c>
       <c r="H127" s="1">
-        <v>44349</v>
+        <v>43480</v>
       </c>
       <c r="I127" s="1">
-        <v>43472</v>
+        <v>43480</v>
       </c>
       <c r="J127" s="1">
         <v>45428</v>
@@ -7307,25 +7521,25 @@
       <c r="K127" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L127" s="2">
+      <c r="L127" s="7">
         <v>5</v>
       </c>
       <c r="N127" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14">
+      <c r="A128" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="B128" t="s">
+        <v>263</v>
+      </c>
+      <c r="C128" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="D128" s="2" t="s">
         <v>265</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14">
-      <c r="A128" t="s">
-        <v>261</v>
-      </c>
-      <c r="B128" t="s">
-        <v>262</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>18</v>
@@ -7334,13 +7548,13 @@
         <v>198</v>
       </c>
       <c r="G128" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="H128" s="1">
-        <v>44349</v>
+        <v>43486</v>
       </c>
       <c r="I128" s="1">
-        <v>43480</v>
+        <v>43486</v>
       </c>
       <c r="J128" s="1">
         <v>45428</v>
@@ -7352,21 +7566,21 @@
         <v>5</v>
       </c>
       <c r="N128" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B129" t="s">
-        <v>262</v>
-      </c>
-      <c r="C129" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C129" s="27" t="s">
         <v>294</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>18</v>
@@ -7378,7 +7592,7 @@
         <v>20</v>
       </c>
       <c r="H129" s="1">
-        <v>44349</v>
+        <v>43500</v>
       </c>
       <c r="I129" s="1">
         <v>43500</v>
@@ -7393,21 +7607,21 @@
         <v>5</v>
       </c>
       <c r="N129" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B130" t="s">
-        <v>262</v>
-      </c>
-      <c r="C130" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C130" s="27" t="s">
         <v>295</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>18</v>
@@ -7419,7 +7633,7 @@
         <v>20</v>
       </c>
       <c r="H130" s="1">
-        <v>44349</v>
+        <v>43509</v>
       </c>
       <c r="I130" s="1">
         <v>43509</v>
@@ -7434,21 +7648,21 @@
         <v>5</v>
       </c>
       <c r="N130" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B131" t="s">
-        <v>262</v>
-      </c>
-      <c r="C131" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C131" s="27" t="s">
         <v>296</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>18</v>
@@ -7456,14 +7670,14 @@
       <c r="F131" t="s">
         <v>198</v>
       </c>
-      <c r="G131" t="s">
-        <v>20</v>
+      <c r="G131" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="H131" s="1">
-        <v>44349</v>
+        <v>43511</v>
       </c>
       <c r="I131" s="1">
-        <v>43524</v>
+        <v>43511</v>
       </c>
       <c r="J131" s="1">
         <v>45428</v>
@@ -7475,21 +7689,21 @@
         <v>5</v>
       </c>
       <c r="N131" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B132" t="s">
-        <v>262</v>
-      </c>
-      <c r="C132" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C132" s="27" t="s">
         <v>297</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>18</v>
@@ -7501,10 +7715,10 @@
         <v>20</v>
       </c>
       <c r="H132" s="1">
-        <v>44349</v>
+        <v>43524</v>
       </c>
       <c r="I132" s="1">
-        <v>43545</v>
+        <v>43524</v>
       </c>
       <c r="J132" s="1">
         <v>45428</v>
@@ -7512,25 +7726,25 @@
       <c r="K132" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L132" s="7">
+      <c r="L132" s="2">
         <v>5</v>
       </c>
       <c r="N132" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B133" t="s">
-        <v>262</v>
-      </c>
-      <c r="C133" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C133" s="27" t="s">
         <v>298</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>18</v>
@@ -7542,10 +7756,10 @@
         <v>20</v>
       </c>
       <c r="H133" s="1">
-        <v>44349</v>
+        <v>43543</v>
       </c>
       <c r="I133" s="1">
-        <v>43545</v>
+        <v>43543</v>
       </c>
       <c r="J133" s="1">
         <v>45428</v>
@@ -7557,21 +7771,21 @@
         <v>5</v>
       </c>
       <c r="N133" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B134" t="s">
-        <v>262</v>
-      </c>
-      <c r="C134" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C134" s="27" t="s">
         <v>299</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>18</v>
@@ -7583,7 +7797,7 @@
         <v>20</v>
       </c>
       <c r="H134" s="1">
-        <v>44349</v>
+        <v>43545</v>
       </c>
       <c r="I134" s="1">
         <v>43545</v>
@@ -7594,25 +7808,25 @@
       <c r="K134" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L134" s="2">
+      <c r="L134" s="7">
         <v>5</v>
       </c>
       <c r="N134" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B135" t="s">
-        <v>262</v>
-      </c>
-      <c r="C135" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C135" s="27" t="s">
         <v>300</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>18</v>
@@ -7624,10 +7838,10 @@
         <v>20</v>
       </c>
       <c r="H135" s="1">
-        <v>44349</v>
+        <v>43545</v>
       </c>
       <c r="I135" s="1">
-        <v>43549</v>
+        <v>43545</v>
       </c>
       <c r="J135" s="1">
         <v>45428</v>
@@ -7635,25 +7849,25 @@
       <c r="K135" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L135" s="2">
+      <c r="L135" s="7">
         <v>5</v>
       </c>
       <c r="N135" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B136" t="s">
-        <v>262</v>
-      </c>
-      <c r="C136" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C136" s="27" t="s">
         <v>301</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>18</v>
@@ -7665,10 +7879,10 @@
         <v>20</v>
       </c>
       <c r="H136" s="1">
-        <v>44349</v>
+        <v>43545</v>
       </c>
       <c r="I136" s="1">
-        <v>43551</v>
+        <v>43545</v>
       </c>
       <c r="J136" s="1">
         <v>45428</v>
@@ -7676,25 +7890,25 @@
       <c r="K136" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L136" s="7">
+      <c r="L136" s="2">
         <v>5</v>
       </c>
       <c r="N136" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B137" t="s">
-        <v>262</v>
-      </c>
-      <c r="C137" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C137" s="27" t="s">
         <v>302</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>18</v>
@@ -7706,10 +7920,10 @@
         <v>20</v>
       </c>
       <c r="H137" s="1">
-        <v>44349</v>
+        <v>43549</v>
       </c>
       <c r="I137" s="1">
-        <v>43461</v>
+        <v>43549</v>
       </c>
       <c r="J137" s="1">
         <v>45428</v>
@@ -7717,25 +7931,25 @@
       <c r="K137" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L137" s="7">
+      <c r="L137" s="2">
         <v>5</v>
       </c>
       <c r="N137" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B138" t="s">
-        <v>262</v>
-      </c>
-      <c r="C138" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C138" s="27" t="s">
         <v>303</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>18</v>
@@ -7747,10 +7961,10 @@
         <v>20</v>
       </c>
       <c r="H138" s="1">
-        <v>44349</v>
+        <v>43551</v>
       </c>
       <c r="I138" s="1">
-        <v>43543</v>
+        <v>43551</v>
       </c>
       <c r="J138" s="1">
         <v>45428</v>
@@ -7761,22 +7975,22 @@
       <c r="L138" s="7">
         <v>5</v>
       </c>
-      <c r="N138" t="s">
-        <v>265</v>
+      <c r="N138" s="21" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B139" t="s">
-        <v>262</v>
-      </c>
-      <c r="C139" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C139" s="27" t="s">
         <v>304</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>18</v>
@@ -7785,13 +7999,13 @@
         <v>198</v>
       </c>
       <c r="G139" t="s">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="H139" s="1">
-        <v>44426</v>
+        <v>43551</v>
       </c>
       <c r="I139" s="1">
-        <v>43511</v>
+        <v>43551</v>
       </c>
       <c r="J139" s="1">
         <v>45428</v>
@@ -7799,25 +8013,26 @@
       <c r="K139" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L139" s="7">
-        <v>5</v>
-      </c>
+      <c r="L139" s="2">
+        <v>5</v>
+      </c>
+      <c r="M139" s="1"/>
       <c r="N139" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B140" t="s">
-        <v>262</v>
-      </c>
-      <c r="C140" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C140" s="27" t="s">
         <v>305</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>18</v>
@@ -7829,36 +8044,36 @@
         <v>20</v>
       </c>
       <c r="H140" s="1">
-        <v>44617</v>
+        <v>43559</v>
       </c>
       <c r="I140" s="1">
-        <v>43503</v>
+        <v>43559</v>
       </c>
       <c r="J140" s="1">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K140" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L140" s="2">
+      <c r="L140" s="7">
         <v>5</v>
       </c>
       <c r="N140" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B141" t="s">
-        <v>262</v>
-      </c>
-      <c r="C141" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C141" s="27" t="s">
         <v>306</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>18</v>
@@ -7867,13 +8082,13 @@
         <v>198</v>
       </c>
       <c r="G141" t="s">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="H141" s="1">
-        <v>45656</v>
+        <v>43570</v>
       </c>
       <c r="I141" s="1">
-        <v>43559</v>
+        <v>43570</v>
       </c>
       <c r="J141" s="1">
         <v>45428</v>
@@ -7881,25 +8096,26 @@
       <c r="K141" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L141" s="7">
-        <v>5</v>
-      </c>
+      <c r="L141" s="2">
+        <v>5</v>
+      </c>
+      <c r="M141" s="1"/>
       <c r="N141" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B142" t="s">
-        <v>262</v>
-      </c>
-      <c r="C142" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C142" s="27" t="s">
         <v>307</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>18</v>
@@ -7911,36 +8127,36 @@
         <v>20</v>
       </c>
       <c r="H142" s="1">
-        <v>45820</v>
+        <v>43571</v>
       </c>
       <c r="I142" s="1">
-        <v>43264</v>
+        <v>43571</v>
       </c>
       <c r="J142" s="1">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K142" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L142" s="7">
+      <c r="L142" s="2">
         <v>5</v>
       </c>
       <c r="N142" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B143" t="s">
-        <v>262</v>
-      </c>
-      <c r="C143" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C143" s="27" t="s">
         <v>308</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>18</v>
@@ -7952,13 +8168,13 @@
         <v>20</v>
       </c>
       <c r="H143" s="1">
-        <v>45820</v>
+        <v>43571</v>
       </c>
       <c r="I143" s="1">
-        <v>43271</v>
+        <v>43571</v>
       </c>
       <c r="J143" s="1">
-        <v>45432</v>
+        <v>45428</v>
       </c>
       <c r="K143" s="3" t="s">
         <v>21</v>
@@ -7967,21 +8183,21 @@
         <v>5</v>
       </c>
       <c r="N143" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B144" t="s">
-        <v>262</v>
-      </c>
-      <c r="C144" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C144" s="27" t="s">
         <v>309</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>18</v>
@@ -7993,10 +8209,10 @@
         <v>20</v>
       </c>
       <c r="H144" s="1">
-        <v>46013</v>
+        <v>43599</v>
       </c>
       <c r="I144" s="1">
-        <v>43294</v>
+        <v>43599</v>
       </c>
       <c r="J144" s="1">
         <v>45428</v>
@@ -8004,25 +8220,25 @@
       <c r="K144" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L144" s="7">
+      <c r="L144" s="2">
         <v>5</v>
       </c>
       <c r="N144" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B145" t="s">
-        <v>262</v>
-      </c>
-      <c r="C145" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C145" s="27" t="s">
         <v>310</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>18</v>
@@ -8031,13 +8247,13 @@
         <v>198</v>
       </c>
       <c r="G145" t="s">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="H145" s="1">
-        <v>44349</v>
+        <v>43609</v>
       </c>
       <c r="I145" s="1">
-        <v>43308</v>
+        <v>43609</v>
       </c>
       <c r="J145" s="1">
         <v>45428</v>
@@ -8045,25 +8261,25 @@
       <c r="K145" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L145" s="2">
+      <c r="L145" s="7">
         <v>5</v>
       </c>
       <c r="N145" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B146" t="s">
-        <v>262</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>312</v>
+        <v>263</v>
+      </c>
+      <c r="C146" s="27" t="s">
+        <v>311</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>18</v>
@@ -8072,13 +8288,13 @@
         <v>198</v>
       </c>
       <c r="G146" t="s">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="H146" s="1">
-        <v>44349</v>
+        <v>43511</v>
       </c>
       <c r="I146" s="1">
-        <v>43308</v>
+        <v>43511</v>
       </c>
       <c r="J146" s="1">
         <v>45428</v>
@@ -8090,21 +8306,21 @@
         <v>5</v>
       </c>
       <c r="N146" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B147" t="s">
-        <v>262</v>
-      </c>
-      <c r="C147" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C147" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="D147" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>18</v>
@@ -8116,37 +8332,36 @@
         <v>314</v>
       </c>
       <c r="H147" s="1">
-        <v>43712</v>
+        <v>45225</v>
       </c>
       <c r="I147" s="1">
-        <v>43570</v>
-      </c>
-      <c r="J147" s="1">
-        <v>45428</v>
+        <v>45225</v>
       </c>
       <c r="K147" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L147" s="2">
-        <v>5</v>
-      </c>
-      <c r="M147" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="L147" s="7">
+        <v>5</v>
+      </c>
+      <c r="M147" s="1">
+        <v>45817</v>
+      </c>
       <c r="N147" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B148" t="s">
-        <v>262</v>
-      </c>
-      <c r="C148" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C148" s="27" t="s">
         <v>315</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>18</v>
@@ -8158,37 +8373,33 @@
         <v>314</v>
       </c>
       <c r="H148" s="1">
-        <v>44349</v>
+        <v>45225</v>
       </c>
       <c r="I148" s="1">
-        <v>43304</v>
-      </c>
-      <c r="J148" s="1">
-        <v>45428</v>
+        <v>45225</v>
       </c>
       <c r="K148" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L148" s="2">
         <v>5</v>
       </c>
-      <c r="M148" s="1"/>
       <c r="N148" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B149" t="s">
-        <v>262</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>316</v>
+        <v>263</v>
+      </c>
+      <c r="C149" s="27" t="s">
+        <v>317</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>264</v>
+        <v>313</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>18</v>
@@ -8196,41 +8407,37 @@
       <c r="F149" t="s">
         <v>198</v>
       </c>
-      <c r="G149" t="s">
-        <v>314</v>
+      <c r="G149" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="H149" s="1">
-        <v>44349</v>
+        <v>45230</v>
       </c>
       <c r="I149" s="1">
-        <v>43325</v>
-      </c>
-      <c r="J149" s="1">
-        <v>45428</v>
+        <v>45230</v>
       </c>
       <c r="K149" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L149" s="7">
-        <v>5</v>
-      </c>
-      <c r="M149" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="L149" s="2">
+        <v>5</v>
+      </c>
       <c r="N149" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B150" t="s">
-        <v>262</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>317</v>
+        <v>263</v>
+      </c>
+      <c r="C150" s="27" t="s">
+        <v>318</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>18</v>
@@ -8238,41 +8445,37 @@
       <c r="F150" t="s">
         <v>198</v>
       </c>
-      <c r="G150" t="s">
-        <v>314</v>
+      <c r="G150" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="H150" s="1">
-        <v>44349</v>
+        <v>45230</v>
       </c>
       <c r="I150" s="1">
-        <v>43346</v>
-      </c>
-      <c r="J150" s="1">
-        <v>45428</v>
+        <v>45230</v>
       </c>
       <c r="K150" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L150" s="7">
         <v>5</v>
       </c>
-      <c r="M150" s="1"/>
       <c r="N150" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B151" t="s">
-        <v>262</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
+      </c>
+      <c r="C151" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="D151" t="s">
+        <v>320</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>18</v>
@@ -8280,1500 +8483,1459 @@
       <c r="F151" t="s">
         <v>198</v>
       </c>
-      <c r="G151" t="s">
-        <v>314</v>
+      <c r="G151" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="H151" s="1">
-        <v>44349</v>
+        <v>45236</v>
       </c>
       <c r="I151" s="1">
-        <v>43551</v>
-      </c>
-      <c r="J151" s="1">
-        <v>45428</v>
-      </c>
+        <v>45236</v>
+      </c>
+      <c r="J151"/>
       <c r="K151" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L151" s="2">
+        <v>5</v>
+      </c>
+      <c r="M151"/>
+      <c r="N151" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14">
+      <c r="A152" t="s">
+        <v>262</v>
+      </c>
+      <c r="B152" t="s">
+        <v>263</v>
+      </c>
+      <c r="C152" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="D152" t="s">
+        <v>322</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G152" t="s">
+        <v>20</v>
+      </c>
+      <c r="H152" s="1">
+        <v>43767</v>
+      </c>
+      <c r="I152" s="1">
+        <v>43767</v>
+      </c>
+      <c r="J152" s="1">
+        <v>45806</v>
+      </c>
+      <c r="K152" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L151" s="2">
-        <v>5</v>
-      </c>
-      <c r="M151" s="1"/>
-      <c r="N151" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14" customFormat="1">
-      <c r="A152" t="s">
-        <v>319</v>
-      </c>
-      <c r="B152" t="s">
-        <v>320</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D152" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="H152" s="1">
-        <v>44617</v>
-      </c>
-      <c r="I152" s="1">
-        <v>44617</v>
-      </c>
-      <c r="J152" s="2"/>
-      <c r="K152" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="L152" s="2">
-        <v>25</v>
-      </c>
-      <c r="M152" s="1">
-        <v>46128</v>
+        <v>5</v>
       </c>
       <c r="N152" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="B153" t="s">
-        <v>320</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D153" s="11" t="s">
-        <v>325</v>
+        <v>263</v>
+      </c>
+      <c r="C153" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>53</v>
+        <v>198</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>323</v>
+        <v>266</v>
       </c>
       <c r="H153" s="1">
-        <v>45821</v>
+        <v>43808</v>
       </c>
       <c r="I153" s="1">
-        <v>44617</v>
-      </c>
-      <c r="K153" s="3" t="s">
-        <v>42</v>
+        <v>43808</v>
+      </c>
+      <c r="J153" s="1">
+        <v>45806</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L153" s="2">
-        <v>25</v>
-      </c>
-      <c r="M153" s="1">
-        <v>46128</v>
+        <v>5</v>
       </c>
       <c r="N153" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="B154" t="s">
-        <v>320</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D154" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C154" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="D154" t="s">
+        <v>325</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G154" t="s">
         <v>326</v>
       </c>
-      <c r="E154" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G154" s="2" t="s">
-        <v>323</v>
-      </c>
       <c r="H154" s="1">
-        <v>45821</v>
+        <v>43808</v>
       </c>
       <c r="I154" s="1">
-        <v>44617</v>
-      </c>
-      <c r="K154" s="3" t="s">
-        <v>42</v>
+        <v>43808</v>
+      </c>
+      <c r="J154" s="1">
+        <v>45806</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L154" s="2">
-        <v>25</v>
-      </c>
-      <c r="M154" s="1">
-        <v>46128</v>
+        <v>5</v>
       </c>
       <c r="N154" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="B155" t="s">
-        <v>320</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D155" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C155" s="25" t="s">
         <v>327</v>
       </c>
+      <c r="D155" t="s">
+        <v>325</v>
+      </c>
       <c r="E155" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>53</v>
+        <v>198</v>
       </c>
       <c r="G155" t="s">
         <v>328</v>
       </c>
       <c r="H155" s="1">
-        <v>44923</v>
+        <v>43808</v>
       </c>
       <c r="I155" s="1">
-        <v>42990</v>
-      </c>
-      <c r="K155" s="3" t="s">
-        <v>42</v>
+        <v>43808</v>
+      </c>
+      <c r="J155" s="1">
+        <v>45806</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L155" s="2">
-        <v>25</v>
-      </c>
-      <c r="M155" s="1">
-        <v>46128</v>
+        <v>5</v>
       </c>
       <c r="N155" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="B156" t="s">
-        <v>320</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D156" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C156" s="25" t="s">
         <v>329</v>
       </c>
+      <c r="D156" t="s">
+        <v>330</v>
+      </c>
       <c r="E156" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G156" t="s">
-        <v>328</v>
+        <v>198</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="H156" s="1">
-        <v>44925</v>
+        <v>43977</v>
       </c>
       <c r="I156" s="1">
-        <v>42990</v>
-      </c>
-      <c r="K156" s="3" t="s">
-        <v>42</v>
+        <v>43977</v>
+      </c>
+      <c r="J156" s="1">
+        <v>45803</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L156" s="2">
-        <v>25</v>
-      </c>
-      <c r="M156" s="1">
-        <v>46128</v>
+        <v>5</v>
       </c>
       <c r="N156" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="B157" t="s">
-        <v>320</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D157" s="11" t="s">
-        <v>330</v>
+        <v>263</v>
+      </c>
+      <c r="C157" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="D157" t="s">
+        <v>332</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>331</v>
+        <v>198</v>
+      </c>
+      <c r="G157" t="s">
+        <v>333</v>
       </c>
       <c r="H157" s="1">
-        <v>44617</v>
+        <v>43972</v>
       </c>
       <c r="I157" s="1">
-        <v>44617</v>
-      </c>
-      <c r="K157" s="3" t="s">
-        <v>42</v>
+        <v>43972</v>
+      </c>
+      <c r="J157" s="1">
+        <v>45796</v>
+      </c>
+      <c r="K157" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L157" s="2">
-        <v>25</v>
-      </c>
-      <c r="M157" s="1">
-        <v>46128</v>
+        <v>5</v>
       </c>
       <c r="N157" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="B158" t="s">
-        <v>320</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D158" s="11" t="s">
-        <v>332</v>
+        <v>263</v>
+      </c>
+      <c r="C158" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="D158" t="s">
+        <v>335</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>53</v>
+        <v>198</v>
       </c>
       <c r="G158" t="s">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="H158" s="1">
-        <v>44194</v>
+        <v>43650</v>
       </c>
       <c r="I158" s="1">
-        <v>42990</v>
-      </c>
-      <c r="K158" s="3" t="s">
-        <v>42</v>
+        <v>43650</v>
+      </c>
+      <c r="J158" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K158" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L158" s="2">
-        <v>25</v>
-      </c>
-      <c r="M158" s="1">
-        <v>46128</v>
+        <v>5</v>
       </c>
       <c r="N158" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="B159" t="s">
-        <v>320</v>
-      </c>
-      <c r="C159" t="s">
-        <v>321</v>
-      </c>
-      <c r="D159" s="17" t="s">
-        <v>334</v>
-      </c>
-      <c r="E159" t="s">
-        <v>210</v>
+        <v>263</v>
+      </c>
+      <c r="C159" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="D159" t="s">
+        <v>337</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>53</v>
+        <v>198</v>
       </c>
       <c r="G159" t="s">
-        <v>333</v>
-      </c>
-      <c r="H159" s="18">
-        <v>44426</v>
+        <v>338</v>
+      </c>
+      <c r="H159" s="1">
+        <v>43651</v>
       </c>
       <c r="I159" s="1">
-        <v>42191</v>
-      </c>
-      <c r="K159" s="3" t="s">
-        <v>42</v>
+        <v>43651</v>
+      </c>
+      <c r="J159" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L159" s="2">
-        <v>25</v>
-      </c>
-      <c r="M159" s="1">
-        <v>46128</v>
+        <v>5</v>
       </c>
       <c r="N159" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="B160" t="s">
-        <v>320</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D160" s="11" t="s">
-        <v>335</v>
+        <v>263</v>
+      </c>
+      <c r="C160" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="D160" t="s">
+        <v>340</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>336</v>
+        <v>198</v>
+      </c>
+      <c r="G160" t="s">
+        <v>20</v>
       </c>
       <c r="H160" s="1">
-        <v>45820</v>
+        <v>43658</v>
       </c>
       <c r="I160" s="1">
-        <v>45820</v>
-      </c>
-      <c r="K160" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L160" s="7">
-        <v>5</v>
-      </c>
-      <c r="M160" s="1">
-        <v>46128</v>
+        <v>43658</v>
+      </c>
+      <c r="J160" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L160" s="2">
+        <v>5</v>
       </c>
       <c r="N160" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="B161" t="s">
-        <v>320</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D161" s="11" t="s">
-        <v>337</v>
+        <v>263</v>
+      </c>
+      <c r="C161" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="D161" t="s">
+        <v>342</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>336</v>
+        <v>198</v>
+      </c>
+      <c r="G161" t="s">
+        <v>275</v>
       </c>
       <c r="H161" s="1">
-        <v>45820</v>
+        <v>43668</v>
       </c>
       <c r="I161" s="1">
-        <v>45820</v>
-      </c>
-      <c r="K161" s="3" t="s">
-        <v>42</v>
+        <v>43668</v>
+      </c>
+      <c r="J161" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K161" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L161" s="2">
         <v>5</v>
       </c>
-      <c r="M161" s="1">
-        <v>46128</v>
-      </c>
       <c r="N161" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="B162" t="s">
-        <v>320</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D162" s="11" t="s">
-        <v>338</v>
+        <v>263</v>
+      </c>
+      <c r="C162" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="D162" t="s">
+        <v>344</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G162" s="2" t="s">
-        <v>339</v>
+        <v>198</v>
+      </c>
+      <c r="G162" t="s">
+        <v>20</v>
       </c>
       <c r="H162" s="1">
-        <v>44734</v>
+        <v>43678</v>
       </c>
       <c r="I162" s="1">
-        <v>44734</v>
-      </c>
-      <c r="K162" s="3" t="s">
-        <v>42</v>
+        <v>43678</v>
+      </c>
+      <c r="J162" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L162" s="2">
         <v>5</v>
       </c>
-      <c r="M162" s="1">
-        <v>46128</v>
-      </c>
       <c r="N162" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" customFormat="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14">
       <c r="A163" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B163" t="s">
-        <v>341</v>
-      </c>
-      <c r="C163" s="17" t="s">
-        <v>342</v>
+        <v>263</v>
+      </c>
+      <c r="C163" s="24" t="s">
+        <v>345</v>
       </c>
       <c r="D163" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F163" t="s">
+        <v>18</v>
+      </c>
+      <c r="F163" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G163" t="s">
-        <v>344</v>
+      <c r="G163" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="H163" s="1">
-        <v>44027</v>
+        <v>43685</v>
       </c>
       <c r="I163" s="1">
-        <v>45656</v>
-      </c>
-      <c r="J163" s="2"/>
-      <c r="K163" s="3" t="s">
-        <v>42</v>
+        <v>43685</v>
+      </c>
+      <c r="J163" s="1">
+        <v>45824</v>
+      </c>
+      <c r="K163" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L163" s="2">
-        <v>25</v>
-      </c>
-      <c r="M163" s="1">
-        <v>46141</v>
+        <v>5</v>
       </c>
       <c r="N163" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B164" t="s">
-        <v>341</v>
-      </c>
-      <c r="C164" s="17" t="s">
-        <v>346</v>
+        <v>263</v>
+      </c>
+      <c r="C164" s="24" t="s">
+        <v>347</v>
       </c>
       <c r="D164" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F164" t="s">
+        <v>18</v>
+      </c>
+      <c r="F164" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G164" t="s">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="H164" s="1">
-        <v>44348</v>
+        <v>43686</v>
       </c>
       <c r="I164" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K164" s="3" t="s">
-        <v>42</v>
+        <v>43686</v>
+      </c>
+      <c r="J164" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K164" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L164" s="2">
-        <v>25</v>
-      </c>
-      <c r="M164" s="1">
-        <v>46141</v>
+        <v>5</v>
       </c>
       <c r="N164" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B165" t="s">
-        <v>341</v>
-      </c>
-      <c r="C165" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="D165" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="24" t="s">
         <v>349</v>
       </c>
+      <c r="D165" t="s">
+        <v>350</v>
+      </c>
       <c r="E165" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F165" t="s">
+        <v>18</v>
+      </c>
+      <c r="F165" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G165" t="s">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="H165" s="1">
-        <v>44348</v>
+        <v>43686</v>
       </c>
       <c r="I165" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K165" s="3" t="s">
-        <v>42</v>
+        <v>43686</v>
+      </c>
+      <c r="J165" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L165" s="2">
-        <v>25</v>
-      </c>
-      <c r="M165" s="1">
-        <v>46141</v>
+        <v>5</v>
       </c>
       <c r="N165" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B166" t="s">
-        <v>341</v>
-      </c>
-      <c r="C166" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="D166" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C166" s="24" t="s">
         <v>351</v>
       </c>
+      <c r="D166" t="s">
+        <v>265</v>
+      </c>
       <c r="E166" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F166" t="s">
+        <v>18</v>
+      </c>
+      <c r="F166" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G166" t="s">
-        <v>174</v>
+        <v>63</v>
       </c>
       <c r="H166" s="1">
-        <v>44348</v>
+        <v>43703</v>
       </c>
       <c r="I166" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K166" s="3" t="s">
-        <v>42</v>
+        <v>43703</v>
+      </c>
+      <c r="J166" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K166" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L166" s="2">
-        <v>25</v>
-      </c>
-      <c r="M166" s="1">
-        <v>46141</v>
+        <v>5</v>
       </c>
       <c r="N166" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B167" t="s">
-        <v>341</v>
-      </c>
-      <c r="C167" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C167" s="25" t="s">
         <v>352</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="D167" t="s">
+        <v>265</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G167" t="s">
+        <v>63</v>
+      </c>
+      <c r="H167" s="1">
+        <v>43707</v>
+      </c>
+      <c r="I167" s="1">
+        <v>43707</v>
+      </c>
+      <c r="J167" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K167" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L167" s="2">
+        <v>5</v>
+      </c>
+      <c r="N167" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14">
+      <c r="A168" t="s">
+        <v>262</v>
+      </c>
+      <c r="B168" t="s">
+        <v>263</v>
+      </c>
+      <c r="C168" s="25" t="s">
         <v>353</v>
       </c>
-      <c r="E167" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F167" t="s">
+      <c r="D168" t="s">
+        <v>265</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G167" t="s">
-        <v>174</v>
-      </c>
-      <c r="H167" s="1">
-        <v>44348</v>
-      </c>
-      <c r="I167" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K167" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L167" s="7">
-        <v>5</v>
-      </c>
-      <c r="M167" s="1">
-        <v>46141</v>
-      </c>
-      <c r="N167" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14" customFormat="1">
-      <c r="A168" t="s">
-        <v>340</v>
-      </c>
-      <c r="B168" t="s">
-        <v>341</v>
-      </c>
-      <c r="C168" s="11" t="s">
+      <c r="G168" t="s">
         <v>354</v>
       </c>
-      <c r="D168" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F168" t="s">
-        <v>198</v>
-      </c>
-      <c r="G168" t="s">
-        <v>174</v>
-      </c>
       <c r="H168" s="1">
-        <v>44348</v>
+        <v>43710</v>
       </c>
       <c r="I168" s="1">
-        <v>44349</v>
-      </c>
-      <c r="J168" s="2"/>
-      <c r="K168" s="3" t="s">
-        <v>42</v>
+        <v>43710</v>
+      </c>
+      <c r="J168" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K168" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L168" s="2">
         <v>5</v>
       </c>
-      <c r="M168" s="1">
-        <v>46141</v>
-      </c>
       <c r="N168" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B169" t="s">
-        <v>341</v>
-      </c>
-      <c r="C169" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C169" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="D169" t="s">
         <v>356</v>
       </c>
-      <c r="D169" s="2" t="s">
-        <v>357</v>
-      </c>
       <c r="E169" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F169" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G169" t="s">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="H169" s="1">
-        <v>44348</v>
+        <v>43732</v>
       </c>
       <c r="I169" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K169" s="3" t="s">
-        <v>42</v>
+        <v>43732</v>
+      </c>
+      <c r="J169" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K169" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L169" s="2">
         <v>5</v>
       </c>
-      <c r="M169" s="1">
-        <v>46141</v>
-      </c>
       <c r="N169" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B170" t="s">
-        <v>341</v>
-      </c>
-      <c r="C170" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>359</v>
+        <v>263</v>
+      </c>
+      <c r="C170" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="D170" t="s">
+        <v>265</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F170" t="s">
+      <c r="F170" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G170" t="s">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="H170" s="1">
-        <v>44348</v>
+        <v>43732</v>
       </c>
       <c r="I170" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K170" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L170" s="7">
-        <v>5</v>
-      </c>
-      <c r="M170" s="1">
-        <v>46141</v>
+        <v>43732</v>
+      </c>
+      <c r="J170" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L170" s="2">
+        <v>5</v>
       </c>
       <c r="N170" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B171" t="s">
-        <v>341</v>
-      </c>
-      <c r="C171" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C171" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="D171" t="s">
+        <v>359</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G171" t="s">
         <v>360</v>
       </c>
-      <c r="D171" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F171" t="s">
-        <v>198</v>
-      </c>
-      <c r="G171" t="s">
-        <v>174</v>
-      </c>
       <c r="H171" s="1">
-        <v>44348</v>
+        <v>43787</v>
       </c>
       <c r="I171" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K171" s="3" t="s">
-        <v>42</v>
+        <v>43787</v>
+      </c>
+      <c r="J171" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K171" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L171" s="2">
-        <v>15</v>
-      </c>
-      <c r="M171" s="1">
-        <v>46141</v>
+        <v>5</v>
       </c>
       <c r="N171" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B172" t="s">
-        <v>341</v>
-      </c>
-      <c r="C172" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C172" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="D172" t="s">
         <v>362</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="E172" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G172" t="s">
+        <v>20</v>
+      </c>
+      <c r="H172" s="1">
+        <v>43791</v>
+      </c>
+      <c r="I172" s="1">
+        <v>43791</v>
+      </c>
+      <c r="J172" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K172" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L172" s="2">
+        <v>5</v>
+      </c>
+      <c r="N172" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14">
+      <c r="A173" t="s">
+        <v>262</v>
+      </c>
+      <c r="B173" t="s">
+        <v>263</v>
+      </c>
+      <c r="C173" s="25" t="s">
         <v>363</v>
       </c>
-      <c r="E172" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F172" t="s">
+      <c r="D173" t="s">
+        <v>364</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F173" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G172" t="s">
-        <v>174</v>
-      </c>
-      <c r="H172" s="1">
-        <v>44348</v>
-      </c>
-      <c r="I172" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K172" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L172" s="2">
-        <v>25</v>
-      </c>
-      <c r="M172" s="1">
-        <v>46141</v>
-      </c>
-      <c r="N172" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14" customFormat="1">
-      <c r="A173" t="s">
-        <v>340</v>
-      </c>
-      <c r="B173" t="s">
-        <v>341</v>
-      </c>
-      <c r="C173" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F173" t="s">
-        <v>198</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>273</v>
+      <c r="G173" t="s">
+        <v>20</v>
       </c>
       <c r="H173" s="1">
-        <v>44348</v>
+        <v>43872</v>
       </c>
       <c r="I173" s="1">
-        <v>44349</v>
-      </c>
-      <c r="J173" s="2"/>
-      <c r="K173" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L173" s="7">
-        <v>5</v>
-      </c>
-      <c r="M173" s="1">
-        <v>46141</v>
+        <v>43872</v>
+      </c>
+      <c r="J173" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L173" s="2">
+        <v>5</v>
       </c>
       <c r="N173" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B174" t="s">
-        <v>341</v>
-      </c>
-      <c r="C174" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>367</v>
+        <v>263</v>
+      </c>
+      <c r="C174" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="D174" t="s">
+        <v>356</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F174" t="s">
+        <v>18</v>
+      </c>
+      <c r="F174" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G174" t="s">
         <v>20</v>
       </c>
       <c r="H174" s="1">
-        <v>44348</v>
+        <v>43874</v>
       </c>
       <c r="I174" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K174" s="3" t="s">
-        <v>42</v>
+        <v>43874</v>
+      </c>
+      <c r="J174" s="1">
+        <v>45793</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L174" s="2">
-        <v>15</v>
-      </c>
-      <c r="M174" s="1">
-        <v>46141</v>
+        <v>5</v>
       </c>
       <c r="N174" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B175" t="s">
-        <v>341</v>
-      </c>
-      <c r="C175" s="17" t="s">
-        <v>368</v>
+        <v>263</v>
+      </c>
+      <c r="C175" s="24" t="s">
+        <v>366</v>
       </c>
       <c r="D175" t="s">
-        <v>369</v>
+        <v>265</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F175" t="s">
+      <c r="F175" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G175" t="s">
-        <v>370</v>
+        <v>326</v>
       </c>
       <c r="H175" s="1">
-        <v>43712</v>
+        <v>42937</v>
       </c>
       <c r="I175" s="1">
-        <v>43712</v>
+        <v>42937</v>
       </c>
       <c r="J175" s="1">
-        <v>45539</v>
-      </c>
-      <c r="K175" s="3" t="s">
+        <v>45489</v>
+      </c>
+      <c r="K175" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L175" s="7">
-        <v>5</v>
-      </c>
-      <c r="M175" s="1">
-        <v>46141</v>
+      <c r="L175" s="2">
+        <v>5</v>
       </c>
       <c r="N175" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B176" t="s">
-        <v>341</v>
-      </c>
-      <c r="C176" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>372</v>
+        <v>263</v>
+      </c>
+      <c r="C176" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="D176" t="s">
+        <v>265</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F176" t="s">
+        <v>18</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G176" t="s">
-        <v>370</v>
+      <c r="G176" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="H176" s="1">
-        <v>44348</v>
+        <v>43130</v>
       </c>
       <c r="I176" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K176" s="3" t="s">
-        <v>42</v>
+        <v>43130</v>
+      </c>
+      <c r="J176" s="1">
+        <v>45489</v>
+      </c>
+      <c r="K176" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L176" s="2">
-        <v>15</v>
-      </c>
-      <c r="M176" s="1">
-        <v>46141</v>
+        <v>5</v>
       </c>
       <c r="N176" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B177" t="s">
-        <v>341</v>
-      </c>
-      <c r="C177" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>374</v>
+        <v>263</v>
+      </c>
+      <c r="C177" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="D177" t="s">
+        <v>265</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F177" t="s">
+        <v>18</v>
+      </c>
+      <c r="F177" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G177" t="s">
-        <v>370</v>
+        <v>326</v>
       </c>
       <c r="H177" s="1">
-        <v>44348</v>
+        <v>43312</v>
       </c>
       <c r="I177" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K177" s="3" t="s">
-        <v>42</v>
+        <v>43312</v>
+      </c>
+      <c r="J177" s="1">
+        <v>45489</v>
+      </c>
+      <c r="K177" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L177" s="2">
-        <v>25</v>
-      </c>
-      <c r="M177" s="1">
-        <v>46141</v>
+        <v>5</v>
       </c>
       <c r="N177" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14" customFormat="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14">
       <c r="A178" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B178" t="s">
-        <v>341</v>
-      </c>
-      <c r="C178" s="11" t="s">
-        <v>375</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>376</v>
+        <v>263</v>
+      </c>
+      <c r="C178" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="D178" t="s">
+        <v>265</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F178" t="s">
+      <c r="F178" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G178" t="s">
         <v>370</v>
       </c>
       <c r="H178" s="1">
-        <v>44348</v>
+        <v>43490</v>
       </c>
       <c r="I178" s="1">
-        <v>44349</v>
-      </c>
-      <c r="J178" s="2"/>
-      <c r="K178" s="3" t="s">
-        <v>42</v>
+        <v>43490</v>
+      </c>
+      <c r="J178" s="1">
+        <v>45489</v>
+      </c>
+      <c r="K178" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L178" s="2">
         <v>5</v>
       </c>
-      <c r="M178" s="1">
-        <v>46141</v>
-      </c>
       <c r="N178" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B179" t="s">
-        <v>341</v>
-      </c>
-      <c r="C179" s="17" t="s">
-        <v>377</v>
+        <v>263</v>
+      </c>
+      <c r="C179" s="24" t="s">
+        <v>371</v>
       </c>
       <c r="D179" t="s">
-        <v>378</v>
+        <v>265</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F179" t="s">
+      <c r="F179" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G179" t="s">
         <v>370</v>
       </c>
       <c r="H179" s="1">
-        <v>44348</v>
+        <v>43490</v>
       </c>
       <c r="I179" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K179" s="3" t="s">
-        <v>42</v>
+        <v>43490</v>
+      </c>
+      <c r="J179" s="1">
+        <v>45489</v>
+      </c>
+      <c r="K179" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L179" s="2">
         <v>5</v>
       </c>
-      <c r="M179" s="1">
-        <v>46141</v>
-      </c>
       <c r="N179" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" t="s">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="B180" t="s">
-        <v>341</v>
-      </c>
-      <c r="C180" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C180" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="D180" t="s">
+        <v>265</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G180" t="s">
+        <v>373</v>
+      </c>
+      <c r="H180" s="1">
+        <v>43490</v>
+      </c>
+      <c r="I180" s="1">
+        <v>43490</v>
+      </c>
+      <c r="J180" s="1">
+        <v>45489</v>
+      </c>
+      <c r="K180" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L180" s="2">
+        <v>5</v>
+      </c>
+      <c r="N180" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14">
+      <c r="A181"/>
+      <c r="B181"/>
+      <c r="D181"/>
+      <c r="G181"/>
+      <c r="H181" s="1"/>
+      <c r="I181" s="1"/>
+      <c r="J181" s="1"/>
+      <c r="N181"/>
+    </row>
+    <row r="182" spans="1:14" customFormat="1">
+      <c r="A182" t="s">
+        <v>374</v>
+      </c>
+      <c r="B182" t="s">
+        <v>375</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D182" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="H182" s="1">
+        <v>44617</v>
+      </c>
+      <c r="I182" s="1">
+        <v>44617</v>
+      </c>
+      <c r="J182" s="2"/>
+      <c r="K182" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L182" s="2">
+        <v>25</v>
+      </c>
+      <c r="M182" s="1">
+        <v>46128</v>
+      </c>
+      <c r="N182" t="s">
         <v>379</v>
       </c>
-      <c r="D180" s="2" t="s">
+    </row>
+    <row r="183" spans="1:14">
+      <c r="A183" t="s">
+        <v>374</v>
+      </c>
+      <c r="B183" t="s">
+        <v>375</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D183" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="E180" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F180" t="s">
-        <v>198</v>
-      </c>
-      <c r="G180" t="s">
-        <v>370</v>
-      </c>
-      <c r="H180" s="1">
-        <v>44348</v>
-      </c>
-      <c r="I180" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K180" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L180" s="7">
-        <v>5</v>
-      </c>
-      <c r="M180" s="1">
-        <v>46141</v>
-      </c>
-      <c r="N180" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14">
-      <c r="A181" t="s">
-        <v>340</v>
-      </c>
-      <c r="B181" t="s">
-        <v>341</v>
-      </c>
-      <c r="C181" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="D181" t="s">
-        <v>382</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F181" t="s">
-        <v>198</v>
-      </c>
-      <c r="G181" t="s">
-        <v>370</v>
-      </c>
-      <c r="H181" s="1">
-        <v>44348</v>
-      </c>
-      <c r="I181" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K181" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L181" s="2">
-        <v>15</v>
-      </c>
-      <c r="M181" s="1">
-        <v>46141</v>
-      </c>
-      <c r="N181" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="182" spans="1:14">
-      <c r="A182" t="s">
-        <v>340</v>
-      </c>
-      <c r="B182" t="s">
-        <v>341</v>
-      </c>
-      <c r="C182" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F182" t="s">
-        <v>198</v>
-      </c>
-      <c r="G182" t="s">
-        <v>370</v>
-      </c>
-      <c r="H182" s="1">
-        <v>44348</v>
-      </c>
-      <c r="I182" s="1">
-        <v>44349</v>
-      </c>
-      <c r="K182" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L182" s="2">
-        <v>15</v>
-      </c>
-      <c r="M182" s="1">
-        <v>46141</v>
-      </c>
-      <c r="N182" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="183" spans="1:14" customFormat="1">
-      <c r="A183" t="s">
-        <v>340</v>
-      </c>
-      <c r="B183" t="s">
-        <v>341</v>
-      </c>
-      <c r="C183" s="11" t="s">
-        <v>385</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="E183" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F183" t="s">
-        <v>198</v>
-      </c>
-      <c r="G183" t="s">
-        <v>370</v>
+        <v>210</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="H183" s="1">
-        <v>44348</v>
+        <v>45821</v>
       </c>
       <c r="I183" s="1">
-        <v>44349</v>
-      </c>
-      <c r="J183" s="2"/>
+        <v>44617</v>
+      </c>
       <c r="K183" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L183" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M183" s="1">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="N183" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B184" t="s">
-        <v>341</v>
-      </c>
-      <c r="C184" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>388</v>
+        <v>375</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D184" s="11" t="s">
+        <v>381</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F184" t="s">
-        <v>198</v>
-      </c>
-      <c r="G184" t="s">
-        <v>370</v>
+        <v>210</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="H184" s="1">
-        <v>44348</v>
+        <v>45821</v>
       </c>
       <c r="I184" s="1">
-        <v>44349</v>
+        <v>44617</v>
       </c>
       <c r="K184" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L184" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M184" s="1">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="N184" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
     </row>
     <row r="185" spans="1:14">
       <c r="A185" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B185" t="s">
-        <v>341</v>
-      </c>
-      <c r="C185" s="17" t="s">
-        <v>389</v>
-      </c>
-      <c r="D185" t="s">
-        <v>390</v>
+        <v>375</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D185" s="11" t="s">
+        <v>382</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F185" t="s">
-        <v>198</v>
+        <v>210</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G185" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="H185" s="1">
-        <v>44348</v>
+        <v>44923</v>
       </c>
       <c r="I185" s="1">
-        <v>44349</v>
+        <v>42990</v>
       </c>
       <c r="K185" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L185" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M185" s="1">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="N185" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B186" t="s">
-        <v>341</v>
-      </c>
-      <c r="C186" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="D186" s="2" t="s">
-        <v>392</v>
+        <v>375</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D186" s="11" t="s">
+        <v>384</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F186" t="s">
-        <v>198</v>
+        <v>210</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G186" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="H186" s="1">
-        <v>44348</v>
+        <v>44925</v>
       </c>
       <c r="I186" s="1">
-        <v>44349</v>
+        <v>42990</v>
       </c>
       <c r="K186" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L186" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M186" s="1">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="N186" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B187" t="s">
-        <v>341</v>
-      </c>
-      <c r="C187" s="17" t="s">
-        <v>394</v>
-      </c>
-      <c r="D187" t="s">
-        <v>395</v>
+        <v>375</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D187" s="11" t="s">
+        <v>385</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F187" t="s">
-        <v>198</v>
-      </c>
-      <c r="G187" t="s">
-        <v>396</v>
+      <c r="F187" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="H187" s="1">
-        <v>44348</v>
+        <v>44617</v>
       </c>
       <c r="I187" s="1">
-        <v>44349</v>
+        <v>44617</v>
       </c>
       <c r="K187" s="3" t="s">
         <v>42</v>
@@ -9782,41 +9944,40 @@
         <v>25</v>
       </c>
       <c r="M187" s="1">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="N187" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="188" spans="1:14" customFormat="1">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14">
       <c r="A188" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B188" t="s">
-        <v>341</v>
-      </c>
-      <c r="C188" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>398</v>
+        <v>375</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D188" s="11" t="s">
+        <v>387</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F188" t="s">
-        <v>198</v>
+      <c r="F188" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G188" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="H188" s="1">
-        <v>44348</v>
+        <v>44194</v>
       </c>
       <c r="I188" s="1">
-        <v>44349</v>
-      </c>
-      <c r="J188" s="2"/>
+        <v>42990</v>
+      </c>
       <c r="K188" s="3" t="s">
         <v>42</v>
       </c>
@@ -9824,162 +9985,162 @@
         <v>25</v>
       </c>
       <c r="M188" s="1">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="N188" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B189" t="s">
-        <v>341</v>
-      </c>
-      <c r="C189" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F189" t="s">
-        <v>198</v>
+        <v>375</v>
+      </c>
+      <c r="C189" t="s">
+        <v>376</v>
+      </c>
+      <c r="D189" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="E189" t="s">
+        <v>210</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G189" t="s">
-        <v>396</v>
-      </c>
-      <c r="H189" s="1">
-        <v>44348</v>
+        <v>388</v>
+      </c>
+      <c r="H189" s="16">
+        <v>44426</v>
       </c>
       <c r="I189" s="1">
-        <v>44349</v>
+        <v>42191</v>
       </c>
       <c r="K189" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L189" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M189" s="1">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="N189" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B190" t="s">
-        <v>341</v>
-      </c>
-      <c r="C190" s="11" t="s">
-        <v>401</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>402</v>
+        <v>375</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D190" s="11" t="s">
+        <v>390</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F190" t="s">
-        <v>198</v>
-      </c>
-      <c r="G190" t="s">
-        <v>396</v>
+        <v>18</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>391</v>
       </c>
       <c r="H190" s="1">
-        <v>44348</v>
+        <v>45820</v>
       </c>
       <c r="I190" s="1">
-        <v>44349</v>
+        <v>45820</v>
       </c>
       <c r="K190" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L190" s="2">
-        <v>25</v>
+      <c r="L190" s="7">
+        <v>5</v>
       </c>
       <c r="M190" s="1">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="N190" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
     </row>
     <row r="191" spans="1:14">
       <c r="A191" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B191" t="s">
-        <v>341</v>
-      </c>
-      <c r="C191" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>404</v>
+        <v>375</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D191" s="11" t="s">
+        <v>392</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F191" t="s">
-        <v>198</v>
-      </c>
-      <c r="G191" t="s">
-        <v>396</v>
+        <v>18</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>391</v>
       </c>
       <c r="H191" s="1">
-        <v>44348</v>
+        <v>45820</v>
       </c>
       <c r="I191" s="1">
-        <v>44349</v>
+        <v>45820</v>
       </c>
       <c r="K191" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L191" s="2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M191" s="1">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="N191" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
     </row>
     <row r="192" spans="1:14">
       <c r="A192" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="B192" t="s">
-        <v>341</v>
-      </c>
-      <c r="C192" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>406</v>
+        <v>375</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D192" s="11" t="s">
+        <v>393</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F192" t="s">
-        <v>198</v>
-      </c>
-      <c r="G192" t="s">
-        <v>396</v>
+      <c r="F192" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>394</v>
       </c>
       <c r="H192" s="1">
-        <v>44348</v>
+        <v>44734</v>
       </c>
       <c r="I192" s="1">
-        <v>44349</v>
+        <v>44734</v>
       </c>
       <c r="K192" s="3" t="s">
         <v>42</v>
@@ -9988,24 +10149,24 @@
         <v>5</v>
       </c>
       <c r="M192" s="1">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="N192" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
     </row>
     <row r="193" spans="1:14" customFormat="1">
       <c r="A193" t="s">
-        <v>340</v>
+        <v>395</v>
       </c>
       <c r="B193" t="s">
-        <v>341</v>
-      </c>
-      <c r="C193" s="11" t="s">
-        <v>407</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>408</v>
+        <v>396</v>
+      </c>
+      <c r="C193" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="D193" t="s">
+        <v>398</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>210</v>
@@ -10014,13 +10175,13 @@
         <v>198</v>
       </c>
       <c r="G193" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="H193" s="1">
-        <v>44348</v>
+        <v>44027</v>
       </c>
       <c r="I193" s="1">
-        <v>44349</v>
+        <v>45656</v>
       </c>
       <c r="J193" s="2"/>
       <c r="K193" s="3" t="s">
@@ -10033,422 +10194,406 @@
         <v>46141</v>
       </c>
       <c r="N193" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="194" spans="1:14" customFormat="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14">
       <c r="A194" t="s">
-        <v>340</v>
+        <v>395</v>
       </c>
       <c r="B194" t="s">
-        <v>341</v>
-      </c>
-      <c r="C194" s="17" t="s">
-        <v>409</v>
+        <v>396</v>
+      </c>
+      <c r="C194" s="15" t="s">
+        <v>401</v>
       </c>
       <c r="D194" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="F194" t="s">
         <v>198</v>
       </c>
       <c r="G194" t="s">
-        <v>411</v>
+        <v>174</v>
       </c>
       <c r="H194" s="1">
-        <v>43910</v>
+        <v>44348</v>
       </c>
       <c r="I194" s="1">
-        <v>46013</v>
-      </c>
-      <c r="J194" s="2"/>
+        <v>44349</v>
+      </c>
       <c r="K194" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L194" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M194" s="1">
         <v>46141</v>
       </c>
       <c r="N194" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="195" spans="1:14" customFormat="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14">
       <c r="A195" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B195" t="s">
-        <v>413</v>
-      </c>
-      <c r="C195" s="20" t="s">
-        <v>414</v>
+        <v>396</v>
+      </c>
+      <c r="C195" s="11" t="s">
+        <v>403</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G195" s="9" t="s">
-        <v>142</v>
+        <v>210</v>
+      </c>
+      <c r="F195" t="s">
+        <v>198</v>
+      </c>
+      <c r="G195" t="s">
+        <v>174</v>
       </c>
       <c r="H195" s="1">
-        <v>44426</v>
+        <v>44348</v>
       </c>
       <c r="I195" s="1">
-        <v>44426</v>
-      </c>
-      <c r="J195" s="2"/>
+        <v>44349</v>
+      </c>
       <c r="K195" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L195" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M195" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N195" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="196" spans="1:14">
       <c r="A196" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B196" t="s">
-        <v>413</v>
-      </c>
-      <c r="C196" s="20" t="s">
-        <v>417</v>
+        <v>396</v>
+      </c>
+      <c r="C196" s="11" t="s">
+        <v>405</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G196" s="9" t="s">
-        <v>142</v>
+        <v>210</v>
+      </c>
+      <c r="F196" t="s">
+        <v>198</v>
+      </c>
+      <c r="G196" t="s">
+        <v>174</v>
       </c>
       <c r="H196" s="1">
-        <v>44426</v>
+        <v>44348</v>
       </c>
       <c r="I196" s="1">
-        <v>44426</v>
+        <v>44349</v>
       </c>
       <c r="K196" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L196" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M196" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N196" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="197" spans="1:14">
       <c r="A197" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B197" t="s">
-        <v>413</v>
-      </c>
-      <c r="C197" s="19" t="s">
-        <v>419</v>
-      </c>
-      <c r="D197" t="s">
-        <v>420</v>
+        <v>396</v>
+      </c>
+      <c r="C197" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>408</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F197" s="2" t="s">
-        <v>160</v>
+      <c r="F197" t="s">
+        <v>198</v>
       </c>
       <c r="G197" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="H197" s="1">
-        <v>42734</v>
+        <v>44348</v>
       </c>
       <c r="I197" s="1">
-        <v>42734</v>
-      </c>
-      <c r="J197" s="1">
-        <v>44925</v>
+        <v>44349</v>
       </c>
       <c r="K197" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L197" s="2">
+        <v>42</v>
+      </c>
+      <c r="L197" s="7">
         <v>5</v>
       </c>
       <c r="M197" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N197" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="198" spans="1:14" customFormat="1">
       <c r="A198" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B198" t="s">
-        <v>413</v>
-      </c>
-      <c r="C198" s="20" t="s">
-        <v>421</v>
+        <v>396</v>
+      </c>
+      <c r="C198" s="11" t="s">
+        <v>409</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F198" s="2" t="s">
-        <v>160</v>
+      <c r="F198" t="s">
+        <v>198</v>
       </c>
       <c r="G198" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="H198" s="1">
-        <v>43132</v>
+        <v>44348</v>
       </c>
       <c r="I198" s="1">
-        <v>43132</v>
-      </c>
-      <c r="J198" s="1">
-        <v>44966</v>
-      </c>
+        <v>44349</v>
+      </c>
+      <c r="J198" s="2"/>
       <c r="K198" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L198" s="2">
         <v>5</v>
       </c>
       <c r="M198" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N198" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="199" spans="1:14">
       <c r="A199" t="s">
+        <v>395</v>
+      </c>
+      <c r="B199" t="s">
+        <v>396</v>
+      </c>
+      <c r="C199" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="D199" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B199" t="s">
-        <v>413</v>
-      </c>
-      <c r="C199" s="20" t="s">
-        <v>423</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>424</v>
-      </c>
       <c r="E199" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F199" s="2" t="s">
-        <v>160</v>
+      <c r="F199" t="s">
+        <v>198</v>
       </c>
       <c r="G199" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="H199" s="1">
-        <v>43500</v>
+        <v>44348</v>
       </c>
       <c r="I199" s="1">
-        <v>43500</v>
-      </c>
-      <c r="J199" s="1">
-        <v>45821</v>
+        <v>44349</v>
       </c>
       <c r="K199" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L199" s="2">
         <v>5</v>
       </c>
       <c r="M199" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N199" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B200" t="s">
+        <v>396</v>
+      </c>
+      <c r="C200" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="C200" s="19" t="s">
-        <v>425</v>
-      </c>
-      <c r="D200" t="s">
-        <v>426</v>
+      <c r="D200" s="2" t="s">
+        <v>414</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F200" s="2" t="s">
-        <v>160</v>
+      <c r="F200" t="s">
+        <v>198</v>
       </c>
       <c r="G200" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="H200" s="1">
-        <v>43819</v>
+        <v>44348</v>
       </c>
       <c r="I200" s="1">
-        <v>43819</v>
-      </c>
-      <c r="J200" s="1">
-        <v>45821</v>
+        <v>44349</v>
       </c>
       <c r="K200" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L200" s="2">
+        <v>42</v>
+      </c>
+      <c r="L200" s="7">
         <v>5</v>
       </c>
       <c r="M200" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N200" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="201" spans="1:14">
       <c r="A201" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B201" t="s">
-        <v>413</v>
-      </c>
-      <c r="C201" s="20" t="s">
-        <v>427</v>
+        <v>396</v>
+      </c>
+      <c r="C201" s="11" t="s">
+        <v>415</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>160</v>
+        <v>41</v>
+      </c>
+      <c r="F201" t="s">
+        <v>198</v>
       </c>
       <c r="G201" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="H201" s="1">
-        <v>44194</v>
+        <v>44348</v>
       </c>
       <c r="I201" s="1">
-        <v>44194</v>
-      </c>
-      <c r="J201" s="1">
-        <v>44994</v>
+        <v>44349</v>
       </c>
       <c r="K201" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L201" s="7">
-        <v>5</v>
+        <v>42</v>
+      </c>
+      <c r="L201" s="2">
+        <v>15</v>
       </c>
       <c r="M201" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N201" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="202" spans="1:14">
       <c r="A202" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B202" t="s">
-        <v>413</v>
-      </c>
-      <c r="C202" s="20" t="s">
-        <v>429</v>
+        <v>396</v>
+      </c>
+      <c r="C202" s="11" t="s">
+        <v>417</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>160</v>
+        <v>210</v>
+      </c>
+      <c r="F202" t="s">
+        <v>198</v>
       </c>
       <c r="G202" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="H202" s="1">
-        <v>44923</v>
+        <v>44348</v>
       </c>
       <c r="I202" s="1">
-        <v>44923</v>
+        <v>44349</v>
       </c>
       <c r="K202" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L202" s="7">
-        <v>5</v>
+      <c r="L202" s="2">
+        <v>25</v>
       </c>
       <c r="M202" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N202" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="203" spans="1:14" customFormat="1">
       <c r="A203" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B203" t="s">
-        <v>413</v>
-      </c>
-      <c r="C203" s="19" t="s">
-        <v>431</v>
-      </c>
-      <c r="D203" t="s">
-        <v>432</v>
+        <v>396</v>
+      </c>
+      <c r="C203" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>420</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F203" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G203" t="s">
-        <v>20</v>
+      <c r="F203" t="s">
+        <v>198</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="H203" s="1">
-        <v>44925</v>
+        <v>44348</v>
       </c>
       <c r="I203" s="1">
-        <v>44925</v>
+        <v>44349</v>
       </c>
       <c r="J203" s="2"/>
       <c r="K203" s="3" t="s">
@@ -10458,297 +10603,1561 @@
         <v>5</v>
       </c>
       <c r="M203" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N203" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="204" spans="1:14">
       <c r="A204" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B204" t="s">
-        <v>413</v>
-      </c>
-      <c r="C204" s="20" t="s">
-        <v>433</v>
+        <v>396</v>
+      </c>
+      <c r="C204" s="11" t="s">
+        <v>421</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F204" s="2" t="s">
-        <v>160</v>
+        <v>41</v>
+      </c>
+      <c r="F204" t="s">
+        <v>198</v>
       </c>
       <c r="G204" t="s">
         <v>20</v>
       </c>
       <c r="H204" s="1">
-        <v>45821</v>
+        <v>44348</v>
       </c>
       <c r="I204" s="1">
-        <v>45821</v>
+        <v>44349</v>
       </c>
       <c r="K204" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L204" s="7">
-        <v>5</v>
+      <c r="L204" s="2">
+        <v>15</v>
       </c>
       <c r="M204" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N204" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="205" spans="1:14">
       <c r="A205" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B205" t="s">
-        <v>413</v>
-      </c>
-      <c r="C205" s="20" t="s">
-        <v>435</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>436</v>
+        <v>396</v>
+      </c>
+      <c r="C205" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="D205" t="s">
+        <v>424</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F205" s="2" t="s">
-        <v>160</v>
+      <c r="F205" t="s">
+        <v>198</v>
       </c>
       <c r="G205" t="s">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="H205" s="1">
-        <v>45821</v>
+        <v>43712</v>
       </c>
       <c r="I205" s="1">
-        <v>45821</v>
+        <v>43712</v>
+      </c>
+      <c r="J205" s="1">
+        <v>45539</v>
       </c>
       <c r="K205" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L205" s="2">
+        <v>21</v>
+      </c>
+      <c r="L205" s="7">
         <v>5</v>
       </c>
       <c r="M205" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N205" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
     </row>
     <row r="206" spans="1:14">
       <c r="A206" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B206" t="s">
-        <v>413</v>
-      </c>
-      <c r="C206" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="C206" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F206" t="s">
+        <v>198</v>
+      </c>
+      <c r="G206" t="s">
+        <v>425</v>
+      </c>
+      <c r="H206" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I206" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K206" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L206" s="2">
+        <v>15</v>
+      </c>
+      <c r="M206" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N206" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14">
+      <c r="A207" t="s">
+        <v>395</v>
+      </c>
+      <c r="B207" t="s">
+        <v>396</v>
+      </c>
+      <c r="C207" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F207" t="s">
+        <v>198</v>
+      </c>
+      <c r="G207" t="s">
+        <v>425</v>
+      </c>
+      <c r="H207" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I207" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K207" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L207" s="2">
+        <v>25</v>
+      </c>
+      <c r="M207" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N207" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" customFormat="1">
+      <c r="A208" t="s">
+        <v>395</v>
+      </c>
+      <c r="B208" t="s">
+        <v>396</v>
+      </c>
+      <c r="C208" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F208" t="s">
+        <v>198</v>
+      </c>
+      <c r="G208" t="s">
+        <v>425</v>
+      </c>
+      <c r="H208" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I208" s="1">
+        <v>44349</v>
+      </c>
+      <c r="J208" s="2"/>
+      <c r="K208" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L208" s="2">
+        <v>5</v>
+      </c>
+      <c r="M208" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N208" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14">
+      <c r="A209" t="s">
+        <v>395</v>
+      </c>
+      <c r="B209" t="s">
+        <v>396</v>
+      </c>
+      <c r="C209" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="D209" t="s">
+        <v>433</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F209" t="s">
+        <v>198</v>
+      </c>
+      <c r="G209" t="s">
+        <v>425</v>
+      </c>
+      <c r="H209" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I209" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K209" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L209" s="2">
+        <v>5</v>
+      </c>
+      <c r="M209" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N209" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14">
+      <c r="A210" t="s">
+        <v>395</v>
+      </c>
+      <c r="B210" t="s">
+        <v>396</v>
+      </c>
+      <c r="C210" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F210" t="s">
+        <v>198</v>
+      </c>
+      <c r="G210" t="s">
+        <v>425</v>
+      </c>
+      <c r="H210" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I210" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K210" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L210" s="7">
+        <v>5</v>
+      </c>
+      <c r="M210" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N210" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14">
+      <c r="A211" t="s">
+        <v>395</v>
+      </c>
+      <c r="B211" t="s">
+        <v>396</v>
+      </c>
+      <c r="C211" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="D211" t="s">
         <v>437</v>
       </c>
-      <c r="D206" s="2" t="s">
+      <c r="E211" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F211" t="s">
+        <v>198</v>
+      </c>
+      <c r="G211" t="s">
+        <v>425</v>
+      </c>
+      <c r="H211" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I211" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K211" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L211" s="2">
+        <v>15</v>
+      </c>
+      <c r="M211" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N211" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14">
+      <c r="A212" t="s">
+        <v>395</v>
+      </c>
+      <c r="B212" t="s">
+        <v>396</v>
+      </c>
+      <c r="C212" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E206" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F206" s="2" t="s">
+      <c r="D212" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F212" t="s">
+        <v>198</v>
+      </c>
+      <c r="G212" t="s">
+        <v>425</v>
+      </c>
+      <c r="H212" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I212" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K212" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L212" s="2">
+        <v>15</v>
+      </c>
+      <c r="M212" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N212" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" customFormat="1">
+      <c r="A213" t="s">
+        <v>395</v>
+      </c>
+      <c r="B213" t="s">
+        <v>396</v>
+      </c>
+      <c r="C213" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F213" t="s">
+        <v>198</v>
+      </c>
+      <c r="G213" t="s">
+        <v>425</v>
+      </c>
+      <c r="H213" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I213" s="1">
+        <v>44349</v>
+      </c>
+      <c r="J213" s="2"/>
+      <c r="K213" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L213" s="2">
+        <v>15</v>
+      </c>
+      <c r="M213" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N213" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14">
+      <c r="A214" t="s">
+        <v>395</v>
+      </c>
+      <c r="B214" t="s">
+        <v>396</v>
+      </c>
+      <c r="C214" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F214" t="s">
+        <v>198</v>
+      </c>
+      <c r="G214" t="s">
+        <v>425</v>
+      </c>
+      <c r="H214" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I214" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K214" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L214" s="2">
+        <v>15</v>
+      </c>
+      <c r="M214" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N214" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14">
+      <c r="A215" t="s">
+        <v>395</v>
+      </c>
+      <c r="B215" t="s">
+        <v>396</v>
+      </c>
+      <c r="C215" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="D215" t="s">
+        <v>445</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F215" t="s">
+        <v>198</v>
+      </c>
+      <c r="G215" t="s">
+        <v>425</v>
+      </c>
+      <c r="H215" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I215" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K215" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L215" s="2">
+        <v>15</v>
+      </c>
+      <c r="M215" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N215" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14">
+      <c r="A216" t="s">
+        <v>395</v>
+      </c>
+      <c r="B216" t="s">
+        <v>396</v>
+      </c>
+      <c r="C216" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F216" t="s">
+        <v>198</v>
+      </c>
+      <c r="G216" t="s">
+        <v>448</v>
+      </c>
+      <c r="H216" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I216" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K216" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L216" s="2">
+        <v>15</v>
+      </c>
+      <c r="M216" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N216" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14">
+      <c r="A217" t="s">
+        <v>395</v>
+      </c>
+      <c r="B217" t="s">
+        <v>396</v>
+      </c>
+      <c r="C217" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="D217" t="s">
+        <v>450</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F217" t="s">
+        <v>198</v>
+      </c>
+      <c r="G217" t="s">
+        <v>451</v>
+      </c>
+      <c r="H217" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I217" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K217" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L217" s="2">
+        <v>25</v>
+      </c>
+      <c r="M217" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N217" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" customFormat="1">
+      <c r="A218" t="s">
+        <v>395</v>
+      </c>
+      <c r="B218" t="s">
+        <v>396</v>
+      </c>
+      <c r="C218" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F218" t="s">
+        <v>198</v>
+      </c>
+      <c r="G218" t="s">
+        <v>451</v>
+      </c>
+      <c r="H218" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I218" s="1">
+        <v>44349</v>
+      </c>
+      <c r="J218" s="2"/>
+      <c r="K218" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L218" s="2">
+        <v>25</v>
+      </c>
+      <c r="M218" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N218" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14">
+      <c r="A219" t="s">
+        <v>395</v>
+      </c>
+      <c r="B219" t="s">
+        <v>396</v>
+      </c>
+      <c r="C219" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F219" t="s">
+        <v>198</v>
+      </c>
+      <c r="G219" t="s">
+        <v>451</v>
+      </c>
+      <c r="H219" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I219" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K219" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L219" s="2">
+        <v>15</v>
+      </c>
+      <c r="M219" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N219" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14">
+      <c r="A220" t="s">
+        <v>395</v>
+      </c>
+      <c r="B220" t="s">
+        <v>396</v>
+      </c>
+      <c r="C220" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F220" t="s">
+        <v>198</v>
+      </c>
+      <c r="G220" t="s">
+        <v>451</v>
+      </c>
+      <c r="H220" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I220" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K220" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L220" s="2">
+        <v>25</v>
+      </c>
+      <c r="M220" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N220" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14">
+      <c r="A221" t="s">
+        <v>395</v>
+      </c>
+      <c r="B221" t="s">
+        <v>396</v>
+      </c>
+      <c r="C221" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F221" t="s">
+        <v>198</v>
+      </c>
+      <c r="G221" t="s">
+        <v>451</v>
+      </c>
+      <c r="H221" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I221" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K221" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L221" s="2">
+        <v>25</v>
+      </c>
+      <c r="M221" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N221" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14">
+      <c r="A222" t="s">
+        <v>395</v>
+      </c>
+      <c r="B222" t="s">
+        <v>396</v>
+      </c>
+      <c r="C222" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F222" t="s">
+        <v>198</v>
+      </c>
+      <c r="G222" t="s">
+        <v>451</v>
+      </c>
+      <c r="H222" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I222" s="1">
+        <v>44349</v>
+      </c>
+      <c r="K222" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L222" s="2">
+        <v>5</v>
+      </c>
+      <c r="M222" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N222" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" customFormat="1">
+      <c r="A223" t="s">
+        <v>395</v>
+      </c>
+      <c r="B223" t="s">
+        <v>396</v>
+      </c>
+      <c r="C223" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F223" t="s">
+        <v>198</v>
+      </c>
+      <c r="G223" t="s">
+        <v>451</v>
+      </c>
+      <c r="H223" s="1">
+        <v>44348</v>
+      </c>
+      <c r="I223" s="1">
+        <v>44349</v>
+      </c>
+      <c r="J223" s="2"/>
+      <c r="K223" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L223" s="2">
+        <v>25</v>
+      </c>
+      <c r="M223" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N223" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" customFormat="1">
+      <c r="A224" t="s">
+        <v>395</v>
+      </c>
+      <c r="B224" t="s">
+        <v>396</v>
+      </c>
+      <c r="C224" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="D224" t="s">
+        <v>465</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F224" t="s">
+        <v>198</v>
+      </c>
+      <c r="G224" t="s">
+        <v>466</v>
+      </c>
+      <c r="H224" s="1">
+        <v>43910</v>
+      </c>
+      <c r="I224" s="1">
+        <v>46013</v>
+      </c>
+      <c r="J224" s="2"/>
+      <c r="K224" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L224" s="2">
+        <v>15</v>
+      </c>
+      <c r="M224" s="1">
+        <v>46141</v>
+      </c>
+      <c r="N224" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" customFormat="1">
+      <c r="A225" t="s">
+        <v>467</v>
+      </c>
+      <c r="B225" t="s">
+        <v>468</v>
+      </c>
+      <c r="C225" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G225" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H225" s="1">
+        <v>44426</v>
+      </c>
+      <c r="I225" s="1">
+        <v>44426</v>
+      </c>
+      <c r="J225" s="2"/>
+      <c r="K225" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L225" s="2">
+        <v>5</v>
+      </c>
+      <c r="M225" s="1">
+        <v>46125</v>
+      </c>
+      <c r="N225" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14">
+      <c r="A226" t="s">
+        <v>467</v>
+      </c>
+      <c r="B226" t="s">
+        <v>468</v>
+      </c>
+      <c r="C226" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G226" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H226" s="1">
+        <v>44426</v>
+      </c>
+      <c r="I226" s="1">
+        <v>44426</v>
+      </c>
+      <c r="K226" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L226" s="2">
+        <v>5</v>
+      </c>
+      <c r="M226" s="1">
+        <v>46125</v>
+      </c>
+      <c r="N226" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14">
+      <c r="A227" t="s">
+        <v>467</v>
+      </c>
+      <c r="B227" t="s">
+        <v>468</v>
+      </c>
+      <c r="C227" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="D227" t="s">
+        <v>475</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F227" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="G206" t="s">
+      <c r="G227" t="s">
         <v>20</v>
       </c>
-      <c r="H206" s="1">
+      <c r="H227" s="1">
+        <v>42734</v>
+      </c>
+      <c r="I227" s="1">
+        <v>42734</v>
+      </c>
+      <c r="J227" s="1">
+        <v>44925</v>
+      </c>
+      <c r="K227" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L227" s="2">
+        <v>5</v>
+      </c>
+      <c r="M227" s="1">
+        <v>46125</v>
+      </c>
+      <c r="N227" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" customFormat="1">
+      <c r="A228" t="s">
+        <v>467</v>
+      </c>
+      <c r="B228" t="s">
+        <v>468</v>
+      </c>
+      <c r="C228" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G228" t="s">
+        <v>20</v>
+      </c>
+      <c r="H228" s="1">
+        <v>43132</v>
+      </c>
+      <c r="I228" s="1">
+        <v>43132</v>
+      </c>
+      <c r="J228" s="1">
+        <v>44966</v>
+      </c>
+      <c r="K228" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L228" s="2">
+        <v>5</v>
+      </c>
+      <c r="M228" s="1">
+        <v>46125</v>
+      </c>
+      <c r="N228" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14">
+      <c r="A229" t="s">
+        <v>467</v>
+      </c>
+      <c r="B229" t="s">
+        <v>468</v>
+      </c>
+      <c r="C229" s="18" t="s">
+        <v>478</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G229" t="s">
+        <v>20</v>
+      </c>
+      <c r="H229" s="1">
+        <v>43500</v>
+      </c>
+      <c r="I229" s="1">
+        <v>43500</v>
+      </c>
+      <c r="J229" s="1">
+        <v>45821</v>
+      </c>
+      <c r="K229" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L229" s="2">
+        <v>5</v>
+      </c>
+      <c r="M229" s="1">
+        <v>46125</v>
+      </c>
+      <c r="N229" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14">
+      <c r="A230" t="s">
+        <v>467</v>
+      </c>
+      <c r="B230" t="s">
+        <v>468</v>
+      </c>
+      <c r="C230" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="D230" t="s">
+        <v>481</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G230" t="s">
+        <v>20</v>
+      </c>
+      <c r="H230" s="1">
+        <v>43819</v>
+      </c>
+      <c r="I230" s="1">
+        <v>43819</v>
+      </c>
+      <c r="J230" s="1">
+        <v>45821</v>
+      </c>
+      <c r="K230" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L230" s="2">
+        <v>5</v>
+      </c>
+      <c r="M230" s="1">
+        <v>46125</v>
+      </c>
+      <c r="N230" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14">
+      <c r="A231" t="s">
+        <v>467</v>
+      </c>
+      <c r="B231" t="s">
+        <v>468</v>
+      </c>
+      <c r="C231" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G231" t="s">
+        <v>20</v>
+      </c>
+      <c r="H231" s="1">
+        <v>44194</v>
+      </c>
+      <c r="I231" s="1">
+        <v>44194</v>
+      </c>
+      <c r="J231" s="1">
+        <v>44994</v>
+      </c>
+      <c r="K231" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L231" s="7">
+        <v>5</v>
+      </c>
+      <c r="M231" s="1">
+        <v>46125</v>
+      </c>
+      <c r="N231" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14">
+      <c r="A232" t="s">
+        <v>467</v>
+      </c>
+      <c r="B232" t="s">
+        <v>468</v>
+      </c>
+      <c r="C232" s="18" t="s">
+        <v>484</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G232" t="s">
+        <v>20</v>
+      </c>
+      <c r="H232" s="1">
+        <v>44923</v>
+      </c>
+      <c r="I232" s="1">
+        <v>44923</v>
+      </c>
+      <c r="K232" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L232" s="7">
+        <v>5</v>
+      </c>
+      <c r="M232" s="1">
+        <v>46125</v>
+      </c>
+      <c r="N232" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" customFormat="1">
+      <c r="A233" t="s">
+        <v>467</v>
+      </c>
+      <c r="B233" t="s">
+        <v>468</v>
+      </c>
+      <c r="C233" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="D233" t="s">
+        <v>487</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G233" t="s">
+        <v>20</v>
+      </c>
+      <c r="H233" s="1">
+        <v>44925</v>
+      </c>
+      <c r="I233" s="1">
+        <v>44925</v>
+      </c>
+      <c r="J233" s="2"/>
+      <c r="K233" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L233" s="7">
+        <v>5</v>
+      </c>
+      <c r="M233" s="1">
+        <v>46125</v>
+      </c>
+      <c r="N233" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14">
+      <c r="A234" t="s">
+        <v>467</v>
+      </c>
+      <c r="B234" t="s">
+        <v>468</v>
+      </c>
+      <c r="C234" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G234" t="s">
+        <v>20</v>
+      </c>
+      <c r="H234" s="1">
+        <v>45821</v>
+      </c>
+      <c r="I234" s="1">
+        <v>45821</v>
+      </c>
+      <c r="K234" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L234" s="7">
+        <v>5</v>
+      </c>
+      <c r="M234" s="1">
+        <v>46125</v>
+      </c>
+      <c r="N234" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14">
+      <c r="A235" t="s">
+        <v>467</v>
+      </c>
+      <c r="B235" t="s">
+        <v>468</v>
+      </c>
+      <c r="C235" s="18" t="s">
+        <v>490</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G235" t="s">
+        <v>20</v>
+      </c>
+      <c r="H235" s="1">
+        <v>45821</v>
+      </c>
+      <c r="I235" s="1">
+        <v>45821</v>
+      </c>
+      <c r="K235" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L235" s="2">
+        <v>5</v>
+      </c>
+      <c r="M235" s="1">
+        <v>46125</v>
+      </c>
+      <c r="N235" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14">
+      <c r="A236" t="s">
+        <v>467</v>
+      </c>
+      <c r="B236" t="s">
+        <v>468</v>
+      </c>
+      <c r="C236" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G236" t="s">
+        <v>20</v>
+      </c>
+      <c r="H236" s="1">
         <v>46022</v>
       </c>
-      <c r="I206" s="1">
+      <c r="I236" s="1">
         <v>46022</v>
       </c>
-      <c r="K206" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L206" s="2">
-        <v>5</v>
-      </c>
-      <c r="M206" s="1">
+      <c r="K236" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L236" s="2">
+        <v>5</v>
+      </c>
+      <c r="M236" s="1">
         <v>46125</v>
       </c>
     </row>
-    <row r="207" spans="1:14">
-      <c r="A207" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C207" s="2">
+    <row r="237" spans="1:14">
+      <c r="A237" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C237" s="2">
         <v>1071501</v>
       </c>
-      <c r="D207" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="E207" s="2" t="s">
+      <c r="D237" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E237" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F207" s="2" t="s">
+      <c r="F237" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G207" t="s">
-        <v>328</v>
-      </c>
-      <c r="H207" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="I207" s="1">
+      <c r="G237" t="s">
+        <v>383</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="I237" s="1">
         <v>45842</v>
       </c>
-      <c r="K207" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L207" s="2">
+      <c r="K237" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L237" s="2">
         <v>15</v>
       </c>
-      <c r="M207" s="1">
+      <c r="M237" s="1">
         <v>46169</v>
       </c>
     </row>
-    <row r="208" spans="1:14">
-      <c r="A208" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C208" s="2">
+    <row r="238" spans="1:14">
+      <c r="A238" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C238" s="2">
         <v>2091501</v>
       </c>
-      <c r="D208" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="E208" s="2" t="s">
+      <c r="D238" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E238" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F208" s="2" t="s">
+      <c r="F238" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G208" t="s">
-        <v>328</v>
-      </c>
-      <c r="H208" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="I208" s="1">
+      <c r="G238" t="s">
+        <v>383</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="I238" s="1">
         <v>45842</v>
       </c>
-      <c r="K208" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L208" s="2">
+      <c r="K238" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L238" s="2">
         <v>15</v>
       </c>
-      <c r="M208" s="1">
+      <c r="M238" s="1">
         <v>46169</v>
       </c>
     </row>
-    <row r="209" spans="1:13">
-      <c r="A209" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C209" s="2">
+    <row r="239" spans="1:14">
+      <c r="A239" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C239" s="2">
         <v>5041501</v>
       </c>
-      <c r="D209" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F209" s="2" t="s">
+      <c r="D239" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F239" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G209" s="2" t="s">
+      <c r="G239" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H209" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="I209" s="1">
+      <c r="H239" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="I239" s="1">
         <v>45820</v>
       </c>
-      <c r="J209" s="1">
+      <c r="J239" s="1">
         <v>46161</v>
       </c>
-      <c r="K209" s="3" t="s">
+      <c r="K239" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L209" s="2">
-        <v>5</v>
-      </c>
-      <c r="M209" s="1">
+      <c r="L239" s="2">
+        <v>5</v>
+      </c>
+      <c r="M239" s="1">
         <v>46169</v>
       </c>
     </row>
-    <row r="210" spans="1:13">
-      <c r="A210" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C210" s="2">
+    <row r="240" spans="1:14">
+      <c r="A240" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C240" s="2">
         <v>6041501</v>
       </c>
-      <c r="D210" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F210" s="2" t="s">
+      <c r="D240" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G210" s="2" t="s">
+      <c r="G240" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H210" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="I210" s="1">
+      <c r="H240" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I240" s="1">
         <v>45820</v>
       </c>
-      <c r="J210" s="1">
+      <c r="J240" s="1">
         <v>46161</v>
       </c>
-      <c r="K210" s="3" t="s">
+      <c r="K240" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L210" s="2">
-        <v>5</v>
-      </c>
-      <c r="M210" s="1">
+      <c r="L240" s="2">
+        <v>5</v>
+      </c>
+      <c r="M240" s="1">
         <v>46169</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N206" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N206">
-      <sortCondition ref="B1:B206"/>
+  <autoFilter ref="A1:N241" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N241">
+      <sortCondition ref="C1:C241"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="C107">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="N19" r:id="rId1" xr:uid="{8220B955-B269-49BB-BD6D-AD834FA30E13}"/>
     <hyperlink ref="N18" r:id="rId2" xr:uid="{B401B411-58A7-4BCC-B48B-D8DA63942597}"/>
@@ -10789,8 +12198,25 @@
     <hyperlink ref="N27" r:id="rId37" xr:uid="{3C1E0CD2-AB6A-4CD8-8320-CAC9C1EA81F2}"/>
     <hyperlink ref="N28" r:id="rId38" xr:uid="{DB27BD91-88FA-44E1-A326-DE5A8086A60F}"/>
     <hyperlink ref="N104" r:id="rId39" xr:uid="{D8AC412C-8BF0-4534-BEB6-9FEE3561C22D}"/>
+    <hyperlink ref="N138" r:id="rId40" xr:uid="{4A962553-E63B-4F0B-8938-44B0D045308D}"/>
+    <hyperlink ref="N87" r:id="rId41" location="transparencia" xr:uid="{99D30359-B9C7-4F51-93F7-1174D017E5BD}"/>
+    <hyperlink ref="N88" r:id="rId42" location="transparencia" xr:uid="{C492F183-39A6-40DD-8A3C-E86E76D651EC}"/>
+    <hyperlink ref="N95" r:id="rId43" location="transparencia" xr:uid="{39E77EEA-E8AF-4BD9-9126-38BCE5A985F5}"/>
+    <hyperlink ref="N100" r:id="rId44" location="transparencia" xr:uid="{1E74F340-DF29-4FE0-84B7-513FDE8356EB}"/>
+    <hyperlink ref="N97" r:id="rId45" location="transparencia" xr:uid="{9AD7F091-6ED9-49C0-8FCA-D17EDE05ED1E}"/>
+    <hyperlink ref="N89" r:id="rId46" location="transparencia" xr:uid="{A4150EFD-D156-4F8A-B0A8-172BFCA4A27C}"/>
+    <hyperlink ref="N99" r:id="rId47" location="transparencia" xr:uid="{7BD5BF84-6A3D-4D30-BD59-519256EFDF65}"/>
+    <hyperlink ref="N96" r:id="rId48" location="transparencia" xr:uid="{8AB2CDB9-9264-4AF9-89D0-8A9E306351A1}"/>
+    <hyperlink ref="N101" r:id="rId49" location="transparencia" xr:uid="{B288CCDF-8536-4983-A830-A0E5F90608B1}"/>
+    <hyperlink ref="N98" r:id="rId50" location="transparencia" xr:uid="{E382E0FF-4569-411C-A961-B02A190F2C15}"/>
+    <hyperlink ref="N90" r:id="rId51" location="transparencia" xr:uid="{C689A52B-3C6F-4FEF-9B5A-83BBE2630362}"/>
+    <hyperlink ref="N91" r:id="rId52" location="transparencia" xr:uid="{CEB52D7E-64E8-4B33-9379-A2C6ECAA522D}"/>
+    <hyperlink ref="N92" r:id="rId53" location="transparencia" xr:uid="{78AE2C1A-D9AC-4393-AAB9-968F2E156E78}"/>
+    <hyperlink ref="N93" r:id="rId54" location="transparencia" xr:uid="{25AAA6EA-B242-4960-B22C-ABC8F0DD9F85}"/>
+    <hyperlink ref="N94" r:id="rId55" location="transparencia" xr:uid="{E7723C31-93D5-4D3B-A353-E51FE7B8111E}"/>
+    <hyperlink ref="N116" r:id="rId56" xr:uid="{2C1FB273-DE81-4F44-B5F6-DCE307D57A03}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId40"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId57"/>
 </worksheet>
 </file>
--- a/upload/informacoes_classificadas_desclassificadas.xlsx
+++ b/upload/informacoes_classificadas_desclassificadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A675BCE2-E29A-4CB7-8727-780731FBA8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4AFEC2D-0846-430E-A1F0-807CB9C9B2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="6420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha2!$A$1:$N$235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha2!$A$1:$N$234</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -2252,7 +2252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N240"/>
+  <dimension ref="A1:N239"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="2" customWidth="1"/>
@@ -3658,10 +3658,10 @@
         <v>89</v>
       </c>
       <c r="H33" s="1">
-        <v>46789</v>
+        <v>43137</v>
       </c>
       <c r="I33" s="1">
-        <v>46789</v>
+        <v>43137</v>
       </c>
       <c r="J33" s="10"/>
       <c r="K33" s="3" t="s">
@@ -9693,17 +9693,49 @@
         <v>267</v>
       </c>
     </row>
-    <row r="181" spans="1:14">
-      <c r="A181"/>
-      <c r="B181"/>
-      <c r="D181"/>
-      <c r="G181"/>
-      <c r="H181" s="1"/>
-      <c r="I181" s="1"/>
-      <c r="J181" s="1"/>
-      <c r="N181"/>
-    </row>
-    <row r="182" spans="1:14" customFormat="1">
+    <row r="181" spans="1:14" customFormat="1">
+      <c r="A181" t="s">
+        <v>374</v>
+      </c>
+      <c r="B181" t="s">
+        <v>375</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D181" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="H181" s="1">
+        <v>44617</v>
+      </c>
+      <c r="I181" s="1">
+        <v>44617</v>
+      </c>
+      <c r="J181" s="2"/>
+      <c r="K181" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L181" s="2">
+        <v>25</v>
+      </c>
+      <c r="M181" s="1">
+        <v>46128</v>
+      </c>
+      <c r="N181" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14">
       <c r="A182" t="s">
         <v>374</v>
       </c>
@@ -9714,7 +9746,7 @@
         <v>376</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>210</v>
@@ -9726,12 +9758,11 @@
         <v>378</v>
       </c>
       <c r="H182" s="1">
-        <v>44617</v>
+        <v>45821</v>
       </c>
       <c r="I182" s="1">
         <v>44617</v>
       </c>
-      <c r="J182" s="2"/>
       <c r="K182" s="3" t="s">
         <v>42</v>
       </c>
@@ -9756,7 +9787,7 @@
         <v>376</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>210</v>
@@ -9797,7 +9828,7 @@
         <v>376</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>210</v>
@@ -9805,14 +9836,14 @@
       <c r="F184" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G184" s="2" t="s">
-        <v>378</v>
+      <c r="G184" t="s">
+        <v>383</v>
       </c>
       <c r="H184" s="1">
-        <v>45821</v>
+        <v>44923</v>
       </c>
       <c r="I184" s="1">
-        <v>44617</v>
+        <v>42990</v>
       </c>
       <c r="K184" s="3" t="s">
         <v>42</v>
@@ -9838,7 +9869,7 @@
         <v>376</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>210</v>
@@ -9850,7 +9881,7 @@
         <v>383</v>
       </c>
       <c r="H185" s="1">
-        <v>44923</v>
+        <v>44925</v>
       </c>
       <c r="I185" s="1">
         <v>42990</v>
@@ -9879,7 +9910,7 @@
         <v>376</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>210</v>
@@ -9887,14 +9918,14 @@
       <c r="F186" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G186" t="s">
-        <v>383</v>
+      <c r="G186" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="H186" s="1">
-        <v>44925</v>
+        <v>44617</v>
       </c>
       <c r="I186" s="1">
-        <v>42990</v>
+        <v>44617</v>
       </c>
       <c r="K186" s="3" t="s">
         <v>42</v>
@@ -9920,7 +9951,7 @@
         <v>376</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>210</v>
@@ -9928,14 +9959,14 @@
       <c r="F187" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G187" s="2" t="s">
-        <v>386</v>
+      <c r="G187" t="s">
+        <v>388</v>
       </c>
       <c r="H187" s="1">
-        <v>44617</v>
+        <v>44194</v>
       </c>
       <c r="I187" s="1">
-        <v>44617</v>
+        <v>42990</v>
       </c>
       <c r="K187" s="3" t="s">
         <v>42</v>
@@ -9957,13 +9988,13 @@
       <c r="B188" t="s">
         <v>375</v>
       </c>
-      <c r="C188" s="2" t="s">
+      <c r="C188" t="s">
         <v>376</v>
       </c>
-      <c r="D188" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="E188" s="2" t="s">
+      <c r="D188" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="E188" t="s">
         <v>210</v>
       </c>
       <c r="F188" s="2" t="s">
@@ -9972,11 +10003,11 @@
       <c r="G188" t="s">
         <v>388</v>
       </c>
-      <c r="H188" s="1">
-        <v>44194</v>
+      <c r="H188" s="16">
+        <v>44426</v>
       </c>
       <c r="I188" s="1">
-        <v>42990</v>
+        <v>42191</v>
       </c>
       <c r="K188" s="3" t="s">
         <v>42</v>
@@ -9998,32 +10029,32 @@
       <c r="B189" t="s">
         <v>375</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C189" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D189" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="E189" t="s">
-        <v>210</v>
+      <c r="D189" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G189" t="s">
-        <v>388</v>
-      </c>
-      <c r="H189" s="16">
-        <v>44426</v>
+      <c r="G189" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="H189" s="1">
+        <v>45820</v>
       </c>
       <c r="I189" s="1">
-        <v>42191</v>
+        <v>45820</v>
       </c>
       <c r="K189" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L189" s="2">
-        <v>25</v>
+      <c r="L189" s="7">
+        <v>5</v>
       </c>
       <c r="M189" s="1">
         <v>46128</v>
@@ -10043,7 +10074,7 @@
         <v>376</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>18</v>
@@ -10063,7 +10094,7 @@
       <c r="K190" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L190" s="7">
+      <c r="L190" s="2">
         <v>5</v>
       </c>
       <c r="M190" s="1">
@@ -10084,7 +10115,7 @@
         <v>376</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>18</v>
@@ -10093,13 +10124,13 @@
         <v>53</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H191" s="1">
-        <v>45820</v>
+        <v>44734</v>
       </c>
       <c r="I191" s="1">
-        <v>45820</v>
+        <v>44734</v>
       </c>
       <c r="K191" s="3" t="s">
         <v>42</v>
@@ -10114,48 +10145,49 @@
         <v>379</v>
       </c>
     </row>
-    <row r="192" spans="1:14">
+    <row r="192" spans="1:14" customFormat="1">
       <c r="A192" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="B192" t="s">
-        <v>375</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D192" s="11" t="s">
-        <v>393</v>
+        <v>396</v>
+      </c>
+      <c r="C192" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="D192" t="s">
+        <v>398</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F192" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G192" s="2" t="s">
-        <v>394</v>
+        <v>210</v>
+      </c>
+      <c r="F192" t="s">
+        <v>198</v>
+      </c>
+      <c r="G192" t="s">
+        <v>399</v>
       </c>
       <c r="H192" s="1">
-        <v>44734</v>
+        <v>44027</v>
       </c>
       <c r="I192" s="1">
-        <v>44734</v>
-      </c>
+        <v>45656</v>
+      </c>
+      <c r="J192" s="2"/>
       <c r="K192" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L192" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M192" s="1">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="N192" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="193" spans="1:14" customFormat="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14">
       <c r="A193" t="s">
         <v>395</v>
       </c>
@@ -10163,10 +10195,10 @@
         <v>396</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D193" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>210</v>
@@ -10175,15 +10207,14 @@
         <v>198</v>
       </c>
       <c r="G193" t="s">
-        <v>399</v>
+        <v>174</v>
       </c>
       <c r="H193" s="1">
-        <v>44027</v>
+        <v>44348</v>
       </c>
       <c r="I193" s="1">
-        <v>45656</v>
-      </c>
-      <c r="J193" s="2"/>
+        <v>44349</v>
+      </c>
       <c r="K193" s="3" t="s">
         <v>42</v>
       </c>
@@ -10204,11 +10235,11 @@
       <c r="B194" t="s">
         <v>396</v>
       </c>
-      <c r="C194" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="D194" t="s">
-        <v>402</v>
+      <c r="C194" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>404</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>210</v>
@@ -10246,10 +10277,10 @@
         <v>396</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>210</v>
@@ -10287,13 +10318,13 @@
         <v>396</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F196" t="s">
         <v>198</v>
@@ -10310,8 +10341,8 @@
       <c r="K196" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L196" s="2">
-        <v>25</v>
+      <c r="L196" s="7">
+        <v>5</v>
       </c>
       <c r="M196" s="1">
         <v>46141</v>
@@ -10320,7 +10351,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="197" spans="1:14">
+    <row r="197" spans="1:14" customFormat="1">
       <c r="A197" t="s">
         <v>395</v>
       </c>
@@ -10328,10 +10359,10 @@
         <v>396</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>18</v>
@@ -10348,10 +10379,11 @@
       <c r="I197" s="1">
         <v>44349</v>
       </c>
+      <c r="J197" s="2"/>
       <c r="K197" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L197" s="7">
+      <c r="L197" s="2">
         <v>5</v>
       </c>
       <c r="M197" s="1">
@@ -10361,7 +10393,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="198" spans="1:14" customFormat="1">
+    <row r="198" spans="1:14">
       <c r="A198" t="s">
         <v>395</v>
       </c>
@@ -10369,10 +10401,10 @@
         <v>396</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>18</v>
@@ -10389,7 +10421,6 @@
       <c r="I198" s="1">
         <v>44349</v>
       </c>
-      <c r="J198" s="2"/>
       <c r="K198" s="3" t="s">
         <v>42</v>
       </c>
@@ -10411,10 +10442,10 @@
         <v>396</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>18</v>
@@ -10434,7 +10465,7 @@
       <c r="K199" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L199" s="2">
+      <c r="L199" s="7">
         <v>5</v>
       </c>
       <c r="M199" s="1">
@@ -10452,13 +10483,13 @@
         <v>396</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F200" t="s">
         <v>198</v>
@@ -10475,8 +10506,8 @@
       <c r="K200" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L200" s="7">
-        <v>5</v>
+      <c r="L200" s="2">
+        <v>15</v>
       </c>
       <c r="M200" s="1">
         <v>46141</v>
@@ -10493,13 +10524,13 @@
         <v>396</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="F201" t="s">
         <v>198</v>
@@ -10517,7 +10548,7 @@
         <v>42</v>
       </c>
       <c r="L201" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M201" s="1">
         <v>46141</v>
@@ -10526,7 +10557,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="202" spans="1:14">
+    <row r="202" spans="1:14" customFormat="1">
       <c r="A202" t="s">
         <v>395</v>
       </c>
@@ -10534,19 +10565,19 @@
         <v>396</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F202" t="s">
         <v>198</v>
       </c>
-      <c r="G202" t="s">
-        <v>174</v>
+      <c r="G202" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="H202" s="1">
         <v>44348</v>
@@ -10554,11 +10585,12 @@
       <c r="I202" s="1">
         <v>44349</v>
       </c>
+      <c r="J202" s="2"/>
       <c r="K202" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L202" s="2">
-        <v>25</v>
+      <c r="L202" s="7">
+        <v>5</v>
       </c>
       <c r="M202" s="1">
         <v>46141</v>
@@ -10567,7 +10599,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="203" spans="1:14" customFormat="1">
+    <row r="203" spans="1:14">
       <c r="A203" t="s">
         <v>395</v>
       </c>
@@ -10575,19 +10607,19 @@
         <v>396</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F203" t="s">
         <v>198</v>
       </c>
-      <c r="G203" s="2" t="s">
-        <v>266</v>
+      <c r="G203" t="s">
+        <v>20</v>
       </c>
       <c r="H203" s="1">
         <v>44348</v>
@@ -10595,12 +10627,11 @@
       <c r="I203" s="1">
         <v>44349</v>
       </c>
-      <c r="J203" s="2"/>
       <c r="K203" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L203" s="7">
-        <v>5</v>
+      <c r="L203" s="2">
+        <v>15</v>
       </c>
       <c r="M203" s="1">
         <v>46141</v>
@@ -10616,32 +10647,35 @@
       <c r="B204" t="s">
         <v>396</v>
       </c>
-      <c r="C204" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>422</v>
+      <c r="C204" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="D204" t="s">
+        <v>424</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F204" t="s">
         <v>198</v>
       </c>
       <c r="G204" t="s">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="H204" s="1">
-        <v>44348</v>
+        <v>43712</v>
       </c>
       <c r="I204" s="1">
-        <v>44349</v>
+        <v>43712</v>
+      </c>
+      <c r="J204" s="1">
+        <v>45539</v>
       </c>
       <c r="K204" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L204" s="2">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="L204" s="7">
+        <v>5</v>
       </c>
       <c r="M204" s="1">
         <v>46141</v>
@@ -10657,14 +10691,14 @@
       <c r="B205" t="s">
         <v>396</v>
       </c>
-      <c r="C205" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="D205" t="s">
-        <v>424</v>
+      <c r="C205" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>427</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F205" t="s">
         <v>198</v>
@@ -10673,19 +10707,16 @@
         <v>425</v>
       </c>
       <c r="H205" s="1">
-        <v>43712</v>
+        <v>44348</v>
       </c>
       <c r="I205" s="1">
-        <v>43712</v>
-      </c>
-      <c r="J205" s="1">
-        <v>45539</v>
+        <v>44349</v>
       </c>
       <c r="K205" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L205" s="7">
-        <v>5</v>
+        <v>42</v>
+      </c>
+      <c r="L205" s="2">
+        <v>15</v>
       </c>
       <c r="M205" s="1">
         <v>46141</v>
@@ -10702,13 +10733,13 @@
         <v>396</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="F206" t="s">
         <v>198</v>
@@ -10726,7 +10757,7 @@
         <v>42</v>
       </c>
       <c r="L206" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M206" s="1">
         <v>46141</v>
@@ -10735,7 +10766,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="207" spans="1:14">
+    <row r="207" spans="1:14" customFormat="1">
       <c r="A207" t="s">
         <v>395</v>
       </c>
@@ -10743,13 +10774,13 @@
         <v>396</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F207" t="s">
         <v>198</v>
@@ -10763,11 +10794,12 @@
       <c r="I207" s="1">
         <v>44349</v>
       </c>
+      <c r="J207" s="2"/>
       <c r="K207" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L207" s="2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M207" s="1">
         <v>46141</v>
@@ -10776,18 +10808,18 @@
         <v>400</v>
       </c>
     </row>
-    <row r="208" spans="1:14" customFormat="1">
+    <row r="208" spans="1:14">
       <c r="A208" t="s">
         <v>395</v>
       </c>
       <c r="B208" t="s">
         <v>396</v>
       </c>
-      <c r="C208" s="11" t="s">
-        <v>430</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>431</v>
+      <c r="C208" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="D208" t="s">
+        <v>433</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>18</v>
@@ -10804,7 +10836,6 @@
       <c r="I208" s="1">
         <v>44349</v>
       </c>
-      <c r="J208" s="2"/>
       <c r="K208" s="3" t="s">
         <v>42</v>
       </c>
@@ -10825,11 +10856,11 @@
       <c r="B209" t="s">
         <v>396</v>
       </c>
-      <c r="C209" s="15" t="s">
-        <v>432</v>
-      </c>
-      <c r="D209" t="s">
-        <v>433</v>
+      <c r="C209" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>435</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>18</v>
@@ -10849,7 +10880,7 @@
       <c r="K209" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L209" s="2">
+      <c r="L209" s="7">
         <v>5</v>
       </c>
       <c r="M209" s="1">
@@ -10866,14 +10897,14 @@
       <c r="B210" t="s">
         <v>396</v>
       </c>
-      <c r="C210" s="11" t="s">
-        <v>434</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>435</v>
+      <c r="C210" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="D210" t="s">
+        <v>437</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F210" t="s">
         <v>198</v>
@@ -10890,8 +10921,8 @@
       <c r="K210" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L210" s="7">
-        <v>5</v>
+      <c r="L210" s="2">
+        <v>15</v>
       </c>
       <c r="M210" s="1">
         <v>46141</v>
@@ -10907,11 +10938,11 @@
       <c r="B211" t="s">
         <v>396</v>
       </c>
-      <c r="C211" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="D211" t="s">
-        <v>437</v>
+      <c r="C211" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>439</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>41</v>
@@ -10941,7 +10972,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="212" spans="1:14">
+    <row r="212" spans="1:14" customFormat="1">
       <c r="A212" t="s">
         <v>395</v>
       </c>
@@ -10949,10 +10980,10 @@
         <v>396</v>
       </c>
       <c r="C212" s="11" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>41</v>
@@ -10969,6 +11000,7 @@
       <c r="I212" s="1">
         <v>44349</v>
       </c>
+      <c r="J212" s="2"/>
       <c r="K212" s="3" t="s">
         <v>42</v>
       </c>
@@ -10982,7 +11014,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="213" spans="1:14" customFormat="1">
+    <row r="213" spans="1:14">
       <c r="A213" t="s">
         <v>395</v>
       </c>
@@ -10990,10 +11022,10 @@
         <v>396</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>41</v>
@@ -11010,7 +11042,6 @@
       <c r="I213" s="1">
         <v>44349</v>
       </c>
-      <c r="J213" s="2"/>
       <c r="K213" s="3" t="s">
         <v>42</v>
       </c>
@@ -11031,11 +11062,11 @@
       <c r="B214" t="s">
         <v>396</v>
       </c>
-      <c r="C214" s="11" t="s">
-        <v>442</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>443</v>
+      <c r="C214" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="D214" t="s">
+        <v>445</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>41</v>
@@ -11072,11 +11103,11 @@
       <c r="B215" t="s">
         <v>396</v>
       </c>
-      <c r="C215" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="D215" t="s">
-        <v>445</v>
+      <c r="C215" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>447</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>41</v>
@@ -11085,7 +11116,7 @@
         <v>198</v>
       </c>
       <c r="G215" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="H215" s="1">
         <v>44348</v>
@@ -11113,20 +11144,20 @@
       <c r="B216" t="s">
         <v>396</v>
       </c>
-      <c r="C216" s="11" t="s">
-        <v>446</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>447</v>
+      <c r="C216" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="D216" t="s">
+        <v>450</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="F216" t="s">
         <v>198</v>
       </c>
       <c r="G216" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="H216" s="1">
         <v>44348</v>
@@ -11138,7 +11169,7 @@
         <v>42</v>
       </c>
       <c r="L216" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M216" s="1">
         <v>46141</v>
@@ -11147,18 +11178,18 @@
         <v>400</v>
       </c>
     </row>
-    <row r="217" spans="1:14">
+    <row r="217" spans="1:14" customFormat="1">
       <c r="A217" t="s">
         <v>395</v>
       </c>
       <c r="B217" t="s">
         <v>396</v>
       </c>
-      <c r="C217" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="D217" t="s">
-        <v>450</v>
+      <c r="C217" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>453</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>210</v>
@@ -11175,6 +11206,7 @@
       <c r="I217" s="1">
         <v>44349</v>
       </c>
+      <c r="J217" s="2"/>
       <c r="K217" s="3" t="s">
         <v>42</v>
       </c>
@@ -11188,7 +11220,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="218" spans="1:14" customFormat="1">
+    <row r="218" spans="1:14">
       <c r="A218" t="s">
         <v>395</v>
       </c>
@@ -11196,13 +11228,13 @@
         <v>396</v>
       </c>
       <c r="C218" s="11" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>210</v>
+        <v>41</v>
       </c>
       <c r="F218" t="s">
         <v>198</v>
@@ -11216,12 +11248,11 @@
       <c r="I218" s="1">
         <v>44349</v>
       </c>
-      <c r="J218" s="2"/>
       <c r="K218" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L218" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M218" s="1">
         <v>46141</v>
@@ -11238,13 +11269,13 @@
         <v>396</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="F219" t="s">
         <v>198</v>
@@ -11262,7 +11293,7 @@
         <v>42</v>
       </c>
       <c r="L219" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M219" s="1">
         <v>46141</v>
@@ -11279,10 +11310,10 @@
         <v>396</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>210</v>
@@ -11320,13 +11351,13 @@
         <v>396</v>
       </c>
       <c r="C221" s="11" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F221" t="s">
         <v>198</v>
@@ -11344,7 +11375,7 @@
         <v>42</v>
       </c>
       <c r="L221" s="2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M221" s="1">
         <v>46141</v>
@@ -11353,7 +11384,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="222" spans="1:14">
+    <row r="222" spans="1:14" customFormat="1">
       <c r="A222" t="s">
         <v>395</v>
       </c>
@@ -11361,13 +11392,13 @@
         <v>396</v>
       </c>
       <c r="C222" s="11" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="F222" t="s">
         <v>198</v>
@@ -11381,11 +11412,12 @@
       <c r="I222" s="1">
         <v>44349</v>
       </c>
+      <c r="J222" s="2"/>
       <c r="K222" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L222" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M222" s="1">
         <v>46141</v>
@@ -11401,33 +11433,33 @@
       <c r="B223" t="s">
         <v>396</v>
       </c>
-      <c r="C223" s="11" t="s">
-        <v>462</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>463</v>
+      <c r="C223" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="D223" t="s">
+        <v>465</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>210</v>
+        <v>41</v>
       </c>
       <c r="F223" t="s">
         <v>198</v>
       </c>
       <c r="G223" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="H223" s="1">
-        <v>44348</v>
+        <v>43910</v>
       </c>
       <c r="I223" s="1">
-        <v>44349</v>
+        <v>46013</v>
       </c>
       <c r="J223" s="2"/>
       <c r="K223" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L223" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M223" s="1">
         <v>46141</v>
@@ -11438,47 +11470,47 @@
     </row>
     <row r="224" spans="1:14" customFormat="1">
       <c r="A224" t="s">
-        <v>395</v>
+        <v>467</v>
       </c>
       <c r="B224" t="s">
-        <v>396</v>
-      </c>
-      <c r="C224" s="15" t="s">
-        <v>464</v>
-      </c>
-      <c r="D224" t="s">
-        <v>465</v>
+        <v>468</v>
+      </c>
+      <c r="C224" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>470</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F224" t="s">
-        <v>198</v>
-      </c>
-      <c r="G224" t="s">
-        <v>466</v>
+        <v>18</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G224" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="H224" s="1">
-        <v>43910</v>
+        <v>44426</v>
       </c>
       <c r="I224" s="1">
-        <v>46013</v>
+        <v>44426</v>
       </c>
       <c r="J224" s="2"/>
       <c r="K224" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L224" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M224" s="1">
-        <v>46141</v>
+        <v>46125</v>
       </c>
       <c r="N224" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="225" spans="1:14" customFormat="1">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14">
       <c r="A225" t="s">
         <v>467</v>
       </c>
@@ -11486,10 +11518,10 @@
         <v>468</v>
       </c>
       <c r="C225" s="18" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>18</v>
@@ -11506,7 +11538,6 @@
       <c r="I225" s="1">
         <v>44426</v>
       </c>
-      <c r="J225" s="2"/>
       <c r="K225" s="3" t="s">
         <v>42</v>
       </c>
@@ -11527,29 +11558,32 @@
       <c r="B226" t="s">
         <v>468</v>
       </c>
-      <c r="C226" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>473</v>
+      <c r="C226" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="D226" t="s">
+        <v>475</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G226" s="9" t="s">
-        <v>142</v>
+        <v>160</v>
+      </c>
+      <c r="G226" t="s">
+        <v>20</v>
       </c>
       <c r="H226" s="1">
-        <v>44426</v>
+        <v>42734</v>
       </c>
       <c r="I226" s="1">
-        <v>44426</v>
+        <v>42734</v>
+      </c>
+      <c r="J226" s="1">
+        <v>44925</v>
       </c>
       <c r="K226" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L226" s="2">
         <v>5</v>
@@ -11561,18 +11595,18 @@
         <v>471</v>
       </c>
     </row>
-    <row r="227" spans="1:14">
+    <row r="227" spans="1:14" customFormat="1">
       <c r="A227" t="s">
         <v>467</v>
       </c>
       <c r="B227" t="s">
         <v>468</v>
       </c>
-      <c r="C227" s="17" t="s">
-        <v>474</v>
-      </c>
-      <c r="D227" t="s">
-        <v>475</v>
+      <c r="C227" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>477</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>18</v>
@@ -11584,13 +11618,13 @@
         <v>20</v>
       </c>
       <c r="H227" s="1">
-        <v>42734</v>
+        <v>43132</v>
       </c>
       <c r="I227" s="1">
-        <v>42734</v>
+        <v>43132</v>
       </c>
       <c r="J227" s="1">
-        <v>44925</v>
+        <v>44966</v>
       </c>
       <c r="K227" s="3" t="s">
         <v>21</v>
@@ -11605,7 +11639,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="228" spans="1:14" customFormat="1">
+    <row r="228" spans="1:14">
       <c r="A228" t="s">
         <v>467</v>
       </c>
@@ -11613,10 +11647,10 @@
         <v>468</v>
       </c>
       <c r="C228" s="18" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>18</v>
@@ -11628,13 +11662,13 @@
         <v>20</v>
       </c>
       <c r="H228" s="1">
-        <v>43132</v>
+        <v>43500</v>
       </c>
       <c r="I228" s="1">
-        <v>43132</v>
+        <v>43500</v>
       </c>
       <c r="J228" s="1">
-        <v>44966</v>
+        <v>45821</v>
       </c>
       <c r="K228" s="3" t="s">
         <v>21</v>
@@ -11656,11 +11690,11 @@
       <c r="B229" t="s">
         <v>468</v>
       </c>
-      <c r="C229" s="18" t="s">
-        <v>478</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>479</v>
+      <c r="C229" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="D229" t="s">
+        <v>481</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>18</v>
@@ -11672,10 +11706,10 @@
         <v>20</v>
       </c>
       <c r="H229" s="1">
-        <v>43500</v>
+        <v>43819</v>
       </c>
       <c r="I229" s="1">
-        <v>43500</v>
+        <v>43819</v>
       </c>
       <c r="J229" s="1">
         <v>45821</v>
@@ -11700,11 +11734,11 @@
       <c r="B230" t="s">
         <v>468</v>
       </c>
-      <c r="C230" s="17" t="s">
-        <v>480</v>
-      </c>
-      <c r="D230" t="s">
-        <v>481</v>
+      <c r="C230" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>483</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>18</v>
@@ -11716,18 +11750,18 @@
         <v>20</v>
       </c>
       <c r="H230" s="1">
-        <v>43819</v>
+        <v>44194</v>
       </c>
       <c r="I230" s="1">
-        <v>43819</v>
+        <v>44194</v>
       </c>
       <c r="J230" s="1">
-        <v>45821</v>
+        <v>44994</v>
       </c>
       <c r="K230" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L230" s="2">
+      <c r="L230" s="7">
         <v>5</v>
       </c>
       <c r="M230" s="1">
@@ -11745,10 +11779,10 @@
         <v>468</v>
       </c>
       <c r="C231" s="18" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>18</v>
@@ -11760,16 +11794,13 @@
         <v>20</v>
       </c>
       <c r="H231" s="1">
-        <v>44194</v>
+        <v>44923</v>
       </c>
       <c r="I231" s="1">
-        <v>44194</v>
-      </c>
-      <c r="J231" s="1">
-        <v>44994</v>
+        <v>44923</v>
       </c>
       <c r="K231" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L231" s="7">
         <v>5</v>
@@ -11781,18 +11812,18 @@
         <v>471</v>
       </c>
     </row>
-    <row r="232" spans="1:14">
+    <row r="232" spans="1:14" customFormat="1">
       <c r="A232" t="s">
         <v>467</v>
       </c>
       <c r="B232" t="s">
         <v>468</v>
       </c>
-      <c r="C232" s="18" t="s">
-        <v>484</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>485</v>
+      <c r="C232" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="D232" t="s">
+        <v>487</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>18</v>
@@ -11804,11 +11835,12 @@
         <v>20</v>
       </c>
       <c r="H232" s="1">
-        <v>44923</v>
+        <v>44925</v>
       </c>
       <c r="I232" s="1">
-        <v>44923</v>
-      </c>
+        <v>44925</v>
+      </c>
+      <c r="J232" s="2"/>
       <c r="K232" s="3" t="s">
         <v>42</v>
       </c>
@@ -11822,18 +11854,18 @@
         <v>471</v>
       </c>
     </row>
-    <row r="233" spans="1:14" customFormat="1">
+    <row r="233" spans="1:14">
       <c r="A233" t="s">
         <v>467</v>
       </c>
       <c r="B233" t="s">
         <v>468</v>
       </c>
-      <c r="C233" s="17" t="s">
-        <v>486</v>
-      </c>
-      <c r="D233" t="s">
-        <v>487</v>
+      <c r="C233" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>489</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>18</v>
@@ -11845,12 +11877,11 @@
         <v>20</v>
       </c>
       <c r="H233" s="1">
-        <v>44925</v>
+        <v>45821</v>
       </c>
       <c r="I233" s="1">
-        <v>44925</v>
-      </c>
-      <c r="J233" s="2"/>
+        <v>45821</v>
+      </c>
       <c r="K233" s="3" t="s">
         <v>42</v>
       </c>
@@ -11872,10 +11903,10 @@
         <v>468</v>
       </c>
       <c r="C234" s="18" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>18</v>
@@ -11895,7 +11926,7 @@
       <c r="K234" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L234" s="7">
+      <c r="L234" s="2">
         <v>5</v>
       </c>
       <c r="M234" s="1">
@@ -11913,10 +11944,10 @@
         <v>468</v>
       </c>
       <c r="C235" s="18" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>18</v>
@@ -11928,10 +11959,10 @@
         <v>20</v>
       </c>
       <c r="H235" s="1">
-        <v>45821</v>
+        <v>46022</v>
       </c>
       <c r="I235" s="1">
-        <v>45821</v>
+        <v>46022</v>
       </c>
       <c r="K235" s="3" t="s">
         <v>42</v>
@@ -11942,46 +11973,43 @@
       <c r="M235" s="1">
         <v>46125</v>
       </c>
-      <c r="N235" t="s">
-        <v>471</v>
-      </c>
     </row>
     <row r="236" spans="1:14">
-      <c r="A236" t="s">
-        <v>467</v>
-      </c>
-      <c r="B236" t="s">
-        <v>468</v>
-      </c>
-      <c r="C236" s="18" t="s">
-        <v>492</v>
+      <c r="A236" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C236" s="2">
+        <v>1071501</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="G236" t="s">
-        <v>20</v>
-      </c>
-      <c r="H236" s="1">
-        <v>46022</v>
+        <v>383</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>497</v>
       </c>
       <c r="I236" s="1">
-        <v>46022</v>
+        <v>45842</v>
       </c>
       <c r="K236" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L236" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M236" s="1">
-        <v>46125</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="237" spans="1:14">
@@ -11992,10 +12020,10 @@
         <v>495</v>
       </c>
       <c r="C237" s="2">
-        <v>1071501</v>
+        <v>2091501</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>41</v>
@@ -12030,31 +12058,34 @@
         <v>495</v>
       </c>
       <c r="C238" s="2">
-        <v>2091501</v>
+        <v>5041501</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G238" t="s">
-        <v>383</v>
-      </c>
-      <c r="H238" s="1" t="s">
-        <v>497</v>
+        <v>19</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>500</v>
       </c>
       <c r="I238" s="1">
-        <v>45842</v>
+        <v>45820</v>
+      </c>
+      <c r="J238" s="1">
+        <v>46161</v>
       </c>
       <c r="K238" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L238" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M238" s="1">
         <v>46169</v>
@@ -12068,10 +12099,10 @@
         <v>495</v>
       </c>
       <c r="C239" s="2">
-        <v>5041501</v>
+        <v>6041501</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>18</v>
@@ -12083,7 +12114,7 @@
         <v>142</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="I239" s="1">
         <v>45820</v>
@@ -12101,51 +12132,10 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="240" spans="1:14">
-      <c r="A240" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C240" s="2">
-        <v>6041501</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G240" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="I240" s="1">
-        <v>45820</v>
-      </c>
-      <c r="J240" s="1">
-        <v>46161</v>
-      </c>
-      <c r="K240" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L240" s="2">
-        <v>5</v>
-      </c>
-      <c r="M240" s="1">
-        <v>46169</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N241" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N241">
-      <sortCondition ref="C1:C241"/>
+  <autoFilter ref="A1:N240" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N240">
+      <sortCondition ref="C1:C240"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/upload/informacoes_classificadas_desclassificadas.xlsx
+++ b/upload/informacoes_classificadas_desclassificadas.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4AFEC2D-0846-430E-A1F0-807CB9C9B2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="6420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11100"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha2!$A$1:$N$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha2!$A$1:$N$235</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="509">
   <si>
     <t>orgao_entidade</t>
   </si>
@@ -451,6 +450,28 @@
   </si>
   <si>
     <t>Nota Técnica de Integridade e Gestão de Riscos - Nota Técnica nº 4/CODEMGE/GICOR/2025</t>
+  </si>
+  <si>
+    <t>Corpo de Bombeiros Militar de Minas Gerais</t>
+  </si>
+  <si>
+    <t>CBMMG</t>
+  </si>
+  <si>
+    <t>001.06.1401</t>
+  </si>
+  <si>
+    <t>Unidade administrativa de lotação de
+servidores em exercício no CBMMG</t>
+  </si>
+  <si>
+    <t>Ultrassecreto</t>
+  </si>
+  <si>
+    <t>6 - Defesa Social e Segurança Pública</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16oaMb_7pgyVlBwV_Uzux5faNpADj5KzV/view</t>
   </si>
   <si>
     <t>Fundação Estadual do Meio Ambiente - FEAM</t>
@@ -737,9 +758,6 @@
     <t>Atos normativos e ordinatórios (como Memorandos e ofícios com recomendações às equipes de segurança)</t>
   </si>
   <si>
-    <t>6 - Defesa Social e Segurança Pública</t>
-  </si>
-  <si>
     <t>Art. 23, inciso VII, da Lei Federal nº 12.527/2011 e Art. 31, Decreto 45.969</t>
   </si>
   <si>
@@ -771,9 +789,6 @@
   </si>
   <si>
     <t>Plantas e Projetos das edificações onde o Governador, Vice-Governador e Chefe do Gabinete Militar exercerem as suas funções e das respectivas residências oficiais</t>
-  </si>
-  <si>
-    <t>Ultrassecreto</t>
   </si>
   <si>
     <t>Art. 31, Decreto 45.969/12, Decreto 46.983/2016, Decreto 45.357/2010</t>
@@ -1679,11 +1694,14 @@
   <si>
     <t>data de conclusão da produção</t>
   </si>
+  <si>
+    <t>Art. 23, incisos III, VII e VIII, e art. 24 da Lei Federal no 12.527/2011</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy;@"/>
@@ -1837,7 +1855,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1909,12 +1927,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Hyperlink" xfId="3" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Hyperlink" xfId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2251,25 +2275,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N239"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N240"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="2"/>
+    <col min="1" max="1" width="12.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.125" style="2"/>
     <col min="3" max="3" width="71" style="2" customWidth="1"/>
-    <col min="4" max="4" width="38.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="121.140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="121.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5703125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="23.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="2"/>
+    <col min="11" max="11" width="22.625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="23.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -4482,61 +4506,62 @@
       <c r="B53" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="29" t="s">
         <v>140</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G53" s="9" t="s">
+      <c r="F53" t="s">
         <v>142</v>
       </c>
-      <c r="H53" s="6">
-        <v>44552</v>
-      </c>
-      <c r="I53" s="6">
-        <v>44552</v>
-      </c>
+      <c r="G53" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="H53" s="3">
+        <v>46233</v>
+      </c>
+      <c r="I53" s="3">
+        <v>46233</v>
+      </c>
+      <c r="J53" s="5"/>
       <c r="K53" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L53" s="7">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M53" s="1">
-        <v>46128</v>
-      </c>
-      <c r="N53" s="2" t="s">
+        <v>46237</v>
+      </c>
+      <c r="N53" s="30" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H54" s="6">
         <v>44552</v>
@@ -4554,71 +4579,71 @@
         <v>46128</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="H55" s="8">
-        <v>44780</v>
-      </c>
-      <c r="I55" s="8">
-        <v>44780</v>
+        <v>149</v>
+      </c>
+      <c r="H55" s="6">
+        <v>44552</v>
+      </c>
+      <c r="I55" s="6">
+        <v>44552</v>
       </c>
       <c r="K55" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L55" s="2">
+      <c r="L55" s="7">
         <v>5</v>
       </c>
       <c r="M55" s="1">
         <v>46128</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C56" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H56" s="8">
         <v>44780</v>
@@ -4636,71 +4661,71 @@
         <v>46128</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H57" s="8">
-        <v>45021</v>
+        <v>44780</v>
       </c>
       <c r="I57" s="8">
-        <v>45021</v>
+        <v>44780</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L57" s="7">
+      <c r="L57" s="2">
         <v>5</v>
       </c>
       <c r="M57" s="1">
         <v>46128</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H58" s="8">
         <v>45021</v>
@@ -4718,71 +4743,71 @@
         <v>46128</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H59" s="8">
-        <v>45292</v>
+        <v>45021</v>
       </c>
       <c r="I59" s="8">
-        <v>45292</v>
+        <v>45021</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L59" s="2">
+      <c r="L59" s="7">
         <v>5</v>
       </c>
       <c r="M59" s="1">
         <v>46128</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H60" s="8">
         <v>45292</v>
@@ -4800,71 +4825,71 @@
         <v>46128</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H61" s="8">
-        <v>45658</v>
+        <v>45292</v>
       </c>
       <c r="I61" s="8">
-        <v>45658</v>
+        <v>45292</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L61" s="7">
+      <c r="L61" s="2">
         <v>5</v>
       </c>
       <c r="M61" s="1">
         <v>46128</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H62" s="8">
         <v>45658</v>
@@ -4882,83 +4907,83 @@
         <v>46128</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>159</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G63" t="s">
-        <v>20</v>
-      </c>
-      <c r="H63" s="6">
-        <v>44194</v>
-      </c>
-      <c r="I63" s="6">
-        <v>44194</v>
-      </c>
-      <c r="J63" s="1">
-        <v>46090</v>
+        <v>19</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="H63" s="8">
+        <v>45658</v>
+      </c>
+      <c r="I63" s="8">
+        <v>45658</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L63" s="2">
+        <v>42</v>
+      </c>
+      <c r="L63" s="7">
         <v>5</v>
       </c>
       <c r="M63" s="1">
         <v>46128</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G64" t="s">
         <v>20</v>
       </c>
       <c r="H64" s="6">
-        <v>44558</v>
+        <v>44194</v>
       </c>
       <c r="I64" s="6">
-        <v>44558</v>
+        <v>44194</v>
+      </c>
+      <c r="J64" s="1">
+        <v>46090</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L64" s="2">
         <v>5</v>
@@ -4967,36 +4992,36 @@
         <v>46128</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G65" t="s">
         <v>20</v>
       </c>
       <c r="H65" s="6">
-        <v>44925</v>
+        <v>44558</v>
       </c>
       <c r="I65" s="6">
-        <v>44925</v>
+        <v>44558</v>
       </c>
       <c r="K65" s="3" t="s">
         <v>42</v>
@@ -5008,77 +5033,77 @@
         <v>46128</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G66" t="s">
         <v>20</v>
       </c>
       <c r="H66" s="6">
-        <v>45289</v>
+        <v>44925</v>
       </c>
       <c r="I66" s="6">
-        <v>45289</v>
+        <v>44925</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L66" s="7">
+      <c r="L66" s="2">
         <v>5</v>
       </c>
       <c r="M66" s="1">
         <v>46128</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C67" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="G67" t="s">
         <v>20</v>
       </c>
       <c r="H67" s="6">
-        <v>45656</v>
+        <v>45289</v>
       </c>
       <c r="I67" s="6">
-        <v>45656</v>
+        <v>45289</v>
       </c>
       <c r="K67" s="3" t="s">
         <v>42</v>
@@ -5090,153 +5115,153 @@
         <v>46128</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="2" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>171</v>
+        <v>145</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>174</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G68" t="s">
-        <v>174</v>
-      </c>
-      <c r="H68" s="1">
-        <v>45925</v>
-      </c>
-      <c r="I68" s="1">
-        <v>45925</v>
+        <v>20</v>
+      </c>
+      <c r="H68" s="6">
+        <v>45656</v>
+      </c>
+      <c r="I68" s="6">
+        <v>45656</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L68" s="2">
-        <v>15</v>
+      <c r="L68" s="7">
+        <v>5</v>
       </c>
       <c r="M68" s="1">
-        <v>46072</v>
+        <v>46128</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>178</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
+      </c>
+      <c r="G69" t="s">
+        <v>181</v>
       </c>
       <c r="H69" s="1">
-        <v>45916</v>
+        <v>45925</v>
       </c>
       <c r="I69" s="1">
-        <v>45916</v>
+        <v>45925</v>
       </c>
       <c r="K69" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L69" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M69" s="1">
         <v>46072</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="G70" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="H70" s="1">
-        <v>45925</v>
+        <v>45916</v>
       </c>
       <c r="I70" s="1">
-        <v>45925</v>
+        <v>45916</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L70" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M70" s="1">
         <v>46072</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="H71" s="1">
         <v>45925</v>
@@ -5254,30 +5279,30 @@
         <v>46072</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="H72" s="1">
         <v>45925</v>
@@ -5295,71 +5320,71 @@
         <v>46072</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C73" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G73" t="s">
-        <v>89</v>
-      </c>
       <c r="H73" s="1">
-        <v>45932</v>
+        <v>45925</v>
       </c>
       <c r="I73" s="1">
-        <v>45932</v>
+        <v>45925</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L73" s="7">
-        <v>5</v>
+      <c r="L73" s="2">
+        <v>15</v>
       </c>
       <c r="M73" s="1">
         <v>46072</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G74" t="s">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="H74" s="1">
         <v>45932</v>
@@ -5377,30 +5402,30 @@
         <v>46072</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G75" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H75" s="1">
         <v>45932</v>
@@ -5418,36 +5443,36 @@
         <v>46072</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
+      </c>
+      <c r="G76" t="s">
+        <v>196</v>
       </c>
       <c r="H76" s="1">
-        <v>45923</v>
+        <v>45932</v>
       </c>
       <c r="I76" s="1">
-        <v>45923</v>
+        <v>45932</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>42</v>
@@ -5459,71 +5484,74 @@
         <v>46072</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="2" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D77" s="14" t="s">
-        <v>197</v>
+        <v>177</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F77" t="s">
-        <v>198</v>
-      </c>
-      <c r="G77" t="s">
-        <v>199</v>
+        <v>18</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="H77" s="1">
-        <v>43697</v>
+        <v>45923</v>
       </c>
       <c r="I77" s="1">
-        <v>43697</v>
+        <v>45923</v>
       </c>
       <c r="K77" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L77" s="2">
-        <v>15</v>
+      <c r="L77" s="7">
+        <v>5</v>
       </c>
       <c r="M77" s="1">
-        <v>46128</v>
+        <v>46072</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F78" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G78" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H78" s="1">
-        <v>43705</v>
+        <v>43697</v>
       </c>
       <c r="I78" s="1">
-        <v>43705</v>
+        <v>43697</v>
       </c>
       <c r="K78" s="3" t="s">
         <v>42</v>
@@ -5535,27 +5563,27 @@
         <v>46128</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F79" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G79" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H79" s="1">
         <v>43705</v>
@@ -5573,27 +5601,27 @@
         <v>46128</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F80" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G80" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H80" s="1">
         <v>43705</v>
@@ -5611,27 +5639,27 @@
         <v>46128</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F81" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H81" s="1">
         <v>43705</v>
@@ -5649,27 +5677,27 @@
         <v>46128</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F82" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H82" s="1">
         <v>43705</v>
@@ -5687,27 +5715,27 @@
         <v>46128</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F83" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H83" s="1">
         <v>43705</v>
@@ -5725,33 +5753,33 @@
         <v>46128</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F84" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G84" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H84" s="1">
-        <v>45826</v>
+        <v>43705</v>
       </c>
       <c r="I84" s="1">
-        <v>45826</v>
+        <v>43705</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>42</v>
@@ -5763,33 +5791,33 @@
         <v>46128</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F85" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G85" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H85" s="1">
-        <v>45833</v>
+        <v>45826</v>
       </c>
       <c r="I85" s="1">
-        <v>45833</v>
+        <v>45826</v>
       </c>
       <c r="K85" s="3" t="s">
         <v>42</v>
@@ -5801,106 +5829,103 @@
         <v>46128</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>210</v>
+        <v>41</v>
       </c>
       <c r="F86" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G86" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H86" s="1">
-        <v>43705</v>
+        <v>45833</v>
       </c>
       <c r="I86" s="1">
-        <v>43705</v>
+        <v>45833</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L86" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M86" s="1">
         <v>46128</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="2" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C87" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="D87" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D87" s="14" t="s">
         <v>215</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F87" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F87" t="s">
+        <v>142</v>
+      </c>
+      <c r="G87" t="s">
         <v>216</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H87" s="22">
-        <v>45303</v>
-      </c>
-      <c r="I87" s="22">
-        <v>45303</v>
+      <c r="H87" s="1">
+        <v>43705</v>
+      </c>
+      <c r="I87" s="1">
+        <v>43705</v>
       </c>
       <c r="K87" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L87" s="7">
-        <v>5</v>
+      <c r="L87" s="2">
+        <v>25</v>
       </c>
       <c r="M87" s="1">
-        <v>46171</v>
+        <v>46128</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>63</v>
@@ -5921,27 +5946,27 @@
         <v>46171</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D89" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F89" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>63</v>
@@ -5955,34 +5980,34 @@
       <c r="K89" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L89" s="2">
+      <c r="L89" s="7">
         <v>5</v>
       </c>
       <c r="M89" s="1">
         <v>46171</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>63</v>
@@ -6003,27 +6028,27 @@
         <v>46171</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>63</v>
@@ -6037,34 +6062,34 @@
       <c r="K91" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L91" s="7">
+      <c r="L91" s="2">
         <v>5</v>
       </c>
       <c r="M91" s="1">
         <v>46171</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>63</v>
@@ -6085,27 +6110,27 @@
         <v>46171</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>63</v>
@@ -6119,34 +6144,34 @@
       <c r="K93" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L93" s="2">
+      <c r="L93" s="7">
         <v>5</v>
       </c>
       <c r="M93" s="1">
         <v>46171</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>63</v>
@@ -6167,30 +6192,30 @@
         <v>46171</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>178</v>
+        <v>63</v>
       </c>
       <c r="H95" s="22">
         <v>45303</v>
@@ -6201,37 +6226,37 @@
       <c r="K95" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L95" s="7">
+      <c r="L95" s="2">
         <v>5</v>
       </c>
       <c r="M95" s="1">
         <v>46171</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G96" t="s">
-        <v>20</v>
+        <v>221</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="H96" s="22">
         <v>45303</v>
@@ -6242,37 +6267,37 @@
       <c r="K96" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L96" s="2">
+      <c r="L96" s="7">
         <v>5</v>
       </c>
       <c r="M96" s="1">
         <v>46171</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>238</v>
+        <v>19</v>
+      </c>
+      <c r="G97" t="s">
+        <v>20</v>
       </c>
       <c r="H97" s="22">
         <v>45303</v>
@@ -6284,36 +6309,36 @@
         <v>42</v>
       </c>
       <c r="L97" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M97" s="1">
         <v>46171</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H98" s="22">
         <v>45303</v>
@@ -6324,37 +6349,37 @@
       <c r="K98" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L98" s="7">
-        <v>5</v>
+      <c r="L98" s="2">
+        <v>15</v>
       </c>
       <c r="M98" s="1">
         <v>46171</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F99" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="H99" s="22">
         <v>45303</v>
@@ -6365,37 +6390,37 @@
       <c r="K99" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L99" s="2">
+      <c r="L99" s="7">
         <v>5</v>
       </c>
       <c r="M99" s="1">
         <v>46171</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C100" s="23" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H100" s="22">
         <v>45303</v>
@@ -6407,36 +6432,36 @@
         <v>42</v>
       </c>
       <c r="L100" s="2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M100" s="1">
         <v>46171</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C101" s="23" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H101" s="22">
         <v>45303</v>
@@ -6448,74 +6473,74 @@
         <v>42</v>
       </c>
       <c r="L101" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M101" s="1">
         <v>46171</v>
       </c>
       <c r="N101" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
+      <c r="A102" s="2" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="102" spans="1:14">
-      <c r="A102" s="20" t="s">
-        <v>249</v>
-      </c>
       <c r="B102" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C102" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C102" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G102" t="s">
-        <v>20</v>
-      </c>
-      <c r="H102" s="1">
-        <v>45352</v>
-      </c>
-      <c r="I102" s="1">
-        <v>45352</v>
+      <c r="G102" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H102" s="22">
+        <v>45303</v>
+      </c>
+      <c r="I102" s="22">
+        <v>45303</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L102" s="7">
+      <c r="L102" s="2">
         <v>5</v>
       </c>
       <c r="M102" s="1">
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="N102" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
+      <c r="A103" s="20" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="103" spans="1:14">
-      <c r="A103" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="B103" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="G103" t="s">
         <v>20</v>
@@ -6536,59 +6561,58 @@
         <v>46156</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C104" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F104" t="s">
-        <v>198</v>
       </c>
       <c r="G104" t="s">
         <v>20</v>
       </c>
       <c r="H104" s="1">
-        <v>44375</v>
+        <v>45352</v>
       </c>
       <c r="I104" s="1">
-        <v>44376</v>
-      </c>
-      <c r="J104" s="1"/>
+        <v>45352</v>
+      </c>
       <c r="K104" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L104" s="2">
+      <c r="L104" s="7">
         <v>5</v>
       </c>
       <c r="M104" s="1">
-        <v>46122</v>
-      </c>
-      <c r="N104" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" customFormat="1">
-      <c r="A105" t="s">
+        <v>46156</v>
+      </c>
+      <c r="N104" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
+      <c r="A105" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C105" s="27" t="s">
+      <c r="C105" s="11" t="s">
         <v>264</v>
       </c>
       <c r="D105" s="2" t="s">
@@ -6598,58 +6622,58 @@
         <v>18</v>
       </c>
       <c r="F105" t="s">
-        <v>198</v>
-      </c>
-      <c r="G105" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G105" t="s">
+        <v>20</v>
+      </c>
+      <c r="H105" s="1">
+        <v>44375</v>
+      </c>
+      <c r="I105" s="1">
+        <v>44376</v>
+      </c>
+      <c r="J105" s="1"/>
+      <c r="K105" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L105" s="2">
+        <v>5</v>
+      </c>
+      <c r="M105" s="1">
+        <v>46122</v>
+      </c>
+      <c r="N105" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="H105" s="1">
+    </row>
+    <row r="106" spans="1:14" customFormat="1">
+      <c r="A106" t="s">
+        <v>267</v>
+      </c>
+      <c r="B106" t="s">
+        <v>268</v>
+      </c>
+      <c r="C106" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F106" t="s">
+        <v>142</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H106" s="1">
         <v>43486</v>
       </c>
-      <c r="I105" s="1">
+      <c r="I106" s="1">
         <v>43486</v>
-      </c>
-      <c r="J105" s="1">
-        <v>45432</v>
-      </c>
-      <c r="K105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L105" s="7">
-        <v>5</v>
-      </c>
-      <c r="M105" s="2"/>
-      <c r="N105" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14">
-      <c r="A106" t="s">
-        <v>262</v>
-      </c>
-      <c r="B106" t="s">
-        <v>263</v>
-      </c>
-      <c r="C106" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F106" t="s">
-        <v>198</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="H106" s="1">
-        <v>43587</v>
-      </c>
-      <c r="I106" s="1">
-        <v>43587</v>
       </c>
       <c r="J106" s="1">
         <v>45432</v>
@@ -6657,40 +6681,41 @@
       <c r="K106" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L106" s="2">
-        <v>5</v>
-      </c>
+      <c r="L106" s="7">
+        <v>5</v>
+      </c>
+      <c r="M106" s="2"/>
       <c r="N106" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B107" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C107" s="27" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F107" t="s">
-        <v>198</v>
-      </c>
-      <c r="G107" t="s">
-        <v>20</v>
+        <v>142</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="H107" s="1">
-        <v>43503</v>
+        <v>43587</v>
       </c>
       <c r="I107" s="1">
-        <v>43503</v>
+        <v>43587</v>
       </c>
       <c r="J107" s="1">
         <v>45432</v>
@@ -6702,77 +6727,77 @@
         <v>5</v>
       </c>
       <c r="N107" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B108" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C108" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="E108" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F108" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G108" t="s">
         <v>20</v>
       </c>
       <c r="H108" s="1">
-        <v>43264</v>
+        <v>43503</v>
       </c>
       <c r="I108" s="1">
-        <v>43264</v>
+        <v>43503</v>
       </c>
       <c r="J108" s="1">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="K108" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L108" s="7">
+      <c r="L108" s="2">
         <v>5</v>
       </c>
       <c r="N108" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B109" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C109" s="27" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F109" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G109" t="s">
         <v>20</v>
       </c>
       <c r="H109" s="1">
-        <v>43271</v>
+        <v>43264</v>
       </c>
       <c r="I109" s="1">
-        <v>43271</v>
+        <v>43264</v>
       </c>
       <c r="J109" s="1">
         <v>45428</v>
@@ -6780,40 +6805,40 @@
       <c r="K109" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L109" s="2">
+      <c r="L109" s="7">
         <v>5</v>
       </c>
       <c r="N109" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B110" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C110" s="27" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F110" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G110" t="s">
         <v>20</v>
       </c>
       <c r="H110" s="1">
-        <v>43294</v>
+        <v>43271</v>
       </c>
       <c r="I110" s="1">
-        <v>43294</v>
+        <v>43271</v>
       </c>
       <c r="J110" s="1">
         <v>45428</v>
@@ -6821,40 +6846,40 @@
       <c r="K110" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L110" s="7">
+      <c r="L110" s="2">
         <v>5</v>
       </c>
       <c r="N110" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B111" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C111" s="27" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F111" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G111" t="s">
         <v>20</v>
       </c>
       <c r="H111" s="1">
-        <v>43297</v>
+        <v>43294</v>
       </c>
       <c r="I111" s="1">
-        <v>43297</v>
+        <v>43294</v>
       </c>
       <c r="J111" s="1">
         <v>45428</v>
@@ -6862,40 +6887,40 @@
       <c r="K111" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L111" s="2">
+      <c r="L111" s="7">
         <v>5</v>
       </c>
       <c r="N111" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B112" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C112" s="27" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F112" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G112" t="s">
-        <v>275</v>
+        <v>20</v>
       </c>
       <c r="H112" s="1">
-        <v>43304</v>
+        <v>43297</v>
       </c>
       <c r="I112" s="1">
-        <v>43304</v>
+        <v>43297</v>
       </c>
       <c r="J112" s="1">
         <v>45428</v>
@@ -6906,38 +6931,37 @@
       <c r="L112" s="2">
         <v>5</v>
       </c>
-      <c r="M112" s="1"/>
       <c r="N112" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B113" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C113" s="27" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F113" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G113" t="s">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="H113" s="1">
-        <v>43308</v>
+        <v>43304</v>
       </c>
       <c r="I113" s="1">
-        <v>43308</v>
+        <v>43304</v>
       </c>
       <c r="J113" s="1">
         <v>45428</v>
@@ -6948,31 +6972,32 @@
       <c r="L113" s="2">
         <v>5</v>
       </c>
+      <c r="M113" s="1"/>
       <c r="N113" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B114" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C114" s="27" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F114" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G114" t="s">
-        <v>278</v>
+        <v>20</v>
       </c>
       <c r="H114" s="1">
         <v>43308</v>
@@ -6990,30 +7015,30 @@
         <v>5</v>
       </c>
       <c r="N114" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B115" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C115" s="27" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F115" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G115" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H115" s="1">
         <v>43308</v>
@@ -7027,40 +7052,40 @@
       <c r="K115" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L115" s="7">
+      <c r="L115" s="2">
         <v>5</v>
       </c>
       <c r="N115" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B116" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C116" s="27" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F116" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G116" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="H116" s="1">
-        <v>43325</v>
+        <v>43308</v>
       </c>
       <c r="I116" s="1">
-        <v>43325</v>
+        <v>43308</v>
       </c>
       <c r="J116" s="1">
         <v>45428</v>
@@ -7071,38 +7096,37 @@
       <c r="L116" s="7">
         <v>5</v>
       </c>
-      <c r="M116" s="1"/>
-      <c r="N116" s="21" t="s">
-        <v>267</v>
+      <c r="N116" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B117" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C117" s="27" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F117" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G117" t="s">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="H117" s="1">
-        <v>43328</v>
+        <v>43325</v>
       </c>
       <c r="I117" s="1">
-        <v>43328</v>
+        <v>43325</v>
       </c>
       <c r="J117" s="1">
         <v>45428</v>
@@ -7113,28 +7137,29 @@
       <c r="L117" s="7">
         <v>5</v>
       </c>
-      <c r="N117" t="s">
-        <v>267</v>
+      <c r="M117" s="1"/>
+      <c r="N117" s="21" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B118" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C118" s="27" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F118" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G118" t="s">
         <v>20</v>
@@ -7155,36 +7180,36 @@
         <v>5</v>
       </c>
       <c r="N118" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B119" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C119" s="27" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F119" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G119" t="s">
         <v>20</v>
       </c>
       <c r="H119" s="1">
-        <v>43329</v>
+        <v>43328</v>
       </c>
       <c r="I119" s="1">
-        <v>43329</v>
+        <v>43328</v>
       </c>
       <c r="J119" s="1">
         <v>45428</v>
@@ -7192,40 +7217,40 @@
       <c r="K119" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L119" s="2">
+      <c r="L119" s="7">
         <v>5</v>
       </c>
       <c r="N119" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B120" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C120" s="27" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F120" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G120" t="s">
         <v>20</v>
       </c>
       <c r="H120" s="1">
-        <v>43339</v>
+        <v>43329</v>
       </c>
       <c r="I120" s="1">
-        <v>43339</v>
+        <v>43329</v>
       </c>
       <c r="J120" s="1">
         <v>45428</v>
@@ -7237,36 +7262,36 @@
         <v>5</v>
       </c>
       <c r="N120" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B121" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C121" s="27" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F121" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G121" t="s">
-        <v>275</v>
+        <v>20</v>
       </c>
       <c r="H121" s="1">
-        <v>43346</v>
+        <v>43339</v>
       </c>
       <c r="I121" s="1">
-        <v>43346</v>
+        <v>43339</v>
       </c>
       <c r="J121" s="1">
         <v>45428</v>
@@ -7274,41 +7299,40 @@
       <c r="K121" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L121" s="7">
-        <v>5</v>
-      </c>
-      <c r="M121" s="1"/>
+      <c r="L121" s="2">
+        <v>5</v>
+      </c>
       <c r="N121" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B122" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C122" s="27" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F122" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G122" t="s">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="H122" s="1">
-        <v>43353</v>
+        <v>43346</v>
       </c>
       <c r="I122" s="1">
-        <v>43353</v>
+        <v>43346</v>
       </c>
       <c r="J122" s="1">
         <v>45428</v>
@@ -7319,37 +7343,38 @@
       <c r="L122" s="7">
         <v>5</v>
       </c>
+      <c r="M122" s="1"/>
       <c r="N122" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B123" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C123" s="27" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F123" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G123" t="s">
         <v>20</v>
       </c>
       <c r="H123" s="1">
-        <v>43415</v>
+        <v>43353</v>
       </c>
       <c r="I123" s="1">
-        <v>43415</v>
+        <v>43353</v>
       </c>
       <c r="J123" s="1">
         <v>45428</v>
@@ -7361,36 +7386,36 @@
         <v>5</v>
       </c>
       <c r="N123" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B124" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C124" s="27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F124" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G124" t="s">
         <v>20</v>
       </c>
       <c r="H124" s="1">
-        <v>43416</v>
+        <v>43415</v>
       </c>
       <c r="I124" s="1">
-        <v>43416</v>
+        <v>43415</v>
       </c>
       <c r="J124" s="1">
         <v>45428</v>
@@ -7398,40 +7423,40 @@
       <c r="K124" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L124" s="2">
+      <c r="L124" s="7">
         <v>5</v>
       </c>
       <c r="N124" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B125" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C125" s="27" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F125" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G125" t="s">
         <v>20</v>
       </c>
       <c r="H125" s="1">
-        <v>43461</v>
+        <v>43416</v>
       </c>
       <c r="I125" s="1">
-        <v>43461</v>
+        <v>43416</v>
       </c>
       <c r="J125" s="1">
         <v>45428</v>
@@ -7439,40 +7464,40 @@
       <c r="K125" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L125" s="7">
+      <c r="L125" s="2">
         <v>5</v>
       </c>
       <c r="N125" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B126" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C126" s="27" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F126" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G126" t="s">
         <v>20</v>
       </c>
       <c r="H126" s="1">
-        <v>43472</v>
+        <v>43461</v>
       </c>
       <c r="I126" s="1">
-        <v>43472</v>
+        <v>43461</v>
       </c>
       <c r="J126" s="1">
         <v>45428</v>
@@ -7480,40 +7505,40 @@
       <c r="K126" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L126" s="2">
+      <c r="L126" s="7">
         <v>5</v>
       </c>
       <c r="N126" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B127" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C127" s="27" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F127" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G127" t="s">
         <v>20</v>
       </c>
       <c r="H127" s="1">
-        <v>43480</v>
+        <v>43472</v>
       </c>
       <c r="I127" s="1">
-        <v>43480</v>
+        <v>43472</v>
       </c>
       <c r="J127" s="1">
         <v>45428</v>
@@ -7521,40 +7546,40 @@
       <c r="K127" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L127" s="7">
+      <c r="L127" s="2">
         <v>5</v>
       </c>
       <c r="N127" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14">
+      <c r="A128" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="128" spans="1:14">
-      <c r="A128" s="26" t="s">
-        <v>262</v>
-      </c>
       <c r="B128" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C128" s="27" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F128" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G128" t="s">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="H128" s="1">
-        <v>43486</v>
+        <v>43480</v>
       </c>
       <c r="I128" s="1">
-        <v>43486</v>
+        <v>43480</v>
       </c>
       <c r="J128" s="1">
         <v>45428</v>
@@ -7566,36 +7591,36 @@
         <v>5</v>
       </c>
       <c r="N128" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14">
+      <c r="A129" s="26" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="129" spans="1:14">
-      <c r="A129" t="s">
-        <v>262</v>
-      </c>
       <c r="B129" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C129" s="27" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F129" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G129" t="s">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="H129" s="1">
-        <v>43500</v>
+        <v>43486</v>
       </c>
       <c r="I129" s="1">
-        <v>43500</v>
+        <v>43486</v>
       </c>
       <c r="J129" s="1">
         <v>45428</v>
@@ -7607,36 +7632,36 @@
         <v>5</v>
       </c>
       <c r="N129" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B130" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C130" s="27" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F130" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G130" t="s">
         <v>20</v>
       </c>
       <c r="H130" s="1">
-        <v>43509</v>
+        <v>43500</v>
       </c>
       <c r="I130" s="1">
-        <v>43509</v>
+        <v>43500</v>
       </c>
       <c r="J130" s="1">
         <v>45428</v>
@@ -7644,40 +7669,40 @@
       <c r="K130" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L130" s="2">
+      <c r="L130" s="7">
         <v>5</v>
       </c>
       <c r="N130" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B131" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C131" s="27" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F131" t="s">
-        <v>198</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>266</v>
+        <v>142</v>
+      </c>
+      <c r="G131" t="s">
+        <v>20</v>
       </c>
       <c r="H131" s="1">
-        <v>43511</v>
+        <v>43509</v>
       </c>
       <c r="I131" s="1">
-        <v>43511</v>
+        <v>43509</v>
       </c>
       <c r="J131" s="1">
         <v>45428</v>
@@ -7689,36 +7714,36 @@
         <v>5</v>
       </c>
       <c r="N131" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B132" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C132" s="27" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>198</v>
-      </c>
-      <c r="G132" t="s">
-        <v>20</v>
+        <v>142</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="H132" s="1">
-        <v>43524</v>
+        <v>43511</v>
       </c>
       <c r="I132" s="1">
-        <v>43524</v>
+        <v>43511</v>
       </c>
       <c r="J132" s="1">
         <v>45428</v>
@@ -7730,36 +7755,36 @@
         <v>5</v>
       </c>
       <c r="N132" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B133" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C133" s="27" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F133" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G133" t="s">
         <v>20</v>
       </c>
       <c r="H133" s="1">
-        <v>43543</v>
+        <v>43524</v>
       </c>
       <c r="I133" s="1">
-        <v>43543</v>
+        <v>43524</v>
       </c>
       <c r="J133" s="1">
         <v>45428</v>
@@ -7767,40 +7792,40 @@
       <c r="K133" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L133" s="7">
+      <c r="L133" s="2">
         <v>5</v>
       </c>
       <c r="N133" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B134" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C134" s="27" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F134" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G134" t="s">
         <v>20</v>
       </c>
       <c r="H134" s="1">
-        <v>43545</v>
+        <v>43543</v>
       </c>
       <c r="I134" s="1">
-        <v>43545</v>
+        <v>43543</v>
       </c>
       <c r="J134" s="1">
         <v>45428</v>
@@ -7812,27 +7837,27 @@
         <v>5</v>
       </c>
       <c r="N134" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B135" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C135" s="27" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F135" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G135" t="s">
         <v>20</v>
@@ -7853,27 +7878,27 @@
         <v>5</v>
       </c>
       <c r="N135" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B136" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C136" s="27" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F136" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G136" t="s">
         <v>20</v>
@@ -7890,40 +7915,40 @@
       <c r="K136" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L136" s="2">
+      <c r="L136" s="7">
         <v>5</v>
       </c>
       <c r="N136" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B137" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C137" s="27" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F137" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G137" t="s">
         <v>20</v>
       </c>
       <c r="H137" s="1">
-        <v>43549</v>
+        <v>43545</v>
       </c>
       <c r="I137" s="1">
-        <v>43549</v>
+        <v>43545</v>
       </c>
       <c r="J137" s="1">
         <v>45428</v>
@@ -7935,36 +7960,36 @@
         <v>5</v>
       </c>
       <c r="N137" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B138" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C138" s="27" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F138" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G138" t="s">
         <v>20</v>
       </c>
       <c r="H138" s="1">
-        <v>43551</v>
+        <v>43549</v>
       </c>
       <c r="I138" s="1">
-        <v>43551</v>
+        <v>43549</v>
       </c>
       <c r="J138" s="1">
         <v>45428</v>
@@ -7972,34 +7997,34 @@
       <c r="K138" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L138" s="7">
-        <v>5</v>
-      </c>
-      <c r="N138" s="21" t="s">
-        <v>267</v>
+      <c r="L138" s="2">
+        <v>5</v>
+      </c>
+      <c r="N138" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B139" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C139" s="27" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F139" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G139" t="s">
-        <v>275</v>
+        <v>20</v>
       </c>
       <c r="H139" s="1">
         <v>43551</v>
@@ -8013,41 +8038,40 @@
       <c r="K139" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L139" s="2">
-        <v>5</v>
-      </c>
-      <c r="M139" s="1"/>
-      <c r="N139" t="s">
-        <v>267</v>
+      <c r="L139" s="7">
+        <v>5</v>
+      </c>
+      <c r="N139" s="21" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B140" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C140" s="27" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F140" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G140" t="s">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="H140" s="1">
-        <v>43559</v>
+        <v>43551</v>
       </c>
       <c r="I140" s="1">
-        <v>43559</v>
+        <v>43551</v>
       </c>
       <c r="J140" s="1">
         <v>45428</v>
@@ -8055,40 +8079,41 @@
       <c r="K140" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L140" s="7">
-        <v>5</v>
-      </c>
+      <c r="L140" s="2">
+        <v>5</v>
+      </c>
+      <c r="M140" s="1"/>
       <c r="N140" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B141" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C141" s="27" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F141" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G141" t="s">
-        <v>275</v>
+        <v>20</v>
       </c>
       <c r="H141" s="1">
-        <v>43570</v>
+        <v>43559</v>
       </c>
       <c r="I141" s="1">
-        <v>43570</v>
+        <v>43559</v>
       </c>
       <c r="J141" s="1">
         <v>45428</v>
@@ -8096,41 +8121,40 @@
       <c r="K141" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L141" s="2">
-        <v>5</v>
-      </c>
-      <c r="M141" s="1"/>
+      <c r="L141" s="7">
+        <v>5</v>
+      </c>
       <c r="N141" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B142" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C142" s="27" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F142" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G142" t="s">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="H142" s="1">
-        <v>43571</v>
+        <v>43570</v>
       </c>
       <c r="I142" s="1">
-        <v>43571</v>
+        <v>43570</v>
       </c>
       <c r="J142" s="1">
         <v>45428</v>
@@ -8141,28 +8165,29 @@
       <c r="L142" s="2">
         <v>5</v>
       </c>
+      <c r="M142" s="1"/>
       <c r="N142" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B143" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C143" s="27" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F143" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G143" t="s">
         <v>20</v>
@@ -8183,36 +8208,36 @@
         <v>5</v>
       </c>
       <c r="N143" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B144" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C144" s="27" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F144" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G144" t="s">
         <v>20</v>
       </c>
       <c r="H144" s="1">
-        <v>43599</v>
+        <v>43571</v>
       </c>
       <c r="I144" s="1">
-        <v>43599</v>
+        <v>43571</v>
       </c>
       <c r="J144" s="1">
         <v>45428</v>
@@ -8224,36 +8249,36 @@
         <v>5</v>
       </c>
       <c r="N144" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B145" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C145" s="27" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F145" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G145" t="s">
         <v>20</v>
       </c>
       <c r="H145" s="1">
-        <v>43609</v>
+        <v>43599</v>
       </c>
       <c r="I145" s="1">
-        <v>43609</v>
+        <v>43599</v>
       </c>
       <c r="J145" s="1">
         <v>45428</v>
@@ -8261,40 +8286,40 @@
       <c r="K145" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L145" s="7">
+      <c r="L145" s="2">
         <v>5</v>
       </c>
       <c r="N145" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B146" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C146" s="27" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F146" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G146" t="s">
         <v>20</v>
       </c>
       <c r="H146" s="1">
-        <v>43511</v>
+        <v>43609</v>
       </c>
       <c r="I146" s="1">
-        <v>43511</v>
+        <v>43609</v>
       </c>
       <c r="J146" s="1">
         <v>45428</v>
@@ -8306,71 +8331,71 @@
         <v>5</v>
       </c>
       <c r="N146" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B147" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C147" s="27" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>313</v>
+        <v>270</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F147" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G147" t="s">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="H147" s="1">
-        <v>45225</v>
+        <v>43511</v>
       </c>
       <c r="I147" s="1">
-        <v>45225</v>
+        <v>43511</v>
+      </c>
+      <c r="J147" s="1">
+        <v>45428</v>
       </c>
       <c r="K147" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L147" s="7">
         <v>5</v>
       </c>
-      <c r="M147" s="1">
-        <v>45817</v>
-      </c>
       <c r="N147" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B148" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C148" s="27" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F148" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G148" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="H148" s="1">
         <v>45225</v>
@@ -8381,40 +8406,43 @@
       <c r="K148" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L148" s="2">
-        <v>5</v>
+      <c r="L148" s="7">
+        <v>5</v>
+      </c>
+      <c r="M148" s="1">
+        <v>45817</v>
       </c>
       <c r="N148" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B149" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C149" s="27" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F149" t="s">
-        <v>198</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>266</v>
+        <v>142</v>
+      </c>
+      <c r="G149" t="s">
+        <v>319</v>
       </c>
       <c r="H149" s="1">
-        <v>45230</v>
+        <v>45225</v>
       </c>
       <c r="I149" s="1">
-        <v>45230</v>
+        <v>45225</v>
       </c>
       <c r="K149" s="3" t="s">
         <v>42</v>
@@ -8423,30 +8451,30 @@
         <v>5</v>
       </c>
       <c r="N149" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B150" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C150" s="27" t="s">
+        <v>322</v>
+      </c>
+      <c r="D150" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D150" s="2" t="s">
-        <v>316</v>
-      </c>
       <c r="E150" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F150" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="H150" s="1">
         <v>45230</v>
@@ -8457,121 +8485,118 @@
       <c r="K150" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L150" s="7">
+      <c r="L150" s="2">
         <v>5</v>
       </c>
       <c r="N150" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B151" t="s">
-        <v>263</v>
-      </c>
-      <c r="C151" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="D151" t="s">
-        <v>320</v>
+        <v>268</v>
+      </c>
+      <c r="C151" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F151" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="H151" s="1">
-        <v>45236</v>
+        <v>45230</v>
       </c>
       <c r="I151" s="1">
-        <v>45236</v>
-      </c>
-      <c r="J151"/>
+        <v>45230</v>
+      </c>
       <c r="K151" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L151" s="2">
-        <v>5</v>
-      </c>
-      <c r="M151"/>
+      <c r="L151" s="7">
+        <v>5</v>
+      </c>
       <c r="N151" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B152" t="s">
-        <v>263</v>
-      </c>
-      <c r="C152" s="24" t="s">
-        <v>321</v>
+        <v>268</v>
+      </c>
+      <c r="C152" s="28" t="s">
+        <v>324</v>
       </c>
       <c r="D152" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F152" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G152" t="s">
-        <v>20</v>
+      <c r="F152" t="s">
+        <v>142</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="H152" s="1">
-        <v>43767</v>
+        <v>45236</v>
       </c>
       <c r="I152" s="1">
-        <v>43767</v>
-      </c>
-      <c r="J152" s="1">
-        <v>45806</v>
-      </c>
-      <c r="K152" s="2" t="s">
-        <v>21</v>
+        <v>45236</v>
+      </c>
+      <c r="J152"/>
+      <c r="K152" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="L152" s="2">
         <v>5</v>
       </c>
+      <c r="M152"/>
       <c r="N152" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B153" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C153" s="24" t="s">
-        <v>323</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>265</v>
+        <v>326</v>
+      </c>
+      <c r="D153" t="s">
+        <v>327</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>266</v>
+        <v>142</v>
+      </c>
+      <c r="G153" t="s">
+        <v>20</v>
       </c>
       <c r="H153" s="1">
-        <v>43808</v>
+        <v>43767</v>
       </c>
       <c r="I153" s="1">
-        <v>43808</v>
+        <v>43767</v>
       </c>
       <c r="J153" s="1">
         <v>45806</v>
@@ -8583,30 +8608,30 @@
         <v>5</v>
       </c>
       <c r="N153" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B154" t="s">
-        <v>263</v>
-      </c>
-      <c r="C154" s="25" t="s">
-        <v>324</v>
-      </c>
-      <c r="D154" t="s">
-        <v>325</v>
+        <v>268</v>
+      </c>
+      <c r="C154" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>270</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G154" t="s">
-        <v>326</v>
+        <v>142</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="H154" s="1">
         <v>43808</v>
@@ -8624,30 +8649,30 @@
         <v>5</v>
       </c>
       <c r="N154" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B155" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C155" s="25" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D155" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G155" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H155" s="1">
         <v>43808</v>
@@ -8665,18 +8690,18 @@
         <v>5</v>
       </c>
       <c r="N155" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B156" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C156" s="25" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D156" t="s">
         <v>330</v>
@@ -8685,19 +8710,19 @@
         <v>18</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>266</v>
+        <v>142</v>
+      </c>
+      <c r="G156" t="s">
+        <v>333</v>
       </c>
       <c r="H156" s="1">
-        <v>43977</v>
+        <v>43808</v>
       </c>
       <c r="I156" s="1">
-        <v>43977</v>
+        <v>43808</v>
       </c>
       <c r="J156" s="1">
-        <v>45803</v>
+        <v>45806</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>21</v>
@@ -8706,39 +8731,39 @@
         <v>5</v>
       </c>
       <c r="N156" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B157" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C157" s="25" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D157" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G157" t="s">
-        <v>333</v>
+        <v>142</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="H157" s="1">
-        <v>43972</v>
+        <v>43977</v>
       </c>
       <c r="I157" s="1">
-        <v>43972</v>
+        <v>43977</v>
       </c>
       <c r="J157" s="1">
-        <v>45796</v>
+        <v>45803</v>
       </c>
       <c r="K157" s="2" t="s">
         <v>21</v>
@@ -8747,39 +8772,39 @@
         <v>5</v>
       </c>
       <c r="N157" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B158" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C158" s="25" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D158" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G158" t="s">
-        <v>20</v>
+        <v>338</v>
       </c>
       <c r="H158" s="1">
-        <v>43650</v>
+        <v>43972</v>
       </c>
       <c r="I158" s="1">
-        <v>43650</v>
+        <v>43972</v>
       </c>
       <c r="J158" s="1">
-        <v>45793</v>
+        <v>45796</v>
       </c>
       <c r="K158" s="2" t="s">
         <v>21</v>
@@ -8788,36 +8813,36 @@
         <v>5</v>
       </c>
       <c r="N158" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B159" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C159" s="25" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D159" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G159" t="s">
-        <v>338</v>
+        <v>20</v>
       </c>
       <c r="H159" s="1">
-        <v>43651</v>
+        <v>43650</v>
       </c>
       <c r="I159" s="1">
-        <v>43651</v>
+        <v>43650</v>
       </c>
       <c r="J159" s="1">
         <v>45793</v>
@@ -8829,36 +8854,36 @@
         <v>5</v>
       </c>
       <c r="N159" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B160" t="s">
-        <v>263</v>
-      </c>
-      <c r="C160" s="24" t="s">
-        <v>339</v>
+        <v>268</v>
+      </c>
+      <c r="C160" s="25" t="s">
+        <v>341</v>
       </c>
       <c r="D160" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G160" t="s">
-        <v>20</v>
+        <v>343</v>
       </c>
       <c r="H160" s="1">
-        <v>43658</v>
+        <v>43651</v>
       </c>
       <c r="I160" s="1">
-        <v>43658</v>
+        <v>43651</v>
       </c>
       <c r="J160" s="1">
         <v>45793</v>
@@ -8870,36 +8895,36 @@
         <v>5</v>
       </c>
       <c r="N160" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B161" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C161" s="24" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D161" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G161" t="s">
-        <v>275</v>
+        <v>20</v>
       </c>
       <c r="H161" s="1">
-        <v>43668</v>
+        <v>43658</v>
       </c>
       <c r="I161" s="1">
-        <v>43668</v>
+        <v>43658</v>
       </c>
       <c r="J161" s="1">
         <v>45793</v>
@@ -8911,36 +8936,36 @@
         <v>5</v>
       </c>
       <c r="N161" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B162" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C162" s="24" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D162" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G162" t="s">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="H162" s="1">
-        <v>43678</v>
+        <v>43668</v>
       </c>
       <c r="I162" s="1">
-        <v>43678</v>
+        <v>43668</v>
       </c>
       <c r="J162" s="1">
         <v>45793</v>
@@ -8952,39 +8977,39 @@
         <v>5</v>
       </c>
       <c r="N162" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:14">
       <c r="A163" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B163" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C163" s="24" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D163" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>266</v>
+        <v>142</v>
+      </c>
+      <c r="G163" t="s">
+        <v>20</v>
       </c>
       <c r="H163" s="1">
-        <v>43685</v>
+        <v>43678</v>
       </c>
       <c r="I163" s="1">
-        <v>43685</v>
+        <v>43678</v>
       </c>
       <c r="J163" s="1">
-        <v>45824</v>
+        <v>45793</v>
       </c>
       <c r="K163" s="2" t="s">
         <v>21</v>
@@ -8993,39 +9018,39 @@
         <v>5</v>
       </c>
       <c r="N163" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B164" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C164" s="24" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D164" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G164" t="s">
-        <v>20</v>
+        <v>142</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="H164" s="1">
-        <v>43686</v>
+        <v>43685</v>
       </c>
       <c r="I164" s="1">
-        <v>43686</v>
+        <v>43685</v>
       </c>
       <c r="J164" s="1">
-        <v>45793</v>
+        <v>45824</v>
       </c>
       <c r="K164" s="2" t="s">
         <v>21</v>
@@ -9034,27 +9059,27 @@
         <v>5</v>
       </c>
       <c r="N164" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B165" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C165" s="24" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D165" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G165" t="s">
         <v>20</v>
@@ -9075,36 +9100,36 @@
         <v>5</v>
       </c>
       <c r="N165" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B166" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C166" s="24" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D166" t="s">
-        <v>265</v>
+        <v>355</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G166" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="H166" s="1">
-        <v>43703</v>
+        <v>43686</v>
       </c>
       <c r="I166" s="1">
-        <v>43703</v>
+        <v>43686</v>
       </c>
       <c r="J166" s="1">
         <v>45793</v>
@@ -9116,36 +9141,36 @@
         <v>5</v>
       </c>
       <c r="N166" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B167" t="s">
-        <v>263</v>
-      </c>
-      <c r="C167" s="25" t="s">
-        <v>352</v>
+        <v>268</v>
+      </c>
+      <c r="C167" s="24" t="s">
+        <v>356</v>
       </c>
       <c r="D167" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G167" t="s">
         <v>63</v>
       </c>
       <c r="H167" s="1">
-        <v>43707</v>
+        <v>43703</v>
       </c>
       <c r="I167" s="1">
-        <v>43707</v>
+        <v>43703</v>
       </c>
       <c r="J167" s="1">
         <v>45793</v>
@@ -9157,36 +9182,36 @@
         <v>5</v>
       </c>
       <c r="N167" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B168" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C168" s="25" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D168" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G168" t="s">
-        <v>354</v>
+        <v>63</v>
       </c>
       <c r="H168" s="1">
-        <v>43710</v>
+        <v>43707</v>
       </c>
       <c r="I168" s="1">
-        <v>43710</v>
+        <v>43707</v>
       </c>
       <c r="J168" s="1">
         <v>45793</v>
@@ -9198,36 +9223,36 @@
         <v>5</v>
       </c>
       <c r="N168" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B169" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C169" s="25" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D169" t="s">
-        <v>356</v>
+        <v>270</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G169" t="s">
-        <v>20</v>
+        <v>359</v>
       </c>
       <c r="H169" s="1">
-        <v>43732</v>
+        <v>43710</v>
       </c>
       <c r="I169" s="1">
-        <v>43732</v>
+        <v>43710</v>
       </c>
       <c r="J169" s="1">
         <v>45793</v>
@@ -9239,27 +9264,27 @@
         <v>5</v>
       </c>
       <c r="N169" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B170" t="s">
-        <v>263</v>
-      </c>
-      <c r="C170" s="24" t="s">
-        <v>357</v>
+        <v>268</v>
+      </c>
+      <c r="C170" s="25" t="s">
+        <v>360</v>
       </c>
       <c r="D170" t="s">
-        <v>265</v>
+        <v>361</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G170" t="s">
         <v>20</v>
@@ -9280,36 +9305,36 @@
         <v>5</v>
       </c>
       <c r="N170" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B171" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C171" s="24" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D171" t="s">
-        <v>359</v>
+        <v>270</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G171" t="s">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="H171" s="1">
-        <v>43787</v>
+        <v>43732</v>
       </c>
       <c r="I171" s="1">
-        <v>43787</v>
+        <v>43732</v>
       </c>
       <c r="J171" s="1">
         <v>45793</v>
@@ -9321,36 +9346,36 @@
         <v>5</v>
       </c>
       <c r="N171" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B172" t="s">
-        <v>263</v>
-      </c>
-      <c r="C172" s="25" t="s">
-        <v>361</v>
+        <v>268</v>
+      </c>
+      <c r="C172" s="24" t="s">
+        <v>363</v>
       </c>
       <c r="D172" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G172" t="s">
-        <v>20</v>
+        <v>365</v>
       </c>
       <c r="H172" s="1">
-        <v>43791</v>
+        <v>43787</v>
       </c>
       <c r="I172" s="1">
-        <v>43791</v>
+        <v>43787</v>
       </c>
       <c r="J172" s="1">
         <v>45793</v>
@@ -9362,36 +9387,36 @@
         <v>5</v>
       </c>
       <c r="N172" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B173" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C173" s="25" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D173" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G173" t="s">
         <v>20</v>
       </c>
       <c r="H173" s="1">
-        <v>43872</v>
+        <v>43791</v>
       </c>
       <c r="I173" s="1">
-        <v>43872</v>
+        <v>43791</v>
       </c>
       <c r="J173" s="1">
         <v>45793</v>
@@ -9403,36 +9428,36 @@
         <v>5</v>
       </c>
       <c r="N173" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B174" t="s">
-        <v>263</v>
-      </c>
-      <c r="C174" s="24" t="s">
-        <v>365</v>
+        <v>268</v>
+      </c>
+      <c r="C174" s="25" t="s">
+        <v>368</v>
       </c>
       <c r="D174" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G174" t="s">
         <v>20</v>
       </c>
       <c r="H174" s="1">
-        <v>43874</v>
+        <v>43872</v>
       </c>
       <c r="I174" s="1">
-        <v>43874</v>
+        <v>43872</v>
       </c>
       <c r="J174" s="1">
         <v>45793</v>
@@ -9444,39 +9469,39 @@
         <v>5</v>
       </c>
       <c r="N174" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B175" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C175" s="24" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D175" t="s">
-        <v>265</v>
+        <v>361</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G175" t="s">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="H175" s="1">
-        <v>42937</v>
+        <v>43874</v>
       </c>
       <c r="I175" s="1">
-        <v>42937</v>
+        <v>43874</v>
       </c>
       <c r="J175" s="1">
-        <v>45489</v>
+        <v>45793</v>
       </c>
       <c r="K175" s="2" t="s">
         <v>21</v>
@@ -9485,36 +9510,36 @@
         <v>5</v>
       </c>
       <c r="N175" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B176" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C176" s="24" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D176" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G176" s="2" t="s">
-        <v>266</v>
+        <v>142</v>
+      </c>
+      <c r="G176" t="s">
+        <v>331</v>
       </c>
       <c r="H176" s="1">
-        <v>43130</v>
+        <v>42937</v>
       </c>
       <c r="I176" s="1">
-        <v>43130</v>
+        <v>42937</v>
       </c>
       <c r="J176" s="1">
         <v>45489</v>
@@ -9526,36 +9551,36 @@
         <v>5</v>
       </c>
       <c r="N176" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B177" t="s">
-        <v>263</v>
-      </c>
-      <c r="C177" s="25" t="s">
-        <v>368</v>
+        <v>268</v>
+      </c>
+      <c r="C177" s="24" t="s">
+        <v>372</v>
       </c>
       <c r="D177" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G177" t="s">
-        <v>326</v>
+        <v>142</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="H177" s="1">
-        <v>43312</v>
+        <v>43130</v>
       </c>
       <c r="I177" s="1">
-        <v>43312</v>
+        <v>43130</v>
       </c>
       <c r="J177" s="1">
         <v>45489</v>
@@ -9567,36 +9592,36 @@
         <v>5</v>
       </c>
       <c r="N177" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="178" spans="1:14">
       <c r="A178" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B178" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C178" s="25" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D178" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G178" t="s">
-        <v>370</v>
+        <v>331</v>
       </c>
       <c r="H178" s="1">
-        <v>43490</v>
+        <v>43312</v>
       </c>
       <c r="I178" s="1">
-        <v>43490</v>
+        <v>43312</v>
       </c>
       <c r="J178" s="1">
         <v>45489</v>
@@ -9608,30 +9633,30 @@
         <v>5</v>
       </c>
       <c r="N178" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B179" t="s">
-        <v>263</v>
-      </c>
-      <c r="C179" s="24" t="s">
-        <v>371</v>
+        <v>268</v>
+      </c>
+      <c r="C179" s="25" t="s">
+        <v>374</v>
       </c>
       <c r="D179" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G179" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H179" s="1">
         <v>43490</v>
@@ -9649,30 +9674,30 @@
         <v>5</v>
       </c>
       <c r="N179" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B180" t="s">
-        <v>263</v>
-      </c>
-      <c r="C180" s="25" t="s">
-        <v>372</v>
+        <v>268</v>
+      </c>
+      <c r="C180" s="24" t="s">
+        <v>376</v>
       </c>
       <c r="D180" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G180" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H180" s="1">
         <v>43490</v>
@@ -9690,79 +9715,79 @@
         <v>5</v>
       </c>
       <c r="N180" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14">
+      <c r="A181" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" customFormat="1">
-      <c r="A181" t="s">
-        <v>374</v>
-      </c>
       <c r="B181" t="s">
-        <v>375</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D181" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C181" s="25" t="s">
         <v>377</v>
       </c>
+      <c r="D181" t="s">
+        <v>270</v>
+      </c>
       <c r="E181" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G181" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G181" t="s">
         <v>378</v>
       </c>
       <c r="H181" s="1">
-        <v>44617</v>
+        <v>43490</v>
       </c>
       <c r="I181" s="1">
-        <v>44617</v>
-      </c>
-      <c r="J181" s="2"/>
-      <c r="K181" s="3" t="s">
-        <v>42</v>
+        <v>43490</v>
+      </c>
+      <c r="J181" s="1">
+        <v>45489</v>
+      </c>
+      <c r="K181" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="L181" s="2">
-        <v>25</v>
-      </c>
-      <c r="M181" s="1">
-        <v>46128</v>
+        <v>5</v>
       </c>
       <c r="N181" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" customFormat="1">
+      <c r="A182" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="182" spans="1:14">
-      <c r="A182" t="s">
-        <v>374</v>
-      </c>
       <c r="B182" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H182" s="1">
-        <v>45821</v>
+        <v>44617</v>
       </c>
       <c r="I182" s="1">
         <v>44617</v>
       </c>
+      <c r="J182" s="2"/>
       <c r="K182" s="3" t="s">
         <v>42</v>
       </c>
@@ -9773,30 +9798,30 @@
         <v>46128</v>
       </c>
       <c r="N182" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="183" spans="1:14">
       <c r="A183" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B183" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H183" s="1">
         <v>45821</v>
@@ -9814,36 +9839,36 @@
         <v>46128</v>
       </c>
       <c r="N183" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B184" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G184" t="s">
+      <c r="G184" s="2" t="s">
         <v>383</v>
       </c>
       <c r="H184" s="1">
-        <v>44923</v>
+        <v>45821</v>
       </c>
       <c r="I184" s="1">
-        <v>42990</v>
+        <v>44617</v>
       </c>
       <c r="K184" s="3" t="s">
         <v>42</v>
@@ -9855,33 +9880,33 @@
         <v>46128</v>
       </c>
       <c r="N184" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="185" spans="1:14">
       <c r="A185" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B185" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G185" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="H185" s="1">
-        <v>44925</v>
+        <v>44923</v>
       </c>
       <c r="I185" s="1">
         <v>42990</v>
@@ -9896,36 +9921,36 @@
         <v>46128</v>
       </c>
       <c r="N185" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B186" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G186" s="2" t="s">
-        <v>386</v>
+      <c r="G186" t="s">
+        <v>388</v>
       </c>
       <c r="H186" s="1">
-        <v>44617</v>
+        <v>44925</v>
       </c>
       <c r="I186" s="1">
-        <v>44617</v>
+        <v>42990</v>
       </c>
       <c r="K186" s="3" t="s">
         <v>42</v>
@@ -9937,36 +9962,36 @@
         <v>46128</v>
       </c>
       <c r="N186" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B187" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G187" t="s">
-        <v>388</v>
+      <c r="G187" s="2" t="s">
+        <v>391</v>
       </c>
       <c r="H187" s="1">
-        <v>44194</v>
+        <v>44617</v>
       </c>
       <c r="I187" s="1">
-        <v>42990</v>
+        <v>44617</v>
       </c>
       <c r="K187" s="3" t="s">
         <v>42</v>
@@ -9978,36 +10003,36 @@
         <v>46128</v>
       </c>
       <c r="N187" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="188" spans="1:14">
       <c r="A188" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B188" t="s">
-        <v>375</v>
-      </c>
-      <c r="C188" t="s">
-        <v>376</v>
-      </c>
-      <c r="D188" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="E188" t="s">
-        <v>210</v>
+        <v>380</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D188" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G188" t="s">
-        <v>388</v>
-      </c>
-      <c r="H188" s="16">
-        <v>44426</v>
+        <v>393</v>
+      </c>
+      <c r="H188" s="1">
+        <v>44194</v>
       </c>
       <c r="I188" s="1">
-        <v>42191</v>
+        <v>42990</v>
       </c>
       <c r="K188" s="3" t="s">
         <v>42</v>
@@ -10019,62 +10044,62 @@
         <v>46128</v>
       </c>
       <c r="N188" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B189" t="s">
-        <v>375</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D189" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>18</v>
+        <v>380</v>
+      </c>
+      <c r="C189" t="s">
+        <v>381</v>
+      </c>
+      <c r="D189" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="E189" t="s">
+        <v>141</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G189" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="H189" s="1">
-        <v>45820</v>
+      <c r="G189" t="s">
+        <v>393</v>
+      </c>
+      <c r="H189" s="16">
+        <v>44426</v>
       </c>
       <c r="I189" s="1">
-        <v>45820</v>
+        <v>42191</v>
       </c>
       <c r="K189" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L189" s="7">
-        <v>5</v>
+      <c r="L189" s="2">
+        <v>25</v>
       </c>
       <c r="M189" s="1">
         <v>46128</v>
       </c>
       <c r="N189" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B190" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>18</v>
@@ -10083,7 +10108,7 @@
         <v>53</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="H190" s="1">
         <v>45820</v>
@@ -10094,28 +10119,28 @@
       <c r="K190" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L190" s="2">
+      <c r="L190" s="7">
         <v>5</v>
       </c>
       <c r="M190" s="1">
         <v>46128</v>
       </c>
       <c r="N190" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="191" spans="1:14">
       <c r="A191" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B191" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>18</v>
@@ -10124,13 +10149,13 @@
         <v>53</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H191" s="1">
-        <v>44734</v>
+        <v>45820</v>
       </c>
       <c r="I191" s="1">
-        <v>44734</v>
+        <v>45820</v>
       </c>
       <c r="K191" s="3" t="s">
         <v>42</v>
@@ -10142,79 +10167,79 @@
         <v>46128</v>
       </c>
       <c r="N191" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14">
+      <c r="A192" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" customFormat="1">
-      <c r="A192" t="s">
-        <v>395</v>
-      </c>
       <c r="B192" t="s">
-        <v>396</v>
-      </c>
-      <c r="C192" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="D192" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D192" s="11" t="s">
         <v>398</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F192" t="s">
-        <v>198</v>
-      </c>
-      <c r="G192" t="s">
+        <v>18</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G192" s="2" t="s">
         <v>399</v>
       </c>
       <c r="H192" s="1">
+        <v>44734</v>
+      </c>
+      <c r="I192" s="1">
+        <v>44734</v>
+      </c>
+      <c r="K192" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L192" s="2">
+        <v>5</v>
+      </c>
+      <c r="M192" s="1">
+        <v>46128</v>
+      </c>
+      <c r="N192" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" customFormat="1">
+      <c r="A193" t="s">
+        <v>400</v>
+      </c>
+      <c r="B193" t="s">
+        <v>401</v>
+      </c>
+      <c r="C193" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="D193" t="s">
+        <v>403</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F193" t="s">
+        <v>142</v>
+      </c>
+      <c r="G193" t="s">
+        <v>404</v>
+      </c>
+      <c r="H193" s="1">
         <v>44027</v>
       </c>
-      <c r="I192" s="1">
+      <c r="I193" s="1">
         <v>45656</v>
       </c>
-      <c r="J192" s="2"/>
-      <c r="K192" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L192" s="2">
-        <v>25</v>
-      </c>
-      <c r="M192" s="1">
-        <v>46141</v>
-      </c>
-      <c r="N192" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="193" spans="1:14">
-      <c r="A193" t="s">
-        <v>395</v>
-      </c>
-      <c r="B193" t="s">
-        <v>396</v>
-      </c>
-      <c r="C193" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="D193" t="s">
-        <v>402</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F193" t="s">
-        <v>198</v>
-      </c>
-      <c r="G193" t="s">
-        <v>174</v>
-      </c>
-      <c r="H193" s="1">
-        <v>44348</v>
-      </c>
-      <c r="I193" s="1">
-        <v>44349</v>
-      </c>
+      <c r="J193" s="2"/>
       <c r="K193" s="3" t="s">
         <v>42</v>
       </c>
@@ -10225,30 +10250,30 @@
         <v>46141</v>
       </c>
       <c r="N193" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="194" spans="1:14">
       <c r="A194" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B194" t="s">
-        <v>396</v>
-      </c>
-      <c r="C194" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
+      </c>
+      <c r="C194" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="D194" t="s">
+        <v>407</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F194" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G194" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H194" s="1">
         <v>44348</v>
@@ -10266,30 +10291,30 @@
         <v>46141</v>
       </c>
       <c r="N194" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="195" spans="1:14">
       <c r="A195" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B195" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F195" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G195" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H195" s="1">
         <v>44348</v>
@@ -10307,30 +10332,30 @@
         <v>46141</v>
       </c>
       <c r="N195" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="196" spans="1:14">
       <c r="A196" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B196" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="F196" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G196" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H196" s="1">
         <v>44348</v>
@@ -10341,37 +10366,37 @@
       <c r="K196" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L196" s="7">
-        <v>5</v>
+      <c r="L196" s="2">
+        <v>25</v>
       </c>
       <c r="M196" s="1">
         <v>46141</v>
       </c>
       <c r="N196" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14">
+      <c r="A197" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" customFormat="1">
-      <c r="A197" t="s">
-        <v>395</v>
-      </c>
       <c r="B197" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F197" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G197" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H197" s="1">
         <v>44348</v>
@@ -10379,41 +10404,40 @@
       <c r="I197" s="1">
         <v>44349</v>
       </c>
-      <c r="J197" s="2"/>
       <c r="K197" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L197" s="2">
+      <c r="L197" s="7">
         <v>5</v>
       </c>
       <c r="M197" s="1">
         <v>46141</v>
       </c>
       <c r="N197" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" customFormat="1">
+      <c r="A198" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="198" spans="1:14">
-      <c r="A198" t="s">
-        <v>395</v>
-      </c>
       <c r="B198" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F198" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G198" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H198" s="1">
         <v>44348</v>
@@ -10421,6 +10445,7 @@
       <c r="I198" s="1">
         <v>44349</v>
       </c>
+      <c r="J198" s="2"/>
       <c r="K198" s="3" t="s">
         <v>42</v>
       </c>
@@ -10431,30 +10456,30 @@
         <v>46141</v>
       </c>
       <c r="N198" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="199" spans="1:14">
       <c r="A199" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B199" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F199" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G199" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H199" s="1">
         <v>44348</v>
@@ -10465,37 +10490,37 @@
       <c r="K199" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L199" s="7">
+      <c r="L199" s="2">
         <v>5</v>
       </c>
       <c r="M199" s="1">
         <v>46141</v>
       </c>
       <c r="N199" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B200" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F200" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G200" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H200" s="1">
         <v>44348</v>
@@ -10506,37 +10531,37 @@
       <c r="K200" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L200" s="2">
-        <v>15</v>
+      <c r="L200" s="7">
+        <v>5</v>
       </c>
       <c r="M200" s="1">
         <v>46141</v>
       </c>
       <c r="N200" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="201" spans="1:14">
       <c r="A201" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B201" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>210</v>
+        <v>41</v>
       </c>
       <c r="F201" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G201" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H201" s="1">
         <v>44348</v>
@@ -10548,36 +10573,36 @@
         <v>42</v>
       </c>
       <c r="L201" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M201" s="1">
         <v>46141</v>
       </c>
       <c r="N201" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14">
+      <c r="A202" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="202" spans="1:14" customFormat="1">
-      <c r="A202" t="s">
-        <v>395</v>
-      </c>
       <c r="B202" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="F202" t="s">
-        <v>198</v>
-      </c>
-      <c r="G202" s="2" t="s">
-        <v>266</v>
+        <v>142</v>
+      </c>
+      <c r="G202" t="s">
+        <v>181</v>
       </c>
       <c r="H202" s="1">
         <v>44348</v>
@@ -10585,41 +10610,40 @@
       <c r="I202" s="1">
         <v>44349</v>
       </c>
-      <c r="J202" s="2"/>
       <c r="K202" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L202" s="7">
-        <v>5</v>
+      <c r="L202" s="2">
+        <v>25</v>
       </c>
       <c r="M202" s="1">
         <v>46141</v>
       </c>
       <c r="N202" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" customFormat="1">
+      <c r="A203" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="203" spans="1:14">
-      <c r="A203" t="s">
-        <v>395</v>
-      </c>
       <c r="B203" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F203" t="s">
-        <v>198</v>
-      </c>
-      <c r="G203" t="s">
-        <v>20</v>
+        <v>142</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="H203" s="1">
         <v>44348</v>
@@ -10627,125 +10651,126 @@
       <c r="I203" s="1">
         <v>44349</v>
       </c>
+      <c r="J203" s="2"/>
       <c r="K203" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L203" s="2">
-        <v>15</v>
+      <c r="L203" s="7">
+        <v>5</v>
       </c>
       <c r="M203" s="1">
         <v>46141</v>
       </c>
       <c r="N203" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="204" spans="1:14">
       <c r="A204" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B204" t="s">
-        <v>396</v>
-      </c>
-      <c r="C204" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="D204" t="s">
-        <v>424</v>
+        <v>401</v>
+      </c>
+      <c r="C204" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>427</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F204" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G204" t="s">
-        <v>425</v>
+        <v>20</v>
       </c>
       <c r="H204" s="1">
-        <v>43712</v>
+        <v>44348</v>
       </c>
       <c r="I204" s="1">
-        <v>43712</v>
-      </c>
-      <c r="J204" s="1">
-        <v>45539</v>
+        <v>44349</v>
       </c>
       <c r="K204" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L204" s="7">
-        <v>5</v>
+        <v>42</v>
+      </c>
+      <c r="L204" s="2">
+        <v>15</v>
       </c>
       <c r="M204" s="1">
         <v>46141</v>
       </c>
       <c r="N204" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="205" spans="1:14">
       <c r="A205" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B205" t="s">
-        <v>396</v>
-      </c>
-      <c r="C205" s="11" t="s">
-        <v>426</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>427</v>
+        <v>401</v>
+      </c>
+      <c r="C205" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="D205" t="s">
+        <v>429</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F205" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G205" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H205" s="1">
-        <v>44348</v>
+        <v>43712</v>
       </c>
       <c r="I205" s="1">
-        <v>44349</v>
+        <v>43712</v>
+      </c>
+      <c r="J205" s="1">
+        <v>45539</v>
       </c>
       <c r="K205" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L205" s="2">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="L205" s="7">
+        <v>5</v>
       </c>
       <c r="M205" s="1">
         <v>46141</v>
       </c>
       <c r="N205" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="206" spans="1:14">
       <c r="A206" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B206" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>210</v>
+        <v>41</v>
       </c>
       <c r="F206" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G206" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H206" s="1">
         <v>44348</v>
@@ -10757,36 +10782,36 @@
         <v>42</v>
       </c>
       <c r="L206" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M206" s="1">
         <v>46141</v>
       </c>
       <c r="N206" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14">
+      <c r="A207" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" customFormat="1">
-      <c r="A207" t="s">
-        <v>395</v>
-      </c>
       <c r="B207" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C207" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F207" t="s">
+        <v>142</v>
+      </c>
+      <c r="G207" t="s">
         <v>430</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F207" t="s">
-        <v>198</v>
-      </c>
-      <c r="G207" t="s">
-        <v>425</v>
       </c>
       <c r="H207" s="1">
         <v>44348</v>
@@ -10794,41 +10819,40 @@
       <c r="I207" s="1">
         <v>44349</v>
       </c>
-      <c r="J207" s="2"/>
       <c r="K207" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L207" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M207" s="1">
         <v>46141</v>
       </c>
       <c r="N207" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" customFormat="1">
+      <c r="A208" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="208" spans="1:14">
-      <c r="A208" t="s">
-        <v>395</v>
-      </c>
       <c r="B208" t="s">
-        <v>396</v>
-      </c>
-      <c r="C208" s="15" t="s">
-        <v>432</v>
-      </c>
-      <c r="D208" t="s">
-        <v>433</v>
+        <v>401</v>
+      </c>
+      <c r="C208" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>436</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F208" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G208" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H208" s="1">
         <v>44348</v>
@@ -10836,6 +10860,7 @@
       <c r="I208" s="1">
         <v>44349</v>
       </c>
+      <c r="J208" s="2"/>
       <c r="K208" s="3" t="s">
         <v>42</v>
       </c>
@@ -10846,30 +10871,30 @@
         <v>46141</v>
       </c>
       <c r="N208" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="209" spans="1:14">
       <c r="A209" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B209" t="s">
-        <v>396</v>
-      </c>
-      <c r="C209" s="11" t="s">
-        <v>434</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>435</v>
+        <v>401</v>
+      </c>
+      <c r="C209" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="D209" t="s">
+        <v>438</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F209" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G209" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H209" s="1">
         <v>44348</v>
@@ -10880,37 +10905,37 @@
       <c r="K209" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L209" s="7">
+      <c r="L209" s="2">
         <v>5</v>
       </c>
       <c r="M209" s="1">
         <v>46141</v>
       </c>
       <c r="N209" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="210" spans="1:14">
       <c r="A210" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B210" t="s">
-        <v>396</v>
-      </c>
-      <c r="C210" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="D210" t="s">
-        <v>437</v>
+        <v>401</v>
+      </c>
+      <c r="C210" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>440</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F210" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G210" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H210" s="1">
         <v>44348</v>
@@ -10921,37 +10946,37 @@
       <c r="K210" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L210" s="2">
-        <v>15</v>
+      <c r="L210" s="7">
+        <v>5</v>
       </c>
       <c r="M210" s="1">
         <v>46141</v>
       </c>
       <c r="N210" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="211" spans="1:14">
       <c r="A211" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B211" t="s">
-        <v>396</v>
-      </c>
-      <c r="C211" s="11" t="s">
-        <v>438</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>439</v>
+        <v>401</v>
+      </c>
+      <c r="C211" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="D211" t="s">
+        <v>442</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F211" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G211" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H211" s="1">
         <v>44348</v>
@@ -10969,30 +10994,30 @@
         <v>46141</v>
       </c>
       <c r="N211" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14">
+      <c r="A212" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="212" spans="1:14" customFormat="1">
-      <c r="A212" t="s">
-        <v>395</v>
-      </c>
       <c r="B212" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C212" s="11" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F212" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G212" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H212" s="1">
         <v>44348</v>
@@ -11000,7 +11025,6 @@
       <c r="I212" s="1">
         <v>44349</v>
       </c>
-      <c r="J212" s="2"/>
       <c r="K212" s="3" t="s">
         <v>42</v>
       </c>
@@ -11011,30 +11035,30 @@
         <v>46141</v>
       </c>
       <c r="N212" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" customFormat="1">
+      <c r="A213" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="213" spans="1:14">
-      <c r="A213" t="s">
-        <v>395</v>
-      </c>
       <c r="B213" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F213" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G213" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H213" s="1">
         <v>44348</v>
@@ -11042,6 +11066,7 @@
       <c r="I213" s="1">
         <v>44349</v>
       </c>
+      <c r="J213" s="2"/>
       <c r="K213" s="3" t="s">
         <v>42</v>
       </c>
@@ -11052,30 +11077,30 @@
         <v>46141</v>
       </c>
       <c r="N213" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="214" spans="1:14">
       <c r="A214" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B214" t="s">
-        <v>396</v>
-      </c>
-      <c r="C214" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="D214" t="s">
-        <v>445</v>
+        <v>401</v>
+      </c>
+      <c r="C214" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>448</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F214" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G214" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H214" s="1">
         <v>44348</v>
@@ -11093,30 +11118,30 @@
         <v>46141</v>
       </c>
       <c r="N214" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="215" spans="1:14">
       <c r="A215" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B215" t="s">
-        <v>396</v>
-      </c>
-      <c r="C215" s="11" t="s">
-        <v>446</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>447</v>
+        <v>401</v>
+      </c>
+      <c r="C215" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="D215" t="s">
+        <v>450</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F215" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G215" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="H215" s="1">
         <v>44348</v>
@@ -11134,30 +11159,30 @@
         <v>46141</v>
       </c>
       <c r="N215" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="216" spans="1:14">
       <c r="A216" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B216" t="s">
-        <v>396</v>
-      </c>
-      <c r="C216" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="D216" t="s">
-        <v>450</v>
+        <v>401</v>
+      </c>
+      <c r="C216" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>452</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>210</v>
+        <v>41</v>
       </c>
       <c r="F216" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G216" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H216" s="1">
         <v>44348</v>
@@ -11169,36 +11194,36 @@
         <v>42</v>
       </c>
       <c r="L216" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M216" s="1">
         <v>46141</v>
       </c>
       <c r="N216" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14">
+      <c r="A217" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" customFormat="1">
-      <c r="A217" t="s">
-        <v>395</v>
-      </c>
       <c r="B217" t="s">
-        <v>396</v>
-      </c>
-      <c r="C217" s="11" t="s">
-        <v>452</v>
-      </c>
-      <c r="D217" s="2" t="s">
-        <v>453</v>
+        <v>401</v>
+      </c>
+      <c r="C217" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="D217" t="s">
+        <v>455</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F217" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G217" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="H217" s="1">
         <v>44348</v>
@@ -11206,7 +11231,6 @@
       <c r="I217" s="1">
         <v>44349</v>
       </c>
-      <c r="J217" s="2"/>
       <c r="K217" s="3" t="s">
         <v>42</v>
       </c>
@@ -11217,30 +11241,30 @@
         <v>46141</v>
       </c>
       <c r="N217" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" customFormat="1">
+      <c r="A218" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="218" spans="1:14">
-      <c r="A218" t="s">
-        <v>395</v>
-      </c>
       <c r="B218" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C218" s="11" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="F218" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G218" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="H218" s="1">
         <v>44348</v>
@@ -11248,40 +11272,41 @@
       <c r="I218" s="1">
         <v>44349</v>
       </c>
+      <c r="J218" s="2"/>
       <c r="K218" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L218" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M218" s="1">
         <v>46141</v>
       </c>
       <c r="N218" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="219" spans="1:14">
       <c r="A219" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B219" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C219" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F219" t="s">
+        <v>142</v>
+      </c>
+      <c r="G219" t="s">
         <v>456</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F219" t="s">
-        <v>198</v>
-      </c>
-      <c r="G219" t="s">
-        <v>451</v>
       </c>
       <c r="H219" s="1">
         <v>44348</v>
@@ -11293,36 +11318,36 @@
         <v>42</v>
       </c>
       <c r="L219" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M219" s="1">
         <v>46141</v>
       </c>
       <c r="N219" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="220" spans="1:14">
       <c r="A220" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B220" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F220" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G220" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="H220" s="1">
         <v>44348</v>
@@ -11340,30 +11365,30 @@
         <v>46141</v>
       </c>
       <c r="N220" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="221" spans="1:14">
       <c r="A221" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B221" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C221" s="11" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="F221" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G221" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="H221" s="1">
         <v>44348</v>
@@ -11375,36 +11400,36 @@
         <v>42</v>
       </c>
       <c r="L221" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M221" s="1">
         <v>46141</v>
       </c>
       <c r="N221" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14">
+      <c r="A222" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="222" spans="1:14" customFormat="1">
-      <c r="A222" t="s">
-        <v>395</v>
-      </c>
       <c r="B222" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C222" s="11" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F222" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G222" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="H222" s="1">
         <v>44348</v>
@@ -11412,116 +11437,115 @@
       <c r="I222" s="1">
         <v>44349</v>
       </c>
-      <c r="J222" s="2"/>
       <c r="K222" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L222" s="2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M222" s="1">
         <v>46141</v>
       </c>
       <c r="N222" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="223" spans="1:14" customFormat="1">
       <c r="A223" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B223" t="s">
-        <v>396</v>
-      </c>
-      <c r="C223" s="15" t="s">
-        <v>464</v>
-      </c>
-      <c r="D223" t="s">
-        <v>465</v>
+        <v>401</v>
+      </c>
+      <c r="C223" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>468</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="F223" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G223" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="H223" s="1">
-        <v>43910</v>
+        <v>44348</v>
       </c>
       <c r="I223" s="1">
-        <v>46013</v>
+        <v>44349</v>
       </c>
       <c r="J223" s="2"/>
       <c r="K223" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L223" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M223" s="1">
         <v>46141</v>
       </c>
       <c r="N223" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="224" spans="1:14" customFormat="1">
       <c r="A224" t="s">
-        <v>467</v>
+        <v>400</v>
       </c>
       <c r="B224" t="s">
-        <v>468</v>
-      </c>
-      <c r="C224" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C224" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="D224" s="2" t="s">
+      <c r="D224" t="s">
         <v>470</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G224" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F224" t="s">
         <v>142</v>
       </c>
+      <c r="G224" t="s">
+        <v>471</v>
+      </c>
       <c r="H224" s="1">
-        <v>44426</v>
+        <v>43910</v>
       </c>
       <c r="I224" s="1">
-        <v>44426</v>
+        <v>46013</v>
       </c>
       <c r="J224" s="2"/>
       <c r="K224" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L224" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M224" s="1">
-        <v>46125</v>
+        <v>46141</v>
       </c>
       <c r="N224" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="225" spans="1:14">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" customFormat="1">
       <c r="A225" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B225" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C225" s="18" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>18</v>
@@ -11530,7 +11554,7 @@
         <v>19</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H225" s="1">
         <v>44426</v>
@@ -11538,6 +11562,7 @@
       <c r="I225" s="1">
         <v>44426</v>
       </c>
+      <c r="J225" s="2"/>
       <c r="K225" s="3" t="s">
         <v>42</v>
       </c>
@@ -11548,42 +11573,39 @@
         <v>46125</v>
       </c>
       <c r="N225" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="226" spans="1:14">
       <c r="A226" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B226" t="s">
-        <v>468</v>
-      </c>
-      <c r="C226" s="17" t="s">
-        <v>474</v>
-      </c>
-      <c r="D226" t="s">
-        <v>475</v>
+        <v>473</v>
+      </c>
+      <c r="C226" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>478</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G226" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="G226" s="9" t="s">
+        <v>149</v>
       </c>
       <c r="H226" s="1">
-        <v>42734</v>
+        <v>44426</v>
       </c>
       <c r="I226" s="1">
-        <v>42734</v>
-      </c>
-      <c r="J226" s="1">
-        <v>44925</v>
+        <v>44426</v>
       </c>
       <c r="K226" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L226" s="2">
         <v>5</v>
@@ -11592,39 +11614,39 @@
         <v>46125</v>
       </c>
       <c r="N226" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="227" spans="1:14" customFormat="1">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14">
       <c r="A227" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B227" t="s">
-        <v>468</v>
-      </c>
-      <c r="C227" s="18" t="s">
-        <v>476</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
+      </c>
+      <c r="C227" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="D227" t="s">
+        <v>480</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G227" t="s">
         <v>20</v>
       </c>
       <c r="H227" s="1">
-        <v>43132</v>
+        <v>42734</v>
       </c>
       <c r="I227" s="1">
-        <v>43132</v>
+        <v>42734</v>
       </c>
       <c r="J227" s="1">
-        <v>44966</v>
+        <v>44925</v>
       </c>
       <c r="K227" s="3" t="s">
         <v>21</v>
@@ -11636,39 +11658,39 @@
         <v>46125</v>
       </c>
       <c r="N227" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="228" spans="1:14">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" customFormat="1">
       <c r="A228" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B228" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C228" s="18" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G228" t="s">
         <v>20</v>
       </c>
       <c r="H228" s="1">
-        <v>43500</v>
+        <v>43132</v>
       </c>
       <c r="I228" s="1">
-        <v>43500</v>
+        <v>43132</v>
       </c>
       <c r="J228" s="1">
-        <v>45821</v>
+        <v>44966</v>
       </c>
       <c r="K228" s="3" t="s">
         <v>21</v>
@@ -11680,36 +11702,36 @@
         <v>46125</v>
       </c>
       <c r="N228" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="229" spans="1:14">
       <c r="A229" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B229" t="s">
-        <v>468</v>
-      </c>
-      <c r="C229" s="17" t="s">
-        <v>480</v>
-      </c>
-      <c r="D229" t="s">
-        <v>481</v>
+        <v>473</v>
+      </c>
+      <c r="C229" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>484</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G229" t="s">
         <v>20</v>
       </c>
       <c r="H229" s="1">
-        <v>43819</v>
+        <v>43500</v>
       </c>
       <c r="I229" s="1">
-        <v>43819</v>
+        <v>43500</v>
       </c>
       <c r="J229" s="1">
         <v>45821</v>
@@ -11724,83 +11746,86 @@
         <v>46125</v>
       </c>
       <c r="N229" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="230" spans="1:14">
       <c r="A230" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B230" t="s">
-        <v>468</v>
-      </c>
-      <c r="C230" s="18" t="s">
-        <v>482</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>483</v>
+        <v>473</v>
+      </c>
+      <c r="C230" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="D230" t="s">
+        <v>486</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G230" t="s">
         <v>20</v>
       </c>
       <c r="H230" s="1">
-        <v>44194</v>
+        <v>43819</v>
       </c>
       <c r="I230" s="1">
-        <v>44194</v>
+        <v>43819</v>
       </c>
       <c r="J230" s="1">
-        <v>44994</v>
+        <v>45821</v>
       </c>
       <c r="K230" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L230" s="7">
+      <c r="L230" s="2">
         <v>5</v>
       </c>
       <c r="M230" s="1">
         <v>46125</v>
       </c>
       <c r="N230" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="231" spans="1:14">
       <c r="A231" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B231" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C231" s="18" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G231" t="s">
         <v>20</v>
       </c>
       <c r="H231" s="1">
-        <v>44923</v>
+        <v>44194</v>
       </c>
       <c r="I231" s="1">
-        <v>44923</v>
+        <v>44194</v>
+      </c>
+      <c r="J231" s="1">
+        <v>44994</v>
       </c>
       <c r="K231" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L231" s="7">
         <v>5</v>
@@ -11809,38 +11834,37 @@
         <v>46125</v>
       </c>
       <c r="N231" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="232" spans="1:14" customFormat="1">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14">
       <c r="A232" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B232" t="s">
-        <v>468</v>
-      </c>
-      <c r="C232" s="17" t="s">
-        <v>486</v>
-      </c>
-      <c r="D232" t="s">
-        <v>487</v>
+        <v>473</v>
+      </c>
+      <c r="C232" s="18" t="s">
+        <v>489</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>490</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G232" t="s">
         <v>20</v>
       </c>
       <c r="H232" s="1">
-        <v>44925</v>
+        <v>44923</v>
       </c>
       <c r="I232" s="1">
-        <v>44925</v>
-      </c>
-      <c r="J232" s="2"/>
+        <v>44923</v>
+      </c>
       <c r="K232" s="3" t="s">
         <v>42</v>
       </c>
@@ -11851,37 +11875,38 @@
         <v>46125</v>
       </c>
       <c r="N232" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="233" spans="1:14">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" customFormat="1">
       <c r="A233" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B233" t="s">
-        <v>468</v>
-      </c>
-      <c r="C233" s="18" t="s">
-        <v>488</v>
-      </c>
-      <c r="D233" s="2" t="s">
-        <v>489</v>
+        <v>473</v>
+      </c>
+      <c r="C233" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="D233" t="s">
+        <v>492</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G233" t="s">
         <v>20</v>
       </c>
       <c r="H233" s="1">
-        <v>45821</v>
+        <v>44925</v>
       </c>
       <c r="I233" s="1">
-        <v>45821</v>
-      </c>
+        <v>44925</v>
+      </c>
+      <c r="J233" s="2"/>
       <c r="K233" s="3" t="s">
         <v>42</v>
       </c>
@@ -11892,27 +11917,27 @@
         <v>46125</v>
       </c>
       <c r="N233" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="234" spans="1:14">
       <c r="A234" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B234" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C234" s="18" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G234" t="s">
         <v>20</v>
@@ -11926,43 +11951,43 @@
       <c r="K234" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L234" s="2">
+      <c r="L234" s="7">
         <v>5</v>
       </c>
       <c r="M234" s="1">
         <v>46125</v>
       </c>
       <c r="N234" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="235" spans="1:14">
       <c r="A235" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B235" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C235" s="18" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G235" t="s">
         <v>20</v>
       </c>
       <c r="H235" s="1">
-        <v>46022</v>
+        <v>45821</v>
       </c>
       <c r="I235" s="1">
-        <v>46022</v>
+        <v>45821</v>
       </c>
       <c r="K235" s="3" t="s">
         <v>42</v>
@@ -11973,57 +11998,60 @@
       <c r="M235" s="1">
         <v>46125</v>
       </c>
+      <c r="N235" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="236" spans="1:14">
-      <c r="A236" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C236" s="2">
-        <v>1071501</v>
+      <c r="A236" t="s">
+        <v>472</v>
+      </c>
+      <c r="B236" t="s">
+        <v>473</v>
+      </c>
+      <c r="C236" s="18" t="s">
+        <v>497</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="G236" t="s">
-        <v>383</v>
-      </c>
-      <c r="H236" s="1" t="s">
-        <v>497</v>
+        <v>20</v>
+      </c>
+      <c r="H236" s="1">
+        <v>46022</v>
       </c>
       <c r="I236" s="1">
-        <v>45842</v>
+        <v>46022</v>
       </c>
       <c r="K236" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L236" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M236" s="1">
-        <v>46169</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="237" spans="1:14">
       <c r="A237" s="12" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C237" s="2">
-        <v>2091501</v>
+        <v>1071501</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>41</v>
@@ -12032,10 +12060,10 @@
         <v>53</v>
       </c>
       <c r="G237" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="I237" s="1">
         <v>45842</v>
@@ -12052,40 +12080,37 @@
     </row>
     <row r="238" spans="1:14">
       <c r="A238" s="12" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C238" s="2">
-        <v>5041501</v>
+        <v>2091501</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G238" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H238" s="2" t="s">
-        <v>500</v>
+        <v>53</v>
+      </c>
+      <c r="G238" t="s">
+        <v>388</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>502</v>
       </c>
       <c r="I238" s="1">
-        <v>45820</v>
-      </c>
-      <c r="J238" s="1">
-        <v>46161</v>
+        <v>45842</v>
       </c>
       <c r="K238" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L238" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M238" s="1">
         <v>46169</v>
@@ -12093,16 +12118,16 @@
     </row>
     <row r="239" spans="1:14">
       <c r="A239" s="12" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C239" s="2">
-        <v>6041501</v>
+        <v>5041501</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>18</v>
@@ -12111,10 +12136,10 @@
         <v>19</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="I239" s="1">
         <v>45820</v>
@@ -12132,14 +12157,55 @@
         <v>46169</v>
       </c>
     </row>
+    <row r="240" spans="1:14">
+      <c r="A240" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C240" s="2">
+        <v>6041501</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H240" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I240" s="1">
+        <v>45820</v>
+      </c>
+      <c r="J240" s="1">
+        <v>46161</v>
+      </c>
+      <c r="K240" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L240" s="2">
+        <v>5</v>
+      </c>
+      <c r="M240" s="1">
+        <v>46169</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N240" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N240">
-      <sortCondition ref="C1:C240"/>
+  <autoFilter ref="A1:N241">
+    <sortState ref="A2:N241">
+      <sortCondition ref="C1:C241"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C107">
+  <conditionalFormatting sqref="C108">
     <cfRule type="iconSet" priority="1">
       <iconSet iconSet="3Arrows">
         <cfvo type="percent" val="0"/>
@@ -12149,64 +12215,65 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N19" r:id="rId1" xr:uid="{8220B955-B269-49BB-BD6D-AD834FA30E13}"/>
-    <hyperlink ref="N18" r:id="rId2" xr:uid="{B401B411-58A7-4BCC-B48B-D8DA63942597}"/>
-    <hyperlink ref="N37" r:id="rId3" xr:uid="{F7481F57-E642-473E-825B-2A3D484E1C5E}"/>
-    <hyperlink ref="N38" r:id="rId4" xr:uid="{79505A78-76AD-446F-8895-A9AAE6ED4D85}"/>
-    <hyperlink ref="N39" r:id="rId5" xr:uid="{D7BD8461-1283-4F76-A6D3-0EBF106113F2}"/>
-    <hyperlink ref="N40" r:id="rId6" xr:uid="{DD84BBDA-48FA-435F-B0C2-7608D96C352C}"/>
-    <hyperlink ref="N41" r:id="rId7" xr:uid="{776DE41F-8E5A-47C4-8A86-4C1520B30BBC}"/>
-    <hyperlink ref="N42" r:id="rId8" xr:uid="{C5398B09-3821-4B69-88BE-F3DAE3703744}"/>
-    <hyperlink ref="N43" r:id="rId9" xr:uid="{BDDDD80E-AC29-45B3-9D33-37F6245D6A87}"/>
-    <hyperlink ref="N44" r:id="rId10" xr:uid="{A05AF763-F1BE-4CB0-B245-3EECD31F52D7}"/>
-    <hyperlink ref="N45" r:id="rId11" xr:uid="{47D99323-3953-458B-A504-96C00FADEC68}"/>
-    <hyperlink ref="N46" r:id="rId12" xr:uid="{8EF44723-3856-4E15-BF22-B7D2D56499C1}"/>
-    <hyperlink ref="N47" r:id="rId13" xr:uid="{DE21238A-D3FD-4D4A-8B08-FC4135744990}"/>
-    <hyperlink ref="N48" r:id="rId14" xr:uid="{FB918246-D1DF-4B8E-B958-F355A1D392AA}"/>
-    <hyperlink ref="N49" r:id="rId15" xr:uid="{9ABC9053-DB90-4039-903C-E830865FA0B0}"/>
-    <hyperlink ref="N50" r:id="rId16" xr:uid="{B1A14EE6-E586-475E-A004-A0A7974021EA}"/>
-    <hyperlink ref="N51" r:id="rId17" xr:uid="{DC7AB8ED-12FF-4553-902F-ABF0C0AA87A0}"/>
-    <hyperlink ref="N52" r:id="rId18" xr:uid="{47B117F6-4AAA-40CE-BA3D-920E867CC01C}"/>
-    <hyperlink ref="N21" r:id="rId19" xr:uid="{173DBD48-C21A-4E6D-AABD-EEB40694EDD0}"/>
-    <hyperlink ref="N22" r:id="rId20" xr:uid="{1274BBA3-6669-4546-A4EA-1D2DFCA1CD9D}"/>
-    <hyperlink ref="N20" r:id="rId21" xr:uid="{264B87E2-07DE-4863-92C2-A75554151B1E}"/>
-    <hyperlink ref="N23" r:id="rId22" xr:uid="{A4B00B57-A4BA-406A-A2E6-3A571C1DE925}"/>
-    <hyperlink ref="N24" r:id="rId23" xr:uid="{30E19A6E-5A66-4CE2-9D18-2AA9292884BD}"/>
-    <hyperlink ref="N25" r:id="rId24" xr:uid="{205ADC83-FAAB-416D-AEFD-829E624A64BF}"/>
-    <hyperlink ref="N30" r:id="rId25" xr:uid="{8E131B5C-9A03-4606-AD38-DC03B6780539}"/>
-    <hyperlink ref="N31" r:id="rId26" xr:uid="{7D50EF81-D643-49A2-9F32-6CA2C7E17DC2}"/>
-    <hyperlink ref="N33" r:id="rId27" xr:uid="{2F2FCB70-920A-46DB-9936-996BFD6F1E44}"/>
-    <hyperlink ref="N29" r:id="rId28" xr:uid="{E67F4C0B-E78E-4885-9DE5-921A1E05F79D}"/>
-    <hyperlink ref="N32" r:id="rId29" xr:uid="{EB8AF4B8-ADA3-4865-8664-DD5D247A2B2E}"/>
-    <hyperlink ref="N34" r:id="rId30" xr:uid="{590BF203-1E3B-473B-9560-1E7AC342850F}"/>
-    <hyperlink ref="N16" r:id="rId31" xr:uid="{707DFEE0-F031-49F2-B879-F29BDE9CC8CE}"/>
-    <hyperlink ref="N15" r:id="rId32" xr:uid="{F30819C5-2CE1-480A-AD45-85D77369AF7A}"/>
-    <hyperlink ref="N26" r:id="rId33" xr:uid="{E0356CEA-79E2-4F83-BBD4-0FC36F3F51F0}"/>
-    <hyperlink ref="N17" r:id="rId34" xr:uid="{FD33E1CA-F48E-47A5-8C92-A9A529CCCE36}"/>
-    <hyperlink ref="N35" r:id="rId35" xr:uid="{0B6CD7D4-5B10-4C12-804A-B828752BAD78}"/>
-    <hyperlink ref="N36" r:id="rId36" xr:uid="{4C6E4D41-53B9-40C4-8A52-DEC4CF7AEC69}"/>
-    <hyperlink ref="N27" r:id="rId37" xr:uid="{3C1E0CD2-AB6A-4CD8-8320-CAC9C1EA81F2}"/>
-    <hyperlink ref="N28" r:id="rId38" xr:uid="{DB27BD91-88FA-44E1-A326-DE5A8086A60F}"/>
-    <hyperlink ref="N104" r:id="rId39" xr:uid="{D8AC412C-8BF0-4534-BEB6-9FEE3561C22D}"/>
-    <hyperlink ref="N138" r:id="rId40" xr:uid="{4A962553-E63B-4F0B-8938-44B0D045308D}"/>
-    <hyperlink ref="N87" r:id="rId41" location="transparencia" xr:uid="{99D30359-B9C7-4F51-93F7-1174D017E5BD}"/>
-    <hyperlink ref="N88" r:id="rId42" location="transparencia" xr:uid="{C492F183-39A6-40DD-8A3C-E86E76D651EC}"/>
-    <hyperlink ref="N95" r:id="rId43" location="transparencia" xr:uid="{39E77EEA-E8AF-4BD9-9126-38BCE5A985F5}"/>
-    <hyperlink ref="N100" r:id="rId44" location="transparencia" xr:uid="{1E74F340-DF29-4FE0-84B7-513FDE8356EB}"/>
-    <hyperlink ref="N97" r:id="rId45" location="transparencia" xr:uid="{9AD7F091-6ED9-49C0-8FCA-D17EDE05ED1E}"/>
-    <hyperlink ref="N89" r:id="rId46" location="transparencia" xr:uid="{A4150EFD-D156-4F8A-B0A8-172BFCA4A27C}"/>
-    <hyperlink ref="N99" r:id="rId47" location="transparencia" xr:uid="{7BD5BF84-6A3D-4D30-BD59-519256EFDF65}"/>
-    <hyperlink ref="N96" r:id="rId48" location="transparencia" xr:uid="{8AB2CDB9-9264-4AF9-89D0-8A9E306351A1}"/>
-    <hyperlink ref="N101" r:id="rId49" location="transparencia" xr:uid="{B288CCDF-8536-4983-A830-A0E5F90608B1}"/>
-    <hyperlink ref="N98" r:id="rId50" location="transparencia" xr:uid="{E382E0FF-4569-411C-A961-B02A190F2C15}"/>
-    <hyperlink ref="N90" r:id="rId51" location="transparencia" xr:uid="{C689A52B-3C6F-4FEF-9B5A-83BBE2630362}"/>
-    <hyperlink ref="N91" r:id="rId52" location="transparencia" xr:uid="{CEB52D7E-64E8-4B33-9379-A2C6ECAA522D}"/>
-    <hyperlink ref="N92" r:id="rId53" location="transparencia" xr:uid="{78AE2C1A-D9AC-4393-AAB9-968F2E156E78}"/>
-    <hyperlink ref="N93" r:id="rId54" location="transparencia" xr:uid="{25AAA6EA-B242-4960-B22C-ABC8F0DD9F85}"/>
-    <hyperlink ref="N94" r:id="rId55" location="transparencia" xr:uid="{E7723C31-93D5-4D3B-A353-E51FE7B8111E}"/>
-    <hyperlink ref="N116" r:id="rId56" xr:uid="{2C1FB273-DE81-4F44-B5F6-DCE307D57A03}"/>
+    <hyperlink ref="N19" r:id="rId1"/>
+    <hyperlink ref="N18" r:id="rId2"/>
+    <hyperlink ref="N37" r:id="rId3"/>
+    <hyperlink ref="N38" r:id="rId4"/>
+    <hyperlink ref="N39" r:id="rId5"/>
+    <hyperlink ref="N40" r:id="rId6"/>
+    <hyperlink ref="N41" r:id="rId7"/>
+    <hyperlink ref="N42" r:id="rId8"/>
+    <hyperlink ref="N43" r:id="rId9"/>
+    <hyperlink ref="N44" r:id="rId10"/>
+    <hyperlink ref="N45" r:id="rId11"/>
+    <hyperlink ref="N46" r:id="rId12"/>
+    <hyperlink ref="N47" r:id="rId13"/>
+    <hyperlink ref="N48" r:id="rId14"/>
+    <hyperlink ref="N49" r:id="rId15"/>
+    <hyperlink ref="N50" r:id="rId16"/>
+    <hyperlink ref="N51" r:id="rId17"/>
+    <hyperlink ref="N52" r:id="rId18"/>
+    <hyperlink ref="N21" r:id="rId19"/>
+    <hyperlink ref="N22" r:id="rId20"/>
+    <hyperlink ref="N20" r:id="rId21"/>
+    <hyperlink ref="N23" r:id="rId22"/>
+    <hyperlink ref="N24" r:id="rId23"/>
+    <hyperlink ref="N25" r:id="rId24"/>
+    <hyperlink ref="N30" r:id="rId25"/>
+    <hyperlink ref="N31" r:id="rId26"/>
+    <hyperlink ref="N33" r:id="rId27"/>
+    <hyperlink ref="N29" r:id="rId28"/>
+    <hyperlink ref="N32" r:id="rId29"/>
+    <hyperlink ref="N34" r:id="rId30"/>
+    <hyperlink ref="N16" r:id="rId31"/>
+    <hyperlink ref="N15" r:id="rId32"/>
+    <hyperlink ref="N26" r:id="rId33"/>
+    <hyperlink ref="N17" r:id="rId34"/>
+    <hyperlink ref="N35" r:id="rId35"/>
+    <hyperlink ref="N36" r:id="rId36"/>
+    <hyperlink ref="N27" r:id="rId37"/>
+    <hyperlink ref="N28" r:id="rId38"/>
+    <hyperlink ref="N105" r:id="rId39"/>
+    <hyperlink ref="N139" r:id="rId40"/>
+    <hyperlink ref="N88" r:id="rId41" location="transparencia"/>
+    <hyperlink ref="N89" r:id="rId42" location="transparencia"/>
+    <hyperlink ref="N96" r:id="rId43" location="transparencia"/>
+    <hyperlink ref="N101" r:id="rId44" location="transparencia"/>
+    <hyperlink ref="N98" r:id="rId45" location="transparencia"/>
+    <hyperlink ref="N90" r:id="rId46" location="transparencia"/>
+    <hyperlink ref="N100" r:id="rId47" location="transparencia"/>
+    <hyperlink ref="N97" r:id="rId48" location="transparencia"/>
+    <hyperlink ref="N102" r:id="rId49" location="transparencia"/>
+    <hyperlink ref="N99" r:id="rId50" location="transparencia"/>
+    <hyperlink ref="N91" r:id="rId51" location="transparencia"/>
+    <hyperlink ref="N92" r:id="rId52" location="transparencia"/>
+    <hyperlink ref="N93" r:id="rId53" location="transparencia"/>
+    <hyperlink ref="N94" r:id="rId54" location="transparencia"/>
+    <hyperlink ref="N95" r:id="rId55" location="transparencia"/>
+    <hyperlink ref="N117" r:id="rId56"/>
+    <hyperlink ref="N53" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId57"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId58"/>
 </worksheet>
 </file>